--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E1EF37E-2575-43B3-9F11-745F6A55D6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EBF8FB9-0B3E-4774-B0B4-EEF857B05CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,6 +12,10 @@
     <sheet name="Revenue_Model" sheetId="2" r:id="rId2"/>
     <sheet name="Expense_Model" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="inflation_rate">Inputs!$E$7:$E$7</definedName>
+    <definedName name="num_accounts">Inputs!$B$8:$B$8</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Water Utility Financial Model</t>
   </si>
@@ -126,6 +152,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -200,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -284,15 +313,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -333,16 +353,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -357,38 +374,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -714,90 +735,98 @@
     <col min="12" max="12" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="41.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:12" ht="21">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-    </row>
-    <row r="2" spans="1:12" ht="30.75">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="30"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="30.75">
-      <c r="A4" s="33" t="s">
+      <c r="B2" s="31"/>
+    </row>
+    <row r="4" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
+      <c r="B4" s="32"/>
     </row>
     <row r="6" spans="1:12" ht="15.75">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="15.75">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="D7" s="11" t="s">
+      <c r="B7" s="34"/>
+      <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="28">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="15.75">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="34">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="28">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="15.75">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="32.25">
-      <c r="I10" s="24" t="s">
+      <c r="B9" s="34"/>
+    </row>
+    <row r="10" spans="1:12" ht="32.25" customHeight="1">
+      <c r="I10" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="2"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>2026</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <f>C11+1</f>
         <v>2027</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <f t="shared" ref="E11:G11" si="0">D11+1</f>
         <v>2028</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -808,75 +837,75 @@
       <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="30.75">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="30.75">
-      <c r="A15" s="10"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="10"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="29"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="24"/>
       <c r="I16" s="3" t="s">
         <v>22</v>
       </c>
@@ -884,194 +913,213 @@
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="29"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="24"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="10">
+      <c r="A18" s="29">
         <v>2000</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="29"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="24"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="5">
+      <c r="A19" s="21">
         <v>3000</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="5">
+      <c r="A20" s="35">
         <v>4000</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="5">
+      <c r="A21" s="35">
         <v>5000</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="28"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:11" ht="30.75">
-      <c r="A25" s="10"/>
-      <c r="B25" s="22" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="10"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="29"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="24"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="29"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="24"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="10">
+      <c r="A28" s="29">
         <v>2000</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="29"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="5">
+      <c r="A29" s="21">
         <v>5000</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="5">
+      <c r="A30" s="35">
         <v>10000</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="5"/>
-      <c r="B31" s="23" t="s">
+      <c r="A31" s="35"/>
+      <c r="B31" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="I10:K10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FD50A9-0884-44AC-8AA5-5AA892507CF5}">
-  <dimension ref="A1"/>
+  <dimension ref="A4:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" cm="1">
+        <f t="array" ref="B4">num_accounts</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EBF8FB9-0B3E-4774-B0B4-EEF857B05CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C81001-1335-4B7E-A2FE-B93793A31B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -13,8 +13,26 @@
     <sheet name="Expense_Model" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="base_chargeRS1">Inputs!$C$14:$G$14</definedName>
+    <definedName name="base_chargeRS2">Inputs!$C$24:$G$24</definedName>
     <definedName name="inflation_rate">Inputs!$E$7:$E$7</definedName>
     <definedName name="num_accounts">Inputs!$B$8:$B$8</definedName>
+    <definedName name="num_accountsRS1">Inputs!$A$16:$A$16</definedName>
+    <definedName name="num_accountsRS2">Inputs!$A$26:$A$26</definedName>
+    <definedName name="pop_growth_rate">Inputs!$E$8:$E$8</definedName>
+    <definedName name="rate_structure_1">Inputs!$A$14:$A$14</definedName>
+    <definedName name="rate_structure_2">Inputs!$A$24:$A$24</definedName>
+    <definedName name="RS1_block_consumption">Inputs!$K$13:$K$15</definedName>
+    <definedName name="RS1_num_accounts">Revenue_Model!$B$5:$F$5</definedName>
+    <definedName name="RS1_num_accounts_currentyear">Inputs!$A$16:$A$16</definedName>
+    <definedName name="RS1_vrates2026">Inputs!$C$19:$C$21</definedName>
+    <definedName name="RS1_vrates2027">Inputs!$D$19:$D$21</definedName>
+    <definedName name="RS1_vrates2028">Inputs!$E$19:$E$21</definedName>
+    <definedName name="RS1_vrates2029">Inputs!$F$19:$F$21</definedName>
+    <definedName name="RS1_vrates2030">Inputs!$G$19:$G$21</definedName>
+    <definedName name="RS2_block_consumption">Inputs!$K$18:$K$20</definedName>
+    <definedName name="RS2_num_accounts">Revenue_Model!$B$14:$F$14</definedName>
+    <definedName name="RS2_num_accounts_currentyear">Inputs!$A$26:$A$26</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +58,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t>Water Utility Financial Model</t>
   </si>
@@ -97,16 +115,28 @@
     <t>Annual Water Consumption:</t>
   </si>
   <si>
-    <t>Monthly Consumption Over Included Amount</t>
-  </si>
-  <si>
     <t>Rate Structure(s)</t>
   </si>
   <si>
     <t>Year:</t>
   </si>
   <si>
+    <t>Monthly Consumption Over Included Amount</t>
+  </si>
+  <si>
+    <t>Annual Operating Expenses</t>
+  </si>
+  <si>
+    <t>Annual Debt Service</t>
+  </si>
+  <si>
     <t>Rate Structure 1:</t>
+  </si>
+  <si>
+    <t>Salaries</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
   <si>
     <t>Block 1:</t>
@@ -115,7 +145,7 @@
     <t>*In gallons/month, excluding included amount</t>
   </si>
   <si>
-    <t>Block 2:</t>
+    <t>Chemicals/Treatments</t>
   </si>
   <si>
     <t>Residential water, inside</t>
@@ -124,16 +154,34 @@
     <t>Base Charge (monthly):</t>
   </si>
   <si>
-    <t>Block 3:</t>
+    <t>Block 2:</t>
+  </si>
+  <si>
+    <t>Energy and Utilities</t>
   </si>
   <si>
     <t>Consumption included with base charge (gallons/month):</t>
   </si>
   <si>
+    <t>Block 3:</t>
+  </si>
+  <si>
+    <t>Maintenance &amp; Repairs</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
     <t>Rate Structure 2:</t>
   </si>
   <si>
-    <t>Block cutoffs (up to, and including)</t>
+    <t>Cash Reserves</t>
+  </si>
+  <si>
+    <t>Block cutoffs, starts at 2000</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
   <si>
     <t>Block rate 1 ($/1000 gal)</t>
@@ -145,17 +193,41 @@
     <t>Block rate 3 ($/1000 gal)</t>
   </si>
   <si>
-    <t>Non-residential water, inside</t>
+    <t>Residential water, outside</t>
+  </si>
+  <si>
+    <t>Revenue Projections | 2026-2030</t>
+  </si>
+  <si>
+    <t>Number of Accounts</t>
+  </si>
+  <si>
+    <t>Base Charge Revenue</t>
+  </si>
+  <si>
+    <t>Block 1 Revenue</t>
+  </si>
+  <si>
+    <t>Block 2 Revenue</t>
+  </si>
+  <si>
+    <t>Block 3 Revenue</t>
+  </si>
+  <si>
+    <t>Total Operating Revenue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,8 +280,24 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,8 +316,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -349,11 +443,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -361,10 +477,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -382,7 +494,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -392,15 +503,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -409,9 +511,60 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,377 +879,3358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:CQ34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:95" ht="21">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="31" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+      <c r="AT1" s="29"/>
+      <c r="AU1" s="29"/>
+      <c r="AV1" s="29"/>
+      <c r="AW1" s="29"/>
+      <c r="AX1" s="29"/>
+      <c r="AY1" s="29"/>
+      <c r="AZ1" s="29"/>
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="29"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="29"/>
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="29"/>
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="29"/>
+      <c r="BI1" s="29"/>
+      <c r="BJ1" s="29"/>
+      <c r="BK1" s="29"/>
+      <c r="BL1" s="29"/>
+      <c r="BM1" s="29"/>
+      <c r="BN1" s="29"/>
+      <c r="BO1" s="29"/>
+      <c r="BP1" s="29"/>
+      <c r="BQ1" s="29"/>
+      <c r="BR1" s="29"/>
+      <c r="BS1" s="29"/>
+      <c r="BT1" s="29"/>
+      <c r="BU1" s="29"/>
+      <c r="BV1" s="29"/>
+      <c r="BW1" s="29"/>
+      <c r="BX1" s="29"/>
+      <c r="BY1" s="29"/>
+      <c r="BZ1" s="29"/>
+      <c r="CA1" s="29"/>
+      <c r="CB1" s="29"/>
+      <c r="CC1" s="29"/>
+      <c r="CD1" s="29"/>
+      <c r="CE1" s="29"/>
+      <c r="CF1" s="29"/>
+      <c r="CG1" s="29"/>
+      <c r="CH1" s="29"/>
+      <c r="CI1" s="29"/>
+      <c r="CJ1" s="29"/>
+      <c r="CK1" s="29"/>
+      <c r="CL1" s="29"/>
+      <c r="CM1" s="29"/>
+      <c r="CN1" s="29"/>
+      <c r="CO1" s="29"/>
+      <c r="CP1" s="29"/>
+      <c r="CQ1" s="29"/>
+    </row>
+    <row r="2" spans="1:95">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A4" s="32" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="29"/>
+      <c r="AW2" s="29"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
+      <c r="BX2" s="29"/>
+      <c r="BY2" s="29"/>
+      <c r="BZ2" s="29"/>
+      <c r="CA2" s="29"/>
+      <c r="CB2" s="29"/>
+      <c r="CC2" s="29"/>
+      <c r="CD2" s="29"/>
+      <c r="CE2" s="29"/>
+      <c r="CF2" s="29"/>
+      <c r="CG2" s="29"/>
+      <c r="CH2" s="29"/>
+      <c r="CI2" s="29"/>
+      <c r="CJ2" s="29"/>
+      <c r="CK2" s="29"/>
+      <c r="CL2" s="29"/>
+      <c r="CM2" s="29"/>
+      <c r="CN2" s="29"/>
+      <c r="CO2" s="29"/>
+      <c r="CP2" s="29"/>
+      <c r="CQ2" s="29"/>
+    </row>
+    <row r="3" spans="1:95">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29"/>
+      <c r="AC3" s="29"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AI3" s="29"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
+      <c r="BX3" s="29"/>
+      <c r="BY3" s="29"/>
+      <c r="BZ3" s="29"/>
+      <c r="CA3" s="29"/>
+      <c r="CB3" s="29"/>
+      <c r="CC3" s="29"/>
+      <c r="CD3" s="29"/>
+      <c r="CE3" s="29"/>
+      <c r="CF3" s="29"/>
+      <c r="CG3" s="29"/>
+      <c r="CH3" s="29"/>
+      <c r="CI3" s="29"/>
+      <c r="CJ3" s="29"/>
+      <c r="CK3" s="29"/>
+      <c r="CL3" s="29"/>
+      <c r="CM3" s="29"/>
+      <c r="CN3" s="29"/>
+      <c r="CO3" s="29"/>
+      <c r="CP3" s="29"/>
+      <c r="CQ3" s="29"/>
+    </row>
+    <row r="4" spans="1:95" ht="22.5" customHeight="1">
+      <c r="A4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="32"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75">
-      <c r="A6" s="36" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
+      <c r="BX4" s="29"/>
+      <c r="BY4" s="29"/>
+      <c r="BZ4" s="29"/>
+      <c r="CA4" s="29"/>
+      <c r="CB4" s="29"/>
+      <c r="CC4" s="29"/>
+      <c r="CD4" s="29"/>
+      <c r="CE4" s="29"/>
+      <c r="CF4" s="29"/>
+      <c r="CG4" s="29"/>
+      <c r="CH4" s="29"/>
+      <c r="CI4" s="29"/>
+      <c r="CJ4" s="29"/>
+      <c r="CK4" s="29"/>
+      <c r="CL4" s="29"/>
+      <c r="CM4" s="29"/>
+      <c r="CN4" s="29"/>
+      <c r="CO4" s="29"/>
+      <c r="CP4" s="29"/>
+      <c r="CQ4" s="29"/>
+    </row>
+    <row r="5" spans="1:95">
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
+      <c r="BX5" s="29"/>
+      <c r="BY5" s="29"/>
+      <c r="BZ5" s="29"/>
+      <c r="CA5" s="29"/>
+      <c r="CB5" s="29"/>
+      <c r="CC5" s="29"/>
+      <c r="CD5" s="29"/>
+      <c r="CE5" s="29"/>
+      <c r="CF5" s="29"/>
+      <c r="CG5" s="29"/>
+      <c r="CH5" s="29"/>
+      <c r="CI5" s="29"/>
+      <c r="CJ5" s="29"/>
+      <c r="CK5" s="29"/>
+      <c r="CL5" s="29"/>
+      <c r="CM5" s="29"/>
+      <c r="CN5" s="29"/>
+      <c r="CO5" s="29"/>
+      <c r="CP5" s="29"/>
+      <c r="CQ5" s="29"/>
+    </row>
+    <row r="6" spans="1:95" ht="15.75">
+      <c r="A6" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="29"/>
+      <c r="D6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75">
-      <c r="A7" s="36" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
+      <c r="BX6" s="29"/>
+      <c r="BY6" s="29"/>
+      <c r="BZ6" s="29"/>
+      <c r="CA6" s="29"/>
+      <c r="CB6" s="29"/>
+      <c r="CC6" s="29"/>
+      <c r="CD6" s="29"/>
+      <c r="CE6" s="29"/>
+      <c r="CF6" s="29"/>
+      <c r="CG6" s="29"/>
+      <c r="CH6" s="29"/>
+      <c r="CI6" s="29"/>
+      <c r="CJ6" s="29"/>
+      <c r="CK6" s="29"/>
+      <c r="CL6" s="29"/>
+      <c r="CM6" s="29"/>
+      <c r="CN6" s="29"/>
+      <c r="CO6" s="29"/>
+      <c r="CP6" s="29"/>
+      <c r="CQ6" s="29"/>
+    </row>
+    <row r="7" spans="1:95" ht="15.75">
+      <c r="A7" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="D7" s="10" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="23">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75">
-      <c r="A8" s="36" t="s">
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
+      <c r="BX7" s="29"/>
+      <c r="BY7" s="29"/>
+      <c r="BZ7" s="29"/>
+      <c r="CA7" s="29"/>
+      <c r="CB7" s="29"/>
+      <c r="CC7" s="29"/>
+      <c r="CD7" s="29"/>
+      <c r="CE7" s="29"/>
+      <c r="CF7" s="29"/>
+      <c r="CG7" s="29"/>
+      <c r="CH7" s="29"/>
+      <c r="CI7" s="29"/>
+      <c r="CJ7" s="29"/>
+      <c r="CK7" s="29"/>
+      <c r="CL7" s="29"/>
+      <c r="CM7" s="29"/>
+      <c r="CN7" s="29"/>
+      <c r="CO7" s="29"/>
+      <c r="CP7" s="29"/>
+      <c r="CQ7" s="29"/>
+    </row>
+    <row r="8" spans="1:95" ht="15.75">
+      <c r="A8" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="26">
         <v>1</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="C8" s="29"/>
+      <c r="D8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="23">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75">
-      <c r="A9" s="36" t="s">
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="29"/>
+      <c r="AL8" s="29"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="29"/>
+      <c r="AR8" s="29"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="29"/>
+      <c r="AU8" s="29"/>
+      <c r="AV8" s="29"/>
+      <c r="AW8" s="29"/>
+      <c r="AX8" s="29"/>
+      <c r="AY8" s="29"/>
+      <c r="AZ8" s="29"/>
+      <c r="BA8" s="29"/>
+      <c r="BB8" s="29"/>
+      <c r="BC8" s="29"/>
+      <c r="BD8" s="29"/>
+      <c r="BE8" s="29"/>
+      <c r="BF8" s="29"/>
+      <c r="BG8" s="29"/>
+      <c r="BH8" s="29"/>
+      <c r="BI8" s="29"/>
+      <c r="BJ8" s="29"/>
+      <c r="BK8" s="29"/>
+      <c r="BL8" s="29"/>
+      <c r="BM8" s="29"/>
+      <c r="BN8" s="29"/>
+      <c r="BO8" s="29"/>
+      <c r="BP8" s="29"/>
+      <c r="BQ8" s="29"/>
+      <c r="BR8" s="29"/>
+      <c r="BS8" s="29"/>
+      <c r="BT8" s="29"/>
+      <c r="BU8" s="29"/>
+      <c r="BV8" s="29"/>
+      <c r="BW8" s="29"/>
+      <c r="BX8" s="29"/>
+      <c r="BY8" s="29"/>
+      <c r="BZ8" s="29"/>
+      <c r="CA8" s="29"/>
+      <c r="CB8" s="29"/>
+      <c r="CC8" s="29"/>
+      <c r="CD8" s="29"/>
+      <c r="CE8" s="29"/>
+      <c r="CF8" s="29"/>
+      <c r="CG8" s="29"/>
+      <c r="CH8" s="29"/>
+      <c r="CI8" s="29"/>
+      <c r="CJ8" s="29"/>
+      <c r="CK8" s="29"/>
+      <c r="CL8" s="29"/>
+      <c r="CM8" s="29"/>
+      <c r="CN8" s="29"/>
+      <c r="CO8" s="29"/>
+      <c r="CP8" s="29"/>
+      <c r="CQ8" s="29"/>
+    </row>
+    <row r="9" spans="1:95" ht="15.75">
+      <c r="A9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="34"/>
-    </row>
-    <row r="10" spans="1:12" ht="32.25" customHeight="1">
-      <c r="I10" s="37" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="29"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="29"/>
+      <c r="AX9" s="29"/>
+      <c r="AY9" s="29"/>
+      <c r="AZ9" s="29"/>
+      <c r="BA9" s="29"/>
+      <c r="BB9" s="29"/>
+      <c r="BC9" s="29"/>
+      <c r="BD9" s="29"/>
+      <c r="BE9" s="29"/>
+      <c r="BF9" s="29"/>
+      <c r="BG9" s="29"/>
+      <c r="BH9" s="29"/>
+      <c r="BI9" s="29"/>
+      <c r="BJ9" s="29"/>
+      <c r="BK9" s="29"/>
+      <c r="BL9" s="29"/>
+      <c r="BM9" s="29"/>
+      <c r="BN9" s="29"/>
+      <c r="BO9" s="29"/>
+      <c r="BP9" s="29"/>
+      <c r="BQ9" s="29"/>
+      <c r="BR9" s="29"/>
+      <c r="BS9" s="29"/>
+      <c r="BT9" s="29"/>
+      <c r="BU9" s="29"/>
+      <c r="BV9" s="29"/>
+      <c r="BW9" s="29"/>
+      <c r="BX9" s="29"/>
+      <c r="BY9" s="29"/>
+      <c r="BZ9" s="29"/>
+      <c r="CA9" s="29"/>
+      <c r="CB9" s="29"/>
+      <c r="CC9" s="29"/>
+      <c r="CD9" s="29"/>
+      <c r="CE9" s="29"/>
+      <c r="CF9" s="29"/>
+      <c r="CG9" s="29"/>
+      <c r="CH9" s="29"/>
+      <c r="CI9" s="29"/>
+      <c r="CJ9" s="29"/>
+      <c r="CK9" s="29"/>
+      <c r="CL9" s="29"/>
+      <c r="CM9" s="29"/>
+      <c r="CN9" s="29"/>
+      <c r="CO9" s="29"/>
+      <c r="CP9" s="29"/>
+      <c r="CQ9" s="29"/>
+    </row>
+    <row r="10" spans="1:95" ht="32.25" customHeight="1">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="29"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="29"/>
+      <c r="AL10" s="29"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+      <c r="AO10" s="29"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="29"/>
+      <c r="AR10" s="29"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="29"/>
+      <c r="AU10" s="29"/>
+      <c r="AV10" s="29"/>
+      <c r="AW10" s="29"/>
+      <c r="AX10" s="29"/>
+      <c r="AY10" s="29"/>
+      <c r="AZ10" s="29"/>
+      <c r="BA10" s="29"/>
+      <c r="BB10" s="29"/>
+      <c r="BC10" s="29"/>
+      <c r="BD10" s="29"/>
+      <c r="BE10" s="29"/>
+      <c r="BF10" s="29"/>
+      <c r="BG10" s="29"/>
+      <c r="BH10" s="29"/>
+      <c r="BI10" s="29"/>
+      <c r="BJ10" s="29"/>
+      <c r="BK10" s="29"/>
+      <c r="BL10" s="29"/>
+      <c r="BM10" s="29"/>
+      <c r="BN10" s="29"/>
+      <c r="BO10" s="29"/>
+      <c r="BP10" s="29"/>
+      <c r="BQ10" s="29"/>
+      <c r="BR10" s="29"/>
+      <c r="BS10" s="29"/>
+      <c r="BT10" s="29"/>
+      <c r="BU10" s="29"/>
+      <c r="BV10" s="29"/>
+      <c r="BW10" s="29"/>
+      <c r="BX10" s="29"/>
+      <c r="BY10" s="29"/>
+      <c r="BZ10" s="29"/>
+      <c r="CA10" s="29"/>
+      <c r="CB10" s="29"/>
+      <c r="CC10" s="29"/>
+      <c r="CD10" s="29"/>
+      <c r="CE10" s="29"/>
+      <c r="CF10" s="29"/>
+      <c r="CG10" s="29"/>
+      <c r="CH10" s="29"/>
+      <c r="CI10" s="29"/>
+      <c r="CJ10" s="29"/>
+      <c r="CK10" s="29"/>
+      <c r="CL10" s="29"/>
+      <c r="CM10" s="29"/>
+      <c r="CN10" s="29"/>
+      <c r="CO10" s="29"/>
+      <c r="CP10" s="29"/>
+      <c r="CQ10" s="29"/>
+    </row>
+    <row r="11" spans="1:95" ht="15.75">
+      <c r="A11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="14" t="s">
+      <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="17">
+      <c r="C11" s="13">
         <v>2026</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="11">
         <f>C11+1</f>
         <v>2027</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="11">
         <f t="shared" ref="E11:G11" si="0">D11+1</f>
         <v>2028</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="11">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="H11" s="29"/>
+      <c r="I11" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" ht="30.75">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="29" t="s">
+      <c r="N11" s="24">
+        <v>2026</v>
+      </c>
+      <c r="O11" s="29"/>
+      <c r="P11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1" t="s">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="29"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="29"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="29"/>
+      <c r="AX11" s="29"/>
+      <c r="AY11" s="29"/>
+      <c r="AZ11" s="29"/>
+      <c r="BA11" s="29"/>
+      <c r="BB11" s="29"/>
+      <c r="BC11" s="29"/>
+      <c r="BD11" s="29"/>
+      <c r="BE11" s="29"/>
+      <c r="BF11" s="29"/>
+      <c r="BG11" s="29"/>
+      <c r="BH11" s="29"/>
+      <c r="BI11" s="29"/>
+      <c r="BJ11" s="29"/>
+      <c r="BK11" s="29"/>
+      <c r="BL11" s="29"/>
+      <c r="BM11" s="29"/>
+      <c r="BN11" s="29"/>
+      <c r="BO11" s="29"/>
+      <c r="BP11" s="29"/>
+      <c r="BQ11" s="29"/>
+      <c r="BR11" s="29"/>
+      <c r="BS11" s="29"/>
+      <c r="BT11" s="29"/>
+      <c r="BU11" s="29"/>
+      <c r="BV11" s="29"/>
+      <c r="BW11" s="29"/>
+      <c r="BX11" s="29"/>
+      <c r="BY11" s="29"/>
+      <c r="BZ11" s="29"/>
+      <c r="CA11" s="29"/>
+      <c r="CB11" s="29"/>
+      <c r="CC11" s="29"/>
+      <c r="CD11" s="29"/>
+      <c r="CE11" s="29"/>
+      <c r="CF11" s="29"/>
+      <c r="CG11" s="29"/>
+      <c r="CH11" s="29"/>
+      <c r="CI11" s="29"/>
+      <c r="CJ11" s="29"/>
+      <c r="CK11" s="29"/>
+      <c r="CL11" s="29"/>
+      <c r="CM11" s="29"/>
+      <c r="CN11" s="29"/>
+      <c r="CO11" s="29"/>
+      <c r="CP11" s="29"/>
+      <c r="CQ11" s="29"/>
+    </row>
+    <row r="12" spans="1:95">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="29" t="s">
+      <c r="J12" s="3"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="27" t="s">
+      <c r="N12" s="40">
+        <v>500000</v>
+      </c>
+      <c r="O12" s="29"/>
+      <c r="P12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="Q12" s="3"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="29"/>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="29"/>
+      <c r="AC12" s="29"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="29"/>
+      <c r="AF12" s="29"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="29"/>
+      <c r="AI12" s="29"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="29"/>
+      <c r="AL12" s="29"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="29"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="29"/>
+      <c r="AR12" s="29"/>
+      <c r="AS12" s="29"/>
+      <c r="AT12" s="29"/>
+      <c r="AU12" s="29"/>
+      <c r="AV12" s="29"/>
+      <c r="AW12" s="29"/>
+      <c r="AX12" s="29"/>
+      <c r="AY12" s="29"/>
+      <c r="AZ12" s="29"/>
+      <c r="BA12" s="29"/>
+      <c r="BB12" s="29"/>
+      <c r="BC12" s="29"/>
+      <c r="BD12" s="29"/>
+      <c r="BE12" s="29"/>
+      <c r="BF12" s="29"/>
+      <c r="BG12" s="29"/>
+      <c r="BH12" s="29"/>
+      <c r="BI12" s="29"/>
+      <c r="BJ12" s="29"/>
+      <c r="BK12" s="29"/>
+      <c r="BL12" s="29"/>
+      <c r="BM12" s="29"/>
+      <c r="BN12" s="29"/>
+      <c r="BO12" s="29"/>
+      <c r="BP12" s="29"/>
+      <c r="BQ12" s="29"/>
+      <c r="BR12" s="29"/>
+      <c r="BS12" s="29"/>
+      <c r="BT12" s="29"/>
+      <c r="BU12" s="29"/>
+      <c r="BV12" s="29"/>
+      <c r="BW12" s="29"/>
+      <c r="BX12" s="29"/>
+      <c r="BY12" s="29"/>
+      <c r="BZ12" s="29"/>
+      <c r="CA12" s="29"/>
+      <c r="CB12" s="29"/>
+      <c r="CC12" s="29"/>
+      <c r="CD12" s="29"/>
+      <c r="CE12" s="29"/>
+      <c r="CF12" s="29"/>
+      <c r="CG12" s="29"/>
+      <c r="CH12" s="29"/>
+      <c r="CI12" s="29"/>
+      <c r="CJ12" s="29"/>
+      <c r="CK12" s="29"/>
+      <c r="CL12" s="29"/>
+      <c r="CM12" s="29"/>
+      <c r="CN12" s="29"/>
+      <c r="CO12" s="29"/>
+      <c r="CP12" s="29"/>
+      <c r="CQ12" s="29"/>
+    </row>
+    <row r="13" spans="1:95" ht="30.75">
+      <c r="A13" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="34" t="str" cm="1">
+        <f t="array" ref="I13">rate_structure_1</f>
+        <v>Residential water, inside</v>
+      </c>
+      <c r="J13" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="K13" s="38">
+        <v>200000</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="40">
+        <v>100000</v>
+      </c>
+      <c r="O13" s="29"/>
+      <c r="P13" s="3">
+        <v>2026</v>
+      </c>
+      <c r="Q13" s="44">
+        <v>155000</v>
+      </c>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="29"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="29"/>
+      <c r="AS13" s="29"/>
+      <c r="AT13" s="29"/>
+      <c r="AU13" s="29"/>
+      <c r="AV13" s="29"/>
+      <c r="AW13" s="29"/>
+      <c r="AX13" s="29"/>
+      <c r="AY13" s="29"/>
+      <c r="AZ13" s="29"/>
+      <c r="BA13" s="29"/>
+      <c r="BB13" s="29"/>
+      <c r="BC13" s="29"/>
+      <c r="BD13" s="29"/>
+      <c r="BE13" s="29"/>
+      <c r="BF13" s="29"/>
+      <c r="BG13" s="29"/>
+      <c r="BH13" s="29"/>
+      <c r="BI13" s="29"/>
+      <c r="BJ13" s="29"/>
+      <c r="BK13" s="29"/>
+      <c r="BL13" s="29"/>
+      <c r="BM13" s="29"/>
+      <c r="BN13" s="29"/>
+      <c r="BO13" s="29"/>
+      <c r="BP13" s="29"/>
+      <c r="BQ13" s="29"/>
+      <c r="BR13" s="29"/>
+      <c r="BS13" s="29"/>
+      <c r="BT13" s="29"/>
+      <c r="BU13" s="29"/>
+      <c r="BV13" s="29"/>
+      <c r="BW13" s="29"/>
+      <c r="BX13" s="29"/>
+      <c r="BY13" s="29"/>
+      <c r="BZ13" s="29"/>
+      <c r="CA13" s="29"/>
+      <c r="CB13" s="29"/>
+      <c r="CC13" s="29"/>
+      <c r="CD13" s="29"/>
+      <c r="CE13" s="29"/>
+      <c r="CF13" s="29"/>
+      <c r="CG13" s="29"/>
+      <c r="CH13" s="29"/>
+      <c r="CI13" s="29"/>
+      <c r="CJ13" s="29"/>
+      <c r="CK13" s="29"/>
+      <c r="CL13" s="29"/>
+      <c r="CM13" s="29"/>
+      <c r="CN13" s="29"/>
+      <c r="CO13" s="29"/>
+      <c r="CP13" s="29"/>
+      <c r="CQ13" s="29"/>
+    </row>
+    <row r="14" spans="1:95">
+      <c r="A14" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="42">
+        <v>22</v>
+      </c>
+      <c r="D14" s="45">
+        <v>25</v>
+      </c>
+      <c r="E14" s="42">
+        <v>25</v>
+      </c>
+      <c r="F14" s="42">
+        <v>25</v>
+      </c>
+      <c r="G14" s="42">
+        <v>25</v>
+      </c>
+      <c r="H14" s="29"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" ht="30.75">
-      <c r="A15" s="9"/>
-      <c r="B15" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="9"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="24"/>
-      <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="29" t="s">
+      <c r="J14" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="38">
+        <v>25000</v>
+      </c>
+      <c r="L14" s="29"/>
+      <c r="M14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="41">
+        <v>65000</v>
+      </c>
+      <c r="O14" s="29"/>
+      <c r="P14" s="3">
+        <f>P13+1</f>
+        <v>2027</v>
+      </c>
+      <c r="Q14" s="44">
+        <v>155000</v>
+      </c>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="29"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="29"/>
+      <c r="AO14" s="29"/>
+      <c r="AP14" s="29"/>
+      <c r="AQ14" s="29"/>
+      <c r="AR14" s="29"/>
+      <c r="AS14" s="29"/>
+      <c r="AT14" s="29"/>
+      <c r="AU14" s="29"/>
+      <c r="AV14" s="29"/>
+      <c r="AW14" s="29"/>
+      <c r="AX14" s="29"/>
+      <c r="AY14" s="29"/>
+      <c r="AZ14" s="29"/>
+      <c r="BA14" s="29"/>
+      <c r="BB14" s="29"/>
+      <c r="BC14" s="29"/>
+      <c r="BD14" s="29"/>
+      <c r="BE14" s="29"/>
+      <c r="BF14" s="29"/>
+      <c r="BG14" s="29"/>
+      <c r="BH14" s="29"/>
+      <c r="BI14" s="29"/>
+      <c r="BJ14" s="29"/>
+      <c r="BK14" s="29"/>
+      <c r="BL14" s="29"/>
+      <c r="BM14" s="29"/>
+      <c r="BN14" s="29"/>
+      <c r="BO14" s="29"/>
+      <c r="BP14" s="29"/>
+      <c r="BQ14" s="29"/>
+      <c r="BR14" s="29"/>
+      <c r="BS14" s="29"/>
+      <c r="BT14" s="29"/>
+      <c r="BU14" s="29"/>
+      <c r="BV14" s="29"/>
+      <c r="BW14" s="29"/>
+      <c r="BX14" s="29"/>
+      <c r="BY14" s="29"/>
+      <c r="BZ14" s="29"/>
+      <c r="CA14" s="29"/>
+      <c r="CB14" s="29"/>
+      <c r="CC14" s="29"/>
+      <c r="CD14" s="29"/>
+      <c r="CE14" s="29"/>
+      <c r="CF14" s="29"/>
+      <c r="CG14" s="29"/>
+      <c r="CH14" s="29"/>
+      <c r="CI14" s="29"/>
+      <c r="CJ14" s="29"/>
+      <c r="CK14" s="29"/>
+      <c r="CL14" s="29"/>
+      <c r="CM14" s="29"/>
+      <c r="CN14" s="29"/>
+      <c r="CO14" s="29"/>
+      <c r="CP14" s="29"/>
+      <c r="CQ14" s="29"/>
+    </row>
+    <row r="15" spans="1:95" ht="30.75">
+      <c r="A15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="38">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="46">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="38">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="38">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="38">
+        <v>2000</v>
+      </c>
+      <c r="H15" s="29"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="38">
+        <v>0</v>
+      </c>
+      <c r="L15" s="29"/>
+      <c r="M15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" s="40">
+        <v>85000</v>
+      </c>
+      <c r="O15" s="29"/>
+      <c r="P15" s="3">
+        <f>P14+1</f>
+        <v>2028</v>
+      </c>
+      <c r="Q15" s="44">
+        <v>165000</v>
+      </c>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="29"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="29"/>
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="29"/>
+      <c r="AO15" s="29"/>
+      <c r="AP15" s="29"/>
+      <c r="AQ15" s="29"/>
+      <c r="AR15" s="29"/>
+      <c r="AS15" s="29"/>
+      <c r="AT15" s="29"/>
+      <c r="AU15" s="29"/>
+      <c r="AV15" s="29"/>
+      <c r="AW15" s="29"/>
+      <c r="AX15" s="29"/>
+      <c r="AY15" s="29"/>
+      <c r="AZ15" s="29"/>
+      <c r="BA15" s="29"/>
+      <c r="BB15" s="29"/>
+      <c r="BC15" s="29"/>
+      <c r="BD15" s="29"/>
+      <c r="BE15" s="29"/>
+      <c r="BF15" s="29"/>
+      <c r="BG15" s="29"/>
+      <c r="BH15" s="29"/>
+      <c r="BI15" s="29"/>
+      <c r="BJ15" s="29"/>
+      <c r="BK15" s="29"/>
+      <c r="BL15" s="29"/>
+      <c r="BM15" s="29"/>
+      <c r="BN15" s="29"/>
+      <c r="BO15" s="29"/>
+      <c r="BP15" s="29"/>
+      <c r="BQ15" s="29"/>
+      <c r="BR15" s="29"/>
+      <c r="BS15" s="29"/>
+      <c r="BT15" s="29"/>
+      <c r="BU15" s="29"/>
+      <c r="BV15" s="29"/>
+      <c r="BW15" s="29"/>
+      <c r="BX15" s="29"/>
+      <c r="BY15" s="29"/>
+      <c r="BZ15" s="29"/>
+      <c r="CA15" s="29"/>
+      <c r="CB15" s="29"/>
+      <c r="CC15" s="29"/>
+      <c r="CD15" s="29"/>
+      <c r="CE15" s="29"/>
+      <c r="CF15" s="29"/>
+      <c r="CG15" s="29"/>
+      <c r="CH15" s="29"/>
+      <c r="CI15" s="29"/>
+      <c r="CJ15" s="29"/>
+      <c r="CK15" s="29"/>
+      <c r="CL15" s="29"/>
+      <c r="CM15" s="29"/>
+      <c r="CN15" s="29"/>
+      <c r="CO15" s="29"/>
+      <c r="CP15" s="29"/>
+      <c r="CQ15" s="29"/>
+    </row>
+    <row r="16" spans="1:95">
+      <c r="A16" s="51">
+        <v>1000</v>
+      </c>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="40">
+        <v>74000</v>
+      </c>
+      <c r="O16" s="29"/>
+      <c r="P16" s="3">
+        <f t="shared" ref="P16:P18" si="1">P15+1</f>
+        <v>2029</v>
+      </c>
+      <c r="Q16" s="44">
+        <v>165000</v>
+      </c>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="29"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="29"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="29"/>
+      <c r="AI16" s="29"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="29"/>
+      <c r="AL16" s="29"/>
+      <c r="AM16" s="29"/>
+      <c r="AN16" s="29"/>
+      <c r="AO16" s="29"/>
+      <c r="AP16" s="29"/>
+      <c r="AQ16" s="29"/>
+      <c r="AR16" s="29"/>
+      <c r="AS16" s="29"/>
+      <c r="AT16" s="29"/>
+      <c r="AU16" s="29"/>
+      <c r="AV16" s="29"/>
+      <c r="AW16" s="29"/>
+      <c r="AX16" s="29"/>
+      <c r="AY16" s="29"/>
+      <c r="AZ16" s="29"/>
+      <c r="BA16" s="29"/>
+      <c r="BB16" s="29"/>
+      <c r="BC16" s="29"/>
+      <c r="BD16" s="29"/>
+      <c r="BE16" s="29"/>
+      <c r="BF16" s="29"/>
+      <c r="BG16" s="29"/>
+      <c r="BH16" s="29"/>
+      <c r="BI16" s="29"/>
+      <c r="BJ16" s="29"/>
+      <c r="BK16" s="29"/>
+      <c r="BL16" s="29"/>
+      <c r="BM16" s="29"/>
+      <c r="BN16" s="29"/>
+      <c r="BO16" s="29"/>
+      <c r="BP16" s="29"/>
+      <c r="BQ16" s="29"/>
+      <c r="BR16" s="29"/>
+      <c r="BS16" s="29"/>
+      <c r="BT16" s="29"/>
+      <c r="BU16" s="29"/>
+      <c r="BV16" s="29"/>
+      <c r="BW16" s="29"/>
+      <c r="BX16" s="29"/>
+      <c r="BY16" s="29"/>
+      <c r="BZ16" s="29"/>
+      <c r="CA16" s="29"/>
+      <c r="CB16" s="29"/>
+      <c r="CC16" s="29"/>
+      <c r="CD16" s="29"/>
+      <c r="CE16" s="29"/>
+      <c r="CF16" s="29"/>
+      <c r="CG16" s="29"/>
+      <c r="CH16" s="29"/>
+      <c r="CI16" s="29"/>
+      <c r="CJ16" s="29"/>
+      <c r="CK16" s="29"/>
+      <c r="CL16" s="29"/>
+      <c r="CM16" s="29"/>
+      <c r="CN16" s="29"/>
+      <c r="CO16" s="29"/>
+      <c r="CP16" s="29"/>
+      <c r="CQ16" s="29"/>
+    </row>
+    <row r="17" spans="1:95">
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="40">
+        <v>200000</v>
+      </c>
+      <c r="O17" s="29"/>
+      <c r="P17" s="3">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="Q17" s="44">
+        <v>165000</v>
+      </c>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="29"/>
+      <c r="AG17" s="29"/>
+      <c r="AH17" s="29"/>
+      <c r="AI17" s="29"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="29"/>
+      <c r="AL17" s="29"/>
+      <c r="AM17" s="29"/>
+      <c r="AN17" s="29"/>
+      <c r="AO17" s="29"/>
+      <c r="AP17" s="29"/>
+      <c r="AQ17" s="29"/>
+      <c r="AR17" s="29"/>
+      <c r="AS17" s="29"/>
+      <c r="AT17" s="29"/>
+      <c r="AU17" s="29"/>
+      <c r="AV17" s="29"/>
+      <c r="AW17" s="29"/>
+      <c r="AX17" s="29"/>
+      <c r="AY17" s="29"/>
+      <c r="AZ17" s="29"/>
+      <c r="BA17" s="29"/>
+      <c r="BB17" s="29"/>
+      <c r="BC17" s="29"/>
+      <c r="BD17" s="29"/>
+      <c r="BE17" s="29"/>
+      <c r="BF17" s="29"/>
+      <c r="BG17" s="29"/>
+      <c r="BH17" s="29"/>
+      <c r="BI17" s="29"/>
+      <c r="BJ17" s="29"/>
+      <c r="BK17" s="29"/>
+      <c r="BL17" s="29"/>
+      <c r="BM17" s="29"/>
+      <c r="BN17" s="29"/>
+      <c r="BO17" s="29"/>
+      <c r="BP17" s="29"/>
+      <c r="BQ17" s="29"/>
+      <c r="BR17" s="29"/>
+      <c r="BS17" s="29"/>
+      <c r="BT17" s="29"/>
+      <c r="BU17" s="29"/>
+      <c r="BV17" s="29"/>
+      <c r="BW17" s="29"/>
+      <c r="BX17" s="29"/>
+      <c r="BY17" s="29"/>
+      <c r="BZ17" s="29"/>
+      <c r="CA17" s="29"/>
+      <c r="CB17" s="29"/>
+      <c r="CC17" s="29"/>
+      <c r="CD17" s="29"/>
+      <c r="CE17" s="29"/>
+      <c r="CF17" s="29"/>
+      <c r="CG17" s="29"/>
+      <c r="CH17" s="29"/>
+      <c r="CI17" s="29"/>
+      <c r="CJ17" s="29"/>
+      <c r="CK17" s="29"/>
+      <c r="CL17" s="29"/>
+      <c r="CM17" s="29"/>
+      <c r="CN17" s="29"/>
+      <c r="CO17" s="29"/>
+      <c r="CP17" s="29"/>
+      <c r="CQ17" s="29"/>
+    </row>
+    <row r="18" spans="1:95">
+      <c r="A18" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="3" t="str" cm="1">
+        <f t="array" ref="I18">rate_structure_2</f>
+        <v>Residential water, outside</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="38">
+        <v>72000</v>
+      </c>
+      <c r="L18" s="29"/>
+      <c r="M18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="40">
+        <v>96000</v>
+      </c>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="29"/>
+      <c r="AC18" s="29"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="29"/>
+      <c r="AF18" s="29"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="29"/>
+      <c r="AI18" s="29"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="29"/>
+      <c r="AL18" s="29"/>
+      <c r="AM18" s="29"/>
+      <c r="AN18" s="29"/>
+      <c r="AO18" s="29"/>
+      <c r="AP18" s="29"/>
+      <c r="AQ18" s="29"/>
+      <c r="AR18" s="29"/>
+      <c r="AS18" s="29"/>
+      <c r="AT18" s="29"/>
+      <c r="AU18" s="29"/>
+      <c r="AV18" s="29"/>
+      <c r="AW18" s="29"/>
+      <c r="AX18" s="29"/>
+      <c r="AY18" s="29"/>
+      <c r="AZ18" s="29"/>
+      <c r="BA18" s="29"/>
+      <c r="BB18" s="29"/>
+      <c r="BC18" s="29"/>
+      <c r="BD18" s="29"/>
+      <c r="BE18" s="29"/>
+      <c r="BF18" s="29"/>
+      <c r="BG18" s="29"/>
+      <c r="BH18" s="29"/>
+      <c r="BI18" s="29"/>
+      <c r="BJ18" s="29"/>
+      <c r="BK18" s="29"/>
+      <c r="BL18" s="29"/>
+      <c r="BM18" s="29"/>
+      <c r="BN18" s="29"/>
+      <c r="BO18" s="29"/>
+      <c r="BP18" s="29"/>
+      <c r="BQ18" s="29"/>
+      <c r="BR18" s="29"/>
+      <c r="BS18" s="29"/>
+      <c r="BT18" s="29"/>
+      <c r="BU18" s="29"/>
+      <c r="BV18" s="29"/>
+      <c r="BW18" s="29"/>
+      <c r="BX18" s="29"/>
+      <c r="BY18" s="29"/>
+      <c r="BZ18" s="29"/>
+      <c r="CA18" s="29"/>
+      <c r="CB18" s="29"/>
+      <c r="CC18" s="29"/>
+      <c r="CD18" s="29"/>
+      <c r="CE18" s="29"/>
+      <c r="CF18" s="29"/>
+      <c r="CG18" s="29"/>
+      <c r="CH18" s="29"/>
+      <c r="CI18" s="29"/>
+      <c r="CJ18" s="29"/>
+      <c r="CK18" s="29"/>
+      <c r="CL18" s="29"/>
+      <c r="CM18" s="29"/>
+      <c r="CN18" s="29"/>
+      <c r="CO18" s="29"/>
+      <c r="CP18" s="29"/>
+      <c r="CQ18" s="29"/>
+    </row>
+    <row r="19" spans="1:95">
+      <c r="A19" s="16">
+        <v>3000</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="42">
+        <v>2</v>
+      </c>
+      <c r="D19" s="45">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="42">
+        <v>1.75</v>
+      </c>
+      <c r="F19" s="42">
+        <v>1.75</v>
+      </c>
+      <c r="G19" s="42">
+        <v>2</v>
+      </c>
+      <c r="H19" s="29"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="38">
+        <v>20000</v>
+      </c>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="29"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="29"/>
+      <c r="AG19" s="29"/>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="29"/>
+      <c r="AJ19" s="29"/>
+      <c r="AK19" s="29"/>
+      <c r="AL19" s="29"/>
+      <c r="AM19" s="29"/>
+      <c r="AN19" s="29"/>
+      <c r="AO19" s="29"/>
+      <c r="AP19" s="29"/>
+      <c r="AQ19" s="29"/>
+      <c r="AR19" s="29"/>
+      <c r="AS19" s="29"/>
+      <c r="AT19" s="29"/>
+      <c r="AU19" s="29"/>
+      <c r="AV19" s="29"/>
+      <c r="AW19" s="29"/>
+      <c r="AX19" s="29"/>
+      <c r="AY19" s="29"/>
+      <c r="AZ19" s="29"/>
+      <c r="BA19" s="29"/>
+      <c r="BB19" s="29"/>
+      <c r="BC19" s="29"/>
+      <c r="BD19" s="29"/>
+      <c r="BE19" s="29"/>
+      <c r="BF19" s="29"/>
+      <c r="BG19" s="29"/>
+      <c r="BH19" s="29"/>
+      <c r="BI19" s="29"/>
+      <c r="BJ19" s="29"/>
+      <c r="BK19" s="29"/>
+      <c r="BL19" s="29"/>
+      <c r="BM19" s="29"/>
+      <c r="BN19" s="29"/>
+      <c r="BO19" s="29"/>
+      <c r="BP19" s="29"/>
+      <c r="BQ19" s="29"/>
+      <c r="BR19" s="29"/>
+      <c r="BS19" s="29"/>
+      <c r="BT19" s="29"/>
+      <c r="BU19" s="29"/>
+      <c r="BV19" s="29"/>
+      <c r="BW19" s="29"/>
+      <c r="BX19" s="29"/>
+      <c r="BY19" s="29"/>
+      <c r="BZ19" s="29"/>
+      <c r="CA19" s="29"/>
+      <c r="CB19" s="29"/>
+      <c r="CC19" s="29"/>
+      <c r="CD19" s="29"/>
+      <c r="CE19" s="29"/>
+      <c r="CF19" s="29"/>
+      <c r="CG19" s="29"/>
+      <c r="CH19" s="29"/>
+      <c r="CI19" s="29"/>
+      <c r="CJ19" s="29"/>
+      <c r="CK19" s="29"/>
+      <c r="CL19" s="29"/>
+      <c r="CM19" s="29"/>
+      <c r="CN19" s="29"/>
+      <c r="CO19" s="29"/>
+      <c r="CP19" s="29"/>
+      <c r="CQ19" s="29"/>
+    </row>
+    <row r="20" spans="1:95">
+      <c r="A20" s="27">
+        <v>4000</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="42">
+        <v>2</v>
+      </c>
+      <c r="D20" s="45">
+        <v>2.25</v>
+      </c>
+      <c r="E20" s="42">
+        <v>2.5</v>
+      </c>
+      <c r="F20" s="42">
+        <v>2.5</v>
+      </c>
+      <c r="G20" s="42">
+        <v>2.75</v>
+      </c>
+      <c r="H20" s="29"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="38">
+        <v>0</v>
+      </c>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="29"/>
+      <c r="AH20" s="29"/>
+      <c r="AI20" s="29"/>
+      <c r="AJ20" s="29"/>
+      <c r="AK20" s="29"/>
+      <c r="AL20" s="29"/>
+      <c r="AM20" s="29"/>
+      <c r="AN20" s="29"/>
+      <c r="AO20" s="29"/>
+      <c r="AP20" s="29"/>
+      <c r="AQ20" s="29"/>
+      <c r="AR20" s="29"/>
+      <c r="AS20" s="29"/>
+      <c r="AT20" s="29"/>
+      <c r="AU20" s="29"/>
+      <c r="AV20" s="29"/>
+      <c r="AW20" s="29"/>
+      <c r="AX20" s="29"/>
+      <c r="AY20" s="29"/>
+      <c r="AZ20" s="29"/>
+      <c r="BA20" s="29"/>
+      <c r="BB20" s="29"/>
+      <c r="BC20" s="29"/>
+      <c r="BD20" s="29"/>
+      <c r="BE20" s="29"/>
+      <c r="BF20" s="29"/>
+      <c r="BG20" s="29"/>
+      <c r="BH20" s="29"/>
+      <c r="BI20" s="29"/>
+      <c r="BJ20" s="29"/>
+      <c r="BK20" s="29"/>
+      <c r="BL20" s="29"/>
+      <c r="BM20" s="29"/>
+      <c r="BN20" s="29"/>
+      <c r="BO20" s="29"/>
+      <c r="BP20" s="29"/>
+      <c r="BQ20" s="29"/>
+      <c r="BR20" s="29"/>
+      <c r="BS20" s="29"/>
+      <c r="BT20" s="29"/>
+      <c r="BU20" s="29"/>
+      <c r="BV20" s="29"/>
+      <c r="BW20" s="29"/>
+      <c r="BX20" s="29"/>
+      <c r="BY20" s="29"/>
+      <c r="BZ20" s="29"/>
+      <c r="CA20" s="29"/>
+      <c r="CB20" s="29"/>
+      <c r="CC20" s="29"/>
+      <c r="CD20" s="29"/>
+      <c r="CE20" s="29"/>
+      <c r="CF20" s="29"/>
+      <c r="CG20" s="29"/>
+      <c r="CH20" s="29"/>
+      <c r="CI20" s="29"/>
+      <c r="CJ20" s="29"/>
+      <c r="CK20" s="29"/>
+      <c r="CL20" s="29"/>
+      <c r="CM20" s="29"/>
+      <c r="CN20" s="29"/>
+      <c r="CO20" s="29"/>
+      <c r="CP20" s="29"/>
+      <c r="CQ20" s="29"/>
+    </row>
+    <row r="21" spans="1:95">
+      <c r="A21" s="27">
+        <v>5000</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="42">
+        <v>2</v>
+      </c>
+      <c r="D21" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="E21" s="42">
+        <v>3.75</v>
+      </c>
+      <c r="F21" s="42">
+        <v>3.75</v>
+      </c>
+      <c r="G21" s="42">
+        <v>4</v>
+      </c>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="29"/>
+      <c r="AC21" s="29"/>
+      <c r="AD21" s="29"/>
+      <c r="AE21" s="29"/>
+      <c r="AF21" s="29"/>
+      <c r="AG21" s="29"/>
+      <c r="AH21" s="29"/>
+      <c r="AI21" s="29"/>
+      <c r="AJ21" s="29"/>
+      <c r="AK21" s="29"/>
+      <c r="AL21" s="29"/>
+      <c r="AM21" s="29"/>
+      <c r="AN21" s="29"/>
+      <c r="AO21" s="29"/>
+      <c r="AP21" s="29"/>
+      <c r="AQ21" s="29"/>
+      <c r="AR21" s="29"/>
+      <c r="AS21" s="29"/>
+      <c r="AT21" s="29"/>
+      <c r="AU21" s="29"/>
+      <c r="AV21" s="29"/>
+      <c r="AW21" s="29"/>
+      <c r="AX21" s="29"/>
+      <c r="AY21" s="29"/>
+      <c r="AZ21" s="29"/>
+      <c r="BA21" s="29"/>
+      <c r="BB21" s="29"/>
+      <c r="BC21" s="29"/>
+      <c r="BD21" s="29"/>
+      <c r="BE21" s="29"/>
+      <c r="BF21" s="29"/>
+      <c r="BG21" s="29"/>
+      <c r="BH21" s="29"/>
+      <c r="BI21" s="29"/>
+      <c r="BJ21" s="29"/>
+      <c r="BK21" s="29"/>
+      <c r="BL21" s="29"/>
+      <c r="BM21" s="29"/>
+      <c r="BN21" s="29"/>
+      <c r="BO21" s="29"/>
+      <c r="BP21" s="29"/>
+      <c r="BQ21" s="29"/>
+      <c r="BR21" s="29"/>
+      <c r="BS21" s="29"/>
+      <c r="BT21" s="29"/>
+      <c r="BU21" s="29"/>
+      <c r="BV21" s="29"/>
+      <c r="BW21" s="29"/>
+      <c r="BX21" s="29"/>
+      <c r="BY21" s="29"/>
+      <c r="BZ21" s="29"/>
+      <c r="CA21" s="29"/>
+      <c r="CB21" s="29"/>
+      <c r="CC21" s="29"/>
+      <c r="CD21" s="29"/>
+      <c r="CE21" s="29"/>
+      <c r="CF21" s="29"/>
+      <c r="CG21" s="29"/>
+      <c r="CH21" s="29"/>
+      <c r="CI21" s="29"/>
+      <c r="CJ21" s="29"/>
+      <c r="CK21" s="29"/>
+      <c r="CL21" s="29"/>
+      <c r="CM21" s="29"/>
+      <c r="CN21" s="29"/>
+      <c r="CO21" s="29"/>
+      <c r="CP21" s="29"/>
+      <c r="CQ21" s="29"/>
+    </row>
+    <row r="22" spans="1:95">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
+      <c r="AC22" s="29"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="29"/>
+      <c r="AF22" s="29"/>
+      <c r="AG22" s="29"/>
+      <c r="AH22" s="29"/>
+      <c r="AI22" s="29"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="29"/>
+      <c r="AL22" s="29"/>
+      <c r="AM22" s="29"/>
+      <c r="AN22" s="29"/>
+      <c r="AO22" s="29"/>
+      <c r="AP22" s="29"/>
+      <c r="AQ22" s="29"/>
+      <c r="AR22" s="29"/>
+      <c r="AS22" s="29"/>
+      <c r="AT22" s="29"/>
+      <c r="AU22" s="29"/>
+      <c r="AV22" s="29"/>
+      <c r="AW22" s="29"/>
+      <c r="AX22" s="29"/>
+      <c r="AY22" s="29"/>
+      <c r="AZ22" s="29"/>
+      <c r="BA22" s="29"/>
+      <c r="BB22" s="29"/>
+      <c r="BC22" s="29"/>
+      <c r="BD22" s="29"/>
+      <c r="BE22" s="29"/>
+      <c r="BF22" s="29"/>
+      <c r="BG22" s="29"/>
+      <c r="BH22" s="29"/>
+      <c r="BI22" s="29"/>
+      <c r="BJ22" s="29"/>
+      <c r="BK22" s="29"/>
+      <c r="BL22" s="29"/>
+      <c r="BM22" s="29"/>
+      <c r="BN22" s="29"/>
+      <c r="BO22" s="29"/>
+      <c r="BP22" s="29"/>
+      <c r="BQ22" s="29"/>
+      <c r="BR22" s="29"/>
+      <c r="BS22" s="29"/>
+      <c r="BT22" s="29"/>
+      <c r="BU22" s="29"/>
+      <c r="BV22" s="29"/>
+      <c r="BW22" s="29"/>
+      <c r="BX22" s="29"/>
+      <c r="BY22" s="29"/>
+      <c r="BZ22" s="29"/>
+      <c r="CA22" s="29"/>
+      <c r="CB22" s="29"/>
+      <c r="CC22" s="29"/>
+      <c r="CD22" s="29"/>
+      <c r="CE22" s="29"/>
+      <c r="CF22" s="29"/>
+      <c r="CG22" s="29"/>
+      <c r="CH22" s="29"/>
+      <c r="CI22" s="29"/>
+      <c r="CJ22" s="29"/>
+      <c r="CK22" s="29"/>
+      <c r="CL22" s="29"/>
+      <c r="CM22" s="29"/>
+      <c r="CN22" s="29"/>
+      <c r="CO22" s="29"/>
+      <c r="CP22" s="29"/>
+      <c r="CQ22" s="29"/>
+    </row>
+    <row r="23" spans="1:95">
+      <c r="A23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
+      <c r="AC23" s="29"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="29"/>
+      <c r="AI23" s="29"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="29"/>
+      <c r="AL23" s="29"/>
+      <c r="AM23" s="29"/>
+      <c r="AN23" s="29"/>
+      <c r="AO23" s="29"/>
+      <c r="AP23" s="29"/>
+      <c r="AQ23" s="29"/>
+      <c r="AR23" s="29"/>
+      <c r="AS23" s="29"/>
+      <c r="AT23" s="29"/>
+      <c r="AU23" s="29"/>
+      <c r="AV23" s="29"/>
+      <c r="AW23" s="29"/>
+      <c r="AX23" s="29"/>
+      <c r="AY23" s="29"/>
+      <c r="AZ23" s="29"/>
+      <c r="BA23" s="29"/>
+      <c r="BB23" s="29"/>
+      <c r="BC23" s="29"/>
+      <c r="BD23" s="29"/>
+      <c r="BE23" s="29"/>
+      <c r="BF23" s="29"/>
+      <c r="BG23" s="29"/>
+      <c r="BH23" s="29"/>
+      <c r="BI23" s="29"/>
+      <c r="BJ23" s="29"/>
+      <c r="BK23" s="29"/>
+      <c r="BL23" s="29"/>
+      <c r="BM23" s="29"/>
+      <c r="BN23" s="29"/>
+      <c r="BO23" s="29"/>
+      <c r="BP23" s="29"/>
+      <c r="BQ23" s="29"/>
+      <c r="BR23" s="29"/>
+      <c r="BS23" s="29"/>
+      <c r="BT23" s="29"/>
+      <c r="BU23" s="29"/>
+      <c r="BV23" s="29"/>
+      <c r="BW23" s="29"/>
+      <c r="BX23" s="29"/>
+      <c r="BY23" s="29"/>
+      <c r="BZ23" s="29"/>
+      <c r="CA23" s="29"/>
+      <c r="CB23" s="29"/>
+      <c r="CC23" s="29"/>
+      <c r="CD23" s="29"/>
+      <c r="CE23" s="29"/>
+      <c r="CF23" s="29"/>
+      <c r="CG23" s="29"/>
+      <c r="CH23" s="29"/>
+      <c r="CI23" s="29"/>
+      <c r="CJ23" s="29"/>
+      <c r="CK23" s="29"/>
+      <c r="CL23" s="29"/>
+      <c r="CM23" s="29"/>
+      <c r="CN23" s="29"/>
+      <c r="CO23" s="29"/>
+      <c r="CP23" s="29"/>
+      <c r="CQ23" s="29"/>
+    </row>
+    <row r="24" spans="1:95">
+      <c r="A24" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="24"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="29">
-        <v>2000</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="24"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="21">
-        <v>3000</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="35">
-        <v>4000</v>
-      </c>
-      <c r="B20" s="29" t="s">
+      <c r="C24" s="42">
         <v>25</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="35">
+      <c r="D24" s="45">
+        <v>30</v>
+      </c>
+      <c r="E24" s="42">
+        <v>30</v>
+      </c>
+      <c r="F24" s="42">
+        <v>30</v>
+      </c>
+      <c r="G24" s="42">
+        <v>32</v>
+      </c>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="29"/>
+      <c r="AC24" s="29"/>
+      <c r="AD24" s="29"/>
+      <c r="AE24" s="29"/>
+      <c r="AF24" s="29"/>
+      <c r="AG24" s="29"/>
+      <c r="AH24" s="29"/>
+      <c r="AI24" s="29"/>
+      <c r="AJ24" s="29"/>
+      <c r="AK24" s="29"/>
+      <c r="AL24" s="29"/>
+      <c r="AM24" s="29"/>
+      <c r="AN24" s="29"/>
+      <c r="AO24" s="29"/>
+      <c r="AP24" s="29"/>
+      <c r="AQ24" s="29"/>
+      <c r="AR24" s="29"/>
+      <c r="AS24" s="29"/>
+      <c r="AT24" s="29"/>
+      <c r="AU24" s="29"/>
+      <c r="AV24" s="29"/>
+      <c r="AW24" s="29"/>
+      <c r="AX24" s="29"/>
+      <c r="AY24" s="29"/>
+      <c r="AZ24" s="29"/>
+      <c r="BA24" s="29"/>
+      <c r="BB24" s="29"/>
+      <c r="BC24" s="29"/>
+      <c r="BD24" s="29"/>
+      <c r="BE24" s="29"/>
+      <c r="BF24" s="29"/>
+      <c r="BG24" s="29"/>
+      <c r="BH24" s="29"/>
+      <c r="BI24" s="29"/>
+      <c r="BJ24" s="29"/>
+      <c r="BK24" s="29"/>
+      <c r="BL24" s="29"/>
+      <c r="BM24" s="29"/>
+      <c r="BN24" s="29"/>
+      <c r="BO24" s="29"/>
+      <c r="BP24" s="29"/>
+      <c r="BQ24" s="29"/>
+      <c r="BR24" s="29"/>
+      <c r="BS24" s="29"/>
+      <c r="BT24" s="29"/>
+      <c r="BU24" s="29"/>
+      <c r="BV24" s="29"/>
+      <c r="BW24" s="29"/>
+      <c r="BX24" s="29"/>
+      <c r="BY24" s="29"/>
+      <c r="BZ24" s="29"/>
+      <c r="CA24" s="29"/>
+      <c r="CB24" s="29"/>
+      <c r="CC24" s="29"/>
+      <c r="CD24" s="29"/>
+      <c r="CE24" s="29"/>
+      <c r="CF24" s="29"/>
+      <c r="CG24" s="29"/>
+      <c r="CH24" s="29"/>
+      <c r="CI24" s="29"/>
+      <c r="CJ24" s="29"/>
+      <c r="CK24" s="29"/>
+      <c r="CL24" s="29"/>
+      <c r="CM24" s="29"/>
+      <c r="CN24" s="29"/>
+      <c r="CO24" s="29"/>
+      <c r="CP24" s="29"/>
+      <c r="CQ24" s="29"/>
+    </row>
+    <row r="25" spans="1:95" ht="30.75">
+      <c r="A25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="26">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="29"/>
+      <c r="AC25" s="29"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="29"/>
+      <c r="AF25" s="29"/>
+      <c r="AG25" s="29"/>
+      <c r="AH25" s="29"/>
+      <c r="AI25" s="29"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="29"/>
+      <c r="AL25" s="29"/>
+      <c r="AM25" s="29"/>
+      <c r="AN25" s="29"/>
+      <c r="AO25" s="29"/>
+      <c r="AP25" s="29"/>
+      <c r="AQ25" s="29"/>
+      <c r="AR25" s="29"/>
+      <c r="AS25" s="29"/>
+      <c r="AT25" s="29"/>
+      <c r="AU25" s="29"/>
+      <c r="AV25" s="29"/>
+      <c r="AW25" s="29"/>
+      <c r="AX25" s="29"/>
+      <c r="AY25" s="29"/>
+      <c r="AZ25" s="29"/>
+      <c r="BA25" s="29"/>
+      <c r="BB25" s="29"/>
+      <c r="BC25" s="29"/>
+      <c r="BD25" s="29"/>
+      <c r="BE25" s="29"/>
+      <c r="BF25" s="29"/>
+      <c r="BG25" s="29"/>
+      <c r="BH25" s="29"/>
+      <c r="BI25" s="29"/>
+      <c r="BJ25" s="29"/>
+      <c r="BK25" s="29"/>
+      <c r="BL25" s="29"/>
+      <c r="BM25" s="29"/>
+      <c r="BN25" s="29"/>
+      <c r="BO25" s="29"/>
+      <c r="BP25" s="29"/>
+      <c r="BQ25" s="29"/>
+      <c r="BR25" s="29"/>
+      <c r="BS25" s="29"/>
+      <c r="BT25" s="29"/>
+      <c r="BU25" s="29"/>
+      <c r="BV25" s="29"/>
+      <c r="BW25" s="29"/>
+      <c r="BX25" s="29"/>
+      <c r="BY25" s="29"/>
+      <c r="BZ25" s="29"/>
+      <c r="CA25" s="29"/>
+      <c r="CB25" s="29"/>
+      <c r="CC25" s="29"/>
+      <c r="CD25" s="29"/>
+      <c r="CE25" s="29"/>
+      <c r="CF25" s="29"/>
+      <c r="CG25" s="29"/>
+      <c r="CH25" s="29"/>
+      <c r="CI25" s="29"/>
+      <c r="CJ25" s="29"/>
+      <c r="CK25" s="29"/>
+      <c r="CL25" s="29"/>
+      <c r="CM25" s="29"/>
+      <c r="CN25" s="29"/>
+      <c r="CO25" s="29"/>
+      <c r="CP25" s="29"/>
+      <c r="CQ25" s="29"/>
+    </row>
+    <row r="26" spans="1:95">
+      <c r="A26" s="51">
+        <v>120</v>
+      </c>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="29"/>
+      <c r="AC26" s="29"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="29"/>
+      <c r="AF26" s="29"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="29"/>
+      <c r="AI26" s="29"/>
+      <c r="AJ26" s="29"/>
+      <c r="AK26" s="29"/>
+      <c r="AL26" s="29"/>
+      <c r="AM26" s="29"/>
+      <c r="AN26" s="29"/>
+      <c r="AO26" s="29"/>
+      <c r="AP26" s="29"/>
+      <c r="AQ26" s="29"/>
+      <c r="AR26" s="29"/>
+      <c r="AS26" s="29"/>
+      <c r="AT26" s="29"/>
+      <c r="AU26" s="29"/>
+      <c r="AV26" s="29"/>
+      <c r="AW26" s="29"/>
+      <c r="AX26" s="29"/>
+      <c r="AY26" s="29"/>
+      <c r="AZ26" s="29"/>
+      <c r="BA26" s="29"/>
+      <c r="BB26" s="29"/>
+      <c r="BC26" s="29"/>
+      <c r="BD26" s="29"/>
+      <c r="BE26" s="29"/>
+      <c r="BF26" s="29"/>
+      <c r="BG26" s="29"/>
+      <c r="BH26" s="29"/>
+      <c r="BI26" s="29"/>
+      <c r="BJ26" s="29"/>
+      <c r="BK26" s="29"/>
+      <c r="BL26" s="29"/>
+      <c r="BM26" s="29"/>
+      <c r="BN26" s="29"/>
+      <c r="BO26" s="29"/>
+      <c r="BP26" s="29"/>
+      <c r="BQ26" s="29"/>
+      <c r="BR26" s="29"/>
+      <c r="BS26" s="29"/>
+      <c r="BT26" s="29"/>
+      <c r="BU26" s="29"/>
+      <c r="BV26" s="29"/>
+      <c r="BW26" s="29"/>
+      <c r="BX26" s="29"/>
+      <c r="BY26" s="29"/>
+      <c r="BZ26" s="29"/>
+      <c r="CA26" s="29"/>
+      <c r="CB26" s="29"/>
+      <c r="CC26" s="29"/>
+      <c r="CD26" s="29"/>
+      <c r="CE26" s="29"/>
+      <c r="CF26" s="29"/>
+      <c r="CG26" s="29"/>
+      <c r="CH26" s="29"/>
+      <c r="CI26" s="29"/>
+      <c r="CJ26" s="29"/>
+      <c r="CK26" s="29"/>
+      <c r="CL26" s="29"/>
+      <c r="CM26" s="29"/>
+      <c r="CN26" s="29"/>
+      <c r="CO26" s="29"/>
+      <c r="CP26" s="29"/>
+      <c r="CQ26" s="29"/>
+    </row>
+    <row r="27" spans="1:95">
+      <c r="A27" s="35"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="29"/>
+      <c r="AC27" s="29"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="29"/>
+      <c r="AF27" s="29"/>
+      <c r="AG27" s="29"/>
+      <c r="AH27" s="29"/>
+      <c r="AI27" s="29"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="29"/>
+      <c r="AL27" s="29"/>
+      <c r="AM27" s="29"/>
+      <c r="AN27" s="29"/>
+      <c r="AO27" s="29"/>
+      <c r="AP27" s="29"/>
+      <c r="AQ27" s="29"/>
+      <c r="AR27" s="29"/>
+      <c r="AS27" s="29"/>
+      <c r="AT27" s="29"/>
+      <c r="AU27" s="29"/>
+      <c r="AV27" s="29"/>
+      <c r="AW27" s="29"/>
+      <c r="AX27" s="29"/>
+      <c r="AY27" s="29"/>
+      <c r="AZ27" s="29"/>
+      <c r="BA27" s="29"/>
+      <c r="BB27" s="29"/>
+      <c r="BC27" s="29"/>
+      <c r="BD27" s="29"/>
+      <c r="BE27" s="29"/>
+      <c r="BF27" s="29"/>
+      <c r="BG27" s="29"/>
+      <c r="BH27" s="29"/>
+      <c r="BI27" s="29"/>
+      <c r="BJ27" s="29"/>
+      <c r="BK27" s="29"/>
+      <c r="BL27" s="29"/>
+      <c r="BM27" s="29"/>
+      <c r="BN27" s="29"/>
+      <c r="BO27" s="29"/>
+      <c r="BP27" s="29"/>
+      <c r="BQ27" s="29"/>
+      <c r="BR27" s="29"/>
+      <c r="BS27" s="29"/>
+      <c r="BT27" s="29"/>
+      <c r="BU27" s="29"/>
+      <c r="BV27" s="29"/>
+      <c r="BW27" s="29"/>
+      <c r="BX27" s="29"/>
+      <c r="BY27" s="29"/>
+      <c r="BZ27" s="29"/>
+      <c r="CA27" s="29"/>
+      <c r="CB27" s="29"/>
+      <c r="CC27" s="29"/>
+      <c r="CD27" s="29"/>
+      <c r="CE27" s="29"/>
+      <c r="CF27" s="29"/>
+      <c r="CG27" s="29"/>
+      <c r="CH27" s="29"/>
+      <c r="CI27" s="29"/>
+      <c r="CJ27" s="29"/>
+      <c r="CK27" s="29"/>
+      <c r="CL27" s="29"/>
+      <c r="CM27" s="29"/>
+      <c r="CN27" s="29"/>
+      <c r="CO27" s="29"/>
+      <c r="CP27" s="29"/>
+      <c r="CQ27" s="29"/>
+    </row>
+    <row r="28" spans="1:95">
+      <c r="A28" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29"/>
+      <c r="AC28" s="29"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="29"/>
+      <c r="AF28" s="29"/>
+      <c r="AG28" s="29"/>
+      <c r="AH28" s="29"/>
+      <c r="AI28" s="29"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="29"/>
+      <c r="AL28" s="29"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="29"/>
+      <c r="AO28" s="29"/>
+      <c r="AP28" s="29"/>
+      <c r="AQ28" s="29"/>
+      <c r="AR28" s="29"/>
+      <c r="AS28" s="29"/>
+      <c r="AT28" s="29"/>
+      <c r="AU28" s="29"/>
+      <c r="AV28" s="29"/>
+      <c r="AW28" s="29"/>
+      <c r="AX28" s="29"/>
+      <c r="AY28" s="29"/>
+      <c r="AZ28" s="29"/>
+      <c r="BA28" s="29"/>
+      <c r="BB28" s="29"/>
+      <c r="BC28" s="29"/>
+      <c r="BD28" s="29"/>
+      <c r="BE28" s="29"/>
+      <c r="BF28" s="29"/>
+      <c r="BG28" s="29"/>
+      <c r="BH28" s="29"/>
+      <c r="BI28" s="29"/>
+      <c r="BJ28" s="29"/>
+      <c r="BK28" s="29"/>
+      <c r="BL28" s="29"/>
+      <c r="BM28" s="29"/>
+      <c r="BN28" s="29"/>
+      <c r="BO28" s="29"/>
+      <c r="BP28" s="29"/>
+      <c r="BQ28" s="29"/>
+      <c r="BR28" s="29"/>
+      <c r="BS28" s="29"/>
+      <c r="BT28" s="29"/>
+      <c r="BU28" s="29"/>
+      <c r="BV28" s="29"/>
+      <c r="BW28" s="29"/>
+      <c r="BX28" s="29"/>
+      <c r="BY28" s="29"/>
+      <c r="BZ28" s="29"/>
+      <c r="CA28" s="29"/>
+      <c r="CB28" s="29"/>
+      <c r="CC28" s="29"/>
+      <c r="CD28" s="29"/>
+      <c r="CE28" s="29"/>
+      <c r="CF28" s="29"/>
+      <c r="CG28" s="29"/>
+      <c r="CH28" s="29"/>
+      <c r="CI28" s="29"/>
+      <c r="CJ28" s="29"/>
+      <c r="CK28" s="29"/>
+      <c r="CL28" s="29"/>
+      <c r="CM28" s="29"/>
+      <c r="CN28" s="29"/>
+      <c r="CO28" s="29"/>
+      <c r="CP28" s="29"/>
+      <c r="CQ28" s="29"/>
+    </row>
+    <row r="29" spans="1:95">
+      <c r="A29" s="16">
         <v>5000</v>
       </c>
-      <c r="B21" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:11" ht="30.75">
-      <c r="A25" s="9"/>
-      <c r="B25" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="9"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="24"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="24"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="29">
-        <v>2000</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="24"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="21">
-        <v>5000</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="35">
+      <c r="B29" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="45">
+        <v>3</v>
+      </c>
+      <c r="D29" s="42">
+        <v>2.5</v>
+      </c>
+      <c r="E29" s="42">
+        <v>3.75</v>
+      </c>
+      <c r="F29" s="42">
+        <v>3.75</v>
+      </c>
+      <c r="G29" s="42">
+        <v>4</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="29"/>
+      <c r="AI29" s="29"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="29"/>
+      <c r="AO29" s="29"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="29"/>
+      <c r="AR29" s="29"/>
+      <c r="AS29" s="29"/>
+      <c r="AT29" s="29"/>
+      <c r="AU29" s="29"/>
+      <c r="AV29" s="29"/>
+      <c r="AW29" s="29"/>
+      <c r="AX29" s="29"/>
+      <c r="AY29" s="29"/>
+      <c r="AZ29" s="29"/>
+      <c r="BA29" s="29"/>
+      <c r="BB29" s="29"/>
+      <c r="BC29" s="29"/>
+      <c r="BD29" s="29"/>
+      <c r="BE29" s="29"/>
+      <c r="BF29" s="29"/>
+      <c r="BG29" s="29"/>
+      <c r="BH29" s="29"/>
+      <c r="BI29" s="29"/>
+      <c r="BJ29" s="29"/>
+      <c r="BK29" s="29"/>
+      <c r="BL29" s="29"/>
+      <c r="BM29" s="29"/>
+      <c r="BN29" s="29"/>
+      <c r="BO29" s="29"/>
+      <c r="BP29" s="29"/>
+      <c r="BQ29" s="29"/>
+      <c r="BR29" s="29"/>
+      <c r="BS29" s="29"/>
+      <c r="BT29" s="29"/>
+      <c r="BU29" s="29"/>
+      <c r="BV29" s="29"/>
+      <c r="BW29" s="29"/>
+      <c r="BX29" s="29"/>
+      <c r="BY29" s="29"/>
+      <c r="BZ29" s="29"/>
+      <c r="CA29" s="29"/>
+      <c r="CB29" s="29"/>
+      <c r="CC29" s="29"/>
+      <c r="CD29" s="29"/>
+      <c r="CE29" s="29"/>
+      <c r="CF29" s="29"/>
+      <c r="CG29" s="29"/>
+      <c r="CH29" s="29"/>
+      <c r="CI29" s="29"/>
+      <c r="CJ29" s="29"/>
+      <c r="CK29" s="29"/>
+      <c r="CL29" s="29"/>
+      <c r="CM29" s="29"/>
+      <c r="CN29" s="29"/>
+      <c r="CO29" s="29"/>
+      <c r="CP29" s="29"/>
+      <c r="CQ29" s="29"/>
+    </row>
+    <row r="30" spans="1:95">
+      <c r="A30" s="27">
         <v>10000</v>
       </c>
-      <c r="B30" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="35"/>
-      <c r="B31" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="B30" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="45">
+        <v>3</v>
+      </c>
+      <c r="D30" s="42">
+        <v>3.25</v>
+      </c>
+      <c r="E30" s="42">
+        <v>3.5</v>
+      </c>
+      <c r="F30" s="42">
+        <v>3.5</v>
+      </c>
+      <c r="G30" s="42">
+        <v>3.75</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="29"/>
+      <c r="AC30" s="29"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="29"/>
+      <c r="AF30" s="29"/>
+      <c r="AG30" s="29"/>
+      <c r="AH30" s="29"/>
+      <c r="AI30" s="29"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="29"/>
+      <c r="AL30" s="29"/>
+      <c r="AM30" s="29"/>
+      <c r="AN30" s="29"/>
+      <c r="AO30" s="29"/>
+      <c r="AP30" s="29"/>
+      <c r="AQ30" s="29"/>
+      <c r="AR30" s="29"/>
+      <c r="AS30" s="29"/>
+      <c r="AT30" s="29"/>
+      <c r="AU30" s="29"/>
+      <c r="AV30" s="29"/>
+      <c r="AW30" s="29"/>
+      <c r="AX30" s="29"/>
+      <c r="AY30" s="29"/>
+      <c r="AZ30" s="29"/>
+      <c r="BA30" s="29"/>
+      <c r="BB30" s="29"/>
+      <c r="BC30" s="29"/>
+      <c r="BD30" s="29"/>
+      <c r="BE30" s="29"/>
+      <c r="BF30" s="29"/>
+      <c r="BG30" s="29"/>
+      <c r="BH30" s="29"/>
+      <c r="BI30" s="29"/>
+      <c r="BJ30" s="29"/>
+      <c r="BK30" s="29"/>
+      <c r="BL30" s="29"/>
+      <c r="BM30" s="29"/>
+      <c r="BN30" s="29"/>
+      <c r="BO30" s="29"/>
+      <c r="BP30" s="29"/>
+      <c r="BQ30" s="29"/>
+      <c r="BR30" s="29"/>
+      <c r="BS30" s="29"/>
+      <c r="BT30" s="29"/>
+      <c r="BU30" s="29"/>
+      <c r="BV30" s="29"/>
+      <c r="BW30" s="29"/>
+      <c r="BX30" s="29"/>
+      <c r="BY30" s="29"/>
+      <c r="BZ30" s="29"/>
+      <c r="CA30" s="29"/>
+      <c r="CB30" s="29"/>
+      <c r="CC30" s="29"/>
+      <c r="CD30" s="29"/>
+      <c r="CE30" s="29"/>
+      <c r="CF30" s="29"/>
+      <c r="CG30" s="29"/>
+      <c r="CH30" s="29"/>
+      <c r="CI30" s="29"/>
+      <c r="CJ30" s="29"/>
+      <c r="CK30" s="29"/>
+      <c r="CL30" s="29"/>
+      <c r="CM30" s="29"/>
+      <c r="CN30" s="29"/>
+      <c r="CO30" s="29"/>
+      <c r="CP30" s="29"/>
+      <c r="CQ30" s="29"/>
+    </row>
+    <row r="31" spans="1:95">
+      <c r="A31" s="27"/>
+      <c r="B31" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="45"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="29"/>
+      <c r="AC31" s="29"/>
+      <c r="AD31" s="29"/>
+      <c r="AE31" s="29"/>
+      <c r="AF31" s="29"/>
+      <c r="AG31" s="29"/>
+      <c r="AH31" s="29"/>
+      <c r="AI31" s="29"/>
+      <c r="AJ31" s="29"/>
+      <c r="AK31" s="29"/>
+      <c r="AL31" s="29"/>
+      <c r="AM31" s="29"/>
+      <c r="AN31" s="29"/>
+      <c r="AO31" s="29"/>
+      <c r="AP31" s="29"/>
+      <c r="AQ31" s="29"/>
+      <c r="AR31" s="29"/>
+      <c r="AS31" s="29"/>
+      <c r="AT31" s="29"/>
+      <c r="AU31" s="29"/>
+      <c r="AV31" s="29"/>
+      <c r="AW31" s="29"/>
+      <c r="AX31" s="29"/>
+      <c r="AY31" s="29"/>
+      <c r="AZ31" s="29"/>
+      <c r="BA31" s="29"/>
+      <c r="BB31" s="29"/>
+      <c r="BC31" s="29"/>
+      <c r="BD31" s="29"/>
+      <c r="BE31" s="29"/>
+      <c r="BF31" s="29"/>
+      <c r="BG31" s="29"/>
+      <c r="BH31" s="29"/>
+      <c r="BI31" s="29"/>
+      <c r="BJ31" s="29"/>
+      <c r="BK31" s="29"/>
+      <c r="BL31" s="29"/>
+      <c r="BM31" s="29"/>
+      <c r="BN31" s="29"/>
+      <c r="BO31" s="29"/>
+      <c r="BP31" s="29"/>
+      <c r="BQ31" s="29"/>
+      <c r="BR31" s="29"/>
+      <c r="BS31" s="29"/>
+      <c r="BT31" s="29"/>
+      <c r="BU31" s="29"/>
+      <c r="BV31" s="29"/>
+      <c r="BW31" s="29"/>
+      <c r="BX31" s="29"/>
+      <c r="BY31" s="29"/>
+      <c r="BZ31" s="29"/>
+      <c r="CA31" s="29"/>
+      <c r="CB31" s="29"/>
+      <c r="CC31" s="29"/>
+      <c r="CD31" s="29"/>
+      <c r="CE31" s="29"/>
+      <c r="CF31" s="29"/>
+      <c r="CG31" s="29"/>
+      <c r="CH31" s="29"/>
+      <c r="CI31" s="29"/>
+      <c r="CJ31" s="29"/>
+      <c r="CK31" s="29"/>
+      <c r="CL31" s="29"/>
+      <c r="CM31" s="29"/>
+      <c r="CN31" s="29"/>
+      <c r="CO31" s="29"/>
+      <c r="CP31" s="29"/>
+      <c r="CQ31" s="29"/>
+    </row>
+    <row r="32" spans="1:95">
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="32"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I11:K11"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="I10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1104,22 +4238,751 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FD50A9-0884-44AC-8AA5-5AA892507CF5}">
-  <dimension ref="A4:B4"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" cm="1">
-        <f t="array" ref="B4">num_accounts</f>
-        <v>1</v>
-      </c>
+    <row r="1" spans="1:12" ht="18.75">
+      <c r="A1" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="3">
+        <f>B4+1</f>
+        <v>2027</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" ref="D4:F4" si="0">C4+1</f>
+        <v>2028</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="55" cm="1">
+        <f t="array" ref="B5">num_accountsRS1</f>
+        <v>1000</v>
+      </c>
+      <c r="C5" s="55" cm="1">
+        <f t="array" ref="C5">ROUND(B5*(1+pop_growth_rate),0)</f>
+        <v>1010</v>
+      </c>
+      <c r="D5" s="55" cm="1">
+        <f t="array" ref="D5">ROUND(C5*(1+pop_growth_rate),0)</f>
+        <v>1020</v>
+      </c>
+      <c r="E5" s="55" cm="1">
+        <f t="array" ref="E5">ROUND(D5*(1+pop_growth_rate),0)</f>
+        <v>1030</v>
+      </c>
+      <c r="F5" s="55" cm="1">
+        <f t="array" ref="F5">ROUND(E5*(1+pop_growth_rate),0)</f>
+        <v>1040</v>
+      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="54" cm="1">
+        <f t="array" ref="B6:F6">base_chargeRS1 * 12 * RS1_num_accounts</f>
+        <v>264000</v>
+      </c>
+      <c r="C6" s="54">
+        <v>303000</v>
+      </c>
+      <c r="D6" s="54">
+        <v>306000</v>
+      </c>
+      <c r="E6" s="54">
+        <v>309000</v>
+      </c>
+      <c r="F6" s="54">
+        <v>312000</v>
+      </c>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="57" cm="1">
+        <f t="array" ref="B7:B9">RS1_block_consumption * RS1_vrates2026</f>
+        <v>400000</v>
+      </c>
+      <c r="C7" s="57" cm="1">
+        <f t="array" ref="C7:C9">RS1_block_consumption * RS1_vrates2027</f>
+        <v>300000</v>
+      </c>
+      <c r="D7" s="57" cm="1">
+        <f t="array" ref="D7:D9">RS1_block_consumption * RS1_vrates2028</f>
+        <v>350000</v>
+      </c>
+      <c r="E7" s="57" cm="1">
+        <f t="array" ref="E7:E9">RS1_block_consumption * RS1_vrates2029</f>
+        <v>350000</v>
+      </c>
+      <c r="F7" s="57" cm="1">
+        <f t="array" ref="F7:F9">RS1_block_consumption * RS1_vrates2030</f>
+        <v>400000</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="57">
+        <v>50000</v>
+      </c>
+      <c r="C8" s="57">
+        <v>56250</v>
+      </c>
+      <c r="D8" s="57">
+        <v>62500</v>
+      </c>
+      <c r="E8" s="57">
+        <v>62500</v>
+      </c>
+      <c r="F8" s="57">
+        <v>68750</v>
+      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="57">
+        <v>0</v>
+      </c>
+      <c r="C9" s="57">
+        <v>0</v>
+      </c>
+      <c r="D9" s="57">
+        <v>0</v>
+      </c>
+      <c r="E9" s="57">
+        <v>0</v>
+      </c>
+      <c r="F9" s="57">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="58">
+        <f>SUM(B6:B9)</f>
+        <v>714000</v>
+      </c>
+      <c r="C10" s="58">
+        <f t="shared" ref="C10:F10" si="1">SUM(C6:C9)</f>
+        <v>659250</v>
+      </c>
+      <c r="D10" s="58">
+        <f t="shared" si="1"/>
+        <v>718500</v>
+      </c>
+      <c r="E10" s="58">
+        <f t="shared" si="1"/>
+        <v>721500</v>
+      </c>
+      <c r="F10" s="58">
+        <f t="shared" si="1"/>
+        <v>780750</v>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="3">
+        <f>B13+1</f>
+        <v>2027</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" ref="D13:F13" si="2">C13+1</f>
+        <v>2028</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="2"/>
+        <v>2029</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="2"/>
+        <v>2030</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="55" cm="1">
+        <f t="array" ref="B14">num_accountsRS2</f>
+        <v>120</v>
+      </c>
+      <c r="C14" s="55" cm="1">
+        <f t="array" ref="C14">ROUND(B14*(1+pop_growth_rate),0)</f>
+        <v>121</v>
+      </c>
+      <c r="D14" s="55" cm="1">
+        <f t="array" ref="D14">ROUND(C14*(1+pop_growth_rate),0)</f>
+        <v>122</v>
+      </c>
+      <c r="E14" s="55" cm="1">
+        <f t="array" ref="E14">ROUND(D14*(1+pop_growth_rate),0)</f>
+        <v>123</v>
+      </c>
+      <c r="F14" s="55" cm="1">
+        <f t="array" ref="F14">ROUND(E14*(1+pop_growth_rate),0)</f>
+        <v>124</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="54" cm="1">
+        <f t="array" ref="B15:F15">base_chargeRS2 * 12 * RS2_num_accounts</f>
+        <v>36000</v>
+      </c>
+      <c r="C15" s="54">
+        <v>43560</v>
+      </c>
+      <c r="D15" s="54">
+        <v>43920</v>
+      </c>
+      <c r="E15" s="54">
+        <v>44280</v>
+      </c>
+      <c r="F15" s="54">
+        <v>47616</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="56" cm="1">
+        <f t="array" ref="B16:B18">RS2_block_consumption * RS1_vrates2026</f>
+        <v>144000</v>
+      </c>
+      <c r="C16" s="56" cm="1">
+        <f t="array" ref="C16:C18">RS2_block_consumption * RS1_vrates2027</f>
+        <v>108000</v>
+      </c>
+      <c r="D16" s="56" cm="1">
+        <f t="array" ref="D16:D18">RS2_block_consumption * RS1_vrates2028</f>
+        <v>126000</v>
+      </c>
+      <c r="E16" s="56" cm="1">
+        <f t="array" ref="E16:E18">RS2_block_consumption * RS1_vrates2029</f>
+        <v>126000</v>
+      </c>
+      <c r="F16" s="56" cm="1">
+        <f t="array" ref="F16:F18">RS2_block_consumption * RS1_vrates2030</f>
+        <v>144000</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="56">
+        <v>40000</v>
+      </c>
+      <c r="C17" s="56">
+        <v>45000</v>
+      </c>
+      <c r="D17" s="56">
+        <v>50000</v>
+      </c>
+      <c r="E17" s="56">
+        <v>50000</v>
+      </c>
+      <c r="F17" s="56">
+        <v>55000</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="56">
+        <v>0</v>
+      </c>
+      <c r="C18" s="56">
+        <v>0</v>
+      </c>
+      <c r="D18" s="56">
+        <v>0</v>
+      </c>
+      <c r="E18" s="56">
+        <v>0</v>
+      </c>
+      <c r="F18" s="56">
+        <v>0</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="58">
+        <f>SUM(B15:B18)</f>
+        <v>220000</v>
+      </c>
+      <c r="C19" s="58">
+        <f t="shared" ref="C19:F19" si="3">SUM(C15:C18)</f>
+        <v>196560</v>
+      </c>
+      <c r="D19" s="58">
+        <f t="shared" si="3"/>
+        <v>219920</v>
+      </c>
+      <c r="E19" s="58">
+        <f t="shared" si="3"/>
+        <v>220280</v>
+      </c>
+      <c r="F19" s="58">
+        <f t="shared" si="3"/>
+        <v>246616</v>
+      </c>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C81001-1335-4B7E-A2FE-B93793A31B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6462D014-B4B3-4BDE-A66E-8FC3706CE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
   <definedNames>
     <definedName name="base_chargeRS1">Inputs!$C$14:$G$14</definedName>
     <definedName name="base_chargeRS2">Inputs!$C$24:$G$24</definedName>
+    <definedName name="expenses_value">Inputs!$N$12:$N$18</definedName>
     <definedName name="inflation_rate">Inputs!$E$7:$E$7</definedName>
     <definedName name="num_accounts">Inputs!$B$8:$B$8</definedName>
     <definedName name="num_accountsRS1">Inputs!$A$16:$A$16</definedName>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="53">
   <si>
     <t>Water Utility Financial Model</t>
   </si>
@@ -196,7 +197,7 @@
     <t>Residential water, outside</t>
   </si>
   <si>
-    <t>Revenue Projections | 2026-2030</t>
+    <t>Revenue Projections | 2026 - 2030</t>
   </si>
   <si>
     <t>Number of Accounts</t>
@@ -214,7 +215,31 @@
     <t>Block 3 Revenue</t>
   </si>
   <si>
+    <t>RS1 Operating Revenue</t>
+  </si>
+  <si>
+    <t>RS2 Operating Revenue</t>
+  </si>
+  <si>
     <t>Total Operating Revenue</t>
+  </si>
+  <si>
+    <t>Expense Projections | 2026 - 2030</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Total Operating Expenses</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Total Cost of Service</t>
+  </si>
+  <si>
+    <t>*Revenue Requirements</t>
   </si>
 </sst>
 </file>
@@ -227,7 +252,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,14 +313,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -323,7 +340,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -465,11 +482,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -560,11 +627,41 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1491,7 +1588,9 @@
       <c r="A7" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="26"/>
+      <c r="B7" s="26">
+        <v>275000</v>
+      </c>
       <c r="C7" s="29"/>
       <c r="D7" s="6" t="s">
         <v>7</v>
@@ -1595,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="26">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="7" t="s">
@@ -1699,7 +1798,10 @@
       <c r="A9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="26"/>
+      <c r="B9" s="46">
+        <f>SUM(K13:K15,K18:K20) * 12</f>
+        <v>3804000</v>
+      </c>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
@@ -1936,12 +2038,12 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
+      <c r="T11" s="74"/>
+      <c r="U11" s="75"/>
+      <c r="V11" s="75"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="75"/>
+      <c r="Y11" s="75"/>
       <c r="Z11" s="29"/>
       <c r="AA11" s="29"/>
       <c r="AB11" s="29"/>
@@ -2041,12 +2143,12 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="76"/>
+      <c r="V12" s="76"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="76"/>
       <c r="Z12" s="29"/>
       <c r="AA12" s="29"/>
       <c r="AB12" s="29"/>
@@ -2484,7 +2586,7 @@
     </row>
     <row r="16" spans="1:95">
       <c r="A16" s="51">
-        <v>1000</v>
+        <v>2560</v>
       </c>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
@@ -3569,7 +3671,7 @@
     </row>
     <row r="26" spans="1:95">
       <c r="A26" s="51">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
@@ -4242,9 +4344,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75">
@@ -4294,25 +4394,25 @@
       <c r="L3" s="29"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="24">
         <v>2026</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="24">
         <f>B4+1</f>
         <v>2027</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="24">
         <f t="shared" ref="D4:F4" si="0">C4+1</f>
         <v>2028</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="24">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="24">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -4324,28 +4424,28 @@
       <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="55" cm="1">
+      <c r="B5" s="70" cm="1">
         <f t="array" ref="B5">num_accountsRS1</f>
-        <v>1000</v>
-      </c>
-      <c r="C5" s="55" cm="1">
+        <v>2560</v>
+      </c>
+      <c r="C5" s="71" cm="1">
         <f t="array" ref="C5">ROUND(B5*(1+pop_growth_rate),0)</f>
-        <v>1010</v>
-      </c>
-      <c r="D5" s="55" cm="1">
+        <v>2586</v>
+      </c>
+      <c r="D5" s="71" cm="1">
         <f t="array" ref="D5">ROUND(C5*(1+pop_growth_rate),0)</f>
-        <v>1020</v>
-      </c>
-      <c r="E5" s="55" cm="1">
+        <v>2612</v>
+      </c>
+      <c r="E5" s="71" cm="1">
         <f t="array" ref="E5">ROUND(D5*(1+pop_growth_rate),0)</f>
-        <v>1030</v>
-      </c>
-      <c r="F5" s="55" cm="1">
+        <v>2638</v>
+      </c>
+      <c r="F5" s="71" cm="1">
         <f t="array" ref="F5">ROUND(E5*(1+pop_growth_rate),0)</f>
-        <v>1040</v>
+        <v>2664</v>
       </c>
       <c r="G5" s="29"/>
       <c r="H5" s="29"/>
@@ -4355,24 +4455,24 @@
       <c r="L5" s="29"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="54" cm="1">
+      <c r="B6" s="67" cm="1">
         <f t="array" ref="B6:F6">base_chargeRS1 * 12 * RS1_num_accounts</f>
-        <v>264000</v>
-      </c>
-      <c r="C6" s="54">
-        <v>303000</v>
-      </c>
-      <c r="D6" s="54">
-        <v>306000</v>
-      </c>
-      <c r="E6" s="54">
-        <v>309000</v>
-      </c>
-      <c r="F6" s="54">
-        <v>312000</v>
+        <v>675840</v>
+      </c>
+      <c r="C6" s="65">
+        <v>775800</v>
+      </c>
+      <c r="D6" s="65">
+        <v>783600</v>
+      </c>
+      <c r="E6" s="65">
+        <v>791400</v>
+      </c>
+      <c r="F6" s="65">
+        <v>799200</v>
       </c>
       <c r="G6" s="29"/>
       <c r="H6" s="29"/>
@@ -4382,26 +4482,26 @@
       <c r="L6" s="29"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="57" cm="1">
+      <c r="B7" s="72" cm="1">
         <f t="array" ref="B7:B9">RS1_block_consumption * RS1_vrates2026</f>
         <v>400000</v>
       </c>
-      <c r="C7" s="57" cm="1">
+      <c r="C7" s="54" cm="1">
         <f t="array" ref="C7:C9">RS1_block_consumption * RS1_vrates2027</f>
         <v>300000</v>
       </c>
-      <c r="D7" s="57" cm="1">
+      <c r="D7" s="54" cm="1">
         <f t="array" ref="D7:D9">RS1_block_consumption * RS1_vrates2028</f>
         <v>350000</v>
       </c>
-      <c r="E7" s="57" cm="1">
+      <c r="E7" s="54" cm="1">
         <f t="array" ref="E7:E9">RS1_block_consumption * RS1_vrates2029</f>
         <v>350000</v>
       </c>
-      <c r="F7" s="57" cm="1">
+      <c r="F7" s="54" cm="1">
         <f t="array" ref="F7:F9">RS1_block_consumption * RS1_vrates2030</f>
         <v>400000</v>
       </c>
@@ -4413,22 +4513,22 @@
       <c r="L7" s="29"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="57">
+      <c r="B8" s="72">
         <v>50000</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="54">
         <v>56250</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="54">
         <v>62500</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="54">
         <v>62500</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="54">
         <v>68750</v>
       </c>
       <c r="G8" s="29"/>
@@ -4439,10 +4539,10 @@
       <c r="L8" s="29"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="57">
+      <c r="B9" s="82">
         <v>0</v>
       </c>
       <c r="C9" s="57">
@@ -4465,28 +4565,28 @@
       <c r="L9" s="29"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="78">
         <f>SUM(B6:B9)</f>
-        <v>714000</v>
-      </c>
-      <c r="C10" s="58">
+        <v>1125840</v>
+      </c>
+      <c r="C10" s="78">
         <f t="shared" ref="C10:F10" si="1">SUM(C6:C9)</f>
-        <v>659250</v>
-      </c>
-      <c r="D10" s="58">
+        <v>1132050</v>
+      </c>
+      <c r="D10" s="78">
         <f t="shared" si="1"/>
-        <v>718500</v>
-      </c>
-      <c r="E10" s="58">
+        <v>1196100</v>
+      </c>
+      <c r="E10" s="78">
         <f t="shared" si="1"/>
-        <v>721500</v>
-      </c>
-      <c r="F10" s="58">
+        <v>1203900</v>
+      </c>
+      <c r="F10" s="78">
         <f t="shared" si="1"/>
-        <v>780750</v>
+        <v>1267950</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
@@ -4526,25 +4626,25 @@
       <c r="L12" s="29"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="24">
         <v>2026</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="24">
         <f>B13+1</f>
         <v>2027</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="24">
         <f t="shared" ref="D13:F13" si="2">C13+1</f>
         <v>2028</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="24">
         <f t="shared" si="2"/>
         <v>2029</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="24">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
@@ -4556,28 +4656,28 @@
       <c r="L13" s="29"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="55" cm="1">
+      <c r="B14" s="70" cm="1">
         <f t="array" ref="B14">num_accountsRS2</f>
-        <v>120</v>
-      </c>
-      <c r="C14" s="55" cm="1">
+        <v>440</v>
+      </c>
+      <c r="C14" s="71" cm="1">
         <f t="array" ref="C14">ROUND(B14*(1+pop_growth_rate),0)</f>
-        <v>121</v>
-      </c>
-      <c r="D14" s="55" cm="1">
+        <v>444</v>
+      </c>
+      <c r="D14" s="71" cm="1">
         <f t="array" ref="D14">ROUND(C14*(1+pop_growth_rate),0)</f>
-        <v>122</v>
-      </c>
-      <c r="E14" s="55" cm="1">
+        <v>448</v>
+      </c>
+      <c r="E14" s="71" cm="1">
         <f t="array" ref="E14">ROUND(D14*(1+pop_growth_rate),0)</f>
-        <v>123</v>
-      </c>
-      <c r="F14" s="55" cm="1">
+        <v>452</v>
+      </c>
+      <c r="F14" s="71" cm="1">
         <f t="array" ref="F14">ROUND(E14*(1+pop_growth_rate),0)</f>
-        <v>124</v>
+        <v>457</v>
       </c>
       <c r="G14" s="29"/>
       <c r="H14" s="29"/>
@@ -4587,24 +4687,24 @@
       <c r="L14" s="29"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="54" cm="1">
+      <c r="B15" s="67" cm="1">
         <f t="array" ref="B15:F15">base_chargeRS2 * 12 * RS2_num_accounts</f>
-        <v>36000</v>
-      </c>
-      <c r="C15" s="54">
-        <v>43560</v>
-      </c>
-      <c r="D15" s="54">
-        <v>43920</v>
-      </c>
-      <c r="E15" s="54">
-        <v>44280</v>
-      </c>
-      <c r="F15" s="54">
-        <v>47616</v>
+        <v>132000</v>
+      </c>
+      <c r="C15" s="65">
+        <v>159840</v>
+      </c>
+      <c r="D15" s="65">
+        <v>161280</v>
+      </c>
+      <c r="E15" s="65">
+        <v>162720</v>
+      </c>
+      <c r="F15" s="65">
+        <v>175488</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="29"/>
@@ -4614,26 +4714,26 @@
       <c r="L15" s="29"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="56" cm="1">
+      <c r="B16" s="68" cm="1">
         <f t="array" ref="B16:B18">RS2_block_consumption * RS1_vrates2026</f>
         <v>144000</v>
       </c>
-      <c r="C16" s="56" cm="1">
+      <c r="C16" s="66" cm="1">
         <f t="array" ref="C16:C18">RS2_block_consumption * RS1_vrates2027</f>
         <v>108000</v>
       </c>
-      <c r="D16" s="56" cm="1">
+      <c r="D16" s="66" cm="1">
         <f t="array" ref="D16:D18">RS2_block_consumption * RS1_vrates2028</f>
         <v>126000</v>
       </c>
-      <c r="E16" s="56" cm="1">
+      <c r="E16" s="66" cm="1">
         <f t="array" ref="E16:E18">RS2_block_consumption * RS1_vrates2029</f>
         <v>126000</v>
       </c>
-      <c r="F16" s="56" cm="1">
+      <c r="F16" s="66" cm="1">
         <f t="array" ref="F16:F18">RS2_block_consumption * RS1_vrates2030</f>
         <v>144000</v>
       </c>
@@ -4645,22 +4745,22 @@
       <c r="L16" s="29"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="56">
+      <c r="B17" s="68">
         <v>40000</v>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="66">
         <v>45000</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="66">
         <v>50000</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="66">
         <v>50000</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="66">
         <v>55000</v>
       </c>
       <c r="G17" s="29"/>
@@ -4671,22 +4771,22 @@
       <c r="L17" s="29"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="56">
+      <c r="B18" s="80">
         <v>0</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="81">
         <v>0</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="81">
         <v>0</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="81">
         <v>0</v>
       </c>
       <c r="G18" s="29"/>
@@ -4697,28 +4797,28 @@
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="58">
+      <c r="A19" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="78">
         <f>SUM(B15:B18)</f>
-        <v>220000</v>
-      </c>
-      <c r="C19" s="58">
+        <v>316000</v>
+      </c>
+      <c r="C19" s="78">
         <f t="shared" ref="C19:F19" si="3">SUM(C15:C18)</f>
-        <v>196560</v>
-      </c>
-      <c r="D19" s="58">
+        <v>312840</v>
+      </c>
+      <c r="D19" s="78">
         <f t="shared" si="3"/>
-        <v>219920</v>
-      </c>
-      <c r="E19" s="58">
+        <v>337280</v>
+      </c>
+      <c r="E19" s="78">
         <f t="shared" si="3"/>
-        <v>220280</v>
-      </c>
-      <c r="F19" s="58">
+        <v>338720</v>
+      </c>
+      <c r="F19" s="78">
         <f t="shared" si="3"/>
-        <v>246616</v>
+        <v>374488</v>
       </c>
       <c r="G19" s="29"/>
       <c r="H19" s="29"/>
@@ -4741,13 +4841,30 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
+    <row r="21" spans="1:12" ht="15.75">
+      <c r="A21" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="77">
+        <f>SUM(B19+B10)</f>
+        <v>1441840</v>
+      </c>
+      <c r="C21" s="77">
+        <f t="shared" ref="C21:F21" si="4">SUM(C19+C10)</f>
+        <v>1444890</v>
+      </c>
+      <c r="D21" s="77">
+        <f t="shared" si="4"/>
+        <v>1533380</v>
+      </c>
+      <c r="E21" s="77">
+        <f t="shared" si="4"/>
+        <v>1542620</v>
+      </c>
+      <c r="F21" s="77">
+        <f t="shared" si="4"/>
+        <v>1642438</v>
+      </c>
       <c r="G21" s="29"/>
       <c r="H21" s="29"/>
       <c r="I21" s="29"/>
@@ -4989,9 +5106,733 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE54F15-E799-41AA-BBC0-A7B3D8B94A35}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="18.75">
+      <c r="A1" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.75">
+      <c r="A3" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="3">
+        <f>B4+1</f>
+        <v>2027</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" ref="D4:F4" si="0">C4+1</f>
+        <v>2028</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="58" cm="1">
+        <f t="array" ref="B5:B11">expenses_value</f>
+        <v>500000</v>
+      </c>
+      <c r="C5" s="54" cm="1">
+        <f t="array" ref="C5">ROUND(B5*(1+inflation_rate),0)</f>
+        <v>515000</v>
+      </c>
+      <c r="D5" s="54" cm="1">
+        <f t="array" ref="D5">ROUND(C5*(1+inflation_rate),0)</f>
+        <v>530450</v>
+      </c>
+      <c r="E5" s="54" cm="1">
+        <f t="array" ref="E5">ROUND(D5*(1+inflation_rate),0)</f>
+        <v>546364</v>
+      </c>
+      <c r="F5" s="54" cm="1">
+        <f t="array" ref="F5">ROUND(E5*(1+inflation_rate),0)</f>
+        <v>562755</v>
+      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="58">
+        <v>100000</v>
+      </c>
+      <c r="C6" s="54" cm="1">
+        <f t="array" ref="C6">ROUND(B6*(1+inflation_rate),0)</f>
+        <v>103000</v>
+      </c>
+      <c r="D6" s="54" cm="1">
+        <f t="array" ref="D6">ROUND(C6*(1+inflation_rate),0)</f>
+        <v>106090</v>
+      </c>
+      <c r="E6" s="54" cm="1">
+        <f t="array" ref="E6">ROUND(D6*(1+inflation_rate),0)</f>
+        <v>109273</v>
+      </c>
+      <c r="F6" s="54" cm="1">
+        <f t="array" ref="F6">ROUND(E6*(1+inflation_rate),0)</f>
+        <v>112551</v>
+      </c>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="59">
+        <v>65000</v>
+      </c>
+      <c r="C7" s="54" cm="1">
+        <f t="array" ref="C7">ROUND(B7*(1+inflation_rate),0)</f>
+        <v>66950</v>
+      </c>
+      <c r="D7" s="54" cm="1">
+        <f t="array" ref="D7">ROUND(C7*(1+inflation_rate),0)</f>
+        <v>68959</v>
+      </c>
+      <c r="E7" s="54" cm="1">
+        <f t="array" ref="E7">ROUND(D7*(1+inflation_rate),0)</f>
+        <v>71028</v>
+      </c>
+      <c r="F7" s="54" cm="1">
+        <f t="array" ref="F7">ROUND(E7*(1+inflation_rate),0)</f>
+        <v>73159</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="58">
+        <v>85000</v>
+      </c>
+      <c r="C8" s="54" cm="1">
+        <f t="array" ref="C8">ROUND(B8*(1+inflation_rate),0)</f>
+        <v>87550</v>
+      </c>
+      <c r="D8" s="54" cm="1">
+        <f t="array" ref="D8">ROUND(C8*(1+inflation_rate),0)</f>
+        <v>90177</v>
+      </c>
+      <c r="E8" s="54" cm="1">
+        <f t="array" ref="E8">ROUND(D8*(1+inflation_rate),0)</f>
+        <v>92882</v>
+      </c>
+      <c r="F8" s="54" cm="1">
+        <f t="array" ref="F8">ROUND(E8*(1+inflation_rate),0)</f>
+        <v>95668</v>
+      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="58">
+        <v>74000</v>
+      </c>
+      <c r="C9" s="54" cm="1">
+        <f t="array" ref="C9">ROUND(B9*(1+inflation_rate),0)</f>
+        <v>76220</v>
+      </c>
+      <c r="D9" s="54" cm="1">
+        <f t="array" ref="D9">ROUND(C9*(1+inflation_rate),0)</f>
+        <v>78507</v>
+      </c>
+      <c r="E9" s="54" cm="1">
+        <f t="array" ref="E9">ROUND(D9*(1+inflation_rate),0)</f>
+        <v>80862</v>
+      </c>
+      <c r="F9" s="54" cm="1">
+        <f t="array" ref="F9">ROUND(E9*(1+inflation_rate),0)</f>
+        <v>83288</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="58">
+        <v>200000</v>
+      </c>
+      <c r="C10" s="54" cm="1">
+        <f t="array" ref="C10">ROUND(B10*(1+inflation_rate),0)</f>
+        <v>206000</v>
+      </c>
+      <c r="D10" s="54" cm="1">
+        <f t="array" ref="D10">ROUND(C10*(1+inflation_rate),0)</f>
+        <v>212180</v>
+      </c>
+      <c r="E10" s="54" cm="1">
+        <f t="array" ref="E10">ROUND(D10*(1+inflation_rate),0)</f>
+        <v>218545</v>
+      </c>
+      <c r="F10" s="54" cm="1">
+        <f t="array" ref="F10">ROUND(E10*(1+inflation_rate),0)</f>
+        <v>225101</v>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="59">
+        <v>96000</v>
+      </c>
+      <c r="C11" s="57" cm="1">
+        <f t="array" ref="C11">ROUND(B11*(1+inflation_rate),0)</f>
+        <v>98880</v>
+      </c>
+      <c r="D11" s="57" cm="1">
+        <f t="array" ref="D11">ROUND(C11*(1+inflation_rate),0)</f>
+        <v>101846</v>
+      </c>
+      <c r="E11" s="57" cm="1">
+        <f t="array" ref="E11">ROUND(D11*(1+inflation_rate),0)</f>
+        <v>104901</v>
+      </c>
+      <c r="F11" s="57" cm="1">
+        <f t="array" ref="F11">ROUND(E11*(1+inflation_rate),0)</f>
+        <v>108048</v>
+      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="56">
+        <f>SUM(B5:B11)</f>
+        <v>1120000</v>
+      </c>
+      <c r="C12" s="56">
+        <f t="shared" ref="C12:F12" si="1">SUM(C5:C11)</f>
+        <v>1153600</v>
+      </c>
+      <c r="D12" s="56">
+        <f t="shared" si="1"/>
+        <v>1188209</v>
+      </c>
+      <c r="E12" s="56">
+        <f t="shared" si="1"/>
+        <v>1223855</v>
+      </c>
+      <c r="F12" s="56">
+        <f t="shared" si="1"/>
+        <v>1260570</v>
+      </c>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.75">
+      <c r="A14" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="3">
+        <f>B15+1</f>
+        <v>2027</v>
+      </c>
+      <c r="D15" s="3">
+        <f>C15+1</f>
+        <v>2028</v>
+      </c>
+      <c r="E15" s="3">
+        <f>D15+1</f>
+        <v>2029</v>
+      </c>
+      <c r="F15" s="3">
+        <f>E15+1</f>
+        <v>2030</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="61">
+        <v>155000</v>
+      </c>
+      <c r="C16" s="61">
+        <v>155000</v>
+      </c>
+      <c r="D16" s="61">
+        <v>165000</v>
+      </c>
+      <c r="E16" s="61">
+        <v>165000</v>
+      </c>
+      <c r="F16" s="61">
+        <v>165000</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+    </row>
+    <row r="18" spans="1:17" ht="15.75">
+      <c r="A18" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="64">
+        <f>SUM(B16+B12)</f>
+        <v>1275000</v>
+      </c>
+      <c r="C18" s="64">
+        <f t="shared" ref="C18:F18" si="2">SUM(C16+C12)</f>
+        <v>1308600</v>
+      </c>
+      <c r="D18" s="64">
+        <f t="shared" si="2"/>
+        <v>1353209</v>
+      </c>
+      <c r="E18" s="64">
+        <f t="shared" si="2"/>
+        <v>1388855</v>
+      </c>
+      <c r="F18" s="64">
+        <f t="shared" si="2"/>
+        <v>1425570</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A14:F14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F6006E-AC4A-427B-A6B9-D8B2844C9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E9AE2ED-6DB5-4F66-86BC-5EF679984FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -410,7 +410,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -602,11 +602,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -651,9 +673,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -674,18 +693,6 @@
     <xf numFmtId="6" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -699,13 +706,6 @@
     <xf numFmtId="6" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -752,16 +752,86 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,7 +969,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="002060"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -965,19 +1035,11 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Rate_Sufficiency_Analysis!$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total Revenue</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Using New Rates</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="375623"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1058,20 +1120,12 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Rate_Sufficiency_Analysis!$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total Cost of Service</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Expenses</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
               <a:round/>
@@ -1079,19 +1133,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="dash"/>
-            <c:size val="15"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
@@ -1892,15 +1934,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
+      <xdr:colOff>628650</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2246,10 +2288,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="21">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
+      <c r="B1" s="117"/>
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
       <c r="E1" s="27"/>
@@ -2345,10 +2387,10 @@
       <c r="CQ1" s="27"/>
     </row>
     <row r="2" spans="1:95">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
+      <c r="B2" s="119"/>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -2444,8 +2486,8 @@
       <c r="CQ2" s="27"/>
     </row>
     <row r="3" spans="1:95">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="83"/>
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
@@ -2540,11 +2582,11 @@
       <c r="CP3" s="27"/>
       <c r="CQ3" s="27"/>
     </row>
-    <row r="4" spans="1:95" ht="22.5" customHeight="1">
-      <c r="A4" s="48" t="s">
+    <row r="4" spans="1:95">
+      <c r="A4" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
+      <c r="B4" s="122"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
@@ -2850,7 +2892,7 @@
       <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="82">
+      <c r="E7" s="74">
         <v>0.03</v>
       </c>
       <c r="F7" s="27"/>
@@ -3053,12 +3095,12 @@
       <c r="A9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="65">
+      <c r="B9" s="57">
         <f>SUM(K13:K15,K18:K20) * 12</f>
         <v>3804000</v>
       </c>
       <c r="C9" s="27"/>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="75" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="2">
@@ -3251,7 +3293,7 @@
       <c r="CP10" s="27"/>
       <c r="CQ10" s="27"/>
     </row>
-    <row r="11" spans="1:95">
+    <row r="11" spans="1:95" ht="15" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>12</v>
       </c>
@@ -3278,15 +3320,15 @@
         <v>2030</v>
       </c>
       <c r="H11" s="27"/>
-      <c r="I11" s="45" t="s">
+      <c r="I11" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="95"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29"/>
@@ -3296,7 +3338,7 @@
       <c r="V11" s="29"/>
       <c r="W11" s="29"/>
       <c r="X11" s="29"/>
-      <c r="Y11" s="73"/>
+      <c r="Y11" s="65"/>
       <c r="Z11" s="27"/>
       <c r="AA11" s="27"/>
       <c r="AB11" s="27"/>
@@ -3377,29 +3419,29 @@
       <c r="F12" s="29"/>
       <c r="G12" s="31"/>
       <c r="H12" s="27"/>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="77" cm="1">
+      <c r="K12" s="69" cm="1">
         <f t="array" ref="K12">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="L12" s="77">
+      <c r="L12" s="69">
         <f>K12+1</f>
         <v>2027</v>
       </c>
-      <c r="M12" s="77">
+      <c r="M12" s="69">
         <f t="shared" ref="M12:O12" si="1">L12+1</f>
         <v>2028</v>
       </c>
-      <c r="N12" s="77">
+      <c r="N12" s="69">
         <f t="shared" si="1"/>
         <v>2029</v>
       </c>
-      <c r="O12" s="77">
+      <c r="O12" s="69">
         <f t="shared" si="1"/>
         <v>2030</v>
       </c>
@@ -3412,7 +3454,7 @@
       <c r="V12" s="29"/>
       <c r="W12" s="29"/>
       <c r="X12" s="29"/>
-      <c r="Y12" s="74"/>
+      <c r="Y12" s="66"/>
       <c r="Z12" s="27"/>
       <c r="AA12" s="27"/>
       <c r="AB12" s="27"/>
@@ -3423,21 +3465,21 @@
       <c r="AG12" s="27"/>
       <c r="AH12" s="27"/>
       <c r="AI12" s="27"/>
-      <c r="AJ12" s="37" t="s">
+      <c r="AJ12" s="36" t="s">
         <v>16</v>
       </c>
       <c r="AK12" s="22">
         <v>2026</v>
       </c>
       <c r="AL12" s="27"/>
-      <c r="AM12" s="37" t="s">
+      <c r="AM12" s="36" t="s">
         <v>17</v>
       </c>
       <c r="AN12" s="1"/>
-      <c r="AO12" s="37" t="s">
+      <c r="AO12" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="AP12" s="41" t="s">
+      <c r="AP12" s="40" t="s">
         <v>18</v>
       </c>
       <c r="AQ12" s="1">
@@ -3519,14 +3561,14 @@
       <c r="F13" s="15"/>
       <c r="G13" s="16"/>
       <c r="H13" s="27"/>
-      <c r="I13" s="32" t="str" cm="1">
+      <c r="I13" s="96" t="str" cm="1">
         <f t="array" ref="I13">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="J13" s="72" t="s">
+      <c r="J13" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="36">
+      <c r="K13" s="35">
         <v>200000</v>
       </c>
       <c r="L13" s="23" cm="1">
@@ -3568,33 +3610,33 @@
       <c r="AJ13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AK13" s="38">
+      <c r="AK13" s="37">
         <v>650000</v>
       </c>
       <c r="AL13" s="27"/>
-      <c r="AM13" s="41" t="s">
+      <c r="AM13" s="40" t="s">
         <v>18</v>
       </c>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
-      <c r="AQ13" s="52">
+      <c r="AQ13" s="47">
         <f>AN14</f>
         <v>165000</v>
       </c>
-      <c r="AR13" s="52">
+      <c r="AR13" s="47">
         <f>AN15</f>
         <v>165000</v>
       </c>
-      <c r="AS13" s="52">
+      <c r="AS13" s="47">
         <f>AN16</f>
         <v>175000</v>
       </c>
-      <c r="AT13" s="52">
+      <c r="AT13" s="47">
         <f>AN17</f>
         <v>175000</v>
       </c>
-      <c r="AU13" s="52">
+      <c r="AU13" s="47">
         <f>AN18</f>
         <v>175000</v>
       </c>
@@ -3654,27 +3696,27 @@
       <c r="B14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="39">
         <v>20</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="42">
         <v>25</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="39">
         <v>25</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="39">
         <v>25</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="39">
         <v>25</v>
       </c>
       <c r="H14" s="27"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="72" t="s">
+      <c r="I14" s="3"/>
+      <c r="J14" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="35">
         <v>25000</v>
       </c>
       <c r="L14" s="23" cm="1">
@@ -3716,14 +3758,14 @@
       <c r="AJ14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AK14" s="38">
+      <c r="AK14" s="37">
         <v>110000</v>
       </c>
       <c r="AL14" s="27"/>
       <c r="AM14" s="1">
         <v>2026</v>
       </c>
-      <c r="AN14" s="42">
+      <c r="AN14" s="41">
         <v>165000</v>
       </c>
       <c r="AO14" s="27"/>
@@ -3789,27 +3831,27 @@
       <c r="B15" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="35">
         <v>2000</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="43">
         <v>2000</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="35">
         <v>2000</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="35">
         <v>2000</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="35">
         <v>2000</v>
       </c>
       <c r="H15" s="27"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="72" t="s">
+      <c r="I15" s="81"/>
+      <c r="J15" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="35">
         <v>0</v>
       </c>
       <c r="L15" s="23" cm="1">
@@ -3851,7 +3893,7 @@
       <c r="AJ15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AK15" s="39">
+      <c r="AK15" s="38">
         <v>85000</v>
       </c>
       <c r="AL15" s="27"/>
@@ -3859,7 +3901,7 @@
         <f>AM14+1</f>
         <v>2027</v>
       </c>
-      <c r="AN15" s="42">
+      <c r="AN15" s="41">
         <v>165000</v>
       </c>
       <c r="AO15" s="27"/>
@@ -3919,11 +3961,11 @@
       <c r="CQ15" s="27"/>
     </row>
     <row r="16" spans="1:95">
-      <c r="A16" s="49">
+      <c r="A16" s="44">
         <v>2520</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
@@ -3959,7 +4001,7 @@
       <c r="AJ16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AK16" s="38">
+      <c r="AK16" s="37">
         <v>85000</v>
       </c>
       <c r="AL16" s="27"/>
@@ -3967,7 +4009,7 @@
         <f>AM15+1</f>
         <v>2028</v>
       </c>
-      <c r="AN16" s="42">
+      <c r="AN16" s="41">
         <v>175000</v>
       </c>
       <c r="AO16" s="27"/>
@@ -4027,9 +4069,9 @@
       <c r="CQ16" s="27"/>
     </row>
     <row r="17" spans="1:95">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
@@ -4045,19 +4087,19 @@
         <f t="array" ref="K17">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="L17" s="77">
+      <c r="L17" s="69">
         <f>K17+1</f>
         <v>2027</v>
       </c>
-      <c r="M17" s="77">
+      <c r="M17" s="69">
         <f t="shared" ref="M17:O17" si="2">L17+1</f>
         <v>2028</v>
       </c>
-      <c r="N17" s="77">
+      <c r="N17" s="69">
         <f t="shared" si="2"/>
         <v>2029</v>
       </c>
-      <c r="O17" s="77">
+      <c r="O17" s="69">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
@@ -4084,7 +4126,7 @@
       <c r="AJ17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AK17" s="38">
+      <c r="AK17" s="37">
         <v>74000</v>
       </c>
       <c r="AL17" s="27"/>
@@ -4092,7 +4134,7 @@
         <f t="shared" ref="AM17:AM18" si="3">AM16+1</f>
         <v>2029</v>
       </c>
-      <c r="AN17" s="42">
+      <c r="AN17" s="41">
         <v>175000</v>
       </c>
       <c r="AO17" s="27"/>
@@ -4152,11 +4194,11 @@
       <c r="CQ17" s="27"/>
     </row>
     <row r="18" spans="1:95">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
@@ -4169,7 +4211,7 @@
       <c r="J18" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="98">
+      <c r="K18" s="91">
         <v>72000</v>
       </c>
       <c r="L18" s="22" cm="1">
@@ -4211,7 +4253,7 @@
       <c r="AJ18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AK18" s="38">
+      <c r="AK18" s="37">
         <v>200000</v>
       </c>
       <c r="AL18" s="27"/>
@@ -4219,7 +4261,7 @@
         <f t="shared" si="3"/>
         <v>2030</v>
       </c>
-      <c r="AN18" s="42">
+      <c r="AN18" s="41">
         <v>175000</v>
       </c>
       <c r="AO18" s="27"/>
@@ -4285,19 +4327,19 @@
       <c r="B19" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="39">
         <v>1.75</v>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="42">
         <v>1.5</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="39">
         <v>1.75</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="39">
         <v>1.75</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="39">
         <v>2</v>
       </c>
       <c r="H19" s="27"/>
@@ -4305,7 +4347,7 @@
       <c r="J19" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="K19" s="98">
+      <c r="K19" s="91">
         <v>20000</v>
       </c>
       <c r="L19" s="22" cm="1">
@@ -4347,7 +4389,7 @@
       <c r="AJ19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK19" s="38">
+      <c r="AK19" s="37">
         <v>96000</v>
       </c>
       <c r="AL19" s="27"/>
@@ -4416,19 +4458,19 @@
       <c r="B20" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="39">
         <v>1.75</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <v>2.25</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="39">
         <v>2.5</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="39">
         <v>2.5</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="39">
         <v>2.5</v>
       </c>
       <c r="H20" s="27"/>
@@ -4436,7 +4478,7 @@
       <c r="J20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="98">
+      <c r="K20" s="91">
         <v>0</v>
       </c>
       <c r="L20" s="22" cm="1">
@@ -4543,26 +4585,26 @@
       <c r="B21" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="39">
         <v>1.75</v>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="42">
         <v>3.5</v>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="39">
         <v>3.75</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="39">
         <v>3.75</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="39">
         <v>3.75</v>
       </c>
       <c r="H21" s="27"/>
       <c r="I21" s="27"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
       <c r="M21" s="29"/>
       <c r="N21" s="29"/>
       <c r="O21" s="29"/>
@@ -4657,11 +4699,11 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="27"/>
-      <c r="J22" s="101" t="s">
+      <c r="J22" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="101"/>
-      <c r="L22" s="101"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
@@ -4852,19 +4894,19 @@
       <c r="B24" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="39">
         <v>25</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="42">
         <v>29</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="39">
         <v>29</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="39">
         <v>29</v>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="39">
         <v>30</v>
       </c>
       <c r="H24" s="27"/>
@@ -5068,12 +5110,12 @@
       <c r="CQ25" s="27"/>
     </row>
     <row r="26" spans="1:95">
-      <c r="A26" s="49">
+      <c r="A26" s="44">
         <f>B8-A16</f>
         <v>550</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
@@ -5168,9 +5210,9 @@
       <c r="CQ26" s="27"/>
     </row>
     <row r="27" spans="1:95">
-      <c r="A27" s="33"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
@@ -5265,11 +5307,11 @@
       <c r="CQ27" s="27"/>
     </row>
     <row r="28" spans="1:95">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
@@ -5370,19 +5412,19 @@
       <c r="B29" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="42">
         <v>3</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="39">
         <v>2.5</v>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="39">
         <v>3</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="39">
         <v>3</v>
       </c>
-      <c r="G29" s="40">
+      <c r="G29" s="39">
         <v>3</v>
       </c>
       <c r="H29" s="27"/>
@@ -5481,19 +5523,19 @@
       <c r="B30" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="42">
         <v>3</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="39">
         <v>3.25</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="39">
         <v>3.25</v>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="39">
         <v>3.25</v>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="39">
         <v>3.25</v>
       </c>
       <c r="H30" s="27"/>
@@ -5590,11 +5632,11 @@
       <c r="B31" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
       <c r="H31" s="27"/>
       <c r="I31" s="27"/>
       <c r="J31" s="27"/>
@@ -5730,7 +5772,7 @@
   <mergeCells count="6">
     <mergeCell ref="J21:L21"/>
     <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I11:O11"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -5748,16 +5790,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30.75" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
@@ -6415,13 +6457,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="18.75">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
       <c r="H1" s="27"/>
@@ -6489,13 +6531,13 @@
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
-      <c r="L2" s="99" t="s">
+      <c r="L2" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
       <c r="Q2" s="99"/>
       <c r="R2" s="27"/>
       <c r="S2" s="27"/>
@@ -6541,25 +6583,25 @@
       <c r="BG2" s="27"/>
     </row>
     <row r="3" spans="1:59" ht="18.75">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
       <c r="F3" s="99"/>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
       <c r="I3" s="27"/>
       <c r="J3" s="27"/>
       <c r="K3" s="27"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="125"/>
       <c r="R3" s="27"/>
       <c r="S3" s="27"/>
       <c r="T3" s="27"/>
@@ -6604,27 +6646,27 @@
       <c r="BG3" s="27"/>
     </row>
     <row r="4" spans="1:59">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="101"/>
       <c r="G4" s="27"/>
       <c r="H4" s="27"/>
       <c r="I4" s="27"/>
       <c r="J4" s="27"/>
       <c r="K4" s="27"/>
-      <c r="L4" s="50" t="s">
+      <c r="L4" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="101"/>
       <c r="R4" s="27"/>
       <c r="S4" s="27"/>
       <c r="T4" s="27"/>
@@ -6632,20 +6674,20 @@
       <c r="V4" s="27"/>
       <c r="W4" s="27"/>
       <c r="X4" s="27"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97">
+      <c r="Y4" s="90"/>
+      <c r="Z4" s="90">
         <f t="shared" ref="Z4:AC4" si="0">$B$22</f>
         <v>1439550</v>
       </c>
-      <c r="AA4" s="97">
+      <c r="AA4" s="90">
         <f t="shared" si="0"/>
         <v>1439550</v>
       </c>
-      <c r="AB4" s="97">
+      <c r="AB4" s="90">
         <f t="shared" si="0"/>
         <v>1439550</v>
       </c>
-      <c r="AC4" s="97">
+      <c r="AC4" s="90">
         <f t="shared" si="0"/>
         <v>1439550</v>
       </c>
@@ -6681,7 +6723,7 @@
       <c r="BG4" s="27"/>
     </row>
     <row r="5" spans="1:59">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="22" cm="1">
@@ -6709,7 +6751,7 @@
       <c r="I5" s="27"/>
       <c r="J5" s="27"/>
       <c r="K5" s="27"/>
-      <c r="L5" s="72" t="s">
+      <c r="L5" s="64" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="22" cm="1">
@@ -6779,23 +6821,23 @@
       <c r="A6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="69" cm="1">
+      <c r="B6" s="61" cm="1">
         <f t="array" ref="B6">num_accountsRS1</f>
         <v>2520</v>
       </c>
-      <c r="C6" s="70" cm="1">
+      <c r="C6" s="62" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+pop_growth_rate),0)</f>
         <v>2545</v>
       </c>
-      <c r="D6" s="70" cm="1">
+      <c r="D6" s="62" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+pop_growth_rate),0)</f>
         <v>2570</v>
       </c>
-      <c r="E6" s="70" cm="1">
+      <c r="E6" s="62" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+pop_growth_rate),0)</f>
         <v>2596</v>
       </c>
-      <c r="F6" s="70" cm="1">
+      <c r="F6" s="62" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
@@ -6807,23 +6849,23 @@
       <c r="L6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="69" cm="1">
+      <c r="M6" s="61" cm="1">
         <f t="array" ref="M6">num_accountsRS1</f>
         <v>2520</v>
       </c>
-      <c r="N6" s="70" cm="1">
+      <c r="N6" s="62" cm="1">
         <f t="array" ref="N6">ROUND(M6 * (1+pop_growth_rate),0)</f>
         <v>2545</v>
       </c>
-      <c r="O6" s="70" cm="1">
+      <c r="O6" s="62" cm="1">
         <f t="array" ref="O6">ROUND(N6 * (1+pop_growth_rate),0)</f>
         <v>2570</v>
       </c>
-      <c r="P6" s="70" cm="1">
+      <c r="P6" s="62" cm="1">
         <f t="array" ref="P6">ROUND(O6 * (1+pop_growth_rate),0)</f>
         <v>2596</v>
       </c>
-      <c r="Q6" s="70" cm="1">
+      <c r="Q6" s="62" cm="1">
         <f t="array" ref="Q6">ROUND(P6 * (1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
@@ -6874,20 +6916,20 @@
       <c r="A7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="66" cm="1">
+      <c r="B7" s="58" cm="1">
         <f t="array" ref="B7:F7">base_chargeRS1 * 12 * RS1_num_accounts</f>
         <v>604800</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="55">
         <v>763500</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="55">
         <v>771000</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="55">
         <v>778800</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="55">
         <v>786600</v>
       </c>
       <c r="G7" s="27"/>
@@ -6895,23 +6937,23 @@
       <c r="I7" s="27"/>
       <c r="J7" s="27"/>
       <c r="K7" s="27"/>
-      <c r="L7" s="22" t="s">
+      <c r="L7" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="66" cm="1">
+      <c r="M7" s="106" cm="1">
         <f t="array" ref="M7:Q7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
         <v>604800</v>
       </c>
-      <c r="N7" s="63">
+      <c r="N7" s="107">
         <v>610800</v>
       </c>
-      <c r="O7" s="63">
+      <c r="O7" s="107">
         <v>616800</v>
       </c>
-      <c r="P7" s="63">
+      <c r="P7" s="107">
         <v>623040</v>
       </c>
-      <c r="Q7" s="63">
+      <c r="Q7" s="107">
         <v>629280</v>
       </c>
       <c r="R7" s="27"/>
@@ -6961,23 +7003,23 @@
       <c r="A8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="71" cm="1">
+      <c r="B8" s="63" cm="1">
         <f t="array" ref="B8:B10">RS1_block_consumption2026 * RS1_vrates2026</f>
         <v>350000</v>
       </c>
-      <c r="C8" s="52" cm="1">
+      <c r="C8" s="47" cm="1">
         <f t="array" ref="C8:C10">RS1_block_consumption2027 * RS1_vrates2027</f>
         <v>303000</v>
       </c>
-      <c r="D8" s="52" cm="1">
+      <c r="D8" s="47" cm="1">
         <f t="array" ref="D8:D10">RS1_block_consumption2028 * RS1_vrates2028</f>
         <v>357035</v>
       </c>
-      <c r="E8" s="52" cm="1">
+      <c r="E8" s="47" cm="1">
         <f t="array" ref="E8:E10">RS1_block_consumption2029 * RS1_vrates2029</f>
         <v>360605</v>
       </c>
-      <c r="F8" s="52" cm="1">
+      <c r="F8" s="47" cm="1">
         <f t="array" ref="F8:F10">RS1_block_consumption2030 * RS1_vrates2030</f>
         <v>416242</v>
       </c>
@@ -6989,23 +7031,23 @@
       <c r="L8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="71" cm="1">
+      <c r="M8" s="63" cm="1">
         <f t="array" ref="M8:M10">RS1_block_consumption2026 * RS1_vrates2026</f>
         <v>350000</v>
       </c>
-      <c r="N8" s="71" cm="1">
+      <c r="N8" s="63" cm="1">
         <f t="array" ref="N8:N10">RS1_block_consumption2027 * RS1_vrates2026</f>
         <v>353500</v>
       </c>
-      <c r="O8" s="71" cm="1">
+      <c r="O8" s="63" cm="1">
         <f t="array" ref="O8:O10">RS1_block_consumption2028 * RS1_vrates2026</f>
         <v>357035</v>
       </c>
-      <c r="P8" s="71" cm="1">
+      <c r="P8" s="63" cm="1">
         <f t="array" ref="P8:P10">RS1_block_consumption2029 * RS1_vrates2026</f>
         <v>360605</v>
       </c>
-      <c r="Q8" s="71" cm="1">
+      <c r="Q8" s="63" cm="1">
         <f t="array" ref="Q8:Q10">RS1_block_consumption2030 * RS1_vrates2026</f>
         <v>364211.75</v>
       </c>
@@ -7056,19 +7098,19 @@
       <c r="A9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="71">
+      <c r="B9" s="63">
         <v>43750</v>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="47">
         <v>56812.5</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="47">
         <v>63757.5</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="47">
         <v>64395</v>
       </c>
-      <c r="F9" s="52">
+      <c r="F9" s="47">
         <v>65040</v>
       </c>
       <c r="G9" s="27"/>
@@ -7079,19 +7121,19 @@
       <c r="L9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="M9" s="71">
+      <c r="M9" s="63">
         <v>43750</v>
       </c>
-      <c r="N9" s="71">
+      <c r="N9" s="63">
         <v>44187.5</v>
       </c>
-      <c r="O9" s="71">
+      <c r="O9" s="63">
         <v>44630.25</v>
       </c>
-      <c r="P9" s="71">
+      <c r="P9" s="63">
         <v>45076.5</v>
       </c>
-      <c r="Q9" s="71">
+      <c r="Q9" s="63">
         <v>45528</v>
       </c>
       <c r="R9" s="27"/>
@@ -7138,22 +7180,22 @@
       <c r="BG9" s="27"/>
     </row>
     <row r="10" spans="1:59">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="80">
+      <c r="B10" s="63">
         <v>0</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="47">
         <v>0</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="47">
         <v>0</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="47">
         <v>0</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="47">
         <v>0</v>
       </c>
       <c r="G10" s="27"/>
@@ -7161,22 +7203,22 @@
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="80">
+      <c r="M10" s="72">
         <v>0</v>
       </c>
-      <c r="N10" s="80">
+      <c r="N10" s="72">
         <v>0</v>
       </c>
-      <c r="O10" s="80">
+      <c r="O10" s="72">
         <v>0</v>
       </c>
-      <c r="P10" s="80">
+      <c r="P10" s="72">
         <v>0</v>
       </c>
-      <c r="Q10" s="80">
+      <c r="Q10" s="72">
         <v>0</v>
       </c>
       <c r="R10" s="27"/>
@@ -7223,26 +7265,26 @@
       <c r="BG10" s="27"/>
     </row>
     <row r="11" spans="1:59">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="76">
+      <c r="B11" s="103">
         <f>SUM(B7:B10)</f>
         <v>998550</v>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="103">
         <f t="shared" ref="C11:F11" si="3">SUM(C7:C10)</f>
         <v>1123312.5</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="103">
         <f t="shared" si="3"/>
         <v>1191792.5</v>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="103">
         <f t="shared" si="3"/>
         <v>1203800</v>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="103">
         <f t="shared" si="3"/>
         <v>1267882</v>
       </c>
@@ -7251,26 +7293,26 @@
       <c r="I11" s="27"/>
       <c r="J11" s="27"/>
       <c r="K11" s="27"/>
-      <c r="L11" s="53" t="s">
+      <c r="L11" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="76">
+      <c r="M11" s="68">
         <f>SUM(M7:M10)</f>
         <v>998550</v>
       </c>
-      <c r="N11" s="76">
+      <c r="N11" s="68">
         <f t="shared" ref="N11" si="4">SUM(N7:N10)</f>
         <v>1008487.5</v>
       </c>
-      <c r="O11" s="76">
+      <c r="O11" s="68">
         <f t="shared" ref="O11" si="5">SUM(O7:O10)</f>
         <v>1018465.25</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="68">
         <f t="shared" ref="P11" si="6">SUM(P7:P10)</f>
         <v>1028721.5</v>
       </c>
-      <c r="Q11" s="76">
+      <c r="Q11" s="68">
         <f t="shared" ref="Q11" si="7">SUM(Q7:Q10)</f>
         <v>1039019.75</v>
       </c>
@@ -7379,20 +7421,20 @@
       <c r="BG12" s="27"/>
     </row>
     <row r="13" spans="1:59">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="105"/>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
       <c r="J13" s="27"/>
       <c r="K13" s="27"/>
-      <c r="L13" s="50" t="s">
+      <c r="L13" s="45" t="s">
         <v>29</v>
       </c>
       <c r="M13" s="1"/>
@@ -7539,26 +7581,26 @@
       <c r="BG14" s="27"/>
     </row>
     <row r="15" spans="1:59">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="69" cm="1">
+      <c r="B15" s="61" cm="1">
         <f t="array" ref="B15">num_accountsRS2</f>
         <v>550</v>
       </c>
-      <c r="C15" s="70" cm="1">
+      <c r="C15" s="62" cm="1">
         <f t="array" ref="C15">ROUND(B15*(1+pop_growth_rate),0)</f>
         <v>556</v>
       </c>
-      <c r="D15" s="70" cm="1">
+      <c r="D15" s="62" cm="1">
         <f t="array" ref="D15">ROUND(C15*(1+pop_growth_rate),0)</f>
         <v>562</v>
       </c>
-      <c r="E15" s="70" cm="1">
+      <c r="E15" s="62" cm="1">
         <f t="array" ref="E15">ROUND(D15*(1+pop_growth_rate),0)</f>
         <v>568</v>
       </c>
-      <c r="F15" s="70" cm="1">
+      <c r="F15" s="62" cm="1">
         <f t="array" ref="F15">ROUND(E15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
@@ -7567,26 +7609,26 @@
       <c r="I15" s="27"/>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
-      <c r="L15" s="68" t="s">
+      <c r="L15" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="69" cm="1">
+      <c r="M15" s="61" cm="1">
         <f t="array" ref="M15">num_accountsRS2</f>
         <v>550</v>
       </c>
-      <c r="N15" s="70" cm="1">
+      <c r="N15" s="62" cm="1">
         <f t="array" ref="N15">ROUND(M15*(1+pop_growth_rate),0)</f>
         <v>556</v>
       </c>
-      <c r="O15" s="70" cm="1">
+      <c r="O15" s="62" cm="1">
         <f t="array" ref="O15">ROUND(N15*(1+pop_growth_rate),0)</f>
         <v>562</v>
       </c>
-      <c r="P15" s="70" cm="1">
+      <c r="P15" s="62" cm="1">
         <f t="array" ref="P15">ROUND(O15*(1+pop_growth_rate),0)</f>
         <v>568</v>
       </c>
-      <c r="Q15" s="70" cm="1">
+      <c r="Q15" s="62" cm="1">
         <f t="array" ref="Q15">ROUND(P15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
@@ -7634,23 +7676,23 @@
       <c r="BG15" s="27"/>
     </row>
     <row r="16" spans="1:59">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="66" cm="1">
+      <c r="B16" s="106" cm="1">
         <f t="array" ref="B16:F16">base_chargeRS2 * 12 * RS2_num_accounts</f>
         <v>165000</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="107">
         <v>193488</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="107">
         <v>195576</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="107">
         <v>197664</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="107">
         <v>206640</v>
       </c>
       <c r="G16" s="27"/>
@@ -7661,20 +7703,20 @@
       <c r="L16" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="66" cm="1">
+      <c r="M16" s="58" cm="1">
         <f t="array" ref="M16:Q16">RS2_base_charge2026 * 12 * RS2_num_accounts</f>
         <v>165000</v>
       </c>
-      <c r="N16" s="63">
+      <c r="N16" s="55">
         <v>166800</v>
       </c>
-      <c r="O16" s="63">
+      <c r="O16" s="55">
         <v>168600</v>
       </c>
-      <c r="P16" s="63">
+      <c r="P16" s="55">
         <v>170400</v>
       </c>
-      <c r="Q16" s="63">
+      <c r="Q16" s="55">
         <v>172200</v>
       </c>
       <c r="R16" s="27"/>
@@ -7724,23 +7766,23 @@
       <c r="A17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="67" cm="1">
+      <c r="B17" s="59" cm="1">
         <f t="array" ref="B17:B19">RS2_block_consumption2026 * RS2_vrates2026</f>
         <v>216000</v>
       </c>
-      <c r="C17" s="64" cm="1">
+      <c r="C17" s="56" cm="1">
         <f t="array" ref="C17:C19">RS2_block_consumption2027 * RS2_vrates2027</f>
         <v>181800</v>
       </c>
-      <c r="D17" s="64" cm="1">
+      <c r="D17" s="56" cm="1">
         <f t="array" ref="D17:D19">RS2_block_consumption2028 * RS2_vrates2028</f>
         <v>220341</v>
       </c>
-      <c r="E17" s="64" cm="1">
+      <c r="E17" s="56" cm="1">
         <f t="array" ref="E17:E19">RS2_block_consumption2029 * RS2_vrates2029</f>
         <v>222543</v>
       </c>
-      <c r="F17" s="64" cm="1">
+      <c r="F17" s="56" cm="1">
         <f t="array" ref="F17:F19">RS2_block_consumption2030 * RS2_vrates2030</f>
         <v>224769</v>
       </c>
@@ -7752,23 +7794,23 @@
       <c r="L17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="M17" s="67" cm="1">
+      <c r="M17" s="59" cm="1">
         <f t="array" ref="M17:M19">RS2_block_consumption2026 * RS2_vrates2026</f>
         <v>216000</v>
       </c>
-      <c r="N17" s="67" cm="1">
+      <c r="N17" s="59" cm="1">
         <f t="array" ref="N17:N19">RS2_block_consumption2027 * RS2_vrates2026</f>
         <v>218160</v>
       </c>
-      <c r="O17" s="67" cm="1">
+      <c r="O17" s="59" cm="1">
         <f t="array" ref="O17:O19">RS2_block_consumption2028 * RS2_vrates2026</f>
         <v>220341</v>
       </c>
-      <c r="P17" s="67" cm="1">
+      <c r="P17" s="59" cm="1">
         <f t="array" ref="P17:P19">RS2_block_consumption2029 * RS2_vrates2026</f>
         <v>222543</v>
       </c>
-      <c r="Q17" s="67" cm="1">
+      <c r="Q17" s="59" cm="1">
         <f t="array" ref="Q17:Q19">RS2_block_consumption2030 * RS2_vrates2026</f>
         <v>224769</v>
       </c>
@@ -7819,19 +7861,19 @@
       <c r="A18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="67">
+      <c r="B18" s="59">
         <v>60000</v>
       </c>
-      <c r="C18" s="64">
+      <c r="C18" s="56">
         <v>65650</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="56">
         <v>66306.5</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="56">
         <v>66969.5</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="56">
         <v>67639</v>
       </c>
       <c r="G18" s="27"/>
@@ -7842,19 +7884,19 @@
       <c r="L18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18" s="59">
         <v>60000</v>
       </c>
-      <c r="N18" s="67">
+      <c r="N18" s="59">
         <v>60600</v>
       </c>
-      <c r="O18" s="67">
+      <c r="O18" s="59">
         <v>61206</v>
       </c>
-      <c r="P18" s="67">
+      <c r="P18" s="59">
         <v>61818</v>
       </c>
-      <c r="Q18" s="67">
+      <c r="Q18" s="59">
         <v>62436</v>
       </c>
       <c r="R18" s="27"/>
@@ -7901,22 +7943,22 @@
       <c r="BG18" s="27"/>
     </row>
     <row r="19" spans="1:59">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="78">
+      <c r="B19" s="70">
         <v>0</v>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="71">
         <v>0</v>
       </c>
-      <c r="D19" s="79">
+      <c r="D19" s="71">
         <v>0</v>
       </c>
-      <c r="E19" s="79">
+      <c r="E19" s="71">
         <v>0</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="71">
         <v>0</v>
       </c>
       <c r="G19" s="27"/>
@@ -7924,22 +7966,22 @@
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
-      <c r="L19" s="77" t="s">
+      <c r="L19" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="M19" s="78">
+      <c r="M19" s="70">
         <v>0</v>
       </c>
-      <c r="N19" s="78">
+      <c r="N19" s="70">
         <v>0</v>
       </c>
-      <c r="O19" s="78">
+      <c r="O19" s="70">
         <v>0</v>
       </c>
-      <c r="P19" s="78">
+      <c r="P19" s="70">
         <v>0</v>
       </c>
-      <c r="Q19" s="78">
+      <c r="Q19" s="70">
         <v>0</v>
       </c>
       <c r="R19" s="27"/>
@@ -7986,26 +8028,26 @@
       <c r="BG19" s="27"/>
     </row>
     <row r="20" spans="1:59">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="76">
+      <c r="B20" s="68">
         <f>SUM(B16:B19)</f>
         <v>441000</v>
       </c>
-      <c r="C20" s="76">
+      <c r="C20" s="68">
         <f t="shared" ref="C20:F20" si="10">SUM(C16:C19)</f>
         <v>440938</v>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="68">
         <f t="shared" si="10"/>
         <v>482223.5</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="68">
         <f t="shared" si="10"/>
         <v>487176.5</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="68">
         <f t="shared" si="10"/>
         <v>499048</v>
       </c>
@@ -8014,26 +8056,26 @@
       <c r="I20" s="27"/>
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
-      <c r="L20" s="53" t="s">
+      <c r="L20" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="M20" s="76">
+      <c r="M20" s="68">
         <f>SUM(M16:M19)</f>
         <v>441000</v>
       </c>
-      <c r="N20" s="76">
+      <c r="N20" s="68">
         <f t="shared" ref="N20" si="11">SUM(N16:N19)</f>
         <v>445560</v>
       </c>
-      <c r="O20" s="76">
+      <c r="O20" s="68">
         <f t="shared" ref="O20" si="12">SUM(O16:O19)</f>
         <v>450147</v>
       </c>
-      <c r="P20" s="76">
+      <c r="P20" s="68">
         <f t="shared" ref="P20" si="13">SUM(P16:P19)</f>
         <v>454761</v>
       </c>
-      <c r="Q20" s="76">
+      <c r="Q20" s="68">
         <f t="shared" ref="Q20" si="14">SUM(Q16:Q19)</f>
         <v>459405</v>
       </c>
@@ -8142,26 +8184,26 @@
       <c r="BG21" s="27"/>
     </row>
     <row r="22" spans="1:59" ht="15.75">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="75">
+      <c r="B22" s="67">
         <f>SUM(B20+B11)</f>
         <v>1439550</v>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="67">
         <f t="shared" ref="C22:F22" si="15">SUM(C20+C11)</f>
         <v>1564250.5</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="67">
         <f t="shared" si="15"/>
         <v>1674016</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="67">
         <f t="shared" si="15"/>
         <v>1690976.5</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="67">
         <f t="shared" si="15"/>
         <v>1766930</v>
       </c>
@@ -8170,26 +8212,26 @@
       <c r="I22" s="27"/>
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
-      <c r="L22" s="61" t="s">
+      <c r="L22" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="75">
+      <c r="M22" s="67">
         <f>SUM(M20+M11)</f>
         <v>1439550</v>
       </c>
-      <c r="N22" s="75">
+      <c r="N22" s="67">
         <f t="shared" ref="N22:Q22" si="16">SUM(N20+N11)</f>
         <v>1454047.5</v>
       </c>
-      <c r="O22" s="75">
+      <c r="O22" s="67">
         <f t="shared" si="16"/>
         <v>1468612.25</v>
       </c>
-      <c r="P22" s="75">
+      <c r="P22" s="67">
         <f t="shared" si="16"/>
         <v>1483482.5</v>
       </c>
-      <c r="Q22" s="75">
+      <c r="Q22" s="67">
         <f t="shared" si="16"/>
         <v>1498424.75</v>
       </c>
@@ -8764,15 +8806,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
       <c r="H1" s="27"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
@@ -8804,14 +8846,14 @@
       <c r="Q2" s="27"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="110"/>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
       <c r="I3" s="27"/>
@@ -8825,25 +8867,25 @@
       <c r="Q3" s="27"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="89">
         <v>2026</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="89">
         <f>B4+1</f>
         <v>2027</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="89">
         <f t="shared" ref="D4:F4" si="0">C4+1</f>
         <v>2028</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="89">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="101">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -8860,26 +8902,26 @@
       <c r="Q4" s="27"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="56" cm="1">
+      <c r="B5" s="51" cm="1">
         <f t="array" ref="B5:B11">expenses_value</f>
         <v>650000</v>
       </c>
-      <c r="C5" s="52" cm="1">
+      <c r="C5" s="47" cm="1">
         <f t="array" ref="C5">ROUND(B5*(1+inflation_rate),0)</f>
         <v>669500</v>
       </c>
-      <c r="D5" s="52" cm="1">
+      <c r="D5" s="47" cm="1">
         <f t="array" ref="D5">ROUND(C5*(1+inflation_rate),0)</f>
         <v>689585</v>
       </c>
-      <c r="E5" s="52" cm="1">
+      <c r="E5" s="47" cm="1">
         <f t="array" ref="E5">ROUND(D5*(1+inflation_rate),0)</f>
         <v>710273</v>
       </c>
-      <c r="F5" s="52" cm="1">
+      <c r="F5" s="47" cm="1">
         <f t="array" ref="F5">ROUND(E5*(1+inflation_rate),0)</f>
         <v>731581</v>
       </c>
@@ -8896,25 +8938,25 @@
       <c r="Q5" s="27"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="51">
         <v>110000</v>
       </c>
-      <c r="C6" s="52" cm="1">
+      <c r="C6" s="47" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+inflation_rate),0)</f>
         <v>113300</v>
       </c>
-      <c r="D6" s="52" cm="1">
+      <c r="D6" s="47" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+inflation_rate),0)</f>
         <v>116699</v>
       </c>
-      <c r="E6" s="52" cm="1">
+      <c r="E6" s="47" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+inflation_rate),0)</f>
         <v>120200</v>
       </c>
-      <c r="F6" s="52" cm="1">
+      <c r="F6" s="47" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+inflation_rate),0)</f>
         <v>123806</v>
       </c>
@@ -8931,25 +8973,25 @@
       <c r="Q6" s="27"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="57">
+      <c r="B7" s="51">
         <v>85000</v>
       </c>
-      <c r="C7" s="52" cm="1">
+      <c r="C7" s="47" cm="1">
         <f t="array" ref="C7">ROUND(B7*(1+inflation_rate),0)</f>
         <v>87550</v>
       </c>
-      <c r="D7" s="52" cm="1">
+      <c r="D7" s="47" cm="1">
         <f t="array" ref="D7">ROUND(C7*(1+inflation_rate),0)</f>
         <v>90177</v>
       </c>
-      <c r="E7" s="52" cm="1">
+      <c r="E7" s="47" cm="1">
         <f t="array" ref="E7">ROUND(D7*(1+inflation_rate),0)</f>
         <v>92882</v>
       </c>
-      <c r="F7" s="52" cm="1">
+      <c r="F7" s="47" cm="1">
         <f t="array" ref="F7">ROUND(E7*(1+inflation_rate),0)</f>
         <v>95668</v>
       </c>
@@ -8969,22 +9011,22 @@
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="111">
         <v>85000</v>
       </c>
-      <c r="C8" s="52" cm="1">
+      <c r="C8" s="112" cm="1">
         <f t="array" ref="C8">ROUND(B8*(1+inflation_rate),0)</f>
         <v>87550</v>
       </c>
-      <c r="D8" s="52" cm="1">
+      <c r="D8" s="112" cm="1">
         <f t="array" ref="D8">ROUND(C8*(1+inflation_rate),0)</f>
         <v>90177</v>
       </c>
-      <c r="E8" s="52" cm="1">
+      <c r="E8" s="112" cm="1">
         <f t="array" ref="E8">ROUND(D8*(1+inflation_rate),0)</f>
         <v>92882</v>
       </c>
-      <c r="F8" s="52" cm="1">
+      <c r="F8" s="112" cm="1">
         <f t="array" ref="F8">ROUND(E8*(1+inflation_rate),0)</f>
         <v>95668</v>
       </c>
@@ -9004,22 +9046,22 @@
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="56">
+      <c r="B9" s="51">
         <v>74000</v>
       </c>
-      <c r="C9" s="52" cm="1">
+      <c r="C9" s="47" cm="1">
         <f t="array" ref="C9">ROUND(B9*(1+inflation_rate),0)</f>
         <v>76220</v>
       </c>
-      <c r="D9" s="52" cm="1">
+      <c r="D9" s="47" cm="1">
         <f t="array" ref="D9">ROUND(C9*(1+inflation_rate),0)</f>
         <v>78507</v>
       </c>
-      <c r="E9" s="52" cm="1">
+      <c r="E9" s="47" cm="1">
         <f t="array" ref="E9">ROUND(D9*(1+inflation_rate),0)</f>
         <v>80862</v>
       </c>
-      <c r="F9" s="52" cm="1">
+      <c r="F9" s="47" cm="1">
         <f t="array" ref="F9">ROUND(E9*(1+inflation_rate),0)</f>
         <v>83288</v>
       </c>
@@ -9039,22 +9081,22 @@
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="51">
         <v>200000</v>
       </c>
-      <c r="C10" s="52" cm="1">
+      <c r="C10" s="47" cm="1">
         <f t="array" ref="C10">ROUND(B10*(1+inflation_rate),0)</f>
         <v>206000</v>
       </c>
-      <c r="D10" s="52" cm="1">
+      <c r="D10" s="47" cm="1">
         <f t="array" ref="D10">ROUND(C10*(1+inflation_rate),0)</f>
         <v>212180</v>
       </c>
-      <c r="E10" s="52" cm="1">
+      <c r="E10" s="47" cm="1">
         <f t="array" ref="E10">ROUND(D10*(1+inflation_rate),0)</f>
         <v>218545</v>
       </c>
-      <c r="F10" s="52" cm="1">
+      <c r="F10" s="47" cm="1">
         <f t="array" ref="F10">ROUND(E10*(1+inflation_rate),0)</f>
         <v>225101</v>
       </c>
@@ -9074,22 +9116,22 @@
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="57">
+      <c r="B11" s="52">
         <v>96000</v>
       </c>
-      <c r="C11" s="55" cm="1">
+      <c r="C11" s="50" cm="1">
         <f t="array" ref="C11">ROUND(B11*(1+inflation_rate),0)</f>
         <v>98880</v>
       </c>
-      <c r="D11" s="55" cm="1">
+      <c r="D11" s="50" cm="1">
         <f t="array" ref="D11">ROUND(C11*(1+inflation_rate),0)</f>
         <v>101846</v>
       </c>
-      <c r="E11" s="55" cm="1">
+      <c r="E11" s="50" cm="1">
         <f t="array" ref="E11">ROUND(D11*(1+inflation_rate),0)</f>
         <v>104901</v>
       </c>
-      <c r="F11" s="55" cm="1">
+      <c r="F11" s="50" cm="1">
         <f t="array" ref="F11">ROUND(E11*(1+inflation_rate),0)</f>
         <v>108048</v>
       </c>
@@ -9106,26 +9148,26 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="49">
         <f>SUM(B5:B11)</f>
         <v>1300000</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="49">
         <f t="shared" ref="C12:F12" si="1">SUM(C5:C11)</f>
         <v>1339000</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="49">
         <f t="shared" si="1"/>
         <v>1379171</v>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="49">
         <f t="shared" si="1"/>
         <v>1420545</v>
       </c>
-      <c r="F12" s="54">
+      <c r="F12" s="49">
         <f t="shared" si="1"/>
         <v>1463160</v>
       </c>
@@ -9161,14 +9203,14 @@
       <c r="Q13" s="27"/>
     </row>
     <row r="14" spans="1:17" ht="15.75">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="110"/>
       <c r="G14" s="27"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27"/>
@@ -9182,25 +9224,25 @@
       <c r="Q14" s="27"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="89">
         <v>2026</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="89">
         <f>B15+1</f>
         <v>2027</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="89">
         <f>C15+1</f>
         <v>2028</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="89">
         <f>D15+1</f>
         <v>2029</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="101">
         <f>E15+1</f>
         <v>2030</v>
       </c>
@@ -9217,23 +9259,23 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="59" cm="1">
+      <c r="B16" s="115" cm="1">
         <f t="array" ref="B16:F16">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="115">
         <v>165000</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="115">
         <v>175000</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="115">
         <v>175000</v>
       </c>
-      <c r="F16" s="59">
+      <c r="F16" s="115">
         <v>175000</v>
       </c>
       <c r="G16" s="27"/>
@@ -9268,26 +9310,26 @@
       <c r="Q17" s="27"/>
     </row>
     <row r="18" spans="1:17" ht="15.75">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="62">
+      <c r="B18" s="54">
         <f>SUM(B16+B12)</f>
         <v>1465000</v>
       </c>
-      <c r="C18" s="62">
+      <c r="C18" s="54">
         <f t="shared" ref="C18:F18" si="2">SUM(C16+C12)</f>
         <v>1504000</v>
       </c>
-      <c r="D18" s="62">
+      <c r="D18" s="54">
         <f t="shared" si="2"/>
         <v>1554171</v>
       </c>
-      <c r="E18" s="62">
+      <c r="E18" s="54">
         <f t="shared" si="2"/>
         <v>1595545</v>
       </c>
-      <c r="F18" s="62">
+      <c r="F18" s="54">
         <f t="shared" si="2"/>
         <v>1638160</v>
       </c>
@@ -9610,16 +9652,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.75">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
@@ -9630,14 +9672,14 @@
       <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18.75">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
@@ -9648,7 +9690,7 @@
       <c r="P2" s="27"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="22" cm="1">
@@ -9683,23 +9725,23 @@
       <c r="P3" s="27"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="84" cm="1">
+      <c r="B4" s="76" cm="1">
         <f t="array" ref="B4:F4">total_operating_revenue_row</f>
         <v>1439550</v>
       </c>
-      <c r="C4" s="84">
+      <c r="C4" s="76">
         <v>1564250.5</v>
       </c>
-      <c r="D4" s="84">
+      <c r="D4" s="76">
         <v>1674016</v>
       </c>
-      <c r="E4" s="84">
+      <c r="E4" s="76">
         <v>1690976.5</v>
       </c>
-      <c r="F4" s="85">
+      <c r="F4" s="77">
         <v>1766930</v>
       </c>
       <c r="G4" s="27"/>
@@ -9714,23 +9756,23 @@
       <c r="P4" s="27"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="84" cm="1">
+      <c r="B5" s="76" cm="1">
         <f t="array" ref="B5:F5">total_cost_of_service_row</f>
         <v>1465000</v>
       </c>
-      <c r="C5" s="84">
+      <c r="C5" s="76">
         <v>1504000</v>
       </c>
-      <c r="D5" s="84">
+      <c r="D5" s="76">
         <v>1554171</v>
       </c>
-      <c r="E5" s="84">
+      <c r="E5" s="76">
         <v>1595545</v>
       </c>
-      <c r="F5" s="85">
+      <c r="F5" s="77">
         <v>1638160</v>
       </c>
       <c r="G5" s="27"/>
@@ -9745,26 +9787,26 @@
       <c r="P5" s="27"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="84">
+      <c r="B6" s="76">
         <f>B4-B5</f>
         <v>-25450</v>
       </c>
-      <c r="C6" s="84">
+      <c r="C6" s="76">
         <f t="shared" ref="C6:F6" si="1">C4-C5</f>
         <v>60250.5</v>
       </c>
-      <c r="D6" s="84">
+      <c r="D6" s="76">
         <f t="shared" si="1"/>
         <v>119845</v>
       </c>
-      <c r="E6" s="84">
+      <c r="E6" s="76">
         <f t="shared" si="1"/>
         <v>95431.5</v>
       </c>
-      <c r="F6" s="85">
+      <c r="F6" s="77">
         <f t="shared" si="1"/>
         <v>128770</v>
       </c>
@@ -9780,26 +9822,26 @@
       <c r="P6" s="27"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="93">
+      <c r="B7" s="85">
         <f>B6</f>
         <v>-25450</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="85">
         <f>B7+C6</f>
         <v>34800.5</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="85">
         <f t="shared" ref="D7:F7" si="2">C7+D6</f>
         <v>154645.5</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="85">
         <f t="shared" si="2"/>
         <v>250077</v>
       </c>
-      <c r="F7" s="94">
+      <c r="F7" s="86">
         <f t="shared" si="2"/>
         <v>378847</v>
       </c>
@@ -9833,7 +9875,7 @@
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="22" cm="1">
@@ -9871,20 +9913,20 @@
       <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="84" cm="1">
+      <c r="B10" s="76" cm="1">
         <f t="array" ref="B10:F10">total_operating_revenue_row - total_operating_expenses</f>
         <v>139550</v>
       </c>
-      <c r="C10" s="84">
+      <c r="C10" s="76">
         <v>225250.5</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="76">
         <v>294845</v>
       </c>
-      <c r="E10" s="84">
+      <c r="E10" s="76">
         <v>270431.5</v>
       </c>
-      <c r="F10" s="85">
+      <c r="F10" s="77">
         <v>303770</v>
       </c>
       <c r="G10" s="27"/>
@@ -9902,20 +9944,20 @@
       <c r="A11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="84" cm="1">
+      <c r="B11" s="76" cm="1">
         <f t="array" ref="B11:F11">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C11" s="84">
+      <c r="C11" s="76">
         <v>165000</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="76">
         <v>175000</v>
       </c>
-      <c r="E11" s="84">
+      <c r="E11" s="76">
         <v>175000</v>
       </c>
-      <c r="F11" s="85">
+      <c r="F11" s="77">
         <v>175000</v>
       </c>
       <c r="G11" s="27"/>
@@ -9930,26 +9972,26 @@
       <c r="P11" s="27"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="87">
+      <c r="B12" s="79">
         <f>B10/B11</f>
         <v>0.84575757575757571</v>
       </c>
-      <c r="C12" s="87">
+      <c r="C12" s="79">
         <f t="shared" ref="C12:F12" si="4">C10/C11</f>
         <v>1.3651545454545455</v>
       </c>
-      <c r="D12" s="87">
+      <c r="D12" s="79">
         <f t="shared" si="4"/>
         <v>1.6848285714285713</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="79">
         <f t="shared" si="4"/>
         <v>1.5453228571428572</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="80">
         <f t="shared" si="4"/>
         <v>1.7358285714285715</v>
       </c>
@@ -9965,26 +10007,26 @@
       <c r="P12" s="27"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="90" t="str" cm="1">
+      <c r="B13" s="82" t="str" cm="1">
         <f t="array" ref="B13">IF(B12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Insufficient</v>
       </c>
-      <c r="C13" s="90" t="str" cm="1">
+      <c r="C13" s="82" t="str" cm="1">
         <f t="array" ref="C13">IF(C12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="D13" s="90" t="str" cm="1">
+      <c r="D13" s="82" t="str" cm="1">
         <f t="array" ref="D13">IF(D12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="E13" s="90" t="str" cm="1">
+      <c r="E13" s="82" t="str" cm="1">
         <f t="array" ref="E13">IF(E12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="F13" s="91" t="str" cm="1">
+      <c r="F13" s="83" t="str" cm="1">
         <f t="array" ref="F13">IF(F12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E9AE2ED-6DB5-4F66-86BC-5EF679984FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C27E69-0928-416A-8C55-3B10933BF7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <definedName name="base_chargeRS1">Inputs!$C$14:$G$14</definedName>
     <definedName name="base_chargeRS2">Inputs!$C$24:$G$24</definedName>
     <definedName name="currentyear">Inputs!$C$11:$C$11</definedName>
-    <definedName name="debt_service_values">Inputs!$AQ$13:$AU$13</definedName>
-    <definedName name="expenses_value">Inputs!$AK$13:$AK$19</definedName>
+    <definedName name="debt_service_values">Inputs!$X$12:$AB$12</definedName>
+    <definedName name="expenses_value">Inputs!$R$12:$R$18</definedName>
     <definedName name="inflation_rate">Inputs!$E$7:$E$7</definedName>
     <definedName name="num_accounts">Inputs!$B$8:$B$8</definedName>
     <definedName name="num_accountsRS1">Inputs!$A$16:$A$16</definedName>
@@ -151,9 +151,6 @@
     <t>Monthly Consumption Over Included Amount</t>
   </si>
   <si>
-    <t>Rate Structure 1:</t>
-  </si>
-  <si>
     <t>Annual Operating Expenses</t>
   </si>
   <si>
@@ -163,10 +160,16 @@
     <t>Year</t>
   </si>
   <si>
+    <t>Rate Structure 1:</t>
+  </si>
+  <si>
+    <t>Salaries</t>
+  </si>
+  <si>
     <t>Block 1:</t>
   </si>
   <si>
-    <t>Salaries</t>
+    <t>Chemicals/Treatments</t>
   </si>
   <si>
     <t>Residential water, inside</t>
@@ -178,7 +181,7 @@
     <t>Block 2:</t>
   </si>
   <si>
-    <t>Chemicals/Treatments</t>
+    <t>Energy and Utilities</t>
   </si>
   <si>
     <t>Consumption included with base charge (gallons/month):</t>
@@ -187,28 +190,25 @@
     <t>Block 3:</t>
   </si>
   <si>
-    <t>Energy and Utilities</t>
+    <t>Maintenance &amp; Repairs</t>
   </si>
   <si>
-    <t>Maintenance &amp; Repairs</t>
+    <t>Administrative</t>
   </si>
   <si>
     <t>Rate Structure 2:</t>
   </si>
   <si>
-    <t>Administrative</t>
+    <t>Cash Reserves</t>
   </si>
   <si>
     <t>Block cutoffs, starts at 2000</t>
   </si>
   <si>
-    <t>Cash Reserves</t>
+    <t>Other</t>
   </si>
   <si>
     <t>Block rate 1 ($/1000 gal)</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>Block rate 2 ($/1000 gal)</t>
@@ -628,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -687,9 +687,6 @@
     <xf numFmtId="6" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -718,8 +715,6 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -833,6 +828,16 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2277,7 +2282,12 @@
     <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="15" width="8.5703125" customWidth="1"/>
     <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="20" bestFit="1" customWidth="1"/>
@@ -2288,10 +2298,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="21">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
+      <c r="B1" s="114"/>
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
       <c r="E1" s="27"/>
@@ -2387,10 +2397,10 @@
       <c r="CQ1" s="27"/>
     </row>
     <row r="2" spans="1:95">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119"/>
+      <c r="B2" s="116"/>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -2486,8 +2496,8 @@
       <c r="CQ2" s="27"/>
     </row>
     <row r="3" spans="1:95">
-      <c r="A3" s="120"/>
-      <c r="B3" s="83"/>
+      <c r="A3" s="117"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
@@ -2583,10 +2593,10 @@
       <c r="CQ3" s="27"/>
     </row>
     <row r="4" spans="1:95">
-      <c r="A4" s="121" t="s">
+      <c r="A4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="122"/>
+      <c r="B4" s="119"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
@@ -2892,7 +2902,7 @@
       <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="71">
         <v>0.03</v>
       </c>
       <c r="F7" s="27"/>
@@ -3095,12 +3105,12 @@
       <c r="A9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="57">
+      <c r="B9" s="56">
         <f>SUM(K13:K15,K18:K20) * 12</f>
         <v>3804000</v>
       </c>
       <c r="C9" s="27"/>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="72" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="2">
@@ -3320,28 +3330,52 @@
         <v>2030</v>
       </c>
       <c r="H11" s="27"/>
-      <c r="I11" s="93" t="s">
+      <c r="I11" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="95"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="92"/>
       <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="65"/>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="27"/>
+      <c r="Q11" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="R11" s="22">
+        <v>2026</v>
+      </c>
+      <c r="S11" s="27"/>
+      <c r="T11" s="123" t="s">
+        <v>16</v>
+      </c>
+      <c r="U11" s="18"/>
+      <c r="V11" s="124" t="s">
+        <v>16</v>
+      </c>
+      <c r="W11" s="125" t="s">
+        <v>17</v>
+      </c>
+      <c r="X11" s="18">
+        <v>2026</v>
+      </c>
+      <c r="Y11" s="18">
+        <f>X11+1</f>
+        <v>2027</v>
+      </c>
+      <c r="Z11" s="18">
+        <f>Y11+1</f>
+        <v>2028</v>
+      </c>
+      <c r="AA11" s="18">
+        <f>Z11+1</f>
+        <v>2029</v>
+      </c>
+      <c r="AB11" s="102">
+        <f>AA11+1</f>
+        <v>2030</v>
+      </c>
       <c r="AC11" s="27"/>
       <c r="AD11" s="27"/>
       <c r="AE11" s="27"/>
@@ -3410,7 +3444,7 @@
       <c r="CP11" s="27"/>
       <c r="CQ11" s="27"/>
     </row>
-    <row r="12" spans="1:95" ht="15.75">
+    <row r="12" spans="1:95">
       <c r="A12" s="28"/>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
@@ -3420,44 +3454,65 @@
       <c r="G12" s="31"/>
       <c r="H12" s="27"/>
       <c r="I12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="89" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="69" cm="1">
+      <c r="K12" s="66" cm="1">
         <f t="array" ref="K12">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="L12" s="69">
+      <c r="L12" s="66">
         <f>K12+1</f>
         <v>2027</v>
       </c>
-      <c r="M12" s="69">
+      <c r="M12" s="66">
         <f t="shared" ref="M12:O12" si="1">L12+1</f>
         <v>2028</v>
       </c>
-      <c r="N12" s="69">
+      <c r="N12" s="66">
         <f t="shared" si="1"/>
         <v>2029</v>
       </c>
-      <c r="O12" s="69">
+      <c r="O12" s="66">
         <f t="shared" si="1"/>
         <v>2030</v>
       </c>
       <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="27"/>
-      <c r="AA12" s="27"/>
-      <c r="AB12" s="27"/>
+      <c r="Q12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R12" s="37">
+        <v>650000</v>
+      </c>
+      <c r="S12" s="27"/>
+      <c r="T12" s="126" t="s">
+        <v>17</v>
+      </c>
+      <c r="U12" s="127"/>
+      <c r="V12" s="127"/>
+      <c r="W12" s="127"/>
+      <c r="X12" s="46">
+        <f>U13</f>
+        <v>165000</v>
+      </c>
+      <c r="Y12" s="46">
+        <f>U14</f>
+        <v>165000</v>
+      </c>
+      <c r="Z12" s="46">
+        <f>U15</f>
+        <v>175000</v>
+      </c>
+      <c r="AA12" s="46">
+        <f>U16</f>
+        <v>175000</v>
+      </c>
+      <c r="AB12" s="46">
+        <f>U17</f>
+        <v>175000</v>
+      </c>
       <c r="AC12" s="27"/>
       <c r="AD12" s="27"/>
       <c r="AE12" s="27"/>
@@ -3465,42 +3520,18 @@
       <c r="AG12" s="27"/>
       <c r="AH12" s="27"/>
       <c r="AI12" s="27"/>
-      <c r="AJ12" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK12" s="22">
-        <v>2026</v>
-      </c>
+      <c r="AJ12" s="27"/>
+      <c r="AK12" s="27"/>
       <c r="AL12" s="27"/>
-      <c r="AM12" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="AP12" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ12" s="1">
-        <v>2026</v>
-      </c>
-      <c r="AR12" s="1">
-        <f>AQ12+1</f>
-        <v>2027</v>
-      </c>
-      <c r="AS12" s="1">
-        <f>AR12+1</f>
-        <v>2028</v>
-      </c>
-      <c r="AT12" s="1">
-        <f>AS12+1</f>
-        <v>2029</v>
-      </c>
-      <c r="AU12" s="1">
-        <f>AT12+1</f>
-        <v>2030</v>
-      </c>
+      <c r="AM12" s="27"/>
+      <c r="AN12" s="27"/>
+      <c r="AO12" s="27"/>
+      <c r="AP12" s="27"/>
+      <c r="AQ12" s="27"/>
+      <c r="AR12" s="27"/>
+      <c r="AS12" s="27"/>
+      <c r="AT12" s="27"/>
+      <c r="AU12" s="27"/>
       <c r="AV12" s="27"/>
       <c r="AW12" s="27"/>
       <c r="AX12" s="27"/>
@@ -3552,7 +3583,7 @@
     </row>
     <row r="13" spans="1:95">
       <c r="A13" s="12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="15"/>
@@ -3561,12 +3592,12 @@
       <c r="F13" s="15"/>
       <c r="G13" s="16"/>
       <c r="H13" s="27"/>
-      <c r="I13" s="96" t="str" cm="1">
+      <c r="I13" s="93" t="str" cm="1">
         <f t="array" ref="I13">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="J13" s="64" t="s">
-        <v>19</v>
+      <c r="J13" s="63" t="s">
+        <v>20</v>
       </c>
       <c r="K13" s="35">
         <v>200000</v>
@@ -3588,15 +3619,23 @@
         <v>208121</v>
       </c>
       <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="29"/>
+      <c r="Q13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" s="37">
+        <v>110000</v>
+      </c>
+      <c r="S13" s="27"/>
+      <c r="T13" s="1">
+        <v>2026</v>
+      </c>
+      <c r="U13" s="128">
+        <v>165000</v>
+      </c>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
       <c r="Z13" s="27"/>
       <c r="AA13" s="27"/>
       <c r="AB13" s="27"/>
@@ -3607,39 +3646,18 @@
       <c r="AG13" s="27"/>
       <c r="AH13" s="27"/>
       <c r="AI13" s="27"/>
-      <c r="AJ13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AK13" s="37">
-        <v>650000</v>
-      </c>
+      <c r="AJ13" s="27"/>
+      <c r="AK13" s="27"/>
       <c r="AL13" s="27"/>
-      <c r="AM13" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN13" s="1"/>
-      <c r="AO13" s="1"/>
-      <c r="AP13" s="1"/>
-      <c r="AQ13" s="47">
-        <f>AN14</f>
-        <v>165000</v>
-      </c>
-      <c r="AR13" s="47">
-        <f>AN15</f>
-        <v>165000</v>
-      </c>
-      <c r="AS13" s="47">
-        <f>AN16</f>
-        <v>175000</v>
-      </c>
-      <c r="AT13" s="47">
-        <f>AN17</f>
-        <v>175000</v>
-      </c>
-      <c r="AU13" s="47">
-        <f>AN18</f>
-        <v>175000</v>
-      </c>
+      <c r="AM13" s="27"/>
+      <c r="AN13" s="27"/>
+      <c r="AO13" s="27"/>
+      <c r="AP13" s="27"/>
+      <c r="AQ13" s="27"/>
+      <c r="AR13" s="27"/>
+      <c r="AS13" s="27"/>
+      <c r="AT13" s="27"/>
+      <c r="AU13" s="27"/>
       <c r="AV13" s="27"/>
       <c r="AW13" s="27"/>
       <c r="AX13" s="27"/>
@@ -3691,15 +3709,15 @@
     </row>
     <row r="14" spans="1:95">
       <c r="A14" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="39">
         <v>20</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="41">
         <v>25</v>
       </c>
       <c r="E14" s="39">
@@ -3713,8 +3731,8 @@
       </c>
       <c r="H14" s="27"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="64" t="s">
-        <v>23</v>
+      <c r="J14" s="63" t="s">
+        <v>24</v>
       </c>
       <c r="K14" s="35">
         <v>25000</v>
@@ -3736,15 +3754,24 @@
         <v>26016</v>
       </c>
       <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
+      <c r="Q14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R14" s="38">
+        <v>85000</v>
+      </c>
+      <c r="S14" s="27"/>
+      <c r="T14" s="1">
+        <f>T13+1</f>
+        <v>2027</v>
+      </c>
+      <c r="U14" s="40">
+        <v>165000</v>
+      </c>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
       <c r="Z14" s="27"/>
       <c r="AA14" s="27"/>
       <c r="AB14" s="27"/>
@@ -3755,19 +3782,11 @@
       <c r="AG14" s="27"/>
       <c r="AH14" s="27"/>
       <c r="AI14" s="27"/>
-      <c r="AJ14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK14" s="37">
-        <v>110000</v>
-      </c>
+      <c r="AJ14" s="27"/>
+      <c r="AK14" s="27"/>
       <c r="AL14" s="27"/>
-      <c r="AM14" s="1">
-        <v>2026</v>
-      </c>
-      <c r="AN14" s="41">
-        <v>165000</v>
-      </c>
+      <c r="AM14" s="27"/>
+      <c r="AN14" s="27"/>
       <c r="AO14" s="27"/>
       <c r="AP14" s="27"/>
       <c r="AQ14" s="27"/>
@@ -3829,12 +3848,12 @@
         <v>8</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="35">
         <v>2000</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="42">
         <v>2000</v>
       </c>
       <c r="E15" s="35">
@@ -3847,9 +3866,9 @@
         <v>2000</v>
       </c>
       <c r="H15" s="27"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="64" t="s">
-        <v>26</v>
+      <c r="I15" s="78"/>
+      <c r="J15" s="63" t="s">
+        <v>27</v>
       </c>
       <c r="K15" s="35">
         <v>0</v>
@@ -3871,15 +3890,24 @@
         <v>0</v>
       </c>
       <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="29"/>
+      <c r="Q15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="37">
+        <v>85000</v>
+      </c>
+      <c r="S15" s="27"/>
+      <c r="T15" s="1">
+        <f>T14+1</f>
+        <v>2028</v>
+      </c>
+      <c r="U15" s="40">
+        <v>175000</v>
+      </c>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
       <c r="Z15" s="27"/>
       <c r="AA15" s="27"/>
       <c r="AB15" s="27"/>
@@ -3890,20 +3918,11 @@
       <c r="AG15" s="27"/>
       <c r="AH15" s="27"/>
       <c r="AI15" s="27"/>
-      <c r="AJ15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK15" s="38">
-        <v>85000</v>
-      </c>
+      <c r="AJ15" s="27"/>
+      <c r="AK15" s="27"/>
       <c r="AL15" s="27"/>
-      <c r="AM15" s="1">
-        <f>AM14+1</f>
-        <v>2027</v>
-      </c>
-      <c r="AN15" s="41">
-        <v>165000</v>
-      </c>
+      <c r="AM15" s="27"/>
+      <c r="AN15" s="27"/>
       <c r="AO15" s="27"/>
       <c r="AP15" s="27"/>
       <c r="AQ15" s="27"/>
@@ -3961,7 +3980,7 @@
       <c r="CQ15" s="27"/>
     </row>
     <row r="16" spans="1:95">
-      <c r="A16" s="44">
+      <c r="A16" s="43">
         <v>2520</v>
       </c>
       <c r="B16" s="33"/>
@@ -3979,15 +3998,24 @@
       <c r="N16" s="29"/>
       <c r="O16" s="29"/>
       <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
+      <c r="Q16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" s="37">
+        <v>74000</v>
+      </c>
+      <c r="S16" s="27"/>
+      <c r="T16" s="1">
+        <f t="shared" ref="T16:T17" si="2">T15+1</f>
+        <v>2029</v>
+      </c>
+      <c r="U16" s="40">
+        <v>175000</v>
+      </c>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
       <c r="Z16" s="27"/>
       <c r="AA16" s="27"/>
       <c r="AB16" s="27"/>
@@ -3998,20 +4026,11 @@
       <c r="AG16" s="27"/>
       <c r="AH16" s="27"/>
       <c r="AI16" s="27"/>
-      <c r="AJ16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK16" s="37">
-        <v>85000</v>
-      </c>
+      <c r="AJ16" s="27"/>
+      <c r="AK16" s="27"/>
       <c r="AL16" s="27"/>
-      <c r="AM16" s="1">
-        <f>AM15+1</f>
-        <v>2028</v>
-      </c>
-      <c r="AN16" s="41">
-        <v>175000</v>
-      </c>
+      <c r="AM16" s="27"/>
+      <c r="AN16" s="27"/>
       <c r="AO16" s="27"/>
       <c r="AP16" s="27"/>
       <c r="AQ16" s="27"/>
@@ -4078,7 +4097,7 @@
       <c r="G17" s="17"/>
       <c r="H17" s="27"/>
       <c r="I17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>13</v>
@@ -4087,32 +4106,41 @@
         <f t="array" ref="K17">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="L17" s="69">
+      <c r="L17" s="66">
         <f>K17+1</f>
         <v>2027</v>
       </c>
-      <c r="M17" s="69">
-        <f t="shared" ref="M17:O17" si="2">L17+1</f>
+      <c r="M17" s="66">
+        <f t="shared" ref="M17:O17" si="3">L17+1</f>
         <v>2028</v>
       </c>
-      <c r="N17" s="69">
-        <f t="shared" si="2"/>
+      <c r="N17" s="66">
+        <f t="shared" si="3"/>
         <v>2029</v>
       </c>
-      <c r="O17" s="69">
+      <c r="O17" s="66">
+        <f t="shared" si="3"/>
+        <v>2030</v>
+      </c>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="37">
+        <v>200000</v>
+      </c>
+      <c r="S17" s="27"/>
+      <c r="T17" s="1">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="29"/>
+      <c r="U17" s="40">
+        <v>175000</v>
+      </c>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
       <c r="Z17" s="27"/>
       <c r="AA17" s="27"/>
       <c r="AB17" s="27"/>
@@ -4123,20 +4151,11 @@
       <c r="AG17" s="27"/>
       <c r="AH17" s="27"/>
       <c r="AI17" s="27"/>
-      <c r="AJ17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AK17" s="37">
-        <v>74000</v>
-      </c>
+      <c r="AJ17" s="27"/>
+      <c r="AK17" s="27"/>
       <c r="AL17" s="27"/>
-      <c r="AM17" s="1">
-        <f t="shared" ref="AM17:AM18" si="3">AM16+1</f>
-        <v>2029</v>
-      </c>
-      <c r="AN17" s="41">
-        <v>175000</v>
-      </c>
+      <c r="AM17" s="27"/>
+      <c r="AN17" s="27"/>
       <c r="AO17" s="27"/>
       <c r="AP17" s="27"/>
       <c r="AQ17" s="27"/>
@@ -4195,7 +4214,7 @@
     </row>
     <row r="18" spans="1:95">
       <c r="A18" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -4209,9 +4228,9 @@
         <v>Residential water, outside</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="91">
+        <v>20</v>
+      </c>
+      <c r="K18" s="88">
         <v>72000</v>
       </c>
       <c r="L18" s="22" cm="1">
@@ -4231,15 +4250,19 @@
         <v>74923</v>
       </c>
       <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="29"/>
+      <c r="Q18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" s="37">
+        <v>96000</v>
+      </c>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
       <c r="Z18" s="27"/>
       <c r="AA18" s="27"/>
       <c r="AB18" s="27"/>
@@ -4250,20 +4273,11 @@
       <c r="AG18" s="27"/>
       <c r="AH18" s="27"/>
       <c r="AI18" s="27"/>
-      <c r="AJ18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK18" s="37">
-        <v>200000</v>
-      </c>
+      <c r="AJ18" s="27"/>
+      <c r="AK18" s="27"/>
       <c r="AL18" s="27"/>
-      <c r="AM18" s="1">
-        <f t="shared" si="3"/>
-        <v>2030</v>
-      </c>
-      <c r="AN18" s="41">
-        <v>175000</v>
-      </c>
+      <c r="AM18" s="27"/>
+      <c r="AN18" s="27"/>
       <c r="AO18" s="27"/>
       <c r="AP18" s="27"/>
       <c r="AQ18" s="27"/>
@@ -4325,12 +4339,12 @@
         <v>3000</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" s="39">
         <v>1.75</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="41">
         <v>1.5</v>
       </c>
       <c r="E19" s="39">
@@ -4345,9 +4359,9 @@
       <c r="H19" s="27"/>
       <c r="I19" s="1"/>
       <c r="J19" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="91">
+        <v>24</v>
+      </c>
+      <c r="K19" s="88">
         <v>20000</v>
       </c>
       <c r="L19" s="22" cm="1">
@@ -4367,15 +4381,15 @@
         <v>20812</v>
       </c>
       <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="29"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
       <c r="Z19" s="27"/>
       <c r="AA19" s="27"/>
       <c r="AB19" s="27"/>
@@ -4386,12 +4400,8 @@
       <c r="AG19" s="27"/>
       <c r="AH19" s="27"/>
       <c r="AI19" s="27"/>
-      <c r="AJ19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK19" s="37">
-        <v>96000</v>
-      </c>
+      <c r="AJ19" s="27"/>
+      <c r="AK19" s="27"/>
       <c r="AL19" s="27"/>
       <c r="AM19" s="27"/>
       <c r="AN19" s="27"/>
@@ -4461,7 +4471,7 @@
       <c r="C20" s="39">
         <v>1.75</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="41">
         <v>2.25</v>
       </c>
       <c r="E20" s="39">
@@ -4476,9 +4486,9 @@
       <c r="H20" s="27"/>
       <c r="I20" s="1"/>
       <c r="J20" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="91">
+        <v>27</v>
+      </c>
+      <c r="K20" s="88">
         <v>0</v>
       </c>
       <c r="L20" s="22" cm="1">
@@ -4588,7 +4598,7 @@
       <c r="C21" s="39">
         <v>1.75</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="41">
         <v>3.5</v>
       </c>
       <c r="E21" s="39">
@@ -4602,9 +4612,9 @@
       </c>
       <c r="H21" s="27"/>
       <c r="I21" s="27"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
       <c r="M21" s="29"/>
       <c r="N21" s="29"/>
       <c r="O21" s="29"/>
@@ -4699,11 +4709,11 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="27"/>
-      <c r="J22" s="92" t="s">
+      <c r="J22" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
@@ -4790,7 +4800,7 @@
     </row>
     <row r="23" spans="1:95">
       <c r="A23" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="15"/>
@@ -4892,12 +4902,12 @@
         <v>38</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="39">
         <v>25</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="41">
         <v>29</v>
       </c>
       <c r="E24" s="39">
@@ -5003,7 +5013,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -5110,7 +5120,7 @@
       <c r="CQ25" s="27"/>
     </row>
     <row r="26" spans="1:95">
-      <c r="A26" s="44">
+      <c r="A26" s="43">
         <f>B8-A16</f>
         <v>550</v>
       </c>
@@ -5308,7 +5318,7 @@
     </row>
     <row r="28" spans="1:95">
       <c r="A28" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -5410,9 +5420,9 @@
         <v>5000</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="42">
+        <v>34</v>
+      </c>
+      <c r="C29" s="41">
         <v>3</v>
       </c>
       <c r="D29" s="39">
@@ -5523,7 +5533,7 @@
       <c r="B30" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="41">
         <v>3</v>
       </c>
       <c r="D30" s="39">
@@ -5632,7 +5642,7 @@
       <c r="B31" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="42"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
@@ -5790,16 +5800,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30.75" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
@@ -6436,6 +6446,7 @@
       <c r="U28" s="27"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -6457,13 +6468,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="18.75">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
       <c r="H1" s="27"/>
@@ -6531,14 +6542,14 @@
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
-      <c r="L2" s="97" t="s">
+      <c r="L2" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="99"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="96"/>
       <c r="R2" s="27"/>
       <c r="S2" s="27"/>
       <c r="T2" s="27"/>
@@ -6583,25 +6594,25 @@
       <c r="BG2" s="27"/>
     </row>
     <row r="3" spans="1:59" ht="18.75">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="99"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="96"/>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
       <c r="I3" s="27"/>
       <c r="J3" s="27"/>
       <c r="K3" s="27"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="125"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="122"/>
       <c r="R3" s="27"/>
       <c r="S3" s="27"/>
       <c r="T3" s="27"/>
@@ -6646,27 +6657,27 @@
       <c r="BG3" s="27"/>
     </row>
     <row r="4" spans="1:59">
-      <c r="A4" s="100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="101"/>
+      <c r="A4" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="98"/>
       <c r="G4" s="27"/>
       <c r="H4" s="27"/>
       <c r="I4" s="27"/>
       <c r="J4" s="27"/>
       <c r="K4" s="27"/>
-      <c r="L4" s="100" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="101"/>
+      <c r="L4" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="86"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="98"/>
       <c r="R4" s="27"/>
       <c r="S4" s="27"/>
       <c r="T4" s="27"/>
@@ -6674,20 +6685,20 @@
       <c r="V4" s="27"/>
       <c r="W4" s="27"/>
       <c r="X4" s="27"/>
-      <c r="Y4" s="90"/>
-      <c r="Z4" s="90">
+      <c r="Y4" s="87"/>
+      <c r="Z4" s="87">
         <f t="shared" ref="Z4:AC4" si="0">$B$22</f>
         <v>1439550</v>
       </c>
-      <c r="AA4" s="90">
+      <c r="AA4" s="87">
         <f t="shared" si="0"/>
         <v>1439550</v>
       </c>
-      <c r="AB4" s="90">
+      <c r="AB4" s="87">
         <f t="shared" si="0"/>
         <v>1439550</v>
       </c>
-      <c r="AC4" s="90">
+      <c r="AC4" s="87">
         <f t="shared" si="0"/>
         <v>1439550</v>
       </c>
@@ -6723,8 +6734,8 @@
       <c r="BG4" s="27"/>
     </row>
     <row r="5" spans="1:59">
-      <c r="A5" s="64" t="s">
-        <v>18</v>
+      <c r="A5" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="B5" s="22" cm="1">
         <f t="array" ref="B5">currentyear</f>
@@ -6751,8 +6762,8 @@
       <c r="I5" s="27"/>
       <c r="J5" s="27"/>
       <c r="K5" s="27"/>
-      <c r="L5" s="64" t="s">
-        <v>18</v>
+      <c r="L5" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="M5" s="22" cm="1">
         <f t="array" ref="M5">currentyear</f>
@@ -6821,23 +6832,23 @@
       <c r="A6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="61" cm="1">
+      <c r="B6" s="60" cm="1">
         <f t="array" ref="B6">num_accountsRS1</f>
         <v>2520</v>
       </c>
-      <c r="C6" s="62" cm="1">
+      <c r="C6" s="61" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+pop_growth_rate),0)</f>
         <v>2545</v>
       </c>
-      <c r="D6" s="62" cm="1">
+      <c r="D6" s="61" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+pop_growth_rate),0)</f>
         <v>2570</v>
       </c>
-      <c r="E6" s="62" cm="1">
+      <c r="E6" s="61" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+pop_growth_rate),0)</f>
         <v>2596</v>
       </c>
-      <c r="F6" s="62" cm="1">
+      <c r="F6" s="61" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
@@ -6849,23 +6860,23 @@
       <c r="L6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="61" cm="1">
+      <c r="M6" s="60" cm="1">
         <f t="array" ref="M6">num_accountsRS1</f>
         <v>2520</v>
       </c>
-      <c r="N6" s="62" cm="1">
+      <c r="N6" s="61" cm="1">
         <f t="array" ref="N6">ROUND(M6 * (1+pop_growth_rate),0)</f>
         <v>2545</v>
       </c>
-      <c r="O6" s="62" cm="1">
+      <c r="O6" s="61" cm="1">
         <f t="array" ref="O6">ROUND(N6 * (1+pop_growth_rate),0)</f>
         <v>2570</v>
       </c>
-      <c r="P6" s="62" cm="1">
+      <c r="P6" s="61" cm="1">
         <f t="array" ref="P6">ROUND(O6 * (1+pop_growth_rate),0)</f>
         <v>2596</v>
       </c>
-      <c r="Q6" s="62" cm="1">
+      <c r="Q6" s="61" cm="1">
         <f t="array" ref="Q6">ROUND(P6 * (1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
@@ -6916,20 +6927,20 @@
       <c r="A7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="58" cm="1">
+      <c r="B7" s="57" cm="1">
         <f t="array" ref="B7:F7">base_chargeRS1 * 12 * RS1_num_accounts</f>
         <v>604800</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="54">
         <v>763500</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="54">
         <v>771000</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="54">
         <v>778800</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="54">
         <v>786600</v>
       </c>
       <c r="G7" s="27"/>
@@ -6937,23 +6948,23 @@
       <c r="I7" s="27"/>
       <c r="J7" s="27"/>
       <c r="K7" s="27"/>
-      <c r="L7" s="60" t="s">
+      <c r="L7" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="106" cm="1">
+      <c r="M7" s="103" cm="1">
         <f t="array" ref="M7:Q7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
         <v>604800</v>
       </c>
-      <c r="N7" s="107">
+      <c r="N7" s="104">
         <v>610800</v>
       </c>
-      <c r="O7" s="107">
+      <c r="O7" s="104">
         <v>616800</v>
       </c>
-      <c r="P7" s="107">
+      <c r="P7" s="104">
         <v>623040</v>
       </c>
-      <c r="Q7" s="107">
+      <c r="Q7" s="104">
         <v>629280</v>
       </c>
       <c r="R7" s="27"/>
@@ -7003,23 +7014,23 @@
       <c r="A8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="63" cm="1">
+      <c r="B8" s="62" cm="1">
         <f t="array" ref="B8:B10">RS1_block_consumption2026 * RS1_vrates2026</f>
         <v>350000</v>
       </c>
-      <c r="C8" s="47" cm="1">
+      <c r="C8" s="46" cm="1">
         <f t="array" ref="C8:C10">RS1_block_consumption2027 * RS1_vrates2027</f>
         <v>303000</v>
       </c>
-      <c r="D8" s="47" cm="1">
+      <c r="D8" s="46" cm="1">
         <f t="array" ref="D8:D10">RS1_block_consumption2028 * RS1_vrates2028</f>
         <v>357035</v>
       </c>
-      <c r="E8" s="47" cm="1">
+      <c r="E8" s="46" cm="1">
         <f t="array" ref="E8:E10">RS1_block_consumption2029 * RS1_vrates2029</f>
         <v>360605</v>
       </c>
-      <c r="F8" s="47" cm="1">
+      <c r="F8" s="46" cm="1">
         <f t="array" ref="F8:F10">RS1_block_consumption2030 * RS1_vrates2030</f>
         <v>416242</v>
       </c>
@@ -7031,23 +7042,23 @@
       <c r="L8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="63" cm="1">
+      <c r="M8" s="62" cm="1">
         <f t="array" ref="M8:M10">RS1_block_consumption2026 * RS1_vrates2026</f>
         <v>350000</v>
       </c>
-      <c r="N8" s="63" cm="1">
+      <c r="N8" s="62" cm="1">
         <f t="array" ref="N8:N10">RS1_block_consumption2027 * RS1_vrates2026</f>
         <v>353500</v>
       </c>
-      <c r="O8" s="63" cm="1">
+      <c r="O8" s="62" cm="1">
         <f t="array" ref="O8:O10">RS1_block_consumption2028 * RS1_vrates2026</f>
         <v>357035</v>
       </c>
-      <c r="P8" s="63" cm="1">
+      <c r="P8" s="62" cm="1">
         <f t="array" ref="P8:P10">RS1_block_consumption2029 * RS1_vrates2026</f>
         <v>360605</v>
       </c>
-      <c r="Q8" s="63" cm="1">
+      <c r="Q8" s="62" cm="1">
         <f t="array" ref="Q8:Q10">RS1_block_consumption2030 * RS1_vrates2026</f>
         <v>364211.75</v>
       </c>
@@ -7098,19 +7109,19 @@
       <c r="A9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="63">
+      <c r="B9" s="62">
         <v>43750</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="46">
         <v>56812.5</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="46">
         <v>63757.5</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="46">
         <v>64395</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="46">
         <v>65040</v>
       </c>
       <c r="G9" s="27"/>
@@ -7121,19 +7132,19 @@
       <c r="L9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="M9" s="63">
+      <c r="M9" s="62">
         <v>43750</v>
       </c>
-      <c r="N9" s="63">
+      <c r="N9" s="62">
         <v>44187.5</v>
       </c>
-      <c r="O9" s="63">
+      <c r="O9" s="62">
         <v>44630.25</v>
       </c>
-      <c r="P9" s="63">
+      <c r="P9" s="62">
         <v>45076.5</v>
       </c>
-      <c r="Q9" s="63">
+      <c r="Q9" s="62">
         <v>45528</v>
       </c>
       <c r="R9" s="27"/>
@@ -7183,19 +7194,19 @@
       <c r="A10" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="62">
         <v>0</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="46">
         <v>0</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="46">
         <v>0</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="46">
         <v>0</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="46">
         <v>0</v>
       </c>
       <c r="G10" s="27"/>
@@ -7203,22 +7214,22 @@
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
-      <c r="L10" s="69" t="s">
+      <c r="L10" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="72">
+      <c r="M10" s="69">
         <v>0</v>
       </c>
-      <c r="N10" s="72">
+      <c r="N10" s="69">
         <v>0</v>
       </c>
-      <c r="O10" s="72">
+      <c r="O10" s="69">
         <v>0</v>
       </c>
-      <c r="P10" s="72">
+      <c r="P10" s="69">
         <v>0</v>
       </c>
-      <c r="Q10" s="72">
+      <c r="Q10" s="69">
         <v>0</v>
       </c>
       <c r="R10" s="27"/>
@@ -7265,26 +7276,26 @@
       <c r="BG10" s="27"/>
     </row>
     <row r="11" spans="1:59">
-      <c r="A11" s="102" t="s">
+      <c r="A11" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="103">
+      <c r="B11" s="100">
         <f>SUM(B7:B10)</f>
         <v>998550</v>
       </c>
-      <c r="C11" s="103">
+      <c r="C11" s="100">
         <f t="shared" ref="C11:F11" si="3">SUM(C7:C10)</f>
         <v>1123312.5</v>
       </c>
-      <c r="D11" s="103">
+      <c r="D11" s="100">
         <f t="shared" si="3"/>
         <v>1191792.5</v>
       </c>
-      <c r="E11" s="103">
+      <c r="E11" s="100">
         <f t="shared" si="3"/>
         <v>1203800</v>
       </c>
-      <c r="F11" s="103">
+      <c r="F11" s="100">
         <f t="shared" si="3"/>
         <v>1267882</v>
       </c>
@@ -7293,26 +7304,26 @@
       <c r="I11" s="27"/>
       <c r="J11" s="27"/>
       <c r="K11" s="27"/>
-      <c r="L11" s="48" t="s">
+      <c r="L11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="68">
+      <c r="M11" s="65">
         <f>SUM(M7:M10)</f>
         <v>998550</v>
       </c>
-      <c r="N11" s="68">
+      <c r="N11" s="65">
         <f t="shared" ref="N11" si="4">SUM(N7:N10)</f>
         <v>1008487.5</v>
       </c>
-      <c r="O11" s="68">
+      <c r="O11" s="65">
         <f t="shared" ref="O11" si="5">SUM(O7:O10)</f>
         <v>1018465.25</v>
       </c>
-      <c r="P11" s="68">
+      <c r="P11" s="65">
         <f t="shared" ref="P11" si="6">SUM(P7:P10)</f>
         <v>1028721.5</v>
       </c>
-      <c r="Q11" s="68">
+      <c r="Q11" s="65">
         <f t="shared" ref="Q11" si="7">SUM(Q7:Q10)</f>
         <v>1039019.75</v>
       </c>
@@ -7421,21 +7432,21 @@
       <c r="BG12" s="27"/>
     </row>
     <row r="13" spans="1:59">
-      <c r="A13" s="104" t="s">
-        <v>29</v>
+      <c r="A13" s="101" t="s">
+        <v>30</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
-      <c r="F13" s="105"/>
+      <c r="F13" s="102"/>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
       <c r="J13" s="27"/>
       <c r="K13" s="27"/>
-      <c r="L13" s="45" t="s">
-        <v>29</v>
+      <c r="L13" s="44" t="s">
+        <v>30</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -7487,7 +7498,7 @@
     </row>
     <row r="14" spans="1:59">
       <c r="A14" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="22" cm="1">
         <f t="array" ref="B14">currentyear</f>
@@ -7515,7 +7526,7 @@
       <c r="J14" s="27"/>
       <c r="K14" s="27"/>
       <c r="L14" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M14" s="22" cm="1">
         <f t="array" ref="M14">currentyear</f>
@@ -7581,26 +7592,26 @@
       <c r="BG14" s="27"/>
     </row>
     <row r="15" spans="1:59">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="61" cm="1">
+      <c r="B15" s="60" cm="1">
         <f t="array" ref="B15">num_accountsRS2</f>
         <v>550</v>
       </c>
-      <c r="C15" s="62" cm="1">
+      <c r="C15" s="61" cm="1">
         <f t="array" ref="C15">ROUND(B15*(1+pop_growth_rate),0)</f>
         <v>556</v>
       </c>
-      <c r="D15" s="62" cm="1">
+      <c r="D15" s="61" cm="1">
         <f t="array" ref="D15">ROUND(C15*(1+pop_growth_rate),0)</f>
         <v>562</v>
       </c>
-      <c r="E15" s="62" cm="1">
+      <c r="E15" s="61" cm="1">
         <f t="array" ref="E15">ROUND(D15*(1+pop_growth_rate),0)</f>
         <v>568</v>
       </c>
-      <c r="F15" s="62" cm="1">
+      <c r="F15" s="61" cm="1">
         <f t="array" ref="F15">ROUND(E15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
@@ -7609,26 +7620,26 @@
       <c r="I15" s="27"/>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
-      <c r="L15" s="60" t="s">
+      <c r="L15" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="61" cm="1">
+      <c r="M15" s="60" cm="1">
         <f t="array" ref="M15">num_accountsRS2</f>
         <v>550</v>
       </c>
-      <c r="N15" s="62" cm="1">
+      <c r="N15" s="61" cm="1">
         <f t="array" ref="N15">ROUND(M15*(1+pop_growth_rate),0)</f>
         <v>556</v>
       </c>
-      <c r="O15" s="62" cm="1">
+      <c r="O15" s="61" cm="1">
         <f t="array" ref="O15">ROUND(N15*(1+pop_growth_rate),0)</f>
         <v>562</v>
       </c>
-      <c r="P15" s="62" cm="1">
+      <c r="P15" s="61" cm="1">
         <f t="array" ref="P15">ROUND(O15*(1+pop_growth_rate),0)</f>
         <v>568</v>
       </c>
-      <c r="Q15" s="62" cm="1">
+      <c r="Q15" s="61" cm="1">
         <f t="array" ref="Q15">ROUND(P15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
@@ -7676,23 +7687,23 @@
       <c r="BG15" s="27"/>
     </row>
     <row r="16" spans="1:59">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="106" cm="1">
+      <c r="B16" s="103" cm="1">
         <f t="array" ref="B16:F16">base_chargeRS2 * 12 * RS2_num_accounts</f>
         <v>165000</v>
       </c>
-      <c r="C16" s="107">
+      <c r="C16" s="104">
         <v>193488</v>
       </c>
-      <c r="D16" s="107">
+      <c r="D16" s="104">
         <v>195576</v>
       </c>
-      <c r="E16" s="107">
+      <c r="E16" s="104">
         <v>197664</v>
       </c>
-      <c r="F16" s="107">
+      <c r="F16" s="104">
         <v>206640</v>
       </c>
       <c r="G16" s="27"/>
@@ -7703,20 +7714,20 @@
       <c r="L16" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="58" cm="1">
+      <c r="M16" s="57" cm="1">
         <f t="array" ref="M16:Q16">RS2_base_charge2026 * 12 * RS2_num_accounts</f>
         <v>165000</v>
       </c>
-      <c r="N16" s="55">
+      <c r="N16" s="54">
         <v>166800</v>
       </c>
-      <c r="O16" s="55">
+      <c r="O16" s="54">
         <v>168600</v>
       </c>
-      <c r="P16" s="55">
+      <c r="P16" s="54">
         <v>170400</v>
       </c>
-      <c r="Q16" s="55">
+      <c r="Q16" s="54">
         <v>172200</v>
       </c>
       <c r="R16" s="27"/>
@@ -7766,23 +7777,23 @@
       <c r="A17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="59" cm="1">
+      <c r="B17" s="58" cm="1">
         <f t="array" ref="B17:B19">RS2_block_consumption2026 * RS2_vrates2026</f>
         <v>216000</v>
       </c>
-      <c r="C17" s="56" cm="1">
+      <c r="C17" s="55" cm="1">
         <f t="array" ref="C17:C19">RS2_block_consumption2027 * RS2_vrates2027</f>
         <v>181800</v>
       </c>
-      <c r="D17" s="56" cm="1">
+      <c r="D17" s="55" cm="1">
         <f t="array" ref="D17:D19">RS2_block_consumption2028 * RS2_vrates2028</f>
         <v>220341</v>
       </c>
-      <c r="E17" s="56" cm="1">
+      <c r="E17" s="55" cm="1">
         <f t="array" ref="E17:E19">RS2_block_consumption2029 * RS2_vrates2029</f>
         <v>222543</v>
       </c>
-      <c r="F17" s="56" cm="1">
+      <c r="F17" s="55" cm="1">
         <f t="array" ref="F17:F19">RS2_block_consumption2030 * RS2_vrates2030</f>
         <v>224769</v>
       </c>
@@ -7794,23 +7805,23 @@
       <c r="L17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="M17" s="59" cm="1">
+      <c r="M17" s="58" cm="1">
         <f t="array" ref="M17:M19">RS2_block_consumption2026 * RS2_vrates2026</f>
         <v>216000</v>
       </c>
-      <c r="N17" s="59" cm="1">
+      <c r="N17" s="58" cm="1">
         <f t="array" ref="N17:N19">RS2_block_consumption2027 * RS2_vrates2026</f>
         <v>218160</v>
       </c>
-      <c r="O17" s="59" cm="1">
+      <c r="O17" s="58" cm="1">
         <f t="array" ref="O17:O19">RS2_block_consumption2028 * RS2_vrates2026</f>
         <v>220341</v>
       </c>
-      <c r="P17" s="59" cm="1">
+      <c r="P17" s="58" cm="1">
         <f t="array" ref="P17:P19">RS2_block_consumption2029 * RS2_vrates2026</f>
         <v>222543</v>
       </c>
-      <c r="Q17" s="59" cm="1">
+      <c r="Q17" s="58" cm="1">
         <f t="array" ref="Q17:Q19">RS2_block_consumption2030 * RS2_vrates2026</f>
         <v>224769</v>
       </c>
@@ -7861,19 +7872,19 @@
       <c r="A18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="59">
+      <c r="B18" s="58">
         <v>60000</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="55">
         <v>65650</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="55">
         <v>66306.5</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="55">
         <v>66969.5</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="55">
         <v>67639</v>
       </c>
       <c r="G18" s="27"/>
@@ -7884,19 +7895,19 @@
       <c r="L18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="M18" s="59">
+      <c r="M18" s="58">
         <v>60000</v>
       </c>
-      <c r="N18" s="59">
+      <c r="N18" s="58">
         <v>60600</v>
       </c>
-      <c r="O18" s="59">
+      <c r="O18" s="58">
         <v>61206</v>
       </c>
-      <c r="P18" s="59">
+      <c r="P18" s="58">
         <v>61818</v>
       </c>
-      <c r="Q18" s="59">
+      <c r="Q18" s="58">
         <v>62436</v>
       </c>
       <c r="R18" s="27"/>
@@ -7943,22 +7954,22 @@
       <c r="BG18" s="27"/>
     </row>
     <row r="19" spans="1:59">
-      <c r="A19" s="69" t="s">
+      <c r="A19" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="70">
+      <c r="B19" s="67">
         <v>0</v>
       </c>
-      <c r="C19" s="71">
+      <c r="C19" s="68">
         <v>0</v>
       </c>
-      <c r="D19" s="71">
+      <c r="D19" s="68">
         <v>0</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E19" s="68">
         <v>0</v>
       </c>
-      <c r="F19" s="71">
+      <c r="F19" s="68">
         <v>0</v>
       </c>
       <c r="G19" s="27"/>
@@ -7966,22 +7977,22 @@
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
-      <c r="L19" s="69" t="s">
+      <c r="L19" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="M19" s="70">
+      <c r="M19" s="67">
         <v>0</v>
       </c>
-      <c r="N19" s="70">
+      <c r="N19" s="67">
         <v>0</v>
       </c>
-      <c r="O19" s="70">
+      <c r="O19" s="67">
         <v>0</v>
       </c>
-      <c r="P19" s="70">
+      <c r="P19" s="67">
         <v>0</v>
       </c>
-      <c r="Q19" s="70">
+      <c r="Q19" s="67">
         <v>0</v>
       </c>
       <c r="R19" s="27"/>
@@ -8028,26 +8039,26 @@
       <c r="BG19" s="27"/>
     </row>
     <row r="20" spans="1:59">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="68">
+      <c r="B20" s="65">
         <f>SUM(B16:B19)</f>
         <v>441000</v>
       </c>
-      <c r="C20" s="68">
+      <c r="C20" s="65">
         <f t="shared" ref="C20:F20" si="10">SUM(C16:C19)</f>
         <v>440938</v>
       </c>
-      <c r="D20" s="68">
+      <c r="D20" s="65">
         <f t="shared" si="10"/>
         <v>482223.5</v>
       </c>
-      <c r="E20" s="68">
+      <c r="E20" s="65">
         <f t="shared" si="10"/>
         <v>487176.5</v>
       </c>
-      <c r="F20" s="68">
+      <c r="F20" s="65">
         <f t="shared" si="10"/>
         <v>499048</v>
       </c>
@@ -8056,26 +8067,26 @@
       <c r="I20" s="27"/>
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
-      <c r="L20" s="48" t="s">
+      <c r="L20" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="M20" s="68">
+      <c r="M20" s="65">
         <f>SUM(M16:M19)</f>
         <v>441000</v>
       </c>
-      <c r="N20" s="68">
+      <c r="N20" s="65">
         <f t="shared" ref="N20" si="11">SUM(N16:N19)</f>
         <v>445560</v>
       </c>
-      <c r="O20" s="68">
+      <c r="O20" s="65">
         <f t="shared" ref="O20" si="12">SUM(O16:O19)</f>
         <v>450147</v>
       </c>
-      <c r="P20" s="68">
+      <c r="P20" s="65">
         <f t="shared" ref="P20" si="13">SUM(P16:P19)</f>
         <v>454761</v>
       </c>
-      <c r="Q20" s="68">
+      <c r="Q20" s="65">
         <f t="shared" ref="Q20" si="14">SUM(Q16:Q19)</f>
         <v>459405</v>
       </c>
@@ -8184,26 +8195,26 @@
       <c r="BG21" s="27"/>
     </row>
     <row r="22" spans="1:59" ht="15.75">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="67">
+      <c r="B22" s="64">
         <f>SUM(B20+B11)</f>
         <v>1439550</v>
       </c>
-      <c r="C22" s="67">
+      <c r="C22" s="64">
         <f t="shared" ref="C22:F22" si="15">SUM(C20+C11)</f>
         <v>1564250.5</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D22" s="64">
         <f t="shared" si="15"/>
         <v>1674016</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E22" s="64">
         <f t="shared" si="15"/>
         <v>1690976.5</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F22" s="64">
         <f t="shared" si="15"/>
         <v>1766930</v>
       </c>
@@ -8212,26 +8223,26 @@
       <c r="I22" s="27"/>
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
-      <c r="L22" s="53" t="s">
+      <c r="L22" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="67">
+      <c r="M22" s="64">
         <f>SUM(M20+M11)</f>
         <v>1439550</v>
       </c>
-      <c r="N22" s="67">
+      <c r="N22" s="64">
         <f t="shared" ref="N22:Q22" si="16">SUM(N20+N11)</f>
         <v>1454047.5</v>
       </c>
-      <c r="O22" s="67">
+      <c r="O22" s="64">
         <f t="shared" si="16"/>
         <v>1468612.25</v>
       </c>
-      <c r="P22" s="67">
+      <c r="P22" s="64">
         <f t="shared" si="16"/>
         <v>1483482.5</v>
       </c>
-      <c r="Q22" s="67">
+      <c r="Q22" s="64">
         <f t="shared" si="16"/>
         <v>1498424.75</v>
       </c>
@@ -8785,6 +8796,7 @@
       <c r="L38" s="27"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="L2:Q2"/>
@@ -8806,15 +8818,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="27"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
@@ -8846,14 +8858,14 @@
       <c r="Q2" s="27"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="110"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="107"/>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
       <c r="I3" s="27"/>
@@ -8868,24 +8880,24 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="89">
+        <v>17</v>
+      </c>
+      <c r="B4" s="86">
         <v>2026</v>
       </c>
-      <c r="C4" s="89">
+      <c r="C4" s="86">
         <f>B4+1</f>
         <v>2027</v>
       </c>
-      <c r="D4" s="89">
+      <c r="D4" s="86">
         <f t="shared" ref="D4:F4" si="0">C4+1</f>
         <v>2028</v>
       </c>
-      <c r="E4" s="89">
+      <c r="E4" s="86">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="F4" s="101">
+      <c r="F4" s="98">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -8903,25 +8915,25 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="51" cm="1">
+        <v>19</v>
+      </c>
+      <c r="B5" s="50" cm="1">
         <f t="array" ref="B5:B11">expenses_value</f>
         <v>650000</v>
       </c>
-      <c r="C5" s="47" cm="1">
+      <c r="C5" s="46" cm="1">
         <f t="array" ref="C5">ROUND(B5*(1+inflation_rate),0)</f>
         <v>669500</v>
       </c>
-      <c r="D5" s="47" cm="1">
+      <c r="D5" s="46" cm="1">
         <f t="array" ref="D5">ROUND(C5*(1+inflation_rate),0)</f>
         <v>689585</v>
       </c>
-      <c r="E5" s="47" cm="1">
+      <c r="E5" s="46" cm="1">
         <f t="array" ref="E5">ROUND(D5*(1+inflation_rate),0)</f>
         <v>710273</v>
       </c>
-      <c r="F5" s="47" cm="1">
+      <c r="F5" s="46" cm="1">
         <f t="array" ref="F5">ROUND(E5*(1+inflation_rate),0)</f>
         <v>731581</v>
       </c>
@@ -8939,24 +8951,24 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="51">
+        <v>21</v>
+      </c>
+      <c r="B6" s="50">
         <v>110000</v>
       </c>
-      <c r="C6" s="47" cm="1">
+      <c r="C6" s="46" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+inflation_rate),0)</f>
         <v>113300</v>
       </c>
-      <c r="D6" s="47" cm="1">
+      <c r="D6" s="46" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+inflation_rate),0)</f>
         <v>116699</v>
       </c>
-      <c r="E6" s="47" cm="1">
+      <c r="E6" s="46" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+inflation_rate),0)</f>
         <v>120200</v>
       </c>
-      <c r="F6" s="47" cm="1">
+      <c r="F6" s="46" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+inflation_rate),0)</f>
         <v>123806</v>
       </c>
@@ -8973,25 +8985,25 @@
       <c r="Q6" s="27"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="51">
+      <c r="A7" s="78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="50">
         <v>85000</v>
       </c>
-      <c r="C7" s="47" cm="1">
+      <c r="C7" s="46" cm="1">
         <f t="array" ref="C7">ROUND(B7*(1+inflation_rate),0)</f>
         <v>87550</v>
       </c>
-      <c r="D7" s="47" cm="1">
+      <c r="D7" s="46" cm="1">
         <f t="array" ref="D7">ROUND(C7*(1+inflation_rate),0)</f>
         <v>90177</v>
       </c>
-      <c r="E7" s="47" cm="1">
+      <c r="E7" s="46" cm="1">
         <f t="array" ref="E7">ROUND(D7*(1+inflation_rate),0)</f>
         <v>92882</v>
       </c>
-      <c r="F7" s="47" cm="1">
+      <c r="F7" s="46" cm="1">
         <f t="array" ref="F7">ROUND(E7*(1+inflation_rate),0)</f>
         <v>95668</v>
       </c>
@@ -9011,22 +9023,22 @@
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="111">
+      <c r="B8" s="108">
         <v>85000</v>
       </c>
-      <c r="C8" s="112" cm="1">
+      <c r="C8" s="109" cm="1">
         <f t="array" ref="C8">ROUND(B8*(1+inflation_rate),0)</f>
         <v>87550</v>
       </c>
-      <c r="D8" s="112" cm="1">
+      <c r="D8" s="109" cm="1">
         <f t="array" ref="D8">ROUND(C8*(1+inflation_rate),0)</f>
         <v>90177</v>
       </c>
-      <c r="E8" s="112" cm="1">
+      <c r="E8" s="109" cm="1">
         <f t="array" ref="E8">ROUND(D8*(1+inflation_rate),0)</f>
         <v>92882</v>
       </c>
-      <c r="F8" s="112" cm="1">
+      <c r="F8" s="109" cm="1">
         <f t="array" ref="F8">ROUND(E8*(1+inflation_rate),0)</f>
         <v>95668</v>
       </c>
@@ -9044,24 +9056,24 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="51">
+        <v>29</v>
+      </c>
+      <c r="B9" s="50">
         <v>74000</v>
       </c>
-      <c r="C9" s="47" cm="1">
+      <c r="C9" s="46" cm="1">
         <f t="array" ref="C9">ROUND(B9*(1+inflation_rate),0)</f>
         <v>76220</v>
       </c>
-      <c r="D9" s="47" cm="1">
+      <c r="D9" s="46" cm="1">
         <f t="array" ref="D9">ROUND(C9*(1+inflation_rate),0)</f>
         <v>78507</v>
       </c>
-      <c r="E9" s="47" cm="1">
+      <c r="E9" s="46" cm="1">
         <f t="array" ref="E9">ROUND(D9*(1+inflation_rate),0)</f>
         <v>80862</v>
       </c>
-      <c r="F9" s="47" cm="1">
+      <c r="F9" s="46" cm="1">
         <f t="array" ref="F9">ROUND(E9*(1+inflation_rate),0)</f>
         <v>83288</v>
       </c>
@@ -9079,24 +9091,24 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="51">
+        <v>31</v>
+      </c>
+      <c r="B10" s="50">
         <v>200000</v>
       </c>
-      <c r="C10" s="47" cm="1">
+      <c r="C10" s="46" cm="1">
         <f t="array" ref="C10">ROUND(B10*(1+inflation_rate),0)</f>
         <v>206000</v>
       </c>
-      <c r="D10" s="47" cm="1">
+      <c r="D10" s="46" cm="1">
         <f t="array" ref="D10">ROUND(C10*(1+inflation_rate),0)</f>
         <v>212180</v>
       </c>
-      <c r="E10" s="47" cm="1">
+      <c r="E10" s="46" cm="1">
         <f t="array" ref="E10">ROUND(D10*(1+inflation_rate),0)</f>
         <v>218545</v>
       </c>
-      <c r="F10" s="47" cm="1">
+      <c r="F10" s="46" cm="1">
         <f t="array" ref="F10">ROUND(E10*(1+inflation_rate),0)</f>
         <v>225101</v>
       </c>
@@ -9114,24 +9126,24 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="52">
+        <v>33</v>
+      </c>
+      <c r="B11" s="51">
         <v>96000</v>
       </c>
-      <c r="C11" s="50" cm="1">
+      <c r="C11" s="49" cm="1">
         <f t="array" ref="C11">ROUND(B11*(1+inflation_rate),0)</f>
         <v>98880</v>
       </c>
-      <c r="D11" s="50" cm="1">
+      <c r="D11" s="49" cm="1">
         <f t="array" ref="D11">ROUND(C11*(1+inflation_rate),0)</f>
         <v>101846</v>
       </c>
-      <c r="E11" s="50" cm="1">
+      <c r="E11" s="49" cm="1">
         <f t="array" ref="E11">ROUND(D11*(1+inflation_rate),0)</f>
         <v>104901</v>
       </c>
-      <c r="F11" s="50" cm="1">
+      <c r="F11" s="49" cm="1">
         <f t="array" ref="F11">ROUND(E11*(1+inflation_rate),0)</f>
         <v>108048</v>
       </c>
@@ -9148,26 +9160,26 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="49">
+      <c r="B12" s="48">
         <f>SUM(B5:B11)</f>
         <v>1300000</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="48">
         <f t="shared" ref="C12:F12" si="1">SUM(C5:C11)</f>
         <v>1339000</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="48">
         <f t="shared" si="1"/>
         <v>1379171</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="48">
         <f t="shared" si="1"/>
         <v>1420545</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="48">
         <f t="shared" si="1"/>
         <v>1463160</v>
       </c>
@@ -9203,14 +9215,14 @@
       <c r="Q13" s="27"/>
     </row>
     <row r="14" spans="1:17" ht="15.75">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="110"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="107"/>
       <c r="G14" s="27"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27"/>
@@ -9224,25 +9236,25 @@
       <c r="Q14" s="27"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="113" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="89">
+      <c r="A15" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="86">
         <v>2026</v>
       </c>
-      <c r="C15" s="89">
+      <c r="C15" s="86">
         <f>B15+1</f>
         <v>2027</v>
       </c>
-      <c r="D15" s="89">
+      <c r="D15" s="86">
         <f>C15+1</f>
         <v>2028</v>
       </c>
-      <c r="E15" s="89">
+      <c r="E15" s="86">
         <f>D15+1</f>
         <v>2029</v>
       </c>
-      <c r="F15" s="101">
+      <c r="F15" s="98">
         <f>E15+1</f>
         <v>2030</v>
       </c>
@@ -9259,23 +9271,23 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="114" t="s">
+      <c r="A16" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="115" cm="1">
+      <c r="B16" s="112" cm="1">
         <f t="array" ref="B16:F16">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C16" s="115">
+      <c r="C16" s="112">
         <v>165000</v>
       </c>
-      <c r="D16" s="115">
+      <c r="D16" s="112">
         <v>175000</v>
       </c>
-      <c r="E16" s="115">
+      <c r="E16" s="112">
         <v>175000</v>
       </c>
-      <c r="F16" s="115">
+      <c r="F16" s="112">
         <v>175000</v>
       </c>
       <c r="G16" s="27"/>
@@ -9310,26 +9322,26 @@
       <c r="Q17" s="27"/>
     </row>
     <row r="18" spans="1:17" ht="15.75">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="54">
+      <c r="B18" s="53">
         <f>SUM(B16+B12)</f>
         <v>1465000</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="53">
         <f t="shared" ref="C18:F18" si="2">SUM(C16+C12)</f>
         <v>1504000</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="53">
         <f t="shared" si="2"/>
         <v>1554171</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="53">
         <f t="shared" si="2"/>
         <v>1595545</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="53">
         <f t="shared" si="2"/>
         <v>1638160</v>
       </c>
@@ -9633,6 +9645,7 @@
       <c r="Q33" s="27"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:F3"/>
@@ -9652,16 +9665,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.75">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
@@ -9672,14 +9685,14 @@
       <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18.75">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
@@ -9690,8 +9703,8 @@
       <c r="P2" s="27"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="64" t="s">
-        <v>18</v>
+      <c r="A3" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="B3" s="22" cm="1">
         <f t="array" ref="B3">currentyear</f>
@@ -9725,23 +9738,23 @@
       <c r="P3" s="27"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="76" cm="1">
+      <c r="B4" s="73" cm="1">
         <f t="array" ref="B4:F4">total_operating_revenue_row</f>
         <v>1439550</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="73">
         <v>1564250.5</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="73">
         <v>1674016</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="73">
         <v>1690976.5</v>
       </c>
-      <c r="F4" s="77">
+      <c r="F4" s="74">
         <v>1766930</v>
       </c>
       <c r="G4" s="27"/>
@@ -9756,23 +9769,23 @@
       <c r="P4" s="27"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="76" cm="1">
+      <c r="B5" s="73" cm="1">
         <f t="array" ref="B5:F5">total_cost_of_service_row</f>
         <v>1465000</v>
       </c>
-      <c r="C5" s="76">
+      <c r="C5" s="73">
         <v>1504000</v>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="73">
         <v>1554171</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="73">
         <v>1595545</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F5" s="74">
         <v>1638160</v>
       </c>
       <c r="G5" s="27"/>
@@ -9787,26 +9800,26 @@
       <c r="P5" s="27"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="73">
         <f>B4-B5</f>
         <v>-25450</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="73">
         <f t="shared" ref="C6:F6" si="1">C4-C5</f>
         <v>60250.5</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="73">
         <f t="shared" si="1"/>
         <v>119845</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="73">
         <f t="shared" si="1"/>
         <v>95431.5</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F6" s="74">
         <f t="shared" si="1"/>
         <v>128770</v>
       </c>
@@ -9822,26 +9835,26 @@
       <c r="P6" s="27"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="85">
+      <c r="B7" s="82">
         <f>B6</f>
         <v>-25450</v>
       </c>
-      <c r="C7" s="85">
+      <c r="C7" s="82">
         <f>B7+C6</f>
         <v>34800.5</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="82">
         <f t="shared" ref="D7:F7" si="2">C7+D6</f>
         <v>154645.5</v>
       </c>
-      <c r="E7" s="85">
+      <c r="E7" s="82">
         <f t="shared" si="2"/>
         <v>250077</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="83">
         <f t="shared" si="2"/>
         <v>378847</v>
       </c>
@@ -9875,8 +9888,8 @@
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="64" t="s">
-        <v>18</v>
+      <c r="A9" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="22" cm="1">
         <f t="array" ref="B9">currentyear</f>
@@ -9913,20 +9926,20 @@
       <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="76" cm="1">
+      <c r="B10" s="73" cm="1">
         <f t="array" ref="B10:F10">total_operating_revenue_row - total_operating_expenses</f>
         <v>139550</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="73">
         <v>225250.5</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="73">
         <v>294845</v>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="73">
         <v>270431.5</v>
       </c>
-      <c r="F10" s="77">
+      <c r="F10" s="74">
         <v>303770</v>
       </c>
       <c r="G10" s="27"/>
@@ -9944,20 +9957,20 @@
       <c r="A11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="76" cm="1">
+      <c r="B11" s="73" cm="1">
         <f t="array" ref="B11:F11">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="73">
         <v>165000</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="73">
         <v>175000</v>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="73">
         <v>175000</v>
       </c>
-      <c r="F11" s="77">
+      <c r="F11" s="74">
         <v>175000</v>
       </c>
       <c r="G11" s="27"/>
@@ -9972,26 +9985,26 @@
       <c r="P11" s="27"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="79">
+      <c r="B12" s="76">
         <f>B10/B11</f>
         <v>0.84575757575757571</v>
       </c>
-      <c r="C12" s="79">
+      <c r="C12" s="76">
         <f t="shared" ref="C12:F12" si="4">C10/C11</f>
         <v>1.3651545454545455</v>
       </c>
-      <c r="D12" s="79">
+      <c r="D12" s="76">
         <f t="shared" si="4"/>
         <v>1.6848285714285713</v>
       </c>
-      <c r="E12" s="79">
+      <c r="E12" s="76">
         <f t="shared" si="4"/>
         <v>1.5453228571428572</v>
       </c>
-      <c r="F12" s="80">
+      <c r="F12" s="77">
         <f t="shared" si="4"/>
         <v>1.7358285714285715</v>
       </c>
@@ -10007,26 +10020,26 @@
       <c r="P12" s="27"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="82" t="str" cm="1">
+      <c r="B13" s="79" t="str" cm="1">
         <f t="array" ref="B13">IF(B12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Insufficient</v>
       </c>
-      <c r="C13" s="82" t="str" cm="1">
+      <c r="C13" s="79" t="str" cm="1">
         <f t="array" ref="C13">IF(C12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="D13" s="82" t="str" cm="1">
+      <c r="D13" s="79" t="str" cm="1">
         <f t="array" ref="D13">IF(D12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="E13" s="82" t="str" cm="1">
+      <c r="E13" s="79" t="str" cm="1">
         <f t="array" ref="E13">IF(E12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="F13" s="83" t="str" cm="1">
+      <c r="F13" s="80" t="str" cm="1">
         <f t="array" ref="F13">IF(F12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
@@ -10366,6 +10379,7 @@
       <c r="P31" s="27"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE07FE46-6380-4676-A24D-985058494B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F421D0D8-1A21-4202-964B-31AABA7706C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="base_chargeRS1">Inputs!$C$14:$G$14</definedName>
+    <definedName name="base_chargeRS12027">Inputs!$D$14:$D$14</definedName>
     <definedName name="base_chargeRS2">Inputs!$C$24:$G$24</definedName>
     <definedName name="currentyear">Inputs!$C$11:$C$11</definedName>
     <definedName name="debt_service_values">Inputs!$X$12:$AB$12</definedName>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -104,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
   <si>
     <t>Water Utility Financial Model</t>
   </si>
@@ -308,6 +309,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Proposed Monthly Bill</t>
   </si>
 </sst>
 </file>
@@ -737,9 +741,6 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -771,9 +772,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -805,12 +803,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -847,6 +848,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -856,15 +860,15 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2327,10 +2331,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="21">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
+      <c r="B1" s="120"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
@@ -2426,10 +2430,10 @@
       <c r="CQ1" s="26"/>
     </row>
     <row r="2" spans="1:95">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119"/>
+      <c r="B2" s="122"/>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
@@ -2525,8 +2529,8 @@
       <c r="CQ2" s="26"/>
     </row>
     <row r="3" spans="1:95">
-      <c r="A3" s="99"/>
-      <c r="B3" s="77"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
@@ -2622,10 +2626,10 @@
       <c r="CQ3" s="26"/>
     </row>
     <row r="4" spans="1:95">
-      <c r="A4" s="120" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="121"/>
+      <c r="B4" s="124"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -2825,7 +2829,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="26"/>
-      <c r="D6" s="93" t="s">
+      <c r="D6" s="106" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="6"/>
@@ -2931,7 +2935,7 @@
       <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="67">
         <v>0.03</v>
       </c>
       <c r="F7" s="26"/>
@@ -3139,7 +3143,7 @@
         <v>410100000</v>
       </c>
       <c r="C9" s="26"/>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="68" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="2">
@@ -3359,15 +3363,15 @@
         <v>2030</v>
       </c>
       <c r="H11" s="26"/>
-      <c r="I11" s="113" t="s">
+      <c r="I11" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="115"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
+      <c r="O11" s="118"/>
       <c r="P11" s="28"/>
       <c r="Q11" s="35" t="s">
         <v>15</v>
@@ -3376,14 +3380,14 @@
         <v>2026</v>
       </c>
       <c r="S11" s="26"/>
-      <c r="T11" s="103" t="s">
+      <c r="T11" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="U11" s="126"/>
-      <c r="V11" s="104" t="s">
+      <c r="U11" s="107"/>
+      <c r="V11" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="W11" s="130" t="s">
+      <c r="W11" s="111" t="s">
         <v>17</v>
       </c>
       <c r="X11" s="17">
@@ -3401,7 +3405,7 @@
         <f>Z11+1</f>
         <v>2029</v>
       </c>
-      <c r="AB11" s="90">
+      <c r="AB11" s="89">
         <f>AA11+1</f>
         <v>2030</v>
       </c>
@@ -3485,7 +3489,7 @@
       <c r="I12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="81" t="s">
+      <c r="J12" s="80" t="s">
         <v>13</v>
       </c>
       <c r="K12" s="63" cm="1">
@@ -3516,12 +3520,12 @@
         <v>725000</v>
       </c>
       <c r="S12" s="26"/>
-      <c r="T12" s="105" t="s">
+      <c r="T12" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="U12" s="75"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="131"/>
+      <c r="U12" s="74"/>
+      <c r="V12" s="104"/>
+      <c r="W12" s="112"/>
       <c r="X12" s="59">
         <f>U13</f>
         <v>165000</v>
@@ -3621,7 +3625,7 @@
       <c r="F13" s="14"/>
       <c r="G13" s="15"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="84" t="str" cm="1">
+      <c r="I13" s="83" t="str" cm="1">
         <f t="array" ref="I13">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
@@ -3655,10 +3659,10 @@
         <v>105000</v>
       </c>
       <c r="S13" s="26"/>
-      <c r="T13" s="127">
+      <c r="T13" s="108">
         <v>2026</v>
       </c>
-      <c r="U13" s="128">
+      <c r="U13" s="109">
         <v>165000</v>
       </c>
       <c r="V13" s="26"/>
@@ -3790,11 +3794,11 @@
         <v>50000</v>
       </c>
       <c r="S14" s="26"/>
-      <c r="T14" s="127">
+      <c r="T14" s="108">
         <f>T13+1</f>
         <v>2027</v>
       </c>
-      <c r="U14" s="129">
+      <c r="U14" s="110">
         <v>165000</v>
       </c>
       <c r="V14" s="26"/>
@@ -3895,7 +3899,7 @@
         <v>2000</v>
       </c>
       <c r="H15" s="26"/>
-      <c r="I15" s="75"/>
+      <c r="I15" s="74"/>
       <c r="J15" s="60" t="s">
         <v>27</v>
       </c>
@@ -3926,11 +3930,11 @@
         <v>98000</v>
       </c>
       <c r="S15" s="26"/>
-      <c r="T15" s="127">
+      <c r="T15" s="108">
         <f>T14+1</f>
         <v>2028</v>
       </c>
-      <c r="U15" s="129">
+      <c r="U15" s="110">
         <v>175000</v>
       </c>
       <c r="V15" s="26"/>
@@ -4034,11 +4038,11 @@
         <v>52000</v>
       </c>
       <c r="S16" s="26"/>
-      <c r="T16" s="127">
+      <c r="T16" s="108">
         <f t="shared" ref="T16:T17" si="2">T15+1</f>
         <v>2029</v>
       </c>
-      <c r="U16" s="129">
+      <c r="U16" s="110">
         <v>175000</v>
       </c>
       <c r="V16" s="26"/>
@@ -4125,7 +4129,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="16"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="126" t="s">
+      <c r="I17" s="107" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="17" t="s">
@@ -4163,7 +4167,7 @@
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="U17" s="129">
+      <c r="U17" s="110">
         <v>175000</v>
       </c>
       <c r="V17" s="26"/>
@@ -4259,7 +4263,7 @@
       <c r="J18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="83">
+      <c r="K18" s="82">
         <v>5500</v>
       </c>
       <c r="L18" s="21" cm="1">
@@ -4390,7 +4394,7 @@
       <c r="J19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="83">
+      <c r="K19" s="82">
         <v>5000</v>
       </c>
       <c r="L19" s="21" cm="1">
@@ -4513,11 +4517,11 @@
         <v>2.5</v>
       </c>
       <c r="H20" s="26"/>
-      <c r="I20" s="75"/>
+      <c r="I20" s="74"/>
       <c r="J20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="83">
+      <c r="K20" s="82">
         <v>995</v>
       </c>
       <c r="L20" s="21" cm="1">
@@ -4641,9 +4645,9 @@
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
@@ -4738,11 +4742,11 @@
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="112" t="s">
+      <c r="J22" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="112"/>
-      <c r="L22" s="112"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="115"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
       <c r="O22" s="26"/>
@@ -5841,16 +5845,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -6509,13 +6513,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="18.75">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
@@ -6583,14 +6587,14 @@
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
-      <c r="L2" s="123" t="s">
+      <c r="L2" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="125"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="129"/>
       <c r="R2" s="26"/>
       <c r="S2" s="26"/>
       <c r="T2" s="26"/>
@@ -6635,25 +6639,25 @@
       <c r="BG2" s="26"/>
     </row>
     <row r="3" spans="1:59" ht="18.75">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="125"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="129"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
       <c r="J3" s="26"/>
       <c r="K3" s="26"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="102"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="100"/>
       <c r="R3" s="26"/>
       <c r="S3" s="26"/>
       <c r="T3" s="26"/>
@@ -6698,27 +6702,27 @@
       <c r="BG3" s="26"/>
     </row>
     <row r="4" spans="1:59">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="86"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="85"/>
       <c r="G4" s="26"/>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
       <c r="J4" s="26"/>
       <c r="K4" s="26"/>
-      <c r="L4" s="85" t="s">
+      <c r="L4" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="81"/>
-      <c r="Q4" s="86"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="85"/>
       <c r="R4" s="26"/>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
@@ -6726,20 +6730,20 @@
       <c r="V4" s="26"/>
       <c r="W4" s="26"/>
       <c r="X4" s="26"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82">
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81">
         <f t="shared" ref="Z4:AC4" si="0">$B$22</f>
         <v>1566210</v>
       </c>
-      <c r="AA4" s="82">
+      <c r="AA4" s="81">
         <f t="shared" si="0"/>
         <v>1566210</v>
       </c>
-      <c r="AB4" s="82">
+      <c r="AB4" s="81">
         <f t="shared" si="0"/>
         <v>1566210</v>
       </c>
-      <c r="AC4" s="82">
+      <c r="AC4" s="81">
         <f t="shared" si="0"/>
         <v>1566210</v>
       </c>
@@ -6992,20 +6996,20 @@
       <c r="L7" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="91" cm="1">
+      <c r="M7" s="90" cm="1">
         <f t="array" ref="M7:Q7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
         <v>514080</v>
       </c>
-      <c r="N7" s="92">
+      <c r="N7" s="91">
         <v>519180</v>
       </c>
-      <c r="O7" s="92">
+      <c r="O7" s="91">
         <v>524280</v>
       </c>
-      <c r="P7" s="92">
+      <c r="P7" s="91">
         <v>529584</v>
       </c>
-      <c r="Q7" s="92">
+      <c r="Q7" s="91">
         <v>534888</v>
       </c>
       <c r="R7" s="26"/>
@@ -7317,26 +7321,26 @@
       <c r="BG10" s="26"/>
     </row>
     <row r="11" spans="1:59">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="87">
         <f>SUM(B7:B10)</f>
         <v>990360</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="87">
         <f t="shared" ref="C11:F11" si="3">SUM(C7:C10)</f>
         <v>1091820</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="87">
         <f t="shared" si="3"/>
         <v>1158534</v>
       </c>
-      <c r="E11" s="88">
+      <c r="E11" s="87">
         <f t="shared" si="3"/>
         <v>1170174</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="87">
         <f t="shared" si="3"/>
         <v>1236924</v>
       </c>
@@ -7473,14 +7477,14 @@
       <c r="BG12" s="26"/>
     </row>
     <row r="13" spans="1:59">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="88" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="90"/>
+      <c r="F13" s="89"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
@@ -7731,20 +7735,20 @@
       <c r="A16" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="91" cm="1">
+      <c r="B16" s="90" cm="1">
         <f t="array" ref="B16:F16">base_chargeRS2 * 12 * RS2_num_accounts</f>
         <v>231000</v>
       </c>
-      <c r="C16" s="92">
+      <c r="C16" s="91">
         <v>233520</v>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="91">
         <v>236040</v>
       </c>
-      <c r="E16" s="92">
+      <c r="E16" s="91">
         <v>238560</v>
       </c>
-      <c r="F16" s="92">
+      <c r="F16" s="91">
         <v>241080</v>
       </c>
       <c r="G16" s="26"/>
@@ -8859,15 +8863,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
@@ -8899,14 +8903,14 @@
       <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="110"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="132"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
@@ -8923,22 +8927,22 @@
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="81">
+      <c r="B4" s="80">
         <v>2026</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="80">
         <f>B4+1</f>
         <v>2027</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="80">
         <f t="shared" ref="D4:F4" si="0">C4+1</f>
         <v>2028</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="80">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="85">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -9026,7 +9030,7 @@
       <c r="Q6" s="26"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="74" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="47">
@@ -9064,22 +9068,22 @@
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="94">
+      <c r="B8" s="92">
         <v>98000</v>
       </c>
-      <c r="C8" s="95" cm="1">
+      <c r="C8" s="93" cm="1">
         <f t="array" ref="C8">ROUND(B8*(1+inflation_rate),0)</f>
         <v>100940</v>
       </c>
-      <c r="D8" s="95" cm="1">
+      <c r="D8" s="93" cm="1">
         <f t="array" ref="D8">ROUND(C8*(1+inflation_rate),0)</f>
         <v>103968</v>
       </c>
-      <c r="E8" s="95" cm="1">
+      <c r="E8" s="93" cm="1">
         <f t="array" ref="E8">ROUND(D8*(1+inflation_rate),0)</f>
         <v>107087</v>
       </c>
-      <c r="F8" s="95" cm="1">
+      <c r="F8" s="93" cm="1">
         <f t="array" ref="F8">ROUND(E8*(1+inflation_rate),0)</f>
         <v>110300</v>
       </c>
@@ -9256,14 +9260,14 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="1:17" ht="15.75">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="110"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="132"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -9277,25 +9281,25 @@
       <c r="Q14" s="26"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="81">
+      <c r="B15" s="80">
         <v>2026</v>
       </c>
-      <c r="C15" s="81">
+      <c r="C15" s="80">
         <f>B15+1</f>
         <v>2027</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="80">
         <f>C15+1</f>
         <v>2028</v>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="80">
         <f>D15+1</f>
         <v>2029</v>
       </c>
-      <c r="F15" s="86">
+      <c r="F15" s="85">
         <f>E15+1</f>
         <v>2030</v>
       </c>
@@ -9312,23 +9316,23 @@
       <c r="Q15" s="26"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="98" cm="1">
+      <c r="B16" s="96" cm="1">
         <f t="array" ref="B16:F16">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C16" s="98">
+      <c r="C16" s="96">
         <v>165000</v>
       </c>
-      <c r="D16" s="98">
+      <c r="D16" s="96">
         <v>175000</v>
       </c>
-      <c r="E16" s="98">
+      <c r="E16" s="96">
         <v>175000</v>
       </c>
-      <c r="F16" s="98">
+      <c r="F16" s="96">
         <v>175000</v>
       </c>
       <c r="G16" s="26"/>
@@ -9708,16 +9712,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.75">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -9728,14 +9732,14 @@
       <c r="P1" s="26"/>
     </row>
     <row r="2" spans="1:16" ht="18.75">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
@@ -9781,23 +9785,23 @@
       <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="70" cm="1">
+      <c r="B4" s="69" cm="1">
         <f t="array" ref="B4:F4">total_operating_revenue_row</f>
         <v>1566210</v>
       </c>
-      <c r="C4" s="70">
+      <c r="C4" s="69">
         <v>1673640</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="69">
         <v>1746384</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="69">
         <v>1764054</v>
       </c>
-      <c r="F4" s="71">
+      <c r="F4" s="70">
         <v>1836894</v>
       </c>
       <c r="G4" s="26"/>
@@ -9812,23 +9816,23 @@
       <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="70" cm="1">
+      <c r="B5" s="69" cm="1">
         <f t="array" ref="B5:F5">total_cost_of_service_row</f>
         <v>1589000</v>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="69">
         <v>1631720</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="69">
         <v>1685723</v>
       </c>
-      <c r="E5" s="70">
+      <c r="E5" s="69">
         <v>1731045</v>
       </c>
-      <c r="F5" s="71">
+      <c r="F5" s="70">
         <v>1777727</v>
       </c>
       <c r="G5" s="26"/>
@@ -9843,26 +9847,26 @@
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="69">
         <f>B4-B5</f>
         <v>-22790</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="69">
         <f t="shared" ref="C6:F6" si="1">C4-C5</f>
         <v>41920</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="69">
         <f t="shared" si="1"/>
         <v>60661</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="69">
         <f t="shared" si="1"/>
         <v>33009</v>
       </c>
-      <c r="F6" s="71">
+      <c r="F6" s="70">
         <f t="shared" si="1"/>
         <v>59167</v>
       </c>
@@ -9878,26 +9882,26 @@
       <c r="P6" s="26"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="79">
+      <c r="B7" s="78">
         <f>B6</f>
         <v>-22790</v>
       </c>
-      <c r="C7" s="79">
+      <c r="C7" s="78">
         <f>B7+C6</f>
         <v>19130</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="78">
         <f t="shared" ref="D7:F7" si="2">C7+D6</f>
         <v>79791</v>
       </c>
-      <c r="E7" s="79">
+      <c r="E7" s="78">
         <f t="shared" si="2"/>
         <v>112800</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="79">
         <f t="shared" si="2"/>
         <v>171967</v>
       </c>
@@ -9969,20 +9973,20 @@
       <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="70" cm="1">
+      <c r="B10" s="69" cm="1">
         <f t="array" ref="B10:F10">total_operating_revenue_row - total_operating_expenses</f>
         <v>142210</v>
       </c>
-      <c r="C10" s="70">
+      <c r="C10" s="69">
         <v>206920</v>
       </c>
-      <c r="D10" s="70">
+      <c r="D10" s="69">
         <v>235661</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="69">
         <v>208009</v>
       </c>
-      <c r="F10" s="71">
+      <c r="F10" s="70">
         <v>234167</v>
       </c>
       <c r="G10" s="26"/>
@@ -10000,20 +10004,20 @@
       <c r="A11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="70" cm="1">
+      <c r="B11" s="69" cm="1">
         <f t="array" ref="B11:F11">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C11" s="70">
+      <c r="C11" s="69">
         <v>165000</v>
       </c>
-      <c r="D11" s="70">
+      <c r="D11" s="69">
         <v>175000</v>
       </c>
-      <c r="E11" s="70">
+      <c r="E11" s="69">
         <v>175000</v>
       </c>
-      <c r="F11" s="71">
+      <c r="F11" s="70">
         <v>175000</v>
       </c>
       <c r="G11" s="26"/>
@@ -10028,26 +10032,26 @@
       <c r="P11" s="26"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="73">
+      <c r="B12" s="72">
         <f>B10/B11</f>
         <v>0.86187878787878791</v>
       </c>
-      <c r="C12" s="73">
+      <c r="C12" s="72">
         <f t="shared" ref="C12:F12" si="4">C10/C11</f>
         <v>1.2540606060606061</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="72">
         <f t="shared" si="4"/>
         <v>1.3466342857142857</v>
       </c>
-      <c r="E12" s="73">
+      <c r="E12" s="72">
         <f t="shared" si="4"/>
         <v>1.1886228571428572</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="73">
         <f t="shared" si="4"/>
         <v>1.3380971428571429</v>
       </c>
@@ -10063,26 +10067,26 @@
       <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="76" t="str" cm="1">
+      <c r="B13" s="75" t="str" cm="1">
         <f t="array" ref="B13">IF(B12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Insufficient</v>
       </c>
-      <c r="C13" s="76" t="str" cm="1">
+      <c r="C13" s="75" t="str" cm="1">
         <f t="array" ref="C13">IF(C12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="D13" s="76" t="str" cm="1">
+      <c r="D13" s="75" t="str" cm="1">
         <f t="array" ref="D13">IF(D12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="E13" s="76" t="str" cm="1">
+      <c r="E13" s="75" t="str" cm="1">
         <f t="array" ref="E13">IF(E12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="F13" s="77" t="str" cm="1">
+      <c r="F13" s="76" t="str" cm="1">
         <f t="array" ref="F13">IF(F12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
@@ -10146,15 +10150,15 @@
         <f t="array" ref="A16">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="B16" s="132" cm="1">
+      <c r="B16" s="113" cm="1">
         <f t="array" ref="B16">RS1_base_charge2026</f>
         <v>17</v>
       </c>
-      <c r="C16" s="132" cm="1">
+      <c r="C16" s="113" cm="1">
         <f t="array" ref="C16">ROUND(SUM(RS1_block_consumption2026 * RS1_vrates2026)/num_accountsRS1,2)</f>
         <v>15.75</v>
       </c>
-      <c r="D16" s="132">
+      <c r="D16" s="113">
         <f>B16+C16</f>
         <v>32.75</v>
       </c>
@@ -10176,14 +10180,14 @@
         <f t="array" ref="A17">rate_structure_2</f>
         <v>Commerical, inside</v>
       </c>
-      <c r="B17" s="132">
+      <c r="B17" s="113">
         <v>35</v>
       </c>
-      <c r="C17" s="132" cm="1">
+      <c r="C17" s="113" cm="1">
         <f t="array" ref="C17">ROUND(SUM(RS2_block_consumption2026 * RS2_vrates2026)/num_accountsRS2,2)</f>
         <v>52.25</v>
       </c>
-      <c r="D17" s="132">
+      <c r="D17" s="113">
         <f>B17+C17</f>
         <v>87.25</v>
       </c>
@@ -10219,10 +10223,18 @@
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
+      <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -10237,10 +10249,22 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
+      <c r="A20" s="1" t="str" cm="1">
+        <f t="array" ref="A20">rate_structure_1</f>
+        <v>Residential water, inside</v>
+      </c>
+      <c r="B20" s="113" cm="1">
+        <f t="array" ref="B20">base_chargeRS12027</f>
+        <v>20</v>
+      </c>
+      <c r="C20" s="113" cm="1">
+        <f t="array" ref="C20">ROUND(SUM(RS1_block_consumption2026 * RS1_vrates2027)/num_accountsRS1,2)</f>
+        <v>15.75</v>
+      </c>
+      <c r="D20" s="113">
+        <f>B20+C20</f>
+        <v>35.75</v>
+      </c>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -10255,10 +10279,21 @@
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
+      <c r="A21" s="1" t="str" cm="1">
+        <f t="array" ref="A21">rate_structure_2</f>
+        <v>Commerical, inside</v>
+      </c>
+      <c r="B21" s="113">
+        <v>35</v>
+      </c>
+      <c r="C21" s="113" cm="1">
+        <f t="array" ref="C21">ROUND(SUM(RS2_block_consumption2026 * RS2_vrates2027)/num_accountsRS2,2)</f>
+        <v>52.25</v>
+      </c>
+      <c r="D21" s="113">
+        <f>B21+C21</f>
+        <v>87.25</v>
+      </c>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F421D0D8-1A21-4202-964B-31AABA7706C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0F186C2-6245-4576-848B-F7CCF4A80083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="5" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="5" r:id="rId1"/>
+    <sheet name="Inputs" sheetId="1" r:id="rId2"/>
     <sheet name="Revenue_Model" sheetId="2" r:id="rId3"/>
     <sheet name="Expense_Model" sheetId="3" r:id="rId4"/>
     <sheet name="Rate_Sufficiency_Analysis" sheetId="4" r:id="rId5"/>
@@ -18,6 +18,8 @@
     <definedName name="base_chargeRS1">Inputs!$C$14:$G$14</definedName>
     <definedName name="base_chargeRS12027">Inputs!$D$14:$D$14</definedName>
     <definedName name="base_chargeRS2">Inputs!$C$24:$G$24</definedName>
+    <definedName name="current_dscr">Rate_Sufficiency_Analysis!$B$12:$B$12</definedName>
+    <definedName name="current_monthly_bill">Rate_Sufficiency_Analysis!$E$16:$E$16</definedName>
     <definedName name="currentyear">Inputs!$C$11:$C$11</definedName>
     <definedName name="debt_service_values">Inputs!$X$12:$AB$12</definedName>
     <definedName name="expenses_value">Inputs!$R$12:$R$18</definedName>
@@ -26,6 +28,8 @@
     <definedName name="num_accountsRS1">Inputs!$A$16:$A$16</definedName>
     <definedName name="num_accountsRS2">Inputs!$A$26:$A$26</definedName>
     <definedName name="pop_growth_rate">Inputs!$E$8:$E$8</definedName>
+    <definedName name="proposed_dscr">Rate_Sufficiency_Analysis!$C$12:$C$12</definedName>
+    <definedName name="proposed_monthly_bill">Rate_Sufficiency_Analysis!$E$20:$E$20</definedName>
     <definedName name="rate_structure_1">Inputs!$A$14:$A$14</definedName>
     <definedName name="rate_structure_2">Inputs!$A$24:$A$24</definedName>
     <definedName name="RS1_base_charge2026">Inputs!$C$14:$C$14</definedName>
@@ -42,6 +46,7 @@
     <definedName name="RS1_vrates2029">Inputs!$F$19:$F$21</definedName>
     <definedName name="RS1_vrates2030">Inputs!$G$19:$G$21</definedName>
     <definedName name="RS2_base_charge2026">Inputs!$C$24:$C$24</definedName>
+    <definedName name="RS2_base_charge2027">Inputs!$D$24:$D$24</definedName>
     <definedName name="RS2_block_consumption2026">Inputs!$K$18:$K$20</definedName>
     <definedName name="RS2_block_consumption2027">Inputs!$L$18:$L$20</definedName>
     <definedName name="RS2_block_consumption2028">Inputs!$M$18:$M$20</definedName>
@@ -105,7 +110,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
+  <si>
+    <t>Stringtown Water Utility Summary Dashboard</t>
+  </si>
+  <si>
+    <t>Current Average Monthly Bill</t>
+  </si>
+  <si>
+    <t>Proposed Average Monthly Bill</t>
+  </si>
+  <si>
+    <t>Current DSCR</t>
+  </si>
+  <si>
+    <t>Proposed DSCR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Financial Summary:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> At current rates, the City of Stringtown's water utility generates a Debt Service Coverage Ratio of 0.73, which is below the 1.15 minimum threshold required by lenders and bond convenants. The utility is currently under-collecting relative to its full cost of service, creating structural revenue gap that grows over the 5-year planning horizon due to inflation and escalation of operating expenses.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rate Recommendation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A rate adjustment of approximately 8% applied across both residential and commercial customer classes is recommended. Under proposed rates, the average residential monthly bill increases from $32.75 to $35.75 and the average commercial bill increases from $95.48 to $100.48, bringing the system-wide average monthly bill from $43.99 to $47.35. This modest adjustment achieves a DSCR of 1.31, restores financial sufficiency, and positions the utility to meet its debt obligations and fund any necessary capital improvement plans throughout 2030.</t>
+    </r>
+  </si>
+  <si>
+    <t>Affordability impact is minimal: the proposed residential bill of $35.75/month represents approximately 1.1% of median household income for a community of this size, which is well within the EPA's 2.5% affordability threshold.</t>
+  </si>
   <si>
     <t>Water Utility Financial Model</t>
   </si>
@@ -224,9 +289,6 @@
     <t>Commerical, inside</t>
   </si>
   <si>
-    <t>Stringtown Water Utility Summary Dashboard</t>
-  </si>
-  <si>
     <t>Revenue Projections | 2026 - 2030</t>
   </si>
   <si>
@@ -311,6 +373,9 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Combined Avg</t>
+  </si>
+  <si>
     <t>Proposed Monthly Bill</t>
   </si>
 </sst>
@@ -318,13 +383,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,8 +466,29 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,8 +513,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -651,11 +751,131 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -797,12 +1017,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -811,7 +1025,73 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -845,9 +1125,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -869,11 +1146,23 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -892,6 +1181,26 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -1044,19 +1353,19 @@
                 <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1566210</c:v>
+                  <c:v>1620495</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1582026</c:v>
+                  <c:v>1636872</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1597965</c:v>
+                  <c:v>1653378</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1614150</c:v>
+                  <c:v>1670130</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1630437</c:v>
+                  <c:v>1686990</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1075,7 +1384,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="375623"/>
+              <a:srgbClr val="548235"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1114,19 +1423,19 @@
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1566210</c:v>
+                  <c:v>1620495</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1673640</c:v>
+                  <c:v>1761846</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1746384</c:v>
+                  <c:v>1835517</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1764054</c:v>
+                  <c:v>1854114</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1836894</c:v>
+                  <c:v>1927887</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1159,12 +1468,14 @@
             <c:v>Expenses</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
+              <a:prstDash val="sysDot"/>
               <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1202,19 +1513,19 @@
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1589000</c:v>
+                  <c:v>1665500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1631720</c:v>
+                  <c:v>1710515</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1685723</c:v>
+                  <c:v>1766882</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1731045</c:v>
+                  <c:v>1814639</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1777727</c:v>
+                  <c:v>1863829</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1294,7 +1605,8 @@
         <c:axId val="1447064584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1850000"/>
+          <c:max val="1950000"/>
+          <c:min val="1500000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1423,7 +1735,1277 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Projected Annual Surplus (Deficit) Using New Rates Starting in 2027</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"Annual Surplus (Deficit)"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Annual Surplus (Deficit)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-CFB2-49B6-AADB-F22A42C83141}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-CFB2-49B6-AADB-F22A42C83141}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-A1D7-46B4-B903-949BB2443B28}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A1D7-46B4-B903-949BB2443B28}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-CC0B-44C4-8580-026CEB7483BB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Rate_Sufficiency_Analysis!$B$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rate_Sufficiency_Analysis!B6:F6</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-45005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51331</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68635</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39475</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>64058</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CFB2-49B6-AADB-F22A42C83141}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1586756616"/>
+        <c:axId val="1447064584"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1586756616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1447064584"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1447064584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100000"/>
+          <c:min val="-100000"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1586756616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>DSCR Trend vs Target DSCR</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"DSCR"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DSCR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="548235"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="548235"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="548235"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="548235"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Rate_Sufficiency_Analysis!B9:F9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rate_Sufficiency_Analysis!$B$12:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.72724242424242425</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3110969696969696</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3922000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2255714285714285</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3660457142857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7FD9-4BFC-A650-7A3FD9041235}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"Target DSCR"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Target DSCR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-6B6F-458B-8B74-FB53BBB479BA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="C00000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Rate_Sufficiency_Analysis!B9:F9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rate_Sufficiency_Analysis!X5:AB5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6B6F-458B-8B74-FB53BBB479BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="751893512"/>
+        <c:axId val="582435848"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="751893512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="582435848"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="582435848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="751893512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1966,20 +3548,1039 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1999,6 +4600,88 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A74B618-5B59-4113-BE2B-6DD492F3208A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B7A55DC1-E0A5-E535-BF13-A1A65604F0AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EABB8824-AAAD-4055-8B3A-C64641E50DC5}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7A74B618-5B59-4113-BE2B-6DD492F3208A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2303,6 +4986,904 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB8B75A-D480-4707-899D-4BDE57EE180A}">
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="30.75" customHeight="1">
+      <c r="A1" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+    </row>
+    <row r="2" spans="1:19" ht="21.75" customHeight="1">
+      <c r="A2" s="26"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="B3" s="121" cm="1">
+        <f t="array" ref="B3">current_monthly_bill</f>
+        <v>43.98827361563518</v>
+      </c>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="127" cm="1">
+        <f t="array" ref="E3">proposed_monthly_bill</f>
+        <v>47.346579804560264</v>
+      </c>
+      <c r="F3" s="127"/>
+      <c r="G3" s="128"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="B5" s="123"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="130"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="B6" s="125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="131" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="131"/>
+      <c r="G6" s="132"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="26"/>
+      <c r="B7" s="133" cm="1">
+        <f t="array" ref="B7">current_dscr</f>
+        <v>0.72724242424242425</v>
+      </c>
+      <c r="C7" s="115"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115" cm="1">
+        <f t="array" ref="E7">proposed_dscr</f>
+        <v>1.3110969696969696</v>
+      </c>
+      <c r="F7" s="115"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="26"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="26"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="115"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="116"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="26"/>
+      <c r="B10" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="118"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="26"/>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
+    </row>
+    <row r="30" spans="1:19" ht="15" customHeight="1">
+      <c r="A30" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="153"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="153"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="153"/>
+      <c r="N30" s="153"/>
+      <c r="O30" s="153"/>
+      <c r="P30" s="153"/>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="153"/>
+      <c r="B31" s="153"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="153"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="153"/>
+      <c r="K31" s="153"/>
+      <c r="L31" s="153"/>
+      <c r="M31" s="153"/>
+      <c r="N31" s="153"/>
+      <c r="O31" s="153"/>
+      <c r="P31" s="153"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="153"/>
+      <c r="B32" s="153"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="153"/>
+      <c r="K32" s="153"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="153"/>
+      <c r="N32" s="153"/>
+      <c r="O32" s="153"/>
+      <c r="P32" s="153"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="153"/>
+      <c r="B33" s="153"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="153"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="153"/>
+      <c r="N33" s="153"/>
+      <c r="O33" s="153"/>
+      <c r="P33" s="153"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="155"/>
+      <c r="C34" s="155"/>
+      <c r="D34" s="155"/>
+      <c r="E34" s="155"/>
+      <c r="F34" s="155"/>
+      <c r="G34" s="155"/>
+      <c r="H34" s="155"/>
+      <c r="I34" s="155"/>
+      <c r="J34" s="155"/>
+      <c r="K34" s="155"/>
+      <c r="L34" s="155"/>
+      <c r="M34" s="155"/>
+      <c r="N34" s="155"/>
+      <c r="O34" s="155"/>
+      <c r="P34" s="155"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="155"/>
+      <c r="B35" s="155"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="155"/>
+      <c r="G35" s="155"/>
+      <c r="H35" s="155"/>
+      <c r="I35" s="155"/>
+      <c r="J35" s="155"/>
+      <c r="K35" s="155"/>
+      <c r="L35" s="155"/>
+      <c r="M35" s="155"/>
+      <c r="N35" s="155"/>
+      <c r="O35" s="155"/>
+      <c r="P35" s="155"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="155"/>
+      <c r="B36" s="155"/>
+      <c r="C36" s="155"/>
+      <c r="D36" s="155"/>
+      <c r="E36" s="155"/>
+      <c r="F36" s="155"/>
+      <c r="G36" s="155"/>
+      <c r="H36" s="155"/>
+      <c r="I36" s="155"/>
+      <c r="J36" s="155"/>
+      <c r="K36" s="155"/>
+      <c r="L36" s="155"/>
+      <c r="M36" s="155"/>
+      <c r="N36" s="155"/>
+      <c r="O36" s="155"/>
+      <c r="P36" s="155"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="155"/>
+      <c r="B37" s="155"/>
+      <c r="C37" s="155"/>
+      <c r="D37" s="155"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="155"/>
+      <c r="G37" s="155"/>
+      <c r="H37" s="155"/>
+      <c r="I37" s="155"/>
+      <c r="J37" s="155"/>
+      <c r="K37" s="155"/>
+      <c r="L37" s="155"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="155"/>
+      <c r="O37" s="155"/>
+      <c r="P37" s="155"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="155" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="155"/>
+      <c r="C38" s="155"/>
+      <c r="D38" s="155"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="155"/>
+      <c r="G38" s="155"/>
+      <c r="H38" s="155"/>
+      <c r="I38" s="155"/>
+      <c r="J38" s="155"/>
+      <c r="K38" s="155"/>
+      <c r="L38" s="155"/>
+      <c r="M38" s="155"/>
+      <c r="N38" s="155"/>
+      <c r="O38" s="155"/>
+      <c r="P38" s="155"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="155"/>
+      <c r="B39" s="155"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="155"/>
+      <c r="E39" s="155"/>
+      <c r="F39" s="155"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="155"/>
+      <c r="I39" s="155"/>
+      <c r="J39" s="155"/>
+      <c r="K39" s="155"/>
+      <c r="L39" s="155"/>
+      <c r="M39" s="155"/>
+      <c r="N39" s="155"/>
+      <c r="O39" s="155"/>
+      <c r="P39" s="155"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="155"/>
+      <c r="B40" s="155"/>
+      <c r="C40" s="155"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
+      <c r="K40" s="155"/>
+      <c r="L40" s="155"/>
+      <c r="M40" s="155"/>
+      <c r="N40" s="155"/>
+      <c r="O40" s="155"/>
+      <c r="P40" s="155"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="155"/>
+      <c r="B41" s="155"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="155"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
+      <c r="K41" s="155"/>
+      <c r="L41" s="155"/>
+      <c r="M41" s="155"/>
+      <c r="N41" s="155"/>
+      <c r="O41" s="155"/>
+      <c r="P41" s="155"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A30:P33"/>
+    <mergeCell ref="A34:P37"/>
+    <mergeCell ref="A38:P41"/>
+    <mergeCell ref="E7:G9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="B3:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E3:G5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B7:D9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{C9025F45-B6EA-457D-B9CB-B8C3183C8DD3}">
+            <xm:f>Inputs!$E$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B7:G9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{3B29EDB2-A1EA-4299-92F2-58911080098F}">
+            <xm:f>Inputs!$E$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B7:G9</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CQ34"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2331,10 +5912,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="21">
-      <c r="A1" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="120"/>
+      <c r="A1" s="139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="140"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
@@ -2430,10 +6011,10 @@
       <c r="CQ1" s="26"/>
     </row>
     <row r="2" spans="1:95">
-      <c r="A2" s="121" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="122"/>
+      <c r="A2" s="141" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="142"/>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
@@ -2626,10 +6207,10 @@
       <c r="CQ3" s="26"/>
     </row>
     <row r="4" spans="1:95">
-      <c r="A4" s="123" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="124"/>
+      <c r="A4" s="143" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="144"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -2823,14 +6404,14 @@
     </row>
     <row r="6" spans="1:95" ht="15.75">
       <c r="A6" s="25" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C6" s="26"/>
-      <c r="D6" s="106" t="s">
-        <v>5</v>
+      <c r="D6" s="113" t="s">
+        <v>13</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="26"/>
@@ -2926,14 +6507,14 @@
     </row>
     <row r="7" spans="1:95" ht="15.75">
       <c r="A7" s="25" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B7" s="23">
         <v>10328</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E7" s="67">
         <v>0.03</v>
@@ -3031,14 +6612,14 @@
     </row>
     <row r="8" spans="1:95" ht="15.75">
       <c r="A8" s="25" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B8" s="23">
         <v>3070</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E8" s="20">
         <v>0.01</v>
@@ -3136,7 +6717,7 @@
     </row>
     <row r="9" spans="1:95" ht="15.75">
       <c r="A9" s="25" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" s="53">
         <f>SUM(K13:K15,K18:K20) * 12 * 1000</f>
@@ -3144,7 +6725,7 @@
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="68" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2">
         <v>1.1499999999999999</v>
@@ -3338,10 +6919,10 @@
     </row>
     <row r="11" spans="1:95" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C11" s="10">
         <v>2026</v>
@@ -3363,32 +6944,32 @@
         <v>2030</v>
       </c>
       <c r="H11" s="26"/>
-      <c r="I11" s="116" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="117"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="117"/>
-      <c r="O11" s="118"/>
+      <c r="I11" s="136" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="138"/>
       <c r="P11" s="28"/>
       <c r="Q11" s="35" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R11" s="21">
         <v>2026</v>
       </c>
       <c r="S11" s="26"/>
       <c r="T11" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="U11" s="107"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="105"/>
       <c r="V11" s="102" t="s">
-        <v>16</v>
-      </c>
-      <c r="W11" s="111" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="W11" s="109" t="s">
+        <v>25</v>
       </c>
       <c r="X11" s="17">
         <v>2026</v>
@@ -3487,10 +7068,10 @@
       <c r="G12" s="30"/>
       <c r="H12" s="26"/>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J12" s="80" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K12" s="63" cm="1">
         <f t="array" ref="K12">currentyear</f>
@@ -3514,18 +7095,18 @@
       </c>
       <c r="P12" s="28"/>
       <c r="Q12" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="R12" s="36">
         <v>725000</v>
       </c>
       <c r="S12" s="26"/>
       <c r="T12" s="103" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="U12" s="74"/>
       <c r="V12" s="104"/>
-      <c r="W12" s="112"/>
+      <c r="W12" s="110"/>
       <c r="X12" s="59">
         <f>U13</f>
         <v>165000</v>
@@ -3616,7 +7197,7 @@
     </row>
     <row r="13" spans="1:95">
       <c r="A13" s="11" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="14"/>
@@ -3630,7 +7211,7 @@
         <v>Residential water, inside</v>
       </c>
       <c r="J13" s="60" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K13" s="34">
         <v>17640</v>
@@ -3653,16 +7234,16 @@
       </c>
       <c r="P13" s="28"/>
       <c r="Q13" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R13" s="36">
-        <v>105000</v>
+        <v>135000</v>
       </c>
       <c r="S13" s="26"/>
-      <c r="T13" s="108">
+      <c r="T13" s="106">
         <v>2026</v>
       </c>
-      <c r="U13" s="109">
+      <c r="U13" s="107">
         <v>165000</v>
       </c>
       <c r="V13" s="26"/>
@@ -3742,10 +7323,10 @@
     </row>
     <row r="14" spans="1:95">
       <c r="A14" s="19" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C14" s="38">
         <v>17</v>
@@ -3765,7 +7346,7 @@
       <c r="H14" s="26"/>
       <c r="I14" s="3"/>
       <c r="J14" s="60" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K14" s="34">
         <v>4410</v>
@@ -3788,17 +7369,17 @@
       </c>
       <c r="P14" s="28"/>
       <c r="Q14" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R14" s="37">
-        <v>50000</v>
+        <v>64000</v>
       </c>
       <c r="S14" s="26"/>
-      <c r="T14" s="108">
+      <c r="T14" s="106">
         <f>T13+1</f>
         <v>2027</v>
       </c>
-      <c r="U14" s="110">
+      <c r="U14" s="108">
         <v>165000</v>
       </c>
       <c r="V14" s="26"/>
@@ -3878,10 +7459,10 @@
     </row>
     <row r="15" spans="1:95" ht="30.75">
       <c r="A15" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C15" s="34">
         <v>2000</v>
@@ -3901,7 +7482,7 @@
       <c r="H15" s="26"/>
       <c r="I15" s="74"/>
       <c r="J15" s="60" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K15" s="34">
         <v>630</v>
@@ -3924,17 +7505,17 @@
       </c>
       <c r="P15" s="28"/>
       <c r="Q15" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R15" s="36">
-        <v>98000</v>
+        <v>130500</v>
       </c>
       <c r="S15" s="26"/>
-      <c r="T15" s="108">
+      <c r="T15" s="106">
         <f>T14+1</f>
         <v>2028</v>
       </c>
-      <c r="U15" s="110">
+      <c r="U15" s="108">
         <v>175000</v>
       </c>
       <c r="V15" s="26"/>
@@ -4032,17 +7613,17 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="R16" s="36">
         <v>52000</v>
       </c>
       <c r="S16" s="26"/>
-      <c r="T16" s="108">
+      <c r="T16" s="106">
         <f t="shared" ref="T16:T17" si="2">T15+1</f>
         <v>2029</v>
       </c>
-      <c r="U16" s="110">
+      <c r="U16" s="108">
         <v>175000</v>
       </c>
       <c r="V16" s="26"/>
@@ -4129,11 +7710,11 @@
       <c r="F17" s="12"/>
       <c r="G17" s="16"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="107" t="s">
-        <v>30</v>
+      <c r="I17" s="105" t="s">
+        <v>38</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K17" s="21" cm="1">
         <f t="array" ref="K17">currentyear</f>
@@ -4157,7 +7738,7 @@
       </c>
       <c r="P17" s="28"/>
       <c r="Q17" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R17" s="36">
         <v>250000</v>
@@ -4167,7 +7748,7 @@
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="U17" s="110">
+      <c r="U17" s="108">
         <v>175000</v>
       </c>
       <c r="V17" s="26"/>
@@ -4247,7 +7828,7 @@
     </row>
     <row r="18" spans="1:95">
       <c r="A18" s="31" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
@@ -4261,7 +7842,7 @@
         <v>Commerical, inside</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K18" s="82">
         <v>5500</v>
@@ -4284,7 +7865,7 @@
       </c>
       <c r="P18" s="28"/>
       <c r="Q18" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R18" s="36">
         <v>144000</v>
@@ -4372,7 +7953,7 @@
         <v>3000</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C19" s="38">
         <v>1.75</v>
@@ -4392,7 +7973,7 @@
       <c r="H19" s="26"/>
       <c r="I19" s="3"/>
       <c r="J19" s="21" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K19" s="82">
         <v>5000</v>
@@ -4499,7 +8080,7 @@
         <v>4000</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C20" s="38">
         <v>1.75</v>
@@ -4519,7 +8100,7 @@
       <c r="H20" s="26"/>
       <c r="I20" s="74"/>
       <c r="J20" s="21" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K20" s="82">
         <v>995</v>
@@ -4626,7 +8207,7 @@
         <v>5000</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C21" s="38">
         <v>1.75</v>
@@ -4645,9 +8226,9 @@
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="134"/>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
@@ -4742,11 +8323,11 @@
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="115" t="s">
-        <v>37</v>
-      </c>
-      <c r="K22" s="115"/>
-      <c r="L22" s="115"/>
+      <c r="J22" s="135" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
       <c r="O22" s="26"/>
@@ -4833,7 +8414,7 @@
     </row>
     <row r="23" spans="1:95">
       <c r="A23" s="11" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="14"/>
@@ -4932,25 +8513,25 @@
     </row>
     <row r="24" spans="1:95">
       <c r="A24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="38">
         <v>38</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="38">
-        <v>35</v>
-      </c>
       <c r="D24" s="39">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E24" s="38">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F24" s="38">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G24" s="38">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
@@ -5043,10 +8624,10 @@
     </row>
     <row r="25" spans="1:95" ht="30.75">
       <c r="A25" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -5351,7 +8932,7 @@
     </row>
     <row r="28" spans="1:95">
       <c r="A28" s="31" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
@@ -5453,22 +9034,22 @@
         <v>5000</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C29" s="39">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="D29" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E29" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="F29" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="G29" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
@@ -5564,22 +9145,22 @@
         <v>10000</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C30" s="39">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="D30" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E30" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="F30" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="G30" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
@@ -5675,22 +9256,22 @@
         <v>15000</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C31" s="39">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="D31" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E31" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="F31" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="G31" s="38">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
@@ -5836,670 +9417,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB8B75A-D480-4707-899D-4BDE57EE180A}">
-  <dimension ref="A1:U28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="36.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" ht="30.75" customHeight="1">
-      <c r="A1" s="125" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="26"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-    </row>
-    <row r="26" spans="1:21">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" s="26"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-    </row>
-    <row r="28" spans="1:21">
-      <c r="A28" s="26"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FD50A9-0884-44AC-8AA5-5AA892507CF5}">
   <dimension ref="A1:BG38"/>
@@ -6513,13 +9430,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="18.75">
-      <c r="A1" s="126" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
+      <c r="A1" s="145" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
@@ -6587,14 +9504,14 @@
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
-      <c r="L2" s="127" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="129"/>
+      <c r="L2" s="146" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="148"/>
       <c r="R2" s="26"/>
       <c r="S2" s="26"/>
       <c r="T2" s="26"/>
@@ -6639,14 +9556,14 @@
       <c r="BG2" s="26"/>
     </row>
     <row r="3" spans="1:59" ht="18.75">
-      <c r="A3" s="127" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="128"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="129"/>
+      <c r="A3" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="148"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
@@ -6703,7 +9620,7 @@
     </row>
     <row r="4" spans="1:59">
       <c r="A4" s="84" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B4" s="80"/>
       <c r="C4" s="80"/>
@@ -6716,7 +9633,7 @@
       <c r="J4" s="26"/>
       <c r="K4" s="26"/>
       <c r="L4" s="84" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M4" s="80"/>
       <c r="N4" s="80"/>
@@ -6733,19 +9650,19 @@
       <c r="Y4" s="81"/>
       <c r="Z4" s="81">
         <f t="shared" ref="Z4:AC4" si="0">$B$22</f>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="AA4" s="81">
         <f t="shared" si="0"/>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="AB4" s="81">
         <f t="shared" si="0"/>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="AC4" s="81">
         <f t="shared" si="0"/>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="AD4" s="26"/>
       <c r="AE4" s="26"/>
@@ -6780,7 +9697,7 @@
     </row>
     <row r="5" spans="1:59">
       <c r="A5" s="60" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B5" s="21" cm="1">
         <f t="array" ref="B5">currentyear</f>
@@ -6808,7 +9725,7 @@
       <c r="J5" s="26"/>
       <c r="K5" s="26"/>
       <c r="L5" s="60" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M5" s="21" cm="1">
         <f t="array" ref="M5">currentyear</f>
@@ -6875,7 +9792,7 @@
     </row>
     <row r="6" spans="1:59">
       <c r="A6" s="21" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B6" s="57" cm="1">
         <f t="array" ref="B6">num_accountsRS1</f>
@@ -6903,7 +9820,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="26"/>
       <c r="L6" s="21" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M6" s="57" cm="1">
         <f t="array" ref="M6">num_accountsRS1</f>
@@ -6970,7 +9887,7 @@
     </row>
     <row r="7" spans="1:59">
       <c r="A7" s="21" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B7" s="54" cm="1">
         <f t="array" ref="B7:F7">base_chargeRS1 * 12 * RS1_num_accounts</f>
@@ -6994,7 +9911,7 @@
       <c r="J7" s="26"/>
       <c r="K7" s="26"/>
       <c r="L7" s="56" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M7" s="90" cm="1">
         <f t="array" ref="M7:Q7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
@@ -7057,7 +9974,7 @@
     </row>
     <row r="8" spans="1:59">
       <c r="A8" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B8" s="59" cm="1">
         <f t="array" ref="B8:B10">RS1_block_consumption2026 * RS1_vrates2026 *12</f>
@@ -7085,7 +10002,7 @@
       <c r="J8" s="26"/>
       <c r="K8" s="26"/>
       <c r="L8" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M8" s="59" cm="1">
         <f t="array" ref="M8:M10">RS1_block_consumption2026 * RS1_vrates2026 *12</f>
@@ -7152,7 +10069,7 @@
     </row>
     <row r="9" spans="1:59">
       <c r="A9" s="21" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B9" s="59">
         <v>92610</v>
@@ -7175,7 +10092,7 @@
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
       <c r="L9" s="21" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M9" s="59">
         <v>92610</v>
@@ -7237,7 +10154,7 @@
     </row>
     <row r="10" spans="1:59">
       <c r="A10" s="21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B10" s="59">
         <v>13230</v>
@@ -7260,7 +10177,7 @@
       <c r="J10" s="26"/>
       <c r="K10" s="26"/>
       <c r="L10" s="63" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M10" s="66">
         <v>13230</v>
@@ -7322,7 +10239,7 @@
     </row>
     <row r="11" spans="1:59">
       <c r="A11" s="86" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B11" s="87">
         <f>SUM(B7:B10)</f>
@@ -7350,7 +10267,7 @@
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="L11" s="44" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M11" s="62">
         <f>SUM(M7:M10)</f>
@@ -7478,7 +10395,7 @@
     </row>
     <row r="13" spans="1:59">
       <c r="A13" s="88" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -7491,7 +10408,7 @@
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
       <c r="L13" s="42" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -7543,7 +10460,7 @@
     </row>
     <row r="14" spans="1:59">
       <c r="A14" s="21" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B14" s="21" cm="1">
         <f t="array" ref="B14">currentyear</f>
@@ -7571,7 +10488,7 @@
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M14" s="21" cm="1">
         <f t="array" ref="M14">currentyear</f>
@@ -7638,7 +10555,7 @@
     </row>
     <row r="15" spans="1:59">
       <c r="A15" s="56" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B15" s="57" cm="1">
         <f t="array" ref="B15">num_accountsRS2</f>
@@ -7666,7 +10583,7 @@
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
       <c r="L15" s="56" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M15" s="57" cm="1">
         <f t="array" ref="M15">num_accountsRS2</f>
@@ -7733,23 +10650,23 @@
     </row>
     <row r="16" spans="1:59">
       <c r="A16" s="56" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B16" s="90" cm="1">
         <f t="array" ref="B16:F16">base_chargeRS2 * 12 * RS2_num_accounts</f>
-        <v>231000</v>
+        <v>250800</v>
       </c>
       <c r="C16" s="91">
-        <v>233520</v>
+        <v>286896</v>
       </c>
       <c r="D16" s="91">
-        <v>236040</v>
+        <v>289992</v>
       </c>
       <c r="E16" s="91">
-        <v>238560</v>
+        <v>293088</v>
       </c>
       <c r="F16" s="91">
-        <v>241080</v>
+        <v>296184</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
@@ -7757,23 +10674,23 @@
       <c r="J16" s="26"/>
       <c r="K16" s="26"/>
       <c r="L16" s="21" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M16" s="54" cm="1">
         <f t="array" ref="M16:Q16">RS2_base_charge2026 * 12 * RS2_num_accounts</f>
-        <v>231000</v>
+        <v>250800</v>
       </c>
       <c r="N16" s="51">
-        <v>233520</v>
+        <v>253536</v>
       </c>
       <c r="O16" s="51">
-        <v>236040</v>
+        <v>256272</v>
       </c>
       <c r="P16" s="51">
-        <v>238560</v>
+        <v>259008</v>
       </c>
       <c r="Q16" s="51">
-        <v>241080</v>
+        <v>261744</v>
       </c>
       <c r="R16" s="26"/>
       <c r="S16" s="26"/>
@@ -7820,27 +10737,27 @@
     </row>
     <row r="17" spans="1:59">
       <c r="A17" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B17" s="55" cm="1">
         <f t="array" ref="B17:B19">RS2_block_consumption2026 * RS2_vrates2026 *12</f>
-        <v>165000</v>
+        <v>181500</v>
       </c>
       <c r="C17" s="52" cm="1">
         <f t="array" ref="C17:C19">RS2_block_consumption2027 * RS2_vrates2027 *12</f>
-        <v>166650</v>
+        <v>183315</v>
       </c>
       <c r="D17" s="52" cm="1">
         <f t="array" ref="D17:D19">RS2_block_consumption2028 * RS2_vrates2028 *12</f>
-        <v>168330</v>
+        <v>185163</v>
       </c>
       <c r="E17" s="52" cm="1">
         <f t="array" ref="E17:E19">RS2_block_consumption2029 * RS2_vrates2029 *12</f>
-        <v>170010</v>
+        <v>187011</v>
       </c>
       <c r="F17" s="52" cm="1">
         <f t="array" ref="F17:F19">RS2_block_consumption2030 * RS2_vrates2030 *12</f>
-        <v>171720</v>
+        <v>188892</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
@@ -7848,27 +10765,27 @@
       <c r="J17" s="26"/>
       <c r="K17" s="26"/>
       <c r="L17" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M17" s="55" cm="1">
         <f t="array" ref="M17:M19">RS2_block_consumption2026 * RS2_vrates2026 *12</f>
-        <v>165000</v>
+        <v>181500</v>
       </c>
       <c r="N17" s="55" cm="1">
         <f t="array" ref="N17:N19">RS2_block_consumption2027 * RS2_vrates2026 *12</f>
-        <v>166650</v>
+        <v>183315</v>
       </c>
       <c r="O17" s="55" cm="1">
         <f t="array" ref="O17:O19">RS2_block_consumption2028 * RS2_vrates2026 *12</f>
-        <v>168330</v>
+        <v>185163</v>
       </c>
       <c r="P17" s="55" cm="1">
         <f t="array" ref="P17:P19">RS2_block_consumption2029 * RS2_vrates2026 *12</f>
-        <v>170010</v>
+        <v>187011</v>
       </c>
       <c r="Q17" s="55" cm="1">
         <f t="array" ref="Q17:Q19">RS2_block_consumption2030 * RS2_vrates2026 *12</f>
-        <v>171720</v>
+        <v>188892</v>
       </c>
       <c r="R17" s="26"/>
       <c r="S17" s="26"/>
@@ -7915,22 +10832,22 @@
     </row>
     <row r="18" spans="1:59">
       <c r="A18" s="21" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B18" s="55">
-        <v>150000</v>
+        <v>165000</v>
       </c>
       <c r="C18" s="52">
-        <v>151500</v>
+        <v>166650</v>
       </c>
       <c r="D18" s="52">
-        <v>153030</v>
+        <v>168333</v>
       </c>
       <c r="E18" s="52">
-        <v>154560</v>
+        <v>170016</v>
       </c>
       <c r="F18" s="52">
-        <v>156120</v>
+        <v>171732</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
@@ -7938,22 +10855,22 @@
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
       <c r="L18" s="21" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M18" s="55">
-        <v>150000</v>
+        <v>165000</v>
       </c>
       <c r="N18" s="55">
-        <v>151500</v>
+        <v>166650</v>
       </c>
       <c r="O18" s="55">
-        <v>153030</v>
+        <v>168333</v>
       </c>
       <c r="P18" s="55">
-        <v>154560</v>
+        <v>170016</v>
       </c>
       <c r="Q18" s="55">
-        <v>156120</v>
+        <v>171732</v>
       </c>
       <c r="R18" s="26"/>
       <c r="S18" s="26"/>
@@ -8000,22 +10917,22 @@
     </row>
     <row r="19" spans="1:59">
       <c r="A19" s="63" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B19" s="64">
-        <v>29850</v>
+        <v>32835</v>
       </c>
       <c r="C19" s="65">
-        <v>30150</v>
+        <v>33165</v>
       </c>
       <c r="D19" s="65">
-        <v>30450</v>
+        <v>33495</v>
       </c>
       <c r="E19" s="65">
-        <v>30750</v>
+        <v>33825</v>
       </c>
       <c r="F19" s="65">
-        <v>31050</v>
+        <v>34155</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
@@ -8023,22 +10940,22 @@
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
       <c r="L19" s="63" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M19" s="64">
-        <v>29850</v>
+        <v>32835</v>
       </c>
       <c r="N19" s="64">
-        <v>30150</v>
+        <v>33165</v>
       </c>
       <c r="O19" s="64">
-        <v>30450</v>
+        <v>33495</v>
       </c>
       <c r="P19" s="64">
-        <v>30750</v>
+        <v>33825</v>
       </c>
       <c r="Q19" s="64">
-        <v>31050</v>
+        <v>34155</v>
       </c>
       <c r="R19" s="26"/>
       <c r="S19" s="26"/>
@@ -8085,27 +11002,27 @@
     </row>
     <row r="20" spans="1:59">
       <c r="A20" s="44" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B20" s="62">
         <f>SUM(B16:B19)</f>
-        <v>575850</v>
+        <v>630135</v>
       </c>
       <c r="C20" s="62">
         <f t="shared" ref="C20:F20" si="10">SUM(C16:C19)</f>
-        <v>581820</v>
+        <v>670026</v>
       </c>
       <c r="D20" s="62">
         <f t="shared" si="10"/>
-        <v>587850</v>
+        <v>676983</v>
       </c>
       <c r="E20" s="62">
         <f t="shared" si="10"/>
-        <v>593880</v>
+        <v>683940</v>
       </c>
       <c r="F20" s="62">
         <f t="shared" si="10"/>
-        <v>599970</v>
+        <v>690963</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
@@ -8113,27 +11030,27 @@
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
       <c r="L20" s="44" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M20" s="62">
         <f>SUM(M16:M19)</f>
-        <v>575850</v>
+        <v>630135</v>
       </c>
       <c r="N20" s="62">
         <f t="shared" ref="N20" si="11">SUM(N16:N19)</f>
-        <v>581820</v>
+        <v>636666</v>
       </c>
       <c r="O20" s="62">
         <f t="shared" ref="O20" si="12">SUM(O16:O19)</f>
-        <v>587850</v>
+        <v>643263</v>
       </c>
       <c r="P20" s="62">
         <f t="shared" ref="P20" si="13">SUM(P16:P19)</f>
-        <v>593880</v>
+        <v>649860</v>
       </c>
       <c r="Q20" s="62">
         <f t="shared" ref="Q20" si="14">SUM(Q16:Q19)</f>
-        <v>599970</v>
+        <v>656523</v>
       </c>
       <c r="R20" s="26"/>
       <c r="S20" s="26"/>
@@ -8241,27 +11158,27 @@
     </row>
     <row r="22" spans="1:59" ht="15.75">
       <c r="A22" s="49" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B22" s="61">
         <f>SUM(B20+B11)</f>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="C22" s="61">
         <f t="shared" ref="C22:F22" si="15">SUM(C20+C11)</f>
-        <v>1673640</v>
+        <v>1761846</v>
       </c>
       <c r="D22" s="61">
         <f t="shared" si="15"/>
-        <v>1746384</v>
+        <v>1835517</v>
       </c>
       <c r="E22" s="61">
         <f t="shared" si="15"/>
-        <v>1764054</v>
+        <v>1854114</v>
       </c>
       <c r="F22" s="61">
         <f t="shared" si="15"/>
-        <v>1836894</v>
+        <v>1927887</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
@@ -8269,27 +11186,27 @@
       <c r="J22" s="26"/>
       <c r="K22" s="26"/>
       <c r="L22" s="49" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M22" s="61">
         <f>SUM(M20+M11)</f>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="N22" s="61">
         <f t="shared" ref="N22:Q22" si="16">SUM(N20+N11)</f>
-        <v>1582026</v>
+        <v>1636872</v>
       </c>
       <c r="O22" s="61">
         <f t="shared" si="16"/>
-        <v>1597965</v>
+        <v>1653378</v>
       </c>
       <c r="P22" s="61">
         <f t="shared" si="16"/>
-        <v>1614150</v>
+        <v>1670130</v>
       </c>
       <c r="Q22" s="61">
         <f t="shared" si="16"/>
-        <v>1630437</v>
+        <v>1686990</v>
       </c>
       <c r="R22" s="26"/>
       <c r="S22" s="26"/>
@@ -8863,15 +11780,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="126" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
+      <c r="A1" s="145" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
@@ -8903,14 +11820,14 @@
       <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="130" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="132"/>
+      <c r="A3" s="149" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="151"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
@@ -8925,7 +11842,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B4" s="80">
         <v>2026</v>
@@ -8960,7 +11877,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B5" s="47" cm="1">
         <f t="array" ref="B5:B11">expenses_value</f>
@@ -8996,26 +11913,26 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B6" s="47">
-        <v>105000</v>
+        <v>135000</v>
       </c>
       <c r="C6" s="43" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+inflation_rate),0)</f>
-        <v>108150</v>
+        <v>139050</v>
       </c>
       <c r="D6" s="43" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+inflation_rate),0)</f>
-        <v>111395</v>
+        <v>143222</v>
       </c>
       <c r="E6" s="43" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+inflation_rate),0)</f>
-        <v>114737</v>
+        <v>147519</v>
       </c>
       <c r="F6" s="43" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+inflation_rate),0)</f>
-        <v>118179</v>
+        <v>151945</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
@@ -9031,26 +11948,26 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="74" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B7" s="47">
-        <v>50000</v>
+        <v>64000</v>
       </c>
       <c r="C7" s="43" cm="1">
         <f t="array" ref="C7">ROUND(B7*(1+inflation_rate),0)</f>
-        <v>51500</v>
+        <v>65920</v>
       </c>
       <c r="D7" s="43" cm="1">
         <f t="array" ref="D7">ROUND(C7*(1+inflation_rate),0)</f>
-        <v>53045</v>
+        <v>67898</v>
       </c>
       <c r="E7" s="43" cm="1">
         <f t="array" ref="E7">ROUND(D7*(1+inflation_rate),0)</f>
-        <v>54636</v>
+        <v>69935</v>
       </c>
       <c r="F7" s="43" cm="1">
         <f t="array" ref="F7">ROUND(E7*(1+inflation_rate),0)</f>
-        <v>56275</v>
+        <v>72033</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
@@ -9066,26 +11983,26 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B8" s="92">
-        <v>98000</v>
+        <v>130500</v>
       </c>
       <c r="C8" s="93" cm="1">
         <f t="array" ref="C8">ROUND(B8*(1+inflation_rate),0)</f>
-        <v>100940</v>
+        <v>134415</v>
       </c>
       <c r="D8" s="93" cm="1">
         <f t="array" ref="D8">ROUND(C8*(1+inflation_rate),0)</f>
-        <v>103968</v>
+        <v>138447</v>
       </c>
       <c r="E8" s="93" cm="1">
         <f t="array" ref="E8">ROUND(D8*(1+inflation_rate),0)</f>
-        <v>107087</v>
+        <v>142600</v>
       </c>
       <c r="F8" s="93" cm="1">
         <f t="array" ref="F8">ROUND(E8*(1+inflation_rate),0)</f>
-        <v>110300</v>
+        <v>146878</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
@@ -9101,7 +12018,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B9" s="47">
         <v>52000</v>
@@ -9136,7 +12053,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B10" s="47">
         <v>250000</v>
@@ -9171,7 +12088,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B11" s="48">
         <v>144000</v>
@@ -9206,27 +12123,27 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="44" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B12" s="45">
         <f>SUM(B5:B11)</f>
-        <v>1424000</v>
+        <v>1500500</v>
       </c>
       <c r="C12" s="45">
         <f t="shared" ref="C12:F12" si="1">SUM(C5:C11)</f>
-        <v>1466720</v>
+        <v>1545515</v>
       </c>
       <c r="D12" s="45">
         <f t="shared" si="1"/>
-        <v>1510723</v>
+        <v>1591882</v>
       </c>
       <c r="E12" s="45">
         <f t="shared" si="1"/>
-        <v>1556045</v>
+        <v>1639639</v>
       </c>
       <c r="F12" s="45">
         <f t="shared" si="1"/>
-        <v>1602727</v>
+        <v>1688829</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
@@ -9260,14 +12177,14 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="1:17" ht="15.75">
-      <c r="A14" s="130" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="131"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="132"/>
+      <c r="A14" s="149" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="151"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -9282,7 +12199,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="94" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B15" s="80">
         <v>2026</v>
@@ -9317,7 +12234,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="95" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B16" s="96" cm="1">
         <f t="array" ref="B16:F16">debt_service_values</f>
@@ -9368,30 +12285,30 @@
     </row>
     <row r="18" spans="1:17" ht="15.75">
       <c r="A18" s="49" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B18" s="50">
         <f>SUM(B16+B12)</f>
-        <v>1589000</v>
+        <v>1665500</v>
       </c>
       <c r="C18" s="50">
         <f t="shared" ref="C18:F18" si="2">SUM(C16+C12)</f>
-        <v>1631720</v>
+        <v>1710515</v>
       </c>
       <c r="D18" s="50">
         <f t="shared" si="2"/>
-        <v>1685723</v>
+        <v>1766882</v>
       </c>
       <c r="E18" s="50">
         <f t="shared" si="2"/>
-        <v>1731045</v>
+        <v>1814639</v>
       </c>
       <c r="F18" s="50">
         <f t="shared" si="2"/>
-        <v>1777727</v>
+        <v>1863829</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
@@ -9702,26 +12619,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24CF71A9-E3E6-4702-9C2B-B190BAB0F6FB}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75">
-      <c r="A1" s="126" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
+    <row r="1" spans="1:28" ht="18.75">
+      <c r="A1" s="145" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -9731,15 +12650,15 @@
       <c r="O1" s="26"/>
       <c r="P1" s="26"/>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
-      <c r="A2" s="105"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
+    <row r="2" spans="1:28" ht="18.75">
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
@@ -9749,9 +12668,9 @@
       <c r="O2" s="26"/>
       <c r="P2" s="26"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:28">
       <c r="A3" s="60" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B3" s="21" cm="1">
         <f t="array" ref="B3">currentyear</f>
@@ -9784,25 +12703,25 @@
       <c r="O3" s="26"/>
       <c r="P3" s="26"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:28">
       <c r="A4" s="71" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B4" s="69" cm="1">
         <f t="array" ref="B4:F4">total_operating_revenue_row</f>
-        <v>1566210</v>
+        <v>1620495</v>
       </c>
       <c r="C4" s="69">
-        <v>1673640</v>
+        <v>1761846</v>
       </c>
       <c r="D4" s="69">
-        <v>1746384</v>
+        <v>1835517</v>
       </c>
       <c r="E4" s="69">
-        <v>1764054</v>
+        <v>1854114</v>
       </c>
       <c r="F4" s="70">
-        <v>1836894</v>
+        <v>1927887</v>
       </c>
       <c r="G4" s="26"/>
       <c r="H4" s="26"/>
@@ -9815,25 +12734,25 @@
       <c r="O4" s="26"/>
       <c r="P4" s="26"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:28">
       <c r="A5" s="71" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B5" s="69" cm="1">
         <f t="array" ref="B5:F5">total_cost_of_service_row</f>
-        <v>1589000</v>
+        <v>1665500</v>
       </c>
       <c r="C5" s="69">
-        <v>1631720</v>
+        <v>1710515</v>
       </c>
       <c r="D5" s="69">
-        <v>1685723</v>
+        <v>1766882</v>
       </c>
       <c r="E5" s="69">
-        <v>1731045</v>
+        <v>1814639</v>
       </c>
       <c r="F5" s="70">
-        <v>1777727</v>
+        <v>1863829</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
@@ -9845,30 +12764,50 @@
       <c r="N5" s="26"/>
       <c r="O5" s="26"/>
       <c r="P5" s="26"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="X5" s="72" cm="1">
+        <f t="array" ref="X5">target_dscr</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Y5" s="72" cm="1">
+        <f t="array" ref="Y5">target_dscr</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Z5" s="72" cm="1">
+        <f t="array" ref="Z5">target_dscr</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AA5" s="72" cm="1">
+        <f t="array" ref="AA5">target_dscr</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AB5" s="72" cm="1">
+        <f t="array" ref="AB5">target_dscr</f>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" s="71" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B6" s="69">
         <f>B4-B5</f>
-        <v>-22790</v>
+        <v>-45005</v>
       </c>
       <c r="C6" s="69">
         <f t="shared" ref="C6:F6" si="1">C4-C5</f>
-        <v>41920</v>
+        <v>51331</v>
       </c>
       <c r="D6" s="69">
         <f t="shared" si="1"/>
-        <v>60661</v>
+        <v>68635</v>
       </c>
       <c r="E6" s="69">
         <f t="shared" si="1"/>
-        <v>33009</v>
+        <v>39475</v>
       </c>
       <c r="F6" s="70">
         <f t="shared" si="1"/>
-        <v>59167</v>
+        <v>64058</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
@@ -9881,29 +12820,29 @@
       <c r="O6" s="26"/>
       <c r="P6" s="26"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:28">
       <c r="A7" s="77" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B7" s="78">
         <f>B6</f>
-        <v>-22790</v>
+        <v>-45005</v>
       </c>
       <c r="C7" s="78">
         <f>B7+C6</f>
-        <v>19130</v>
+        <v>6326</v>
       </c>
       <c r="D7" s="78">
         <f t="shared" ref="D7:F7" si="2">C7+D6</f>
-        <v>79791</v>
+        <v>74961</v>
       </c>
       <c r="E7" s="78">
         <f t="shared" si="2"/>
-        <v>112800</v>
+        <v>114436</v>
       </c>
       <c r="F7" s="79">
         <f t="shared" si="2"/>
-        <v>171967</v>
+        <v>178494</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
@@ -9916,7 +12855,7 @@
       <c r="O7" s="26"/>
       <c r="P7" s="26"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:28">
       <c r="A8" s="26"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -9934,9 +12873,9 @@
       <c r="O8" s="26"/>
       <c r="P8" s="26"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:28">
       <c r="A9" s="60" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B9" s="21" cm="1">
         <f t="array" ref="B9">currentyear</f>
@@ -9969,25 +12908,25 @@
       <c r="O9" s="26"/>
       <c r="P9" s="26"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:28">
       <c r="A10" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B10" s="69" cm="1">
         <f t="array" ref="B10:F10">total_operating_revenue_row - total_operating_expenses</f>
-        <v>142210</v>
+        <v>119995</v>
       </c>
       <c r="C10" s="69">
-        <v>206920</v>
+        <v>216331</v>
       </c>
       <c r="D10" s="69">
-        <v>235661</v>
+        <v>243635</v>
       </c>
       <c r="E10" s="69">
-        <v>208009</v>
+        <v>214475</v>
       </c>
       <c r="F10" s="70">
-        <v>234167</v>
+        <v>239058</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
@@ -10000,9 +12939,9 @@
       <c r="O10" s="26"/>
       <c r="P10" s="26"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:28">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B11" s="69" cm="1">
         <f t="array" ref="B11:F11">debt_service_values</f>
@@ -10031,29 +12970,29 @@
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
     </row>
-    <row r="12" spans="1:16" ht="21" customHeight="1">
+    <row r="12" spans="1:28" ht="21" customHeight="1">
       <c r="A12" s="71" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B12" s="72">
         <f>B10/B11</f>
-        <v>0.86187878787878791</v>
+        <v>0.72724242424242425</v>
       </c>
       <c r="C12" s="72">
         <f t="shared" ref="C12:F12" si="4">C10/C11</f>
-        <v>1.2540606060606061</v>
+        <v>1.3110969696969696</v>
       </c>
       <c r="D12" s="72">
         <f t="shared" si="4"/>
-        <v>1.3466342857142857</v>
+        <v>1.3922000000000001</v>
       </c>
       <c r="E12" s="72">
         <f t="shared" si="4"/>
-        <v>1.1886228571428572</v>
+        <v>1.2255714285714285</v>
       </c>
       <c r="F12" s="73">
         <f t="shared" si="4"/>
-        <v>1.3380971428571429</v>
+        <v>1.3660457142857143</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
@@ -10066,9 +13005,9 @@
       <c r="O12" s="26"/>
       <c r="P12" s="26"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:28">
       <c r="A13" s="74" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B13" s="75" t="str" cm="1">
         <f t="array" ref="B13">IF(B12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
@@ -10101,7 +13040,7 @@
       <c r="O13" s="26"/>
       <c r="P13" s="26"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:28">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
@@ -10119,20 +13058,22 @@
       <c r="O14" s="26"/>
       <c r="P14" s="26"/>
     </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="26"/>
+    <row r="15" spans="1:28">
+      <c r="A15" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="114" t="s">
+        <v>75</v>
+      </c>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
@@ -10145,24 +13086,27 @@
       <c r="O15" s="26"/>
       <c r="P15" s="26"/>
     </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="1" t="str" cm="1">
+    <row r="16" spans="1:28">
+      <c r="A16" s="21" t="str" cm="1">
         <f t="array" ref="A16">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="B16" s="113" cm="1">
+      <c r="B16" s="51" cm="1">
         <f t="array" ref="B16">RS1_base_charge2026</f>
         <v>17</v>
       </c>
-      <c r="C16" s="113" cm="1">
+      <c r="C16" s="51" cm="1">
         <f t="array" ref="C16">ROUND(SUM(RS1_block_consumption2026 * RS1_vrates2026)/num_accountsRS1,2)</f>
         <v>15.75</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="51">
         <f>B16+C16</f>
         <v>32.75</v>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="54" cm="1">
+        <f t="array" ref="E16">((D16*num_accountsRS1) + (D17*num_accountsRS2)) / num_accounts</f>
+        <v>43.98827361563518</v>
+      </c>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
@@ -10176,20 +13120,21 @@
       <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="1" t="str" cm="1">
+      <c r="A17" s="21" t="str" cm="1">
         <f t="array" ref="A17">rate_structure_2</f>
         <v>Commerical, inside</v>
       </c>
-      <c r="B17" s="113">
-        <v>35</v>
-      </c>
-      <c r="C17" s="113" cm="1">
+      <c r="B17" s="51" cm="1">
+        <f t="array" ref="B17">RS2_base_charge2026</f>
+        <v>38</v>
+      </c>
+      <c r="C17" s="51" cm="1">
         <f t="array" ref="C17">ROUND(SUM(RS2_block_consumption2026 * RS2_vrates2026)/num_accountsRS2,2)</f>
-        <v>52.25</v>
-      </c>
-      <c r="D17" s="113">
+        <v>57.48</v>
+      </c>
+      <c r="D17" s="51">
         <f>B17+C17</f>
-        <v>87.25</v>
+        <v>95.47999999999999</v>
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
@@ -10223,19 +13168,21 @@
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="26"/>
+      <c r="A19" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="114" t="s">
+        <v>75</v>
+      </c>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
@@ -10249,23 +13196,26 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="1" t="str" cm="1">
+      <c r="A20" s="21" t="str" cm="1">
         <f t="array" ref="A20">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="B20" s="113" cm="1">
+      <c r="B20" s="51" cm="1">
         <f t="array" ref="B20">base_chargeRS12027</f>
         <v>20</v>
       </c>
-      <c r="C20" s="113" cm="1">
+      <c r="C20" s="51" cm="1">
         <f t="array" ref="C20">ROUND(SUM(RS1_block_consumption2026 * RS1_vrates2027)/num_accountsRS1,2)</f>
         <v>15.75</v>
       </c>
-      <c r="D20" s="113">
+      <c r="D20" s="51">
         <f>B20+C20</f>
         <v>35.75</v>
       </c>
-      <c r="E20" s="26"/>
+      <c r="E20" s="54" cm="1">
+        <f t="array" ref="E20">((D20*num_accountsRS1) + (D21*num_accountsRS2))/num_accounts</f>
+        <v>47.346579804560264</v>
+      </c>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
@@ -10279,20 +13229,21 @@
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="1" t="str" cm="1">
+      <c r="A21" s="21" t="str" cm="1">
         <f t="array" ref="A21">rate_structure_2</f>
         <v>Commerical, inside</v>
       </c>
-      <c r="B21" s="113">
-        <v>35</v>
-      </c>
-      <c r="C21" s="113" cm="1">
+      <c r="B21" s="51" cm="1">
+        <f t="array" ref="B21">RS2_base_charge2027</f>
+        <v>43</v>
+      </c>
+      <c r="C21" s="51" cm="1">
         <f t="array" ref="C21">ROUND(SUM(RS2_block_consumption2026 * RS2_vrates2027)/num_accountsRS2,2)</f>
-        <v>52.25</v>
-      </c>
-      <c r="D21" s="113">
+        <v>57.48</v>
+      </c>
+      <c r="D21" s="51">
         <f>B21+C21</f>
-        <v>87.25</v>
+        <v>100.47999999999999</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0F186C2-6245-4576-848B-F7CCF4A80083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{965B75D7-33A8-42D1-9A7D-E5E2CBB8AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="5" r:id="rId1"/>
@@ -292,10 +292,10 @@
     <t>Revenue Projections | 2026 - 2030</t>
   </si>
   <si>
-    <t>Using Existing Rates</t>
+    <t>Using New Rates Starting in 2027</t>
   </si>
   <si>
-    <t>Using New Rates Starting in 2027</t>
+    <t>Using Existing Rates</t>
   </si>
   <si>
     <t>Number of Accounts</t>
@@ -875,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1002,15 +1002,6 @@
     </xf>
     <xf numFmtId="6" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1158,6 +1149,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1348,7 +1340,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Revenue_Model!M22:Q22</c:f>
+              <c:f>Revenue_Model!J22:N22</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2757,7 +2749,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Rate_Sufficiency_Analysis!X5:AB5</c:f>
+              <c:f>Rate_Sufficiency_Analysis!AL5:AP5</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -4997,16 +4989,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30.75" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -5021,13 +5013,13 @@
     </row>
     <row r="2" spans="1:19" ht="21.75" customHeight="1">
       <c r="A2" s="26"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
@@ -5041,18 +5033,18 @@
       <c r="S2" s="26"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="B3" s="121" cm="1">
+      <c r="B3" s="118" cm="1">
         <f t="array" ref="B3">current_monthly_bill</f>
         <v>43.98827361563518</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="127" cm="1">
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="124" cm="1">
         <f t="array" ref="E3">proposed_monthly_bill</f>
         <v>47.346579804560264</v>
       </c>
-      <c r="F3" s="127"/>
-      <c r="G3" s="128"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="125"/>
       <c r="M3" s="26"/>
       <c r="N3" s="26"/>
       <c r="O3" s="26"/>
@@ -5062,12 +5054,12 @@
       <c r="S3" s="26"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="130"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
       <c r="M4" s="26"/>
       <c r="N4" s="26"/>
       <c r="O4" s="26"/>
@@ -5077,12 +5069,12 @@
       <c r="S4" s="26"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="B5" s="123"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="130"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="127"/>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
       <c r="O5" s="26"/>
@@ -5092,16 +5084,16 @@
       <c r="S5" s="26"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="131" t="s">
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="131"/>
-      <c r="G6" s="132"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="129"/>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
       <c r="O6" s="26"/>
@@ -5112,18 +5104,18 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="26"/>
-      <c r="B7" s="133" cm="1">
+      <c r="B7" s="130" cm="1">
         <f t="array" ref="B7">current_dscr</f>
         <v>0.72724242424242425</v>
       </c>
-      <c r="C7" s="115"/>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115" cm="1">
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112" cm="1">
         <f t="array" ref="E7">proposed_dscr</f>
         <v>1.3110969696969696</v>
       </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="116"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="113"/>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
@@ -5139,12 +5131,12 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="26"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="116"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="113"/>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
@@ -5160,12 +5152,12 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="26"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="116"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="113"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
@@ -5180,16 +5172,16 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="26"/>
-      <c r="B10" s="117" t="s">
+      <c r="B10" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118" t="s">
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="118"/>
-      <c r="G10" s="119"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="116"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
@@ -5603,226 +5595,226 @@
       <c r="S29" s="26"/>
     </row>
     <row r="30" spans="1:19" ht="15" customHeight="1">
-      <c r="A30" s="152" t="s">
+      <c r="A30" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="153"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="153"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="153"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="153"/>
-      <c r="P30" s="153"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="150"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="150"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="150"/>
+      <c r="N30" s="150"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="150"/>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="153"/>
-      <c r="B31" s="153"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="153"/>
-      <c r="I31" s="153"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="153"/>
-      <c r="N31" s="153"/>
-      <c r="O31" s="153"/>
-      <c r="P31" s="153"/>
+      <c r="A31" s="150"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="150"/>
+      <c r="D31" s="150"/>
+      <c r="E31" s="150"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="150"/>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="153"/>
-      <c r="B32" s="153"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="153"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="153"/>
-      <c r="I32" s="153"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="153"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="153"/>
-      <c r="N32" s="153"/>
-      <c r="O32" s="153"/>
-      <c r="P32" s="153"/>
+      <c r="A32" s="150"/>
+      <c r="B32" s="150"/>
+      <c r="C32" s="150"/>
+      <c r="D32" s="150"/>
+      <c r="E32" s="150"/>
+      <c r="F32" s="150"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
+      <c r="K32" s="150"/>
+      <c r="L32" s="150"/>
+      <c r="M32" s="150"/>
+      <c r="N32" s="150"/>
+      <c r="O32" s="150"/>
+      <c r="P32" s="150"/>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="153"/>
-      <c r="B33" s="153"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="153"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="153"/>
-      <c r="N33" s="153"/>
-      <c r="O33" s="153"/>
-      <c r="P33" s="153"/>
+      <c r="A33" s="150"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="150"/>
+      <c r="D33" s="150"/>
+      <c r="E33" s="150"/>
+      <c r="F33" s="150"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="150"/>
+      <c r="L33" s="150"/>
+      <c r="M33" s="150"/>
+      <c r="N33" s="150"/>
+      <c r="O33" s="150"/>
+      <c r="P33" s="150"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="154" t="s">
+      <c r="A34" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="155"/>
-      <c r="C34" s="155"/>
-      <c r="D34" s="155"/>
-      <c r="E34" s="155"/>
-      <c r="F34" s="155"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="155"/>
-      <c r="J34" s="155"/>
-      <c r="K34" s="155"/>
-      <c r="L34" s="155"/>
-      <c r="M34" s="155"/>
-      <c r="N34" s="155"/>
-      <c r="O34" s="155"/>
-      <c r="P34" s="155"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="152"/>
+      <c r="D34" s="152"/>
+      <c r="E34" s="152"/>
+      <c r="F34" s="152"/>
+      <c r="G34" s="152"/>
+      <c r="H34" s="152"/>
+      <c r="I34" s="152"/>
+      <c r="J34" s="152"/>
+      <c r="K34" s="152"/>
+      <c r="L34" s="152"/>
+      <c r="M34" s="152"/>
+      <c r="N34" s="152"/>
+      <c r="O34" s="152"/>
+      <c r="P34" s="152"/>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="155"/>
-      <c r="B35" s="155"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="155"/>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="155"/>
-      <c r="J35" s="155"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="155"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-      <c r="O35" s="155"/>
-      <c r="P35" s="155"/>
+      <c r="A35" s="152"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="152"/>
+      <c r="I35" s="152"/>
+      <c r="J35" s="152"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="152"/>
+      <c r="N35" s="152"/>
+      <c r="O35" s="152"/>
+      <c r="P35" s="152"/>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="155"/>
-      <c r="B36" s="155"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
-      <c r="F36" s="155"/>
-      <c r="G36" s="155"/>
-      <c r="H36" s="155"/>
-      <c r="I36" s="155"/>
-      <c r="J36" s="155"/>
-      <c r="K36" s="155"/>
-      <c r="L36" s="155"/>
-      <c r="M36" s="155"/>
-      <c r="N36" s="155"/>
-      <c r="O36" s="155"/>
-      <c r="P36" s="155"/>
+      <c r="A36" s="152"/>
+      <c r="B36" s="152"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="152"/>
+      <c r="H36" s="152"/>
+      <c r="I36" s="152"/>
+      <c r="J36" s="152"/>
+      <c r="K36" s="152"/>
+      <c r="L36" s="152"/>
+      <c r="M36" s="152"/>
+      <c r="N36" s="152"/>
+      <c r="O36" s="152"/>
+      <c r="P36" s="152"/>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="155"/>
-      <c r="B37" s="155"/>
-      <c r="C37" s="155"/>
-      <c r="D37" s="155"/>
-      <c r="E37" s="155"/>
-      <c r="F37" s="155"/>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
-      <c r="I37" s="155"/>
-      <c r="J37" s="155"/>
-      <c r="K37" s="155"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-      <c r="O37" s="155"/>
-      <c r="P37" s="155"/>
+      <c r="A37" s="152"/>
+      <c r="B37" s="152"/>
+      <c r="C37" s="152"/>
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="152"/>
+      <c r="H37" s="152"/>
+      <c r="I37" s="152"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="152"/>
+      <c r="L37" s="152"/>
+      <c r="M37" s="152"/>
+      <c r="N37" s="152"/>
+      <c r="O37" s="152"/>
+      <c r="P37" s="152"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="155" t="s">
+      <c r="A38" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="155"/>
-      <c r="C38" s="155"/>
-      <c r="D38" s="155"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="155"/>
-      <c r="G38" s="155"/>
-      <c r="H38" s="155"/>
-      <c r="I38" s="155"/>
-      <c r="J38" s="155"/>
-      <c r="K38" s="155"/>
-      <c r="L38" s="155"/>
-      <c r="M38" s="155"/>
-      <c r="N38" s="155"/>
-      <c r="O38" s="155"/>
-      <c r="P38" s="155"/>
+      <c r="B38" s="152"/>
+      <c r="C38" s="152"/>
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="152"/>
+      <c r="H38" s="152"/>
+      <c r="I38" s="152"/>
+      <c r="J38" s="152"/>
+      <c r="K38" s="152"/>
+      <c r="L38" s="152"/>
+      <c r="M38" s="152"/>
+      <c r="N38" s="152"/>
+      <c r="O38" s="152"/>
+      <c r="P38" s="152"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="155"/>
-      <c r="B39" s="155"/>
-      <c r="C39" s="155"/>
-      <c r="D39" s="155"/>
-      <c r="E39" s="155"/>
-      <c r="F39" s="155"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="155"/>
-      <c r="I39" s="155"/>
-      <c r="J39" s="155"/>
-      <c r="K39" s="155"/>
-      <c r="L39" s="155"/>
-      <c r="M39" s="155"/>
-      <c r="N39" s="155"/>
-      <c r="O39" s="155"/>
-      <c r="P39" s="155"/>
+      <c r="A39" s="152"/>
+      <c r="B39" s="152"/>
+      <c r="C39" s="152"/>
+      <c r="D39" s="152"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="152"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="152"/>
+      <c r="I39" s="152"/>
+      <c r="J39" s="152"/>
+      <c r="K39" s="152"/>
+      <c r="L39" s="152"/>
+      <c r="M39" s="152"/>
+      <c r="N39" s="152"/>
+      <c r="O39" s="152"/>
+      <c r="P39" s="152"/>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="155"/>
-      <c r="B40" s="155"/>
-      <c r="C40" s="155"/>
-      <c r="D40" s="155"/>
-      <c r="E40" s="155"/>
-      <c r="F40" s="155"/>
-      <c r="G40" s="155"/>
-      <c r="H40" s="155"/>
-      <c r="I40" s="155"/>
-      <c r="J40" s="155"/>
-      <c r="K40" s="155"/>
-      <c r="L40" s="155"/>
-      <c r="M40" s="155"/>
-      <c r="N40" s="155"/>
-      <c r="O40" s="155"/>
-      <c r="P40" s="155"/>
+      <c r="A40" s="152"/>
+      <c r="B40" s="152"/>
+      <c r="C40" s="152"/>
+      <c r="D40" s="152"/>
+      <c r="E40" s="152"/>
+      <c r="F40" s="152"/>
+      <c r="G40" s="152"/>
+      <c r="H40" s="152"/>
+      <c r="I40" s="152"/>
+      <c r="J40" s="152"/>
+      <c r="K40" s="152"/>
+      <c r="L40" s="152"/>
+      <c r="M40" s="152"/>
+      <c r="N40" s="152"/>
+      <c r="O40" s="152"/>
+      <c r="P40" s="152"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="155"/>
-      <c r="B41" s="155"/>
-      <c r="C41" s="155"/>
-      <c r="D41" s="155"/>
-      <c r="E41" s="155"/>
-      <c r="F41" s="155"/>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
-      <c r="I41" s="155"/>
-      <c r="J41" s="155"/>
-      <c r="K41" s="155"/>
-      <c r="L41" s="155"/>
-      <c r="M41" s="155"/>
-      <c r="N41" s="155"/>
-      <c r="O41" s="155"/>
-      <c r="P41" s="155"/>
+      <c r="A41" s="152"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="152"/>
+      <c r="D41" s="152"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="152"/>
+      <c r="G41" s="152"/>
+      <c r="H41" s="152"/>
+      <c r="I41" s="152"/>
+      <c r="J41" s="152"/>
+      <c r="K41" s="152"/>
+      <c r="L41" s="152"/>
+      <c r="M41" s="152"/>
+      <c r="N41" s="152"/>
+      <c r="O41" s="152"/>
+      <c r="P41" s="152"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -5894,7 +5886,7 @@
     <col min="10" max="10" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="15" width="8.5703125" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="20" bestFit="1" customWidth="1"/>
@@ -5912,10 +5904,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="21">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="140"/>
+      <c r="B1" s="137"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
@@ -6011,10 +6003,10 @@
       <c r="CQ1" s="26"/>
     </row>
     <row r="2" spans="1:95">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="142"/>
+      <c r="B2" s="139"/>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
@@ -6207,10 +6199,10 @@
       <c r="CQ3" s="26"/>
     </row>
     <row r="4" spans="1:95">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="144"/>
+      <c r="B4" s="141"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -6410,7 +6402,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="26"/>
-      <c r="D6" s="113" t="s">
+      <c r="D6" s="110" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="6"/>
@@ -6944,15 +6936,15 @@
         <v>2030</v>
       </c>
       <c r="H11" s="26"/>
-      <c r="I11" s="136" t="s">
+      <c r="I11" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="138"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="134"/>
+      <c r="O11" s="135"/>
       <c r="P11" s="28"/>
       <c r="Q11" s="35" t="s">
         <v>23</v>
@@ -6961,14 +6953,14 @@
         <v>2026</v>
       </c>
       <c r="S11" s="26"/>
-      <c r="T11" s="101" t="s">
+      <c r="T11" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="U11" s="105"/>
-      <c r="V11" s="102" t="s">
+      <c r="U11" s="102"/>
+      <c r="V11" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="W11" s="109" t="s">
+      <c r="W11" s="106" t="s">
         <v>25</v>
       </c>
       <c r="X11" s="17">
@@ -7101,12 +7093,12 @@
         <v>725000</v>
       </c>
       <c r="S12" s="26"/>
-      <c r="T12" s="103" t="s">
+      <c r="T12" s="100" t="s">
         <v>25</v>
       </c>
       <c r="U12" s="74"/>
-      <c r="V12" s="104"/>
-      <c r="W12" s="110"/>
+      <c r="V12" s="101"/>
+      <c r="W12" s="107"/>
       <c r="X12" s="59">
         <f>U13</f>
         <v>165000</v>
@@ -7240,10 +7232,10 @@
         <v>135000</v>
       </c>
       <c r="S13" s="26"/>
-      <c r="T13" s="106">
+      <c r="T13" s="103">
         <v>2026</v>
       </c>
-      <c r="U13" s="107">
+      <c r="U13" s="104">
         <v>165000</v>
       </c>
       <c r="V13" s="26"/>
@@ -7375,11 +7367,11 @@
         <v>64000</v>
       </c>
       <c r="S14" s="26"/>
-      <c r="T14" s="106">
+      <c r="T14" s="103">
         <f>T13+1</f>
         <v>2027</v>
       </c>
-      <c r="U14" s="108">
+      <c r="U14" s="105">
         <v>165000</v>
       </c>
       <c r="V14" s="26"/>
@@ -7511,11 +7503,11 @@
         <v>130500</v>
       </c>
       <c r="S15" s="26"/>
-      <c r="T15" s="106">
+      <c r="T15" s="103">
         <f>T14+1</f>
         <v>2028</v>
       </c>
-      <c r="U15" s="108">
+      <c r="U15" s="105">
         <v>175000</v>
       </c>
       <c r="V15" s="26"/>
@@ -7619,11 +7611,11 @@
         <v>52000</v>
       </c>
       <c r="S16" s="26"/>
-      <c r="T16" s="106">
+      <c r="T16" s="103">
         <f t="shared" ref="T16:T17" si="2">T15+1</f>
         <v>2029</v>
       </c>
-      <c r="U16" s="108">
+      <c r="U16" s="105">
         <v>175000</v>
       </c>
       <c r="V16" s="26"/>
@@ -7710,7 +7702,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="16"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="105" t="s">
+      <c r="I17" s="102" t="s">
         <v>38</v>
       </c>
       <c r="J17" s="17" t="s">
@@ -7748,7 +7740,7 @@
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="U17" s="108">
+      <c r="U17" s="105">
         <v>175000</v>
       </c>
       <c r="V17" s="26"/>
@@ -8226,9 +8218,9 @@
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="134"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
@@ -8323,11 +8315,11 @@
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="135" t="s">
+      <c r="J22" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
       <c r="O22" s="26"/>
@@ -9419,24 +9411,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FD50A9-0884-44AC-8AA5-5AA892507CF5}">
-  <dimension ref="A1:BG38"/>
+  <dimension ref="A1:BD38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="18.75">
-      <c r="A1" s="145" t="s">
+    <row r="1" spans="1:56" ht="18.75">
+      <c r="A1" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
@@ -9488,11 +9480,8 @@
       <c r="BB1" s="26"/>
       <c r="BC1" s="26"/>
       <c r="BD1" s="26"/>
-      <c r="BE1" s="26"/>
-      <c r="BF1" s="26"/>
-      <c r="BG1" s="26"/>
-    </row>
-    <row r="2" spans="1:59" ht="18.75">
+    </row>
+    <row r="2" spans="1:56">
       <c r="A2" s="26"/>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -9501,17 +9490,9 @@
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="146" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="148"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
       <c r="R2" s="26"/>
       <c r="S2" s="26"/>
       <c r="T2" s="26"/>
@@ -9551,30 +9532,29 @@
       <c r="BB2" s="26"/>
       <c r="BC2" s="26"/>
       <c r="BD2" s="26"/>
-      <c r="BE2" s="26"/>
-      <c r="BF2" s="26"/>
-      <c r="BG2" s="26"/>
-    </row>
-    <row r="3" spans="1:59" ht="18.75">
-      <c r="A3" s="146" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
+    </row>
+    <row r="3" spans="1:56" ht="18.75">
+      <c r="A3" s="143" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="100"/>
+      <c r="I3" s="143" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
       <c r="R3" s="26"/>
       <c r="S3" s="26"/>
       <c r="T3" s="26"/>
@@ -9614,11 +9594,8 @@
       <c r="BB3" s="26"/>
       <c r="BC3" s="26"/>
       <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-    </row>
-    <row r="4" spans="1:59">
+    </row>
+    <row r="4" spans="1:56">
       <c r="A4" s="84" t="s">
         <v>26</v>
       </c>
@@ -9629,41 +9606,41 @@
       <c r="F4" s="85"/>
       <c r="G4" s="26"/>
       <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="84" t="s">
+      <c r="I4" s="84" t="s">
         <v>26</v>
       </c>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
       <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
       <c r="R4" s="26"/>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
       <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81">
-        <f t="shared" ref="Z4:AC4" si="0">$B$22</f>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81">
+        <f t="shared" ref="W4:Z4" si="0">$B$22</f>
         <v>1620495</v>
       </c>
-      <c r="AA4" s="81">
+      <c r="X4" s="81">
         <f t="shared" si="0"/>
         <v>1620495</v>
       </c>
-      <c r="AB4" s="81">
+      <c r="Y4" s="81">
         <f t="shared" si="0"/>
         <v>1620495</v>
       </c>
-      <c r="AC4" s="81">
+      <c r="Z4" s="81">
         <f t="shared" si="0"/>
         <v>1620495</v>
       </c>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
       <c r="AD4" s="26"/>
       <c r="AE4" s="26"/>
       <c r="AF4" s="26"/>
@@ -9691,11 +9668,8 @@
       <c r="BB4" s="26"/>
       <c r="BC4" s="26"/>
       <c r="BD4" s="26"/>
-      <c r="BE4" s="26"/>
-      <c r="BF4" s="26"/>
-      <c r="BG4" s="26"/>
-    </row>
-    <row r="5" spans="1:59">
+    </row>
+    <row r="5" spans="1:56">
       <c r="A5" s="60" t="s">
         <v>25</v>
       </c>
@@ -9721,32 +9695,32 @@
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="60" t="s">
+      <c r="I5" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="21" cm="1">
-        <f t="array" ref="M5">currentyear</f>
+      <c r="J5" s="21" cm="1">
+        <f t="array" ref="J5">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="N5" s="21">
-        <f>M5+1</f>
+      <c r="K5" s="21">
+        <f>J5+1</f>
         <v>2027</v>
       </c>
-      <c r="O5" s="21">
-        <f t="shared" ref="O5:Q5" si="2">N5+1</f>
+      <c r="L5" s="21">
+        <f t="shared" ref="L5:N5" si="2">K5+1</f>
         <v>2028</v>
       </c>
-      <c r="P5" s="21">
+      <c r="M5" s="21">
         <f t="shared" si="2"/>
         <v>2029</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="N5" s="21">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
       <c r="R5" s="26"/>
       <c r="S5" s="26"/>
       <c r="T5" s="26"/>
@@ -9786,11 +9760,8 @@
       <c r="BB5" s="26"/>
       <c r="BC5" s="26"/>
       <c r="BD5" s="26"/>
-      <c r="BE5" s="26"/>
-      <c r="BF5" s="26"/>
-      <c r="BG5" s="26"/>
-    </row>
-    <row r="6" spans="1:59">
+    </row>
+    <row r="6" spans="1:56">
       <c r="A6" s="21" t="s">
         <v>50</v>
       </c>
@@ -9816,32 +9787,32 @@
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="21" t="s">
+      <c r="I6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="57" cm="1">
-        <f t="array" ref="M6">num_accountsRS1</f>
+      <c r="J6" s="57" cm="1">
+        <f t="array" ref="J6">num_accountsRS1</f>
         <v>2520</v>
+      </c>
+      <c r="K6" s="58" cm="1">
+        <f t="array" ref="K6">ROUND(J6 * (1+pop_growth_rate),0)</f>
+        <v>2545</v>
+      </c>
+      <c r="L6" s="58" cm="1">
+        <f t="array" ref="L6">ROUND(K6 * (1+pop_growth_rate),0)</f>
+        <v>2570</v>
+      </c>
+      <c r="M6" s="58" cm="1">
+        <f t="array" ref="M6">ROUND(L6 * (1+pop_growth_rate),0)</f>
+        <v>2596</v>
       </c>
       <c r="N6" s="58" cm="1">
         <f t="array" ref="N6">ROUND(M6 * (1+pop_growth_rate),0)</f>
-        <v>2545</v>
-      </c>
-      <c r="O6" s="58" cm="1">
-        <f t="array" ref="O6">ROUND(N6 * (1+pop_growth_rate),0)</f>
-        <v>2570</v>
-      </c>
-      <c r="P6" s="58" cm="1">
-        <f t="array" ref="P6">ROUND(O6 * (1+pop_growth_rate),0)</f>
-        <v>2596</v>
-      </c>
-      <c r="Q6" s="58" cm="1">
-        <f t="array" ref="Q6">ROUND(P6 * (1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
       <c r="R6" s="26"/>
       <c r="S6" s="26"/>
       <c r="T6" s="26"/>
@@ -9881,11 +9852,8 @@
       <c r="BB6" s="26"/>
       <c r="BC6" s="26"/>
       <c r="BD6" s="26"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
-      <c r="BG6" s="26"/>
-    </row>
-    <row r="7" spans="1:59">
+    </row>
+    <row r="7" spans="1:56">
       <c r="A7" s="21" t="s">
         <v>51</v>
       </c>
@@ -9907,28 +9875,28 @@
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="56" t="s">
+      <c r="I7" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="90" cm="1">
-        <f t="array" ref="M7:Q7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
+      <c r="J7" s="90" cm="1">
+        <f t="array" ref="J7:N7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
         <v>514080</v>
       </c>
+      <c r="K7" s="91">
+        <v>519180</v>
+      </c>
+      <c r="L7" s="91">
+        <v>524280</v>
+      </c>
+      <c r="M7" s="91">
+        <v>529584</v>
+      </c>
       <c r="N7" s="91">
-        <v>519180</v>
-      </c>
-      <c r="O7" s="91">
-        <v>524280</v>
-      </c>
-      <c r="P7" s="91">
-        <v>529584</v>
-      </c>
-      <c r="Q7" s="91">
         <v>534888</v>
       </c>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
       <c r="S7" s="26"/>
       <c r="T7" s="26"/>
@@ -9968,11 +9936,8 @@
       <c r="BB7" s="26"/>
       <c r="BC7" s="26"/>
       <c r="BD7" s="26"/>
-      <c r="BE7" s="26"/>
-      <c r="BF7" s="26"/>
-      <c r="BG7" s="26"/>
-    </row>
-    <row r="8" spans="1:59">
+    </row>
+    <row r="8" spans="1:56">
       <c r="A8" s="21" t="s">
         <v>52</v>
       </c>
@@ -9998,32 +9963,32 @@
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="21" t="s">
+      <c r="I8" s="21" t="s">
         <v>52</v>
       </c>
+      <c r="J8" s="59" cm="1">
+        <f t="array" ref="J8:J10">RS1_block_consumption2026 * RS1_vrates2026 *12</f>
+        <v>370440</v>
+      </c>
+      <c r="K8" s="59" cm="1">
+        <f t="array" ref="K8:K10">RS1_block_consumption2027 * RS1_vrates2026 *12</f>
+        <v>374136</v>
+      </c>
+      <c r="L8" s="59" cm="1">
+        <f t="array" ref="L8:L10">RS1_block_consumption2028 * RS1_vrates2026 *12</f>
+        <v>377874</v>
+      </c>
       <c r="M8" s="59" cm="1">
-        <f t="array" ref="M8:M10">RS1_block_consumption2026 * RS1_vrates2026 *12</f>
-        <v>370440</v>
+        <f t="array" ref="M8:M10">RS1_block_consumption2029 * RS1_vrates2026 *12</f>
+        <v>381654</v>
       </c>
       <c r="N8" s="59" cm="1">
-        <f t="array" ref="N8:N10">RS1_block_consumption2027 * RS1_vrates2026 *12</f>
-        <v>374136</v>
-      </c>
-      <c r="O8" s="59" cm="1">
-        <f t="array" ref="O8:O10">RS1_block_consumption2028 * RS1_vrates2026 *12</f>
-        <v>377874</v>
-      </c>
-      <c r="P8" s="59" cm="1">
-        <f t="array" ref="P8:P10">RS1_block_consumption2029 * RS1_vrates2026 *12</f>
-        <v>381654</v>
-      </c>
-      <c r="Q8" s="59" cm="1">
-        <f t="array" ref="Q8:Q10">RS1_block_consumption2030 * RS1_vrates2026 *12</f>
+        <f t="array" ref="N8:N10">RS1_block_consumption2030 * RS1_vrates2026 *12</f>
         <v>385476</v>
       </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
       <c r="R8" s="26"/>
       <c r="S8" s="26"/>
       <c r="T8" s="26"/>
@@ -10063,11 +10028,8 @@
       <c r="BB8" s="26"/>
       <c r="BC8" s="26"/>
       <c r="BD8" s="26"/>
-      <c r="BE8" s="26"/>
-      <c r="BF8" s="26"/>
-      <c r="BG8" s="26"/>
-    </row>
-    <row r="9" spans="1:59">
+    </row>
+    <row r="9" spans="1:56">
       <c r="A9" s="21" t="s">
         <v>53</v>
       </c>
@@ -10088,27 +10050,27 @@
       </c>
       <c r="G9" s="26"/>
       <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="21" t="s">
+      <c r="I9" s="21" t="s">
         <v>53</v>
       </c>
+      <c r="J9" s="59">
+        <v>92610</v>
+      </c>
+      <c r="K9" s="59">
+        <v>93534</v>
+      </c>
+      <c r="L9" s="59">
+        <v>94479</v>
+      </c>
       <c r="M9" s="59">
-        <v>92610</v>
+        <v>95424</v>
       </c>
       <c r="N9" s="59">
-        <v>93534</v>
-      </c>
-      <c r="O9" s="59">
-        <v>94479</v>
-      </c>
-      <c r="P9" s="59">
-        <v>95424</v>
-      </c>
-      <c r="Q9" s="59">
         <v>96369</v>
       </c>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
       <c r="R9" s="26"/>
       <c r="S9" s="26"/>
       <c r="T9" s="26"/>
@@ -10148,11 +10110,8 @@
       <c r="BB9" s="26"/>
       <c r="BC9" s="26"/>
       <c r="BD9" s="26"/>
-      <c r="BE9" s="26"/>
-      <c r="BF9" s="26"/>
-      <c r="BG9" s="26"/>
-    </row>
-    <row r="10" spans="1:59">
+    </row>
+    <row r="10" spans="1:56">
       <c r="A10" s="21" t="s">
         <v>54</v>
       </c>
@@ -10173,27 +10132,27 @@
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="63" t="s">
+      <c r="I10" s="63" t="s">
         <v>54</v>
       </c>
+      <c r="J10" s="66">
+        <v>13230</v>
+      </c>
+      <c r="K10" s="66">
+        <v>13356</v>
+      </c>
+      <c r="L10" s="66">
+        <v>13482</v>
+      </c>
       <c r="M10" s="66">
-        <v>13230</v>
+        <v>13608</v>
       </c>
       <c r="N10" s="66">
-        <v>13356</v>
-      </c>
-      <c r="O10" s="66">
-        <v>13482</v>
-      </c>
-      <c r="P10" s="66">
-        <v>13608</v>
-      </c>
-      <c r="Q10" s="66">
         <v>13734</v>
       </c>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
       <c r="R10" s="26"/>
       <c r="S10" s="26"/>
       <c r="T10" s="26"/>
@@ -10233,11 +10192,8 @@
       <c r="BB10" s="26"/>
       <c r="BC10" s="26"/>
       <c r="BD10" s="26"/>
-      <c r="BE10" s="26"/>
-      <c r="BF10" s="26"/>
-      <c r="BG10" s="26"/>
-    </row>
-    <row r="11" spans="1:59">
+    </row>
+    <row r="11" spans="1:56">
       <c r="A11" s="86" t="s">
         <v>55</v>
       </c>
@@ -10263,32 +10219,32 @@
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="44" t="s">
+      <c r="I11" s="44" t="s">
         <v>55</v>
       </c>
+      <c r="J11" s="62">
+        <f>SUM(J7:J10)</f>
+        <v>990360</v>
+      </c>
+      <c r="K11" s="62">
+        <f t="shared" ref="K11" si="4">SUM(K7:K10)</f>
+        <v>1000206</v>
+      </c>
+      <c r="L11" s="62">
+        <f t="shared" ref="L11" si="5">SUM(L7:L10)</f>
+        <v>1010115</v>
+      </c>
       <c r="M11" s="62">
-        <f>SUM(M7:M10)</f>
-        <v>990360</v>
+        <f t="shared" ref="M11" si="6">SUM(M7:M10)</f>
+        <v>1020270</v>
       </c>
       <c r="N11" s="62">
-        <f t="shared" ref="N11" si="4">SUM(N7:N10)</f>
-        <v>1000206</v>
-      </c>
-      <c r="O11" s="62">
-        <f t="shared" ref="O11" si="5">SUM(O7:O10)</f>
-        <v>1010115</v>
-      </c>
-      <c r="P11" s="62">
-        <f t="shared" ref="P11" si="6">SUM(P7:P10)</f>
-        <v>1020270</v>
-      </c>
-      <c r="Q11" s="62">
-        <f t="shared" ref="Q11" si="7">SUM(Q7:Q10)</f>
+        <f t="shared" ref="N11" si="7">SUM(N7:N10)</f>
         <v>1030467</v>
       </c>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
       <c r="R11" s="26"/>
       <c r="S11" s="26"/>
       <c r="T11" s="26"/>
@@ -10328,11 +10284,8 @@
       <c r="BB11" s="26"/>
       <c r="BC11" s="26"/>
       <c r="BD11" s="26"/>
-      <c r="BE11" s="26"/>
-      <c r="BF11" s="26"/>
-      <c r="BG11" s="26"/>
-    </row>
-    <row r="12" spans="1:59">
+    </row>
+    <row r="12" spans="1:56">
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
@@ -10389,11 +10342,8 @@
       <c r="BB12" s="26"/>
       <c r="BC12" s="26"/>
       <c r="BD12" s="26"/>
-      <c r="BE12" s="26"/>
-      <c r="BF12" s="26"/>
-      <c r="BG12" s="26"/>
-    </row>
-    <row r="13" spans="1:59">
+    </row>
+    <row r="13" spans="1:56">
       <c r="A13" s="88" t="s">
         <v>38</v>
       </c>
@@ -10404,17 +10354,17 @@
       <c r="F13" s="89"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="42" t="s">
+      <c r="I13" s="42" t="s">
         <v>38</v>
       </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
       <c r="R13" s="26"/>
       <c r="S13" s="26"/>
       <c r="T13" s="26"/>
@@ -10454,11 +10404,8 @@
       <c r="BB13" s="26"/>
       <c r="BC13" s="26"/>
       <c r="BD13" s="26"/>
-      <c r="BE13" s="26"/>
-      <c r="BF13" s="26"/>
-      <c r="BG13" s="26"/>
-    </row>
-    <row r="14" spans="1:59">
+    </row>
+    <row r="14" spans="1:56">
       <c r="A14" s="21" t="s">
         <v>25</v>
       </c>
@@ -10484,32 +10431,32 @@
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="21" t="s">
+      <c r="I14" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="21" cm="1">
-        <f t="array" ref="M14">currentyear</f>
+      <c r="J14" s="21" cm="1">
+        <f t="array" ref="J14">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="N14" s="21">
-        <f>M14+1</f>
+      <c r="K14" s="21">
+        <f>J14+1</f>
         <v>2027</v>
       </c>
-      <c r="O14" s="21">
-        <f t="shared" ref="O14:Q14" si="9">N14+1</f>
+      <c r="L14" s="21">
+        <f t="shared" ref="L14:N14" si="9">K14+1</f>
         <v>2028</v>
       </c>
-      <c r="P14" s="21">
+      <c r="M14" s="21">
         <f t="shared" si="9"/>
         <v>2029</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="N14" s="21">
         <f t="shared" si="9"/>
         <v>2030</v>
       </c>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
       <c r="R14" s="26"/>
       <c r="S14" s="26"/>
       <c r="T14" s="26"/>
@@ -10549,11 +10496,8 @@
       <c r="BB14" s="26"/>
       <c r="BC14" s="26"/>
       <c r="BD14" s="26"/>
-      <c r="BE14" s="26"/>
-      <c r="BF14" s="26"/>
-      <c r="BG14" s="26"/>
-    </row>
-    <row r="15" spans="1:59">
+    </row>
+    <row r="15" spans="1:56">
       <c r="A15" s="56" t="s">
         <v>50</v>
       </c>
@@ -10579,32 +10523,32 @@
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="56" t="s">
+      <c r="I15" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="57" cm="1">
-        <f t="array" ref="M15">num_accountsRS2</f>
+      <c r="J15" s="57" cm="1">
+        <f t="array" ref="J15">num_accountsRS2</f>
         <v>550</v>
+      </c>
+      <c r="K15" s="58" cm="1">
+        <f t="array" ref="K15">ROUND(J15*(1+pop_growth_rate),0)</f>
+        <v>556</v>
+      </c>
+      <c r="L15" s="58" cm="1">
+        <f t="array" ref="L15">ROUND(K15*(1+pop_growth_rate),0)</f>
+        <v>562</v>
+      </c>
+      <c r="M15" s="58" cm="1">
+        <f t="array" ref="M15">ROUND(L15*(1+pop_growth_rate),0)</f>
+        <v>568</v>
       </c>
       <c r="N15" s="58" cm="1">
         <f t="array" ref="N15">ROUND(M15*(1+pop_growth_rate),0)</f>
-        <v>556</v>
-      </c>
-      <c r="O15" s="58" cm="1">
-        <f t="array" ref="O15">ROUND(N15*(1+pop_growth_rate),0)</f>
-        <v>562</v>
-      </c>
-      <c r="P15" s="58" cm="1">
-        <f t="array" ref="P15">ROUND(O15*(1+pop_growth_rate),0)</f>
-        <v>568</v>
-      </c>
-      <c r="Q15" s="58" cm="1">
-        <f t="array" ref="Q15">ROUND(P15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
       <c r="R15" s="26"/>
       <c r="S15" s="26"/>
       <c r="T15" s="26"/>
@@ -10644,11 +10588,8 @@
       <c r="BB15" s="26"/>
       <c r="BC15" s="26"/>
       <c r="BD15" s="26"/>
-      <c r="BE15" s="26"/>
-      <c r="BF15" s="26"/>
-      <c r="BG15" s="26"/>
-    </row>
-    <row r="16" spans="1:59">
+    </row>
+    <row r="16" spans="1:56">
       <c r="A16" s="56" t="s">
         <v>51</v>
       </c>
@@ -10670,28 +10611,28 @@
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="21" t="s">
+      <c r="I16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="54" cm="1">
-        <f t="array" ref="M16:Q16">RS2_base_charge2026 * 12 * RS2_num_accounts</f>
+      <c r="J16" s="54" cm="1">
+        <f t="array" ref="J16:N16">RS2_base_charge2026 * 12 * RS2_num_accounts</f>
         <v>250800</v>
       </c>
+      <c r="K16" s="51">
+        <v>253536</v>
+      </c>
+      <c r="L16" s="51">
+        <v>256272</v>
+      </c>
+      <c r="M16" s="51">
+        <v>259008</v>
+      </c>
       <c r="N16" s="51">
-        <v>253536</v>
-      </c>
-      <c r="O16" s="51">
-        <v>256272</v>
-      </c>
-      <c r="P16" s="51">
-        <v>259008</v>
-      </c>
-      <c r="Q16" s="51">
         <v>261744</v>
       </c>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
       <c r="R16" s="26"/>
       <c r="S16" s="26"/>
       <c r="T16" s="26"/>
@@ -10731,11 +10672,8 @@
       <c r="BB16" s="26"/>
       <c r="BC16" s="26"/>
       <c r="BD16" s="26"/>
-      <c r="BE16" s="26"/>
-      <c r="BF16" s="26"/>
-      <c r="BG16" s="26"/>
-    </row>
-    <row r="17" spans="1:59">
+    </row>
+    <row r="17" spans="1:56">
       <c r="A17" s="21" t="s">
         <v>52</v>
       </c>
@@ -10761,32 +10699,32 @@
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="21" t="s">
+      <c r="I17" s="21" t="s">
         <v>52</v>
       </c>
+      <c r="J17" s="55" cm="1">
+        <f t="array" ref="J17:J19">RS2_block_consumption2026 * RS2_vrates2026 *12</f>
+        <v>181500</v>
+      </c>
+      <c r="K17" s="55" cm="1">
+        <f t="array" ref="K17:K19">RS2_block_consumption2027 * RS2_vrates2026 *12</f>
+        <v>183315</v>
+      </c>
+      <c r="L17" s="55" cm="1">
+        <f t="array" ref="L17:L19">RS2_block_consumption2028 * RS2_vrates2026 *12</f>
+        <v>185163</v>
+      </c>
       <c r="M17" s="55" cm="1">
-        <f t="array" ref="M17:M19">RS2_block_consumption2026 * RS2_vrates2026 *12</f>
-        <v>181500</v>
+        <f t="array" ref="M17:M19">RS2_block_consumption2029 * RS2_vrates2026 *12</f>
+        <v>187011</v>
       </c>
       <c r="N17" s="55" cm="1">
-        <f t="array" ref="N17:N19">RS2_block_consumption2027 * RS2_vrates2026 *12</f>
-        <v>183315</v>
-      </c>
-      <c r="O17" s="55" cm="1">
-        <f t="array" ref="O17:O19">RS2_block_consumption2028 * RS2_vrates2026 *12</f>
-        <v>185163</v>
-      </c>
-      <c r="P17" s="55" cm="1">
-        <f t="array" ref="P17:P19">RS2_block_consumption2029 * RS2_vrates2026 *12</f>
-        <v>187011</v>
-      </c>
-      <c r="Q17" s="55" cm="1">
-        <f t="array" ref="Q17:Q19">RS2_block_consumption2030 * RS2_vrates2026 *12</f>
+        <f t="array" ref="N17:N19">RS2_block_consumption2030 * RS2_vrates2026 *12</f>
         <v>188892</v>
       </c>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
       <c r="R17" s="26"/>
       <c r="S17" s="26"/>
       <c r="T17" s="26"/>
@@ -10826,11 +10764,8 @@
       <c r="BB17" s="26"/>
       <c r="BC17" s="26"/>
       <c r="BD17" s="26"/>
-      <c r="BE17" s="26"/>
-      <c r="BF17" s="26"/>
-      <c r="BG17" s="26"/>
-    </row>
-    <row r="18" spans="1:59">
+    </row>
+    <row r="18" spans="1:56">
       <c r="A18" s="21" t="s">
         <v>53</v>
       </c>
@@ -10851,27 +10786,27 @@
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="21" t="s">
+      <c r="I18" s="21" t="s">
         <v>53</v>
       </c>
+      <c r="J18" s="55">
+        <v>165000</v>
+      </c>
+      <c r="K18" s="55">
+        <v>166650</v>
+      </c>
+      <c r="L18" s="55">
+        <v>168333</v>
+      </c>
       <c r="M18" s="55">
-        <v>165000</v>
+        <v>170016</v>
       </c>
       <c r="N18" s="55">
-        <v>166650</v>
-      </c>
-      <c r="O18" s="55">
-        <v>168333</v>
-      </c>
-      <c r="P18" s="55">
-        <v>170016</v>
-      </c>
-      <c r="Q18" s="55">
         <v>171732</v>
       </c>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
       <c r="R18" s="26"/>
       <c r="S18" s="26"/>
       <c r="T18" s="26"/>
@@ -10911,11 +10846,8 @@
       <c r="BB18" s="26"/>
       <c r="BC18" s="26"/>
       <c r="BD18" s="26"/>
-      <c r="BE18" s="26"/>
-      <c r="BF18" s="26"/>
-      <c r="BG18" s="26"/>
-    </row>
-    <row r="19" spans="1:59">
+    </row>
+    <row r="19" spans="1:56">
       <c r="A19" s="63" t="s">
         <v>54</v>
       </c>
@@ -10936,27 +10868,27 @@
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="63" t="s">
+      <c r="I19" s="63" t="s">
         <v>54</v>
       </c>
+      <c r="J19" s="64">
+        <v>32835</v>
+      </c>
+      <c r="K19" s="64">
+        <v>33165</v>
+      </c>
+      <c r="L19" s="64">
+        <v>33495</v>
+      </c>
       <c r="M19" s="64">
-        <v>32835</v>
+        <v>33825</v>
       </c>
       <c r="N19" s="64">
-        <v>33165</v>
-      </c>
-      <c r="O19" s="64">
-        <v>33495</v>
-      </c>
-      <c r="P19" s="64">
-        <v>33825</v>
-      </c>
-      <c r="Q19" s="64">
         <v>34155</v>
       </c>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
       <c r="R19" s="26"/>
       <c r="S19" s="26"/>
       <c r="T19" s="26"/>
@@ -10996,11 +10928,8 @@
       <c r="BB19" s="26"/>
       <c r="BC19" s="26"/>
       <c r="BD19" s="26"/>
-      <c r="BE19" s="26"/>
-      <c r="BF19" s="26"/>
-      <c r="BG19" s="26"/>
-    </row>
-    <row r="20" spans="1:59">
+    </row>
+    <row r="20" spans="1:56">
       <c r="A20" s="44" t="s">
         <v>56</v>
       </c>
@@ -11026,32 +10955,32 @@
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="44" t="s">
+      <c r="I20" s="44" t="s">
         <v>56</v>
       </c>
+      <c r="J20" s="62">
+        <f>SUM(J16:J19)</f>
+        <v>630135</v>
+      </c>
+      <c r="K20" s="62">
+        <f t="shared" ref="K20" si="11">SUM(K16:K19)</f>
+        <v>636666</v>
+      </c>
+      <c r="L20" s="62">
+        <f t="shared" ref="L20" si="12">SUM(L16:L19)</f>
+        <v>643263</v>
+      </c>
       <c r="M20" s="62">
-        <f>SUM(M16:M19)</f>
-        <v>630135</v>
+        <f t="shared" ref="M20" si="13">SUM(M16:M19)</f>
+        <v>649860</v>
       </c>
       <c r="N20" s="62">
-        <f t="shared" ref="N20" si="11">SUM(N16:N19)</f>
-        <v>636666</v>
-      </c>
-      <c r="O20" s="62">
-        <f t="shared" ref="O20" si="12">SUM(O16:O19)</f>
-        <v>643263</v>
-      </c>
-      <c r="P20" s="62">
-        <f t="shared" ref="P20" si="13">SUM(P16:P19)</f>
-        <v>649860</v>
-      </c>
-      <c r="Q20" s="62">
-        <f t="shared" ref="Q20" si="14">SUM(Q16:Q19)</f>
+        <f t="shared" ref="N20" si="14">SUM(N16:N19)</f>
         <v>656523</v>
       </c>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
       <c r="R20" s="26"/>
       <c r="S20" s="26"/>
       <c r="T20" s="26"/>
@@ -11091,11 +11020,8 @@
       <c r="BB20" s="26"/>
       <c r="BC20" s="26"/>
       <c r="BD20" s="26"/>
-      <c r="BE20" s="26"/>
-      <c r="BF20" s="26"/>
-      <c r="BG20" s="26"/>
-    </row>
-    <row r="21" spans="1:59">
+    </row>
+    <row r="21" spans="1:56">
       <c r="A21" s="26"/>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
@@ -11152,11 +11078,8 @@
       <c r="BB21" s="26"/>
       <c r="BC21" s="26"/>
       <c r="BD21" s="26"/>
-      <c r="BE21" s="26"/>
-      <c r="BF21" s="26"/>
-      <c r="BG21" s="26"/>
-    </row>
-    <row r="22" spans="1:59" ht="15.75">
+    </row>
+    <row r="22" spans="1:56" ht="15.75">
       <c r="A22" s="49" t="s">
         <v>57</v>
       </c>
@@ -11182,32 +11105,32 @@
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="49" t="s">
+      <c r="I22" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="M22" s="61">
-        <f>SUM(M20+M11)</f>
+      <c r="J22" s="61">
+        <f>SUM(J20+J11)</f>
         <v>1620495</v>
       </c>
-      <c r="N22" s="61">
-        <f t="shared" ref="N22:Q22" si="16">SUM(N20+N11)</f>
+      <c r="K22" s="61">
+        <f t="shared" ref="K22:N22" si="16">SUM(K20+K11)</f>
         <v>1636872</v>
       </c>
-      <c r="O22" s="61">
+      <c r="L22" s="61">
         <f t="shared" si="16"/>
         <v>1653378</v>
       </c>
-      <c r="P22" s="61">
+      <c r="M22" s="61">
         <f t="shared" si="16"/>
         <v>1670130</v>
       </c>
-      <c r="Q22" s="61">
+      <c r="N22" s="61">
         <f t="shared" si="16"/>
         <v>1686990</v>
       </c>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
       <c r="R22" s="26"/>
       <c r="S22" s="26"/>
       <c r="T22" s="26"/>
@@ -11247,11 +11170,8 @@
       <c r="BB22" s="26"/>
       <c r="BC22" s="26"/>
       <c r="BD22" s="26"/>
-      <c r="BE22" s="26"/>
-      <c r="BF22" s="26"/>
-      <c r="BG22" s="26"/>
-    </row>
-    <row r="23" spans="1:59">
+    </row>
+    <row r="23" spans="1:56">
       <c r="A23" s="26"/>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
@@ -11308,11 +11228,8 @@
       <c r="BB23" s="26"/>
       <c r="BC23" s="26"/>
       <c r="BD23" s="26"/>
-      <c r="BE23" s="26"/>
-      <c r="BF23" s="26"/>
-      <c r="BG23" s="26"/>
-    </row>
-    <row r="24" spans="1:59">
+    </row>
+    <row r="24" spans="1:56">
       <c r="A24" s="26"/>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -11369,11 +11286,8 @@
       <c r="BB24" s="26"/>
       <c r="BC24" s="26"/>
       <c r="BD24" s="26"/>
-      <c r="BE24" s="26"/>
-      <c r="BF24" s="26"/>
-      <c r="BG24" s="26"/>
-    </row>
-    <row r="25" spans="1:59">
+    </row>
+    <row r="25" spans="1:56">
       <c r="A25" s="26"/>
       <c r="B25" s="26"/>
       <c r="C25" s="26"/>
@@ -11430,11 +11344,8 @@
       <c r="BB25" s="26"/>
       <c r="BC25" s="26"/>
       <c r="BD25" s="26"/>
-      <c r="BE25" s="26"/>
-      <c r="BF25" s="26"/>
-      <c r="BG25" s="26"/>
-    </row>
-    <row r="26" spans="1:59">
+    </row>
+    <row r="26" spans="1:56">
       <c r="A26" s="26"/>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -11491,11 +11402,8 @@
       <c r="BB26" s="26"/>
       <c r="BC26" s="26"/>
       <c r="BD26" s="26"/>
-      <c r="BE26" s="26"/>
-      <c r="BF26" s="26"/>
-      <c r="BG26" s="26"/>
-    </row>
-    <row r="27" spans="1:59">
+    </row>
+    <row r="27" spans="1:56">
       <c r="A27" s="26"/>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -11552,11 +11460,8 @@
       <c r="BB27" s="26"/>
       <c r="BC27" s="26"/>
       <c r="BD27" s="26"/>
-      <c r="BE27" s="26"/>
-      <c r="BF27" s="26"/>
-      <c r="BG27" s="26"/>
-    </row>
-    <row r="28" spans="1:59">
+    </row>
+    <row r="28" spans="1:56">
       <c r="A28" s="26"/>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -11613,11 +11518,8 @@
       <c r="BB28" s="26"/>
       <c r="BC28" s="26"/>
       <c r="BD28" s="26"/>
-      <c r="BE28" s="26"/>
-      <c r="BF28" s="26"/>
-      <c r="BG28" s="26"/>
-    </row>
-    <row r="29" spans="1:59">
+    </row>
+    <row r="29" spans="1:56">
       <c r="A29" s="26"/>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -11627,11 +11529,8 @@
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-    </row>
-    <row r="30" spans="1:59">
+    </row>
+    <row r="30" spans="1:56">
       <c r="A30" s="26"/>
       <c r="B30" s="26"/>
       <c r="C30" s="26"/>
@@ -11641,11 +11540,8 @@
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-    </row>
-    <row r="31" spans="1:59">
+    </row>
+    <row r="31" spans="1:56">
       <c r="A31" s="26"/>
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
@@ -11655,11 +11551,8 @@
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-    </row>
-    <row r="32" spans="1:59">
+    </row>
+    <row r="32" spans="1:56">
       <c r="A32" s="26"/>
       <c r="B32" s="26"/>
       <c r="C32" s="26"/>
@@ -11669,11 +11562,8 @@
       <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-    </row>
-    <row r="33" spans="1:12">
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="26"/>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
@@ -11683,11 +11573,8 @@
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-    </row>
-    <row r="34" spans="1:12">
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="26"/>
       <c r="B34" s="26"/>
       <c r="C34" s="26"/>
@@ -11697,11 +11584,8 @@
       <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-    </row>
-    <row r="35" spans="1:12">
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="26"/>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -11711,11 +11595,8 @@
       <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-    </row>
-    <row r="36" spans="1:12">
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="26"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -11725,11 +11606,8 @@
       <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-    </row>
-    <row r="37" spans="1:12">
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="26"/>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -11739,11 +11617,8 @@
       <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-    </row>
-    <row r="38" spans="1:12">
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="26"/>
       <c r="B38" s="26"/>
       <c r="C38" s="26"/>
@@ -11753,15 +11628,12 @@
       <c r="G38" s="26"/>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="I3:N3"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11780,15 +11652,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="153"/>
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
@@ -11820,14 +11692,14 @@
       <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="149" t="s">
+      <c r="A3" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="150"/>
-      <c r="C3" s="150"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="151"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="148"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
@@ -12177,14 +12049,14 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="1:17" ht="15.75">
-      <c r="A14" s="149" t="s">
+      <c r="A14" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="151"/>
+      <c r="B14" s="147"/>
+      <c r="C14" s="147"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="148"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -12609,9 +12481,9 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12619,7 +12491,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24CF71A9-E3E6-4702-9C2B-B190BAB0F6FB}">
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.42578125" customWidth="1"/>
@@ -12630,17 +12502,17 @@
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18.75">
-      <c r="A1" s="145" t="s">
+    <row r="1" spans="1:42" ht="18.75">
+      <c r="A1" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -12650,15 +12522,15 @@
       <c r="O1" s="26"/>
       <c r="P1" s="26"/>
     </row>
-    <row r="2" spans="1:28" ht="18.75">
-      <c r="A2" s="111"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
+    <row r="2" spans="1:42" ht="18.75">
+      <c r="A2" s="108"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
@@ -12668,7 +12540,7 @@
       <c r="O2" s="26"/>
       <c r="P2" s="26"/>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:42">
       <c r="A3" s="60" t="s">
         <v>25</v>
       </c>
@@ -12703,7 +12575,7 @@
       <c r="O3" s="26"/>
       <c r="P3" s="26"/>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:42">
       <c r="A4" s="71" t="s">
         <v>65</v>
       </c>
@@ -12734,7 +12606,7 @@
       <c r="O4" s="26"/>
       <c r="P4" s="26"/>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:42">
       <c r="A5" s="71" t="s">
         <v>62</v>
       </c>
@@ -12764,28 +12636,28 @@
       <c r="N5" s="26"/>
       <c r="O5" s="26"/>
       <c r="P5" s="26"/>
-      <c r="X5" s="72" cm="1">
-        <f t="array" ref="X5">target_dscr</f>
+      <c r="AL5" s="72" cm="1">
+        <f t="array" ref="AL5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y5" s="72" cm="1">
-        <f t="array" ref="Y5">target_dscr</f>
+      <c r="AM5" s="72" cm="1">
+        <f t="array" ref="AM5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="Z5" s="72" cm="1">
-        <f t="array" ref="Z5">target_dscr</f>
+      <c r="AN5" s="72" cm="1">
+        <f t="array" ref="AN5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AA5" s="72" cm="1">
-        <f t="array" ref="AA5">target_dscr</f>
+      <c r="AO5" s="72" cm="1">
+        <f t="array" ref="AO5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AB5" s="72" cm="1">
-        <f t="array" ref="AB5">target_dscr</f>
+      <c r="AP5" s="72" cm="1">
+        <f t="array" ref="AP5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:42">
       <c r="A6" s="71" t="s">
         <v>66</v>
       </c>
@@ -12820,7 +12692,7 @@
       <c r="O6" s="26"/>
       <c r="P6" s="26"/>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:42">
       <c r="A7" s="77" t="s">
         <v>67</v>
       </c>
@@ -12855,7 +12727,7 @@
       <c r="O7" s="26"/>
       <c r="P7" s="26"/>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:42">
       <c r="A8" s="26"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -12873,7 +12745,7 @@
       <c r="O8" s="26"/>
       <c r="P8" s="26"/>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:42">
       <c r="A9" s="60" t="s">
         <v>25</v>
       </c>
@@ -12908,7 +12780,7 @@
       <c r="O9" s="26"/>
       <c r="P9" s="26"/>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:42">
       <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
@@ -12939,7 +12811,7 @@
       <c r="O10" s="26"/>
       <c r="P10" s="26"/>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:42">
       <c r="A11" s="3" t="s">
         <v>61</v>
       </c>
@@ -12970,7 +12842,7 @@
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
     </row>
-    <row r="12" spans="1:28" ht="21" customHeight="1">
+    <row r="12" spans="1:42" ht="21" customHeight="1">
       <c r="A12" s="71" t="s">
         <v>69</v>
       </c>
@@ -13005,7 +12877,7 @@
       <c r="O12" s="26"/>
       <c r="P12" s="26"/>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:42">
       <c r="A13" s="74" t="s">
         <v>70</v>
       </c>
@@ -13040,7 +12912,7 @@
       <c r="O13" s="26"/>
       <c r="P13" s="26"/>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:42">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
@@ -13058,7 +12930,7 @@
       <c r="O14" s="26"/>
       <c r="P14" s="26"/>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:42">
       <c r="A15" s="21" t="s">
         <v>71</v>
       </c>
@@ -13071,7 +12943,7 @@
       <c r="D15" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="114" t="s">
+      <c r="E15" s="111" t="s">
         <v>75</v>
       </c>
       <c r="F15" s="26"/>
@@ -13086,7 +12958,7 @@
       <c r="O15" s="26"/>
       <c r="P15" s="26"/>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:42">
       <c r="A16" s="21" t="str" cm="1">
         <f t="array" ref="A16">rate_structure_1</f>
         <v>Residential water, inside</v>
@@ -13180,7 +13052,7 @@
       <c r="D19" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="114" t="s">
+      <c r="E19" s="111" t="s">
         <v>75</v>
       </c>
       <c r="F19" s="26"/>
@@ -13441,7 +13313,7 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:F13">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Sufficient">

--- a/Water_Utility_Rate_Model_MichaelPham.xlsx
+++ b/Water_Utility_Rate_Model_MichaelPham.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{965B75D7-33A8-42D1-9A7D-E5E2CBB8AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C0412B0-82E7-478A-A6CB-409D0658F8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="5" r:id="rId1"/>
@@ -875,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -927,7 +927,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -936,7 +935,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -963,20 +961,15 @@
     <xf numFmtId="6" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1150,6 +1143,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4989,16 +4985,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -5013,13 +5009,13 @@
     </row>
     <row r="2" spans="1:19" ht="21.75" customHeight="1">
       <c r="A2" s="26"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
@@ -5033,18 +5029,18 @@
       <c r="S2" s="26"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="B3" s="118" cm="1">
+      <c r="B3" s="111" cm="1">
         <f t="array" ref="B3">current_monthly_bill</f>
         <v>43.98827361563518</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="124" cm="1">
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="117" cm="1">
         <f t="array" ref="E3">proposed_monthly_bill</f>
         <v>47.346579804560264</v>
       </c>
-      <c r="F3" s="124"/>
-      <c r="G3" s="125"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="118"/>
       <c r="M3" s="26"/>
       <c r="N3" s="26"/>
       <c r="O3" s="26"/>
@@ -5054,12 +5050,12 @@
       <c r="S3" s="26"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="B4" s="120"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="127"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="120"/>
       <c r="M4" s="26"/>
       <c r="N4" s="26"/>
       <c r="O4" s="26"/>
@@ -5069,12 +5065,12 @@
       <c r="S4" s="26"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="B5" s="120"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="127"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="120"/>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
       <c r="O5" s="26"/>
@@ -5084,16 +5080,16 @@
       <c r="S5" s="26"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="128" t="s">
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="128"/>
-      <c r="G6" s="129"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
       <c r="O6" s="26"/>
@@ -5104,18 +5100,18 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="26"/>
-      <c r="B7" s="130" cm="1">
+      <c r="B7" s="123" cm="1">
         <f t="array" ref="B7">current_dscr</f>
         <v>0.72724242424242425</v>
       </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112" cm="1">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105" cm="1">
         <f t="array" ref="E7">proposed_dscr</f>
         <v>1.3110969696969696</v>
       </c>
-      <c r="F7" s="112"/>
-      <c r="G7" s="113"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="106"/>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
@@ -5131,12 +5127,12 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="26"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="113"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106"/>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
@@ -5152,12 +5148,12 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="26"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="113"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="106"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
@@ -5172,16 +5168,16 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="26"/>
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115" t="s">
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="116"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="109"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
@@ -5595,226 +5591,226 @@
       <c r="S29" s="26"/>
     </row>
     <row r="30" spans="1:19" ht="15" customHeight="1">
-      <c r="A30" s="149" t="s">
+      <c r="A30" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="150"/>
-      <c r="D30" s="150"/>
-      <c r="E30" s="150"/>
-      <c r="F30" s="150"/>
-      <c r="G30" s="150"/>
-      <c r="H30" s="150"/>
-      <c r="I30" s="150"/>
-      <c r="J30" s="150"/>
-      <c r="K30" s="150"/>
-      <c r="L30" s="150"/>
-      <c r="M30" s="150"/>
-      <c r="N30" s="150"/>
-      <c r="O30" s="150"/>
-      <c r="P30" s="150"/>
+      <c r="B30" s="143"/>
+      <c r="C30" s="143"/>
+      <c r="D30" s="143"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="143"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="143"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="143"/>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="150"/>
-      <c r="B31" s="150"/>
-      <c r="C31" s="150"/>
-      <c r="D31" s="150"/>
-      <c r="E31" s="150"/>
-      <c r="F31" s="150"/>
-      <c r="G31" s="150"/>
-      <c r="H31" s="150"/>
-      <c r="I31" s="150"/>
-      <c r="J31" s="150"/>
-      <c r="K31" s="150"/>
-      <c r="L31" s="150"/>
-      <c r="M31" s="150"/>
-      <c r="N31" s="150"/>
-      <c r="O31" s="150"/>
-      <c r="P31" s="150"/>
+      <c r="A31" s="143"/>
+      <c r="B31" s="143"/>
+      <c r="C31" s="143"/>
+      <c r="D31" s="143"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="143"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="143"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="143"/>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="150"/>
-      <c r="B32" s="150"/>
-      <c r="C32" s="150"/>
-      <c r="D32" s="150"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="150"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="150"/>
-      <c r="K32" s="150"/>
-      <c r="L32" s="150"/>
-      <c r="M32" s="150"/>
-      <c r="N32" s="150"/>
-      <c r="O32" s="150"/>
-      <c r="P32" s="150"/>
+      <c r="A32" s="143"/>
+      <c r="B32" s="143"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="143"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="143"/>
+      <c r="I32" s="143"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="143"/>
+      <c r="L32" s="143"/>
+      <c r="M32" s="143"/>
+      <c r="N32" s="143"/>
+      <c r="O32" s="143"/>
+      <c r="P32" s="143"/>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="150"/>
-      <c r="B33" s="150"/>
-      <c r="C33" s="150"/>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="150"/>
-      <c r="G33" s="150"/>
-      <c r="H33" s="150"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="150"/>
-      <c r="K33" s="150"/>
-      <c r="L33" s="150"/>
-      <c r="M33" s="150"/>
-      <c r="N33" s="150"/>
-      <c r="O33" s="150"/>
-      <c r="P33" s="150"/>
+      <c r="A33" s="143"/>
+      <c r="B33" s="143"/>
+      <c r="C33" s="143"/>
+      <c r="D33" s="143"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="143"/>
+      <c r="I33" s="143"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="143"/>
+      <c r="L33" s="143"/>
+      <c r="M33" s="143"/>
+      <c r="N33" s="143"/>
+      <c r="O33" s="143"/>
+      <c r="P33" s="143"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="151" t="s">
+      <c r="A34" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="152"/>
-      <c r="C34" s="152"/>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="152"/>
-      <c r="G34" s="152"/>
-      <c r="H34" s="152"/>
-      <c r="I34" s="152"/>
-      <c r="J34" s="152"/>
-      <c r="K34" s="152"/>
-      <c r="L34" s="152"/>
-      <c r="M34" s="152"/>
-      <c r="N34" s="152"/>
-      <c r="O34" s="152"/>
-      <c r="P34" s="152"/>
+      <c r="B34" s="145"/>
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="145"/>
+      <c r="G34" s="145"/>
+      <c r="H34" s="145"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+      <c r="M34" s="145"/>
+      <c r="N34" s="145"/>
+      <c r="O34" s="145"/>
+      <c r="P34" s="145"/>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="152"/>
-      <c r="B35" s="152"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="152"/>
-      <c r="I35" s="152"/>
-      <c r="J35" s="152"/>
-      <c r="K35" s="152"/>
-      <c r="L35" s="152"/>
-      <c r="M35" s="152"/>
-      <c r="N35" s="152"/>
-      <c r="O35" s="152"/>
-      <c r="P35" s="152"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="145"/>
+      <c r="F35" s="145"/>
+      <c r="G35" s="145"/>
+      <c r="H35" s="145"/>
+      <c r="I35" s="145"/>
+      <c r="J35" s="145"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="145"/>
+      <c r="M35" s="145"/>
+      <c r="N35" s="145"/>
+      <c r="O35" s="145"/>
+      <c r="P35" s="145"/>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="152"/>
-      <c r="B36" s="152"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
-      <c r="F36" s="152"/>
-      <c r="G36" s="152"/>
-      <c r="H36" s="152"/>
-      <c r="I36" s="152"/>
-      <c r="J36" s="152"/>
-      <c r="K36" s="152"/>
-      <c r="L36" s="152"/>
-      <c r="M36" s="152"/>
-      <c r="N36" s="152"/>
-      <c r="O36" s="152"/>
-      <c r="P36" s="152"/>
+      <c r="A36" s="145"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="145"/>
+      <c r="D36" s="145"/>
+      <c r="E36" s="145"/>
+      <c r="F36" s="145"/>
+      <c r="G36" s="145"/>
+      <c r="H36" s="145"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+      <c r="M36" s="145"/>
+      <c r="N36" s="145"/>
+      <c r="O36" s="145"/>
+      <c r="P36" s="145"/>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="152"/>
-      <c r="B37" s="152"/>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
-      <c r="F37" s="152"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="152"/>
-      <c r="I37" s="152"/>
-      <c r="J37" s="152"/>
-      <c r="K37" s="152"/>
-      <c r="L37" s="152"/>
-      <c r="M37" s="152"/>
-      <c r="N37" s="152"/>
-      <c r="O37" s="152"/>
-      <c r="P37" s="152"/>
+      <c r="A37" s="145"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="145"/>
+      <c r="D37" s="145"/>
+      <c r="E37" s="145"/>
+      <c r="F37" s="145"/>
+      <c r="G37" s="145"/>
+      <c r="H37" s="145"/>
+      <c r="I37" s="145"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+      <c r="M37" s="145"/>
+      <c r="N37" s="145"/>
+      <c r="O37" s="145"/>
+      <c r="P37" s="145"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="152" t="s">
+      <c r="A38" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="152"/>
-      <c r="C38" s="152"/>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="152"/>
-      <c r="H38" s="152"/>
-      <c r="I38" s="152"/>
-      <c r="J38" s="152"/>
-      <c r="K38" s="152"/>
-      <c r="L38" s="152"/>
-      <c r="M38" s="152"/>
-      <c r="N38" s="152"/>
-      <c r="O38" s="152"/>
-      <c r="P38" s="152"/>
+      <c r="B38" s="145"/>
+      <c r="C38" s="145"/>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="145"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="145"/>
+      <c r="N38" s="145"/>
+      <c r="O38" s="145"/>
+      <c r="P38" s="145"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="152"/>
-      <c r="B39" s="152"/>
-      <c r="C39" s="152"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="152"/>
-      <c r="F39" s="152"/>
-      <c r="G39" s="152"/>
-      <c r="H39" s="152"/>
-      <c r="I39" s="152"/>
-      <c r="J39" s="152"/>
-      <c r="K39" s="152"/>
-      <c r="L39" s="152"/>
-      <c r="M39" s="152"/>
-      <c r="N39" s="152"/>
-      <c r="O39" s="152"/>
-      <c r="P39" s="152"/>
+      <c r="A39" s="145"/>
+      <c r="B39" s="145"/>
+      <c r="C39" s="145"/>
+      <c r="D39" s="145"/>
+      <c r="E39" s="145"/>
+      <c r="F39" s="145"/>
+      <c r="G39" s="145"/>
+      <c r="H39" s="145"/>
+      <c r="I39" s="145"/>
+      <c r="J39" s="145"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="145"/>
+      <c r="N39" s="145"/>
+      <c r="O39" s="145"/>
+      <c r="P39" s="145"/>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="152"/>
-      <c r="B40" s="152"/>
-      <c r="C40" s="152"/>
-      <c r="D40" s="152"/>
-      <c r="E40" s="152"/>
-      <c r="F40" s="152"/>
-      <c r="G40" s="152"/>
-      <c r="H40" s="152"/>
-      <c r="I40" s="152"/>
-      <c r="J40" s="152"/>
-      <c r="K40" s="152"/>
-      <c r="L40" s="152"/>
-      <c r="M40" s="152"/>
-      <c r="N40" s="152"/>
-      <c r="O40" s="152"/>
-      <c r="P40" s="152"/>
+      <c r="A40" s="145"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="145"/>
+      <c r="D40" s="145"/>
+      <c r="E40" s="145"/>
+      <c r="F40" s="145"/>
+      <c r="G40" s="145"/>
+      <c r="H40" s="145"/>
+      <c r="I40" s="145"/>
+      <c r="J40" s="145"/>
+      <c r="K40" s="145"/>
+      <c r="L40" s="145"/>
+      <c r="M40" s="145"/>
+      <c r="N40" s="145"/>
+      <c r="O40" s="145"/>
+      <c r="P40" s="145"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="152"/>
-      <c r="B41" s="152"/>
-      <c r="C41" s="152"/>
-      <c r="D41" s="152"/>
-      <c r="E41" s="152"/>
-      <c r="F41" s="152"/>
-      <c r="G41" s="152"/>
-      <c r="H41" s="152"/>
-      <c r="I41" s="152"/>
-      <c r="J41" s="152"/>
-      <c r="K41" s="152"/>
-      <c r="L41" s="152"/>
-      <c r="M41" s="152"/>
-      <c r="N41" s="152"/>
-      <c r="O41" s="152"/>
-      <c r="P41" s="152"/>
+      <c r="A41" s="145"/>
+      <c r="B41" s="145"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="145"/>
+      <c r="E41" s="145"/>
+      <c r="F41" s="145"/>
+      <c r="G41" s="145"/>
+      <c r="H41" s="145"/>
+      <c r="I41" s="145"/>
+      <c r="J41" s="145"/>
+      <c r="K41" s="145"/>
+      <c r="L41" s="145"/>
+      <c r="M41" s="145"/>
+      <c r="N41" s="145"/>
+      <c r="O41" s="145"/>
+      <c r="P41" s="145"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -5904,10 +5900,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="21">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="137"/>
+      <c r="B1" s="130"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
@@ -6003,10 +5999,10 @@
       <c r="CQ1" s="26"/>
     </row>
     <row r="2" spans="1:95">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="139"/>
+      <c r="B2" s="132"/>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
@@ -6102,8 +6098,8 @@
       <c r="CQ2" s="26"/>
     </row>
     <row r="3" spans="1:95">
-      <c r="A3" s="97"/>
-      <c r="B3" s="76"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="70"/>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
@@ -6199,10 +6195,10 @@
       <c r="CQ3" s="26"/>
     </row>
     <row r="4" spans="1:95">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="141"/>
+      <c r="B4" s="134"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -6402,7 +6398,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="26"/>
-      <c r="D6" s="110" t="s">
+      <c r="D6" s="103" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="6"/>
@@ -6508,7 +6504,7 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="65">
         <v>0.03</v>
       </c>
       <c r="F7" s="26"/>
@@ -6711,12 +6707,12 @@
       <c r="A9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="51">
         <f>SUM(K13:K15,K18:K20) * 12 * 1000</f>
         <v>410100000</v>
       </c>
       <c r="C9" s="26"/>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="66" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="2">
@@ -6936,31 +6932,31 @@
         <v>2030</v>
       </c>
       <c r="H11" s="26"/>
-      <c r="I11" s="133" t="s">
+      <c r="I11" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="135"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="128"/>
       <c r="P11" s="28"/>
-      <c r="Q11" s="35" t="s">
+      <c r="Q11" s="91" t="s">
         <v>23</v>
       </c>
       <c r="R11" s="21">
         <v>2026</v>
       </c>
       <c r="S11" s="26"/>
-      <c r="T11" s="98" t="s">
+      <c r="T11" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="U11" s="102"/>
-      <c r="V11" s="99" t="s">
+      <c r="U11" s="95"/>
+      <c r="V11" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="W11" s="106" t="s">
+      <c r="W11" s="99" t="s">
         <v>25</v>
       </c>
       <c r="X11" s="17">
@@ -6978,7 +6974,7 @@
         <f>Z11+1</f>
         <v>2029</v>
       </c>
-      <c r="AB11" s="89">
+      <c r="AB11" s="82">
         <f>AA11+1</f>
         <v>2030</v>
       </c>
@@ -7062,60 +7058,60 @@
       <c r="I12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="80" t="s">
+      <c r="J12" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="63" cm="1">
+      <c r="K12" s="61" cm="1">
         <f t="array" ref="K12">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="L12" s="63">
+      <c r="L12" s="61">
         <f>K12+1</f>
         <v>2027</v>
       </c>
-      <c r="M12" s="63">
+      <c r="M12" s="61">
         <f t="shared" ref="M12:O12" si="1">L12+1</f>
         <v>2028</v>
       </c>
-      <c r="N12" s="63">
+      <c r="N12" s="61">
         <f t="shared" si="1"/>
         <v>2029</v>
       </c>
-      <c r="O12" s="63">
+      <c r="O12" s="61">
         <f t="shared" si="1"/>
         <v>2030</v>
       </c>
       <c r="P12" s="28"/>
-      <c r="Q12" s="1" t="s">
+      <c r="Q12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="R12" s="36">
+      <c r="R12" s="35">
         <v>725000</v>
       </c>
       <c r="S12" s="26"/>
-      <c r="T12" s="100" t="s">
+      <c r="T12" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="U12" s="74"/>
-      <c r="V12" s="101"/>
-      <c r="W12" s="107"/>
-      <c r="X12" s="59">
+      <c r="U12" s="69"/>
+      <c r="V12" s="94"/>
+      <c r="W12" s="100"/>
+      <c r="X12" s="57">
         <f>U13</f>
         <v>165000</v>
       </c>
-      <c r="Y12" s="43">
+      <c r="Y12" s="41">
         <f>U14</f>
         <v>165000</v>
       </c>
-      <c r="Z12" s="43">
+      <c r="Z12" s="41">
         <f>U15</f>
         <v>175000</v>
       </c>
-      <c r="AA12" s="43">
+      <c r="AA12" s="41">
         <f>U16</f>
         <v>175000</v>
       </c>
-      <c r="AB12" s="43">
+      <c r="AB12" s="41">
         <f>U17</f>
         <v>175000</v>
       </c>
@@ -7198,11 +7194,11 @@
       <c r="F13" s="14"/>
       <c r="G13" s="15"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="83" t="str" cm="1">
+      <c r="I13" s="76" t="str" cm="1">
         <f t="array" ref="I13">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="J13" s="60" t="s">
+      <c r="J13" s="58" t="s">
         <v>28</v>
       </c>
       <c r="K13" s="34">
@@ -7225,17 +7221,17 @@
         <v>18356</v>
       </c>
       <c r="P13" s="28"/>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="36">
+      <c r="R13" s="35">
         <v>135000</v>
       </c>
       <c r="S13" s="26"/>
-      <c r="T13" s="103">
+      <c r="T13" s="96">
         <v>2026</v>
       </c>
-      <c r="U13" s="104">
+      <c r="U13" s="97">
         <v>165000</v>
       </c>
       <c r="V13" s="26"/>
@@ -7320,24 +7316,24 @@
       <c r="B14" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="37">
         <v>17</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="38">
         <v>20</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="37">
         <v>20</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="37">
         <v>20</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="37">
         <v>20</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="60" t="s">
+      <c r="J14" s="58" t="s">
         <v>32</v>
       </c>
       <c r="K14" s="34">
@@ -7360,18 +7356,18 @@
         <v>4589</v>
       </c>
       <c r="P14" s="28"/>
-      <c r="Q14" s="1" t="s">
+      <c r="Q14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R14" s="37">
+      <c r="R14" s="36">
         <v>64000</v>
       </c>
       <c r="S14" s="26"/>
-      <c r="T14" s="103">
+      <c r="T14" s="96">
         <f>T13+1</f>
         <v>2027</v>
       </c>
-      <c r="U14" s="105">
+      <c r="U14" s="98">
         <v>165000</v>
       </c>
       <c r="V14" s="26"/>
@@ -7459,7 +7455,7 @@
       <c r="C15" s="34">
         <v>2000</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="39">
         <v>2000</v>
       </c>
       <c r="E15" s="34">
@@ -7472,8 +7468,8 @@
         <v>2000</v>
       </c>
       <c r="H15" s="26"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="60" t="s">
+      <c r="I15" s="69"/>
+      <c r="J15" s="58" t="s">
         <v>35</v>
       </c>
       <c r="K15" s="34">
@@ -7496,18 +7492,18 @@
         <v>654</v>
       </c>
       <c r="P15" s="28"/>
-      <c r="Q15" s="1" t="s">
+      <c r="Q15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="R15" s="36">
+      <c r="R15" s="35">
         <v>130500</v>
       </c>
       <c r="S15" s="26"/>
-      <c r="T15" s="103">
+      <c r="T15" s="96">
         <f>T14+1</f>
         <v>2028</v>
       </c>
-      <c r="U15" s="105">
+      <c r="U15" s="98">
         <v>175000</v>
       </c>
       <c r="V15" s="26"/>
@@ -7586,7 +7582,7 @@
       <c r="CQ15" s="26"/>
     </row>
     <row r="16" spans="1:95">
-      <c r="A16" s="41">
+      <c r="A16" s="40">
         <v>2520</v>
       </c>
       <c r="B16" s="32"/>
@@ -7604,18 +7600,18 @@
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
-      <c r="Q16" s="1" t="s">
+      <c r="Q16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R16" s="36">
+      <c r="R16" s="35">
         <v>52000</v>
       </c>
       <c r="S16" s="26"/>
-      <c r="T16" s="103">
+      <c r="T16" s="96">
         <f t="shared" ref="T16:T17" si="2">T15+1</f>
         <v>2029</v>
       </c>
-      <c r="U16" s="105">
+      <c r="U16" s="98">
         <v>175000</v>
       </c>
       <c r="V16" s="26"/>
@@ -7702,7 +7698,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="16"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="102" t="s">
+      <c r="I17" s="95" t="s">
         <v>38</v>
       </c>
       <c r="J17" s="17" t="s">
@@ -7712,35 +7708,35 @@
         <f t="array" ref="K17">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="L17" s="63">
+      <c r="L17" s="61">
         <f>K17+1</f>
         <v>2027</v>
       </c>
-      <c r="M17" s="63">
+      <c r="M17" s="61">
         <f t="shared" ref="M17:O17" si="3">L17+1</f>
         <v>2028</v>
       </c>
-      <c r="N17" s="63">
+      <c r="N17" s="61">
         <f t="shared" si="3"/>
         <v>2029</v>
       </c>
-      <c r="O17" s="63">
+      <c r="O17" s="61">
         <f t="shared" si="3"/>
         <v>2030</v>
       </c>
       <c r="P17" s="28"/>
-      <c r="Q17" s="1" t="s">
+      <c r="Q17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="R17" s="36">
+      <c r="R17" s="35">
         <v>250000</v>
       </c>
       <c r="S17" s="26"/>
-      <c r="T17" s="56">
+      <c r="T17" s="54">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="U17" s="105">
+      <c r="U17" s="98">
         <v>175000</v>
       </c>
       <c r="V17" s="26"/>
@@ -7836,7 +7832,7 @@
       <c r="J18" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="82">
+      <c r="K18" s="75">
         <v>5500</v>
       </c>
       <c r="L18" s="21" cm="1">
@@ -7856,10 +7852,10 @@
         <v>5724</v>
       </c>
       <c r="P18" s="28"/>
-      <c r="Q18" s="1" t="s">
+      <c r="Q18" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="R18" s="36">
+      <c r="R18" s="35">
         <v>144000</v>
       </c>
       <c r="S18" s="26"/>
@@ -7947,19 +7943,19 @@
       <c r="B19" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="37">
         <v>1.75</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="38">
         <v>1.5</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="37">
         <v>1.75</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="37">
         <v>1.75</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="37">
         <v>2</v>
       </c>
       <c r="H19" s="26"/>
@@ -7967,7 +7963,7 @@
       <c r="J19" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="82">
+      <c r="K19" s="75">
         <v>5000</v>
       </c>
       <c r="L19" s="21" cm="1">
@@ -8074,27 +8070,27 @@
       <c r="B20" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="37">
         <v>1.75</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="38">
         <v>2.5</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="37">
         <v>2.5</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="37">
         <v>2.5</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="37">
         <v>2.5</v>
       </c>
       <c r="H20" s="26"/>
-      <c r="I20" s="74"/>
+      <c r="I20" s="69"/>
       <c r="J20" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="82">
+      <c r="K20" s="75">
         <v>995</v>
       </c>
       <c r="L20" s="21" cm="1">
@@ -8201,26 +8197,26 @@
       <c r="B21" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="37">
         <v>1.75</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="38">
         <v>3.5</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="37">
         <v>3.75</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="37">
         <v>3.75</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21" s="37">
         <v>3.75</v>
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="124"/>
+      <c r="L21" s="124"/>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
@@ -8315,11 +8311,11 @@
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="132" t="s">
+      <c r="J22" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="K22" s="132"/>
-      <c r="L22" s="132"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="125"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
       <c r="O22" s="26"/>
@@ -8510,19 +8506,19 @@
       <c r="B24" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="37">
         <v>38</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="38">
         <v>43</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="37">
         <v>43</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="37">
         <v>43</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="37">
         <v>43</v>
       </c>
       <c r="H24" s="26"/>
@@ -8726,7 +8722,7 @@
       <c r="CQ25" s="26"/>
     </row>
     <row r="26" spans="1:95">
-      <c r="A26" s="41">
+      <c r="A26" s="40">
         <f>B8-A16</f>
         <v>550</v>
       </c>
@@ -9028,19 +9024,19 @@
       <c r="B29" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="39">
+      <c r="C29" s="38">
         <v>2.75</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="37">
         <v>2.75</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="37">
         <v>2.75</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="37">
         <v>2.75</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="37">
         <v>2.75</v>
       </c>
       <c r="H29" s="26"/>
@@ -9139,19 +9135,19 @@
       <c r="B30" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="38">
         <v>2.75</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="37">
         <v>2.75</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="37">
         <v>2.75</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="37">
         <v>2.75</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="37">
         <v>2.75</v>
       </c>
       <c r="H30" s="26"/>
@@ -9250,19 +9246,19 @@
       <c r="B31" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="38">
         <v>2.75</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="37">
         <v>2.75</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="37">
         <v>2.75</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="37">
         <v>2.75</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31" s="37">
         <v>2.75</v>
       </c>
       <c r="H31" s="26"/>
@@ -9422,13 +9418,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="18.75">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
@@ -9534,24 +9530,24 @@
       <c r="BD2" s="26"/>
     </row>
     <row r="3" spans="1:56" ht="18.75">
-      <c r="A3" s="143" t="s">
+      <c r="A3" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="145"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="138"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
-      <c r="I3" s="143" t="s">
+      <c r="I3" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="145"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137"/>
+      <c r="N3" s="138"/>
       <c r="O3" s="26"/>
       <c r="P3" s="26"/>
       <c r="Q3" s="26"/>
@@ -9596,24 +9592,24 @@
       <c r="BD3" s="26"/>
     </row>
     <row r="4" spans="1:56">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="78"/>
       <c r="G4" s="26"/>
       <c r="H4" s="26"/>
-      <c r="I4" s="84" t="s">
+      <c r="I4" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="85"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="78"/>
       <c r="O4" s="26"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -9621,20 +9617,20 @@
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
       <c r="U4" s="26"/>
-      <c r="V4" s="81"/>
-      <c r="W4" s="81">
+      <c r="V4" s="74"/>
+      <c r="W4" s="74">
         <f t="shared" ref="W4:Z4" si="0">$B$22</f>
         <v>1620495</v>
       </c>
-      <c r="X4" s="81">
+      <c r="X4" s="74">
         <f t="shared" si="0"/>
         <v>1620495</v>
       </c>
-      <c r="Y4" s="81">
+      <c r="Y4" s="74">
         <f t="shared" si="0"/>
         <v>1620495</v>
       </c>
-      <c r="Z4" s="81">
+      <c r="Z4" s="74">
         <f t="shared" si="0"/>
         <v>1620495</v>
       </c>
@@ -9670,7 +9666,7 @@
       <c r="BD4" s="26"/>
     </row>
     <row r="5" spans="1:56">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="58" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="21" cm="1">
@@ -9695,7 +9691,7 @@
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
-      <c r="I5" s="60" t="s">
+      <c r="I5" s="58" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="21" cm="1">
@@ -9765,23 +9761,23 @@
       <c r="A6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="57" cm="1">
+      <c r="B6" s="55" cm="1">
         <f t="array" ref="B6">num_accountsRS1</f>
         <v>2520</v>
       </c>
-      <c r="C6" s="58" cm="1">
+      <c r="C6" s="56" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+pop_growth_rate),0)</f>
         <v>2545</v>
       </c>
-      <c r="D6" s="58" cm="1">
+      <c r="D6" s="56" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+pop_growth_rate),0)</f>
         <v>2570</v>
       </c>
-      <c r="E6" s="58" cm="1">
+      <c r="E6" s="56" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+pop_growth_rate),0)</f>
         <v>2596</v>
       </c>
-      <c r="F6" s="58" cm="1">
+      <c r="F6" s="56" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
@@ -9790,23 +9786,23 @@
       <c r="I6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="57" cm="1">
+      <c r="J6" s="55" cm="1">
         <f t="array" ref="J6">num_accountsRS1</f>
         <v>2520</v>
       </c>
-      <c r="K6" s="58" cm="1">
+      <c r="K6" s="56" cm="1">
         <f t="array" ref="K6">ROUND(J6 * (1+pop_growth_rate),0)</f>
         <v>2545</v>
       </c>
-      <c r="L6" s="58" cm="1">
+      <c r="L6" s="56" cm="1">
         <f t="array" ref="L6">ROUND(K6 * (1+pop_growth_rate),0)</f>
         <v>2570</v>
       </c>
-      <c r="M6" s="58" cm="1">
+      <c r="M6" s="56" cm="1">
         <f t="array" ref="M6">ROUND(L6 * (1+pop_growth_rate),0)</f>
         <v>2596</v>
       </c>
-      <c r="N6" s="58" cm="1">
+      <c r="N6" s="56" cm="1">
         <f t="array" ref="N6">ROUND(M6 * (1+pop_growth_rate),0)</f>
         <v>2622</v>
       </c>
@@ -9857,41 +9853,41 @@
       <c r="A7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="54" cm="1">
+      <c r="B7" s="52" cm="1">
         <f t="array" ref="B7:F7">base_chargeRS1 * 12 * RS1_num_accounts</f>
         <v>514080</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="49">
         <v>610800</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="49">
         <v>616800</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="49">
         <v>623040</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="49">
         <v>629280</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="90" cm="1">
+      <c r="J7" s="83" cm="1">
         <f t="array" ref="J7:N7">RS1_base_charge2026 * 12 * RS1_num_accounts</f>
         <v>514080</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7" s="84">
         <v>519180</v>
       </c>
-      <c r="L7" s="91">
+      <c r="L7" s="84">
         <v>524280</v>
       </c>
-      <c r="M7" s="91">
+      <c r="M7" s="84">
         <v>529584</v>
       </c>
-      <c r="N7" s="91">
+      <c r="N7" s="84">
         <v>534888</v>
       </c>
       <c r="O7" s="26"/>
@@ -9941,23 +9937,23 @@
       <c r="A8" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="59" cm="1">
+      <c r="B8" s="57" cm="1">
         <f t="array" ref="B8:B10">RS1_block_consumption2026 * RS1_vrates2026 *12</f>
         <v>370440</v>
       </c>
-      <c r="C8" s="43" cm="1">
+      <c r="C8" s="41" cm="1">
         <f t="array" ref="C8:C10">RS1_block_consumption2027 * RS1_vrates2027 *12</f>
         <v>320688</v>
       </c>
-      <c r="D8" s="43" cm="1">
+      <c r="D8" s="41" cm="1">
         <f t="array" ref="D8:D10">RS1_block_consumption2028 * RS1_vrates2028 *12</f>
         <v>377874</v>
       </c>
-      <c r="E8" s="43" cm="1">
+      <c r="E8" s="41" cm="1">
         <f t="array" ref="E8:E10">RS1_block_consumption2029 * RS1_vrates2029 *12</f>
         <v>381654</v>
       </c>
-      <c r="F8" s="43" cm="1">
+      <c r="F8" s="41" cm="1">
         <f t="array" ref="F8:F10">RS1_block_consumption2030 * RS1_vrates2030 *12</f>
         <v>440544</v>
       </c>
@@ -9966,23 +9962,23 @@
       <c r="I8" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="59" cm="1">
+      <c r="J8" s="57" cm="1">
         <f t="array" ref="J8:J10">RS1_block_consumption2026 * RS1_vrates2026 *12</f>
         <v>370440</v>
       </c>
-      <c r="K8" s="59" cm="1">
+      <c r="K8" s="57" cm="1">
         <f t="array" ref="K8:K10">RS1_block_consumption2027 * RS1_vrates2026 *12</f>
         <v>374136</v>
       </c>
-      <c r="L8" s="59" cm="1">
+      <c r="L8" s="57" cm="1">
         <f t="array" ref="L8:L10">RS1_block_consumption2028 * RS1_vrates2026 *12</f>
         <v>377874</v>
       </c>
-      <c r="M8" s="59" cm="1">
+      <c r="M8" s="57" cm="1">
         <f t="array" ref="M8:M10">RS1_block_consumption2029 * RS1_vrates2026 *12</f>
         <v>381654</v>
       </c>
-      <c r="N8" s="59" cm="1">
+      <c r="N8" s="57" cm="1">
         <f t="array" ref="N8:N10">RS1_block_consumption2030 * RS1_vrates2026 *12</f>
         <v>385476</v>
       </c>
@@ -10033,19 +10029,19 @@
       <c r="A9" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="59">
+      <c r="B9" s="57">
         <v>92610</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="41">
         <v>133620</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="41">
         <v>134970</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="41">
         <v>136320</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="41">
         <v>137670</v>
       </c>
       <c r="G9" s="26"/>
@@ -10053,19 +10049,19 @@
       <c r="I9" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="57">
         <v>92610</v>
       </c>
-      <c r="K9" s="59">
+      <c r="K9" s="57">
         <v>93534</v>
       </c>
-      <c r="L9" s="59">
+      <c r="L9" s="57">
         <v>94479</v>
       </c>
-      <c r="M9" s="59">
+      <c r="M9" s="57">
         <v>95424</v>
       </c>
-      <c r="N9" s="59">
+      <c r="N9" s="57">
         <v>96369</v>
       </c>
       <c r="O9" s="26"/>
@@ -10115,39 +10111,39 @@
       <c r="A10" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="59">
+      <c r="B10" s="57">
         <v>13230</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="41">
         <v>26712</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="41">
         <v>28890</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="41">
         <v>29160</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="41">
         <v>29430</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="66">
+      <c r="J10" s="64">
         <v>13230</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="64">
         <v>13356</v>
       </c>
-      <c r="L10" s="66">
+      <c r="L10" s="64">
         <v>13482</v>
       </c>
-      <c r="M10" s="66">
+      <c r="M10" s="64">
         <v>13608</v>
       </c>
-      <c r="N10" s="66">
+      <c r="N10" s="64">
         <v>13734</v>
       </c>
       <c r="O10" s="26"/>
@@ -10194,51 +10190,51 @@
       <c r="BD10" s="26"/>
     </row>
     <row r="11" spans="1:56">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="87">
+      <c r="B11" s="80">
         <f>SUM(B7:B10)</f>
         <v>990360</v>
       </c>
-      <c r="C11" s="87">
+      <c r="C11" s="80">
         <f t="shared" ref="C11:F11" si="3">SUM(C7:C10)</f>
         <v>1091820</v>
       </c>
-      <c r="D11" s="87">
+      <c r="D11" s="80">
         <f t="shared" si="3"/>
         <v>1158534</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="80">
         <f t="shared" si="3"/>
         <v>1170174</v>
       </c>
-      <c r="F11" s="87">
+      <c r="F11" s="80">
         <f t="shared" si="3"/>
         <v>1236924</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="44" t="s">
+      <c r="I11" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="62">
+      <c r="J11" s="60">
         <f>SUM(J7:J10)</f>
         <v>990360</v>
       </c>
-      <c r="K11" s="62">
+      <c r="K11" s="60">
         <f t="shared" ref="K11" si="4">SUM(K7:K10)</f>
         <v>1000206</v>
       </c>
-      <c r="L11" s="62">
+      <c r="L11" s="60">
         <f t="shared" ref="L11" si="5">SUM(L7:L10)</f>
         <v>1010115</v>
       </c>
-      <c r="M11" s="62">
+      <c r="M11" s="60">
         <f t="shared" ref="M11" si="6">SUM(M7:M10)</f>
         <v>1020270</v>
       </c>
-      <c r="N11" s="62">
+      <c r="N11" s="60">
         <f t="shared" ref="N11" si="7">SUM(N7:N10)</f>
         <v>1030467</v>
       </c>
@@ -10344,24 +10340,24 @@
       <c r="BD12" s="26"/>
     </row>
     <row r="13" spans="1:56">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="81" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="89"/>
+      <c r="F13" s="82"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="104"/>
       <c r="O13" s="26"/>
       <c r="P13" s="26"/>
       <c r="Q13" s="26"/>
@@ -10431,26 +10427,26 @@
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="J14" s="21" cm="1">
+      <c r="J14" s="54" cm="1">
         <f t="array" ref="J14">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="54">
         <f>J14+1</f>
         <v>2027</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="54">
         <f t="shared" ref="L14:N14" si="9">K14+1</f>
         <v>2028</v>
       </c>
-      <c r="M14" s="21">
+      <c r="M14" s="54">
         <f t="shared" si="9"/>
         <v>2029</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="54">
         <f t="shared" si="9"/>
         <v>2030</v>
       </c>
@@ -10498,51 +10494,51 @@
       <c r="BD14" s="26"/>
     </row>
     <row r="15" spans="1:56">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="57" cm="1">
+      <c r="B15" s="55" cm="1">
         <f t="array" ref="B15">num_accountsRS2</f>
         <v>550</v>
       </c>
-      <c r="C15" s="58" cm="1">
+      <c r="C15" s="56" cm="1">
         <f t="array" ref="C15">ROUND(B15*(1+pop_growth_rate),0)</f>
         <v>556</v>
       </c>
-      <c r="D15" s="58" cm="1">
+      <c r="D15" s="56" cm="1">
         <f t="array" ref="D15">ROUND(C15*(1+pop_growth_rate),0)</f>
         <v>562</v>
       </c>
-      <c r="E15" s="58" cm="1">
+      <c r="E15" s="56" cm="1">
         <f t="array" ref="E15">ROUND(D15*(1+pop_growth_rate),0)</f>
         <v>568</v>
       </c>
-      <c r="F15" s="58" cm="1">
+      <c r="F15" s="56" cm="1">
         <f t="array" ref="F15">ROUND(E15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="57" cm="1">
+      <c r="J15" s="55" cm="1">
         <f t="array" ref="J15">num_accountsRS2</f>
         <v>550</v>
       </c>
-      <c r="K15" s="58" cm="1">
+      <c r="K15" s="56" cm="1">
         <f t="array" ref="K15">ROUND(J15*(1+pop_growth_rate),0)</f>
         <v>556</v>
       </c>
-      <c r="L15" s="58" cm="1">
+      <c r="L15" s="56" cm="1">
         <f t="array" ref="L15">ROUND(K15*(1+pop_growth_rate),0)</f>
         <v>562</v>
       </c>
-      <c r="M15" s="58" cm="1">
+      <c r="M15" s="56" cm="1">
         <f t="array" ref="M15">ROUND(L15*(1+pop_growth_rate),0)</f>
         <v>568</v>
       </c>
-      <c r="N15" s="58" cm="1">
+      <c r="N15" s="56" cm="1">
         <f t="array" ref="N15">ROUND(M15*(1+pop_growth_rate),0)</f>
         <v>574</v>
       </c>
@@ -10590,23 +10586,23 @@
       <c r="BD15" s="26"/>
     </row>
     <row r="16" spans="1:56">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="90" cm="1">
+      <c r="B16" s="83" cm="1">
         <f t="array" ref="B16:F16">base_chargeRS2 * 12 * RS2_num_accounts</f>
         <v>250800</v>
       </c>
-      <c r="C16" s="91">
+      <c r="C16" s="84">
         <v>286896</v>
       </c>
-      <c r="D16" s="91">
+      <c r="D16" s="84">
         <v>289992</v>
       </c>
-      <c r="E16" s="91">
+      <c r="E16" s="84">
         <v>293088</v>
       </c>
-      <c r="F16" s="91">
+      <c r="F16" s="84">
         <v>296184</v>
       </c>
       <c r="G16" s="26"/>
@@ -10614,20 +10610,20 @@
       <c r="I16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="54" cm="1">
+      <c r="J16" s="52" cm="1">
         <f t="array" ref="J16:N16">RS2_base_charge2026 * 12 * RS2_num_accounts</f>
         <v>250800</v>
       </c>
-      <c r="K16" s="51">
+      <c r="K16" s="49">
         <v>253536</v>
       </c>
-      <c r="L16" s="51">
+      <c r="L16" s="49">
         <v>256272</v>
       </c>
-      <c r="M16" s="51">
+      <c r="M16" s="49">
         <v>259008</v>
       </c>
-      <c r="N16" s="51">
+      <c r="N16" s="49">
         <v>261744</v>
       </c>
       <c r="O16" s="26"/>
@@ -10677,23 +10673,23 @@
       <c r="A17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="55" cm="1">
+      <c r="B17" s="53" cm="1">
         <f t="array" ref="B17:B19">RS2_block_consumption2026 * RS2_vrates2026 *12</f>
         <v>181500</v>
       </c>
-      <c r="C17" s="52" cm="1">
+      <c r="C17" s="50" cm="1">
         <f t="array" ref="C17:C19">RS2_block_consumption2027 * RS2_vrates2027 *12</f>
         <v>183315</v>
       </c>
-      <c r="D17" s="52" cm="1">
+      <c r="D17" s="50" cm="1">
         <f t="array" ref="D17:D19">RS2_block_consumption2028 * RS2_vrates2028 *12</f>
         <v>185163</v>
       </c>
-      <c r="E17" s="52" cm="1">
+      <c r="E17" s="50" cm="1">
         <f t="array" ref="E17:E19">RS2_block_consumption2029 * RS2_vrates2029 *12</f>
         <v>187011</v>
       </c>
-      <c r="F17" s="52" cm="1">
+      <c r="F17" s="50" cm="1">
         <f t="array" ref="F17:F19">RS2_block_consumption2030 * RS2_vrates2030 *12</f>
         <v>188892</v>
       </c>
@@ -10702,23 +10698,23 @@
       <c r="I17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="55" cm="1">
+      <c r="J17" s="53" cm="1">
         <f t="array" ref="J17:J19">RS2_block_consumption2026 * RS2_vrates2026 *12</f>
         <v>181500</v>
       </c>
-      <c r="K17" s="55" cm="1">
+      <c r="K17" s="53" cm="1">
         <f t="array" ref="K17:K19">RS2_block_consumption2027 * RS2_vrates2026 *12</f>
         <v>183315</v>
       </c>
-      <c r="L17" s="55" cm="1">
+      <c r="L17" s="53" cm="1">
         <f t="array" ref="L17:L19">RS2_block_consumption2028 * RS2_vrates2026 *12</f>
         <v>185163</v>
       </c>
-      <c r="M17" s="55" cm="1">
+      <c r="M17" s="53" cm="1">
         <f t="array" ref="M17:M19">RS2_block_consumption2029 * RS2_vrates2026 *12</f>
         <v>187011</v>
       </c>
-      <c r="N17" s="55" cm="1">
+      <c r="N17" s="53" cm="1">
         <f t="array" ref="N17:N19">RS2_block_consumption2030 * RS2_vrates2026 *12</f>
         <v>188892</v>
       </c>
@@ -10769,19 +10765,19 @@
       <c r="A18" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="55">
+      <c r="B18" s="53">
         <v>165000</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="50">
         <v>166650</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="50">
         <v>168333</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="50">
         <v>170016</v>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="50">
         <v>171732</v>
       </c>
       <c r="G18" s="26"/>
@@ -10789,19 +10785,19 @@
       <c r="I18" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="J18" s="55">
+      <c r="J18" s="53">
         <v>165000</v>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="53">
         <v>166650</v>
       </c>
-      <c r="L18" s="55">
+      <c r="L18" s="53">
         <v>168333</v>
       </c>
-      <c r="M18" s="55">
+      <c r="M18" s="53">
         <v>170016</v>
       </c>
-      <c r="N18" s="55">
+      <c r="N18" s="53">
         <v>171732</v>
       </c>
       <c r="O18" s="26"/>
@@ -10848,42 +10844,42 @@
       <c r="BD18" s="26"/>
     </row>
     <row r="19" spans="1:56">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="64">
+      <c r="B19" s="62">
         <v>32835</v>
       </c>
-      <c r="C19" s="65">
+      <c r="C19" s="63">
         <v>33165</v>
       </c>
-      <c r="D19" s="65">
+      <c r="D19" s="63">
         <v>33495</v>
       </c>
-      <c r="E19" s="65">
+      <c r="E19" s="63">
         <v>33825</v>
       </c>
-      <c r="F19" s="65">
+      <c r="F19" s="63">
         <v>34155</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="63" t="s">
+      <c r="I19" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="J19" s="64">
+      <c r="J19" s="62">
         <v>32835</v>
       </c>
-      <c r="K19" s="64">
+      <c r="K19" s="62">
         <v>33165</v>
       </c>
-      <c r="L19" s="64">
+      <c r="L19" s="62">
         <v>33495</v>
       </c>
-      <c r="M19" s="64">
+      <c r="M19" s="62">
         <v>33825</v>
       </c>
-      <c r="N19" s="64">
+      <c r="N19" s="62">
         <v>34155</v>
       </c>
       <c r="O19" s="26"/>
@@ -10930,51 +10926,51 @@
       <c r="BD19" s="26"/>
     </row>
     <row r="20" spans="1:56">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="62">
+      <c r="B20" s="60">
         <f>SUM(B16:B19)</f>
         <v>630135</v>
       </c>
-      <c r="C20" s="62">
+      <c r="C20" s="60">
         <f t="shared" ref="C20:F20" si="10">SUM(C16:C19)</f>
         <v>670026</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D20" s="60">
         <f t="shared" si="10"/>
         <v>676983</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E20" s="60">
         <f t="shared" si="10"/>
         <v>683940</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F20" s="60">
         <f t="shared" si="10"/>
         <v>690963</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="44" t="s">
+      <c r="I20" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J20" s="60">
         <f>SUM(J16:J19)</f>
         <v>630135</v>
       </c>
-      <c r="K20" s="62">
+      <c r="K20" s="60">
         <f t="shared" ref="K20" si="11">SUM(K16:K19)</f>
         <v>636666</v>
       </c>
-      <c r="L20" s="62">
+      <c r="L20" s="60">
         <f t="shared" ref="L20" si="12">SUM(L16:L19)</f>
         <v>643263</v>
       </c>
-      <c r="M20" s="62">
+      <c r="M20" s="60">
         <f t="shared" ref="M20" si="13">SUM(M16:M19)</f>
         <v>649860</v>
       </c>
-      <c r="N20" s="62">
+      <c r="N20" s="60">
         <f t="shared" ref="N20" si="14">SUM(N16:N19)</f>
         <v>656523</v>
       </c>
@@ -11080,51 +11076,51 @@
       <c r="BD21" s="26"/>
     </row>
     <row r="22" spans="1:56" ht="15.75">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="61">
+      <c r="B22" s="59">
         <f>SUM(B20+B11)</f>
         <v>1620495</v>
       </c>
-      <c r="C22" s="61">
+      <c r="C22" s="59">
         <f t="shared" ref="C22:F22" si="15">SUM(C20+C11)</f>
         <v>1761846</v>
       </c>
-      <c r="D22" s="61">
+      <c r="D22" s="59">
         <f t="shared" si="15"/>
         <v>1835517</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="59">
         <f t="shared" si="15"/>
         <v>1854114</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F22" s="59">
         <f t="shared" si="15"/>
         <v>1927887</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
-      <c r="I22" s="49" t="s">
+      <c r="I22" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="61">
+      <c r="J22" s="59">
         <f>SUM(J20+J11)</f>
         <v>1620495</v>
       </c>
-      <c r="K22" s="61">
+      <c r="K22" s="59">
         <f t="shared" ref="K22:N22" si="16">SUM(K20+K11)</f>
         <v>1636872</v>
       </c>
-      <c r="L22" s="61">
+      <c r="L22" s="59">
         <f t="shared" si="16"/>
         <v>1653378</v>
       </c>
-      <c r="M22" s="61">
+      <c r="M22" s="59">
         <f t="shared" si="16"/>
         <v>1670130</v>
       </c>
-      <c r="N22" s="61">
+      <c r="N22" s="59">
         <f t="shared" si="16"/>
         <v>1686990</v>
       </c>
@@ -11652,15 +11648,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="153"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="146"/>
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
@@ -11692,14 +11688,14 @@
       <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="139" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="141"/>
       <c r="G3" s="26"/>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
@@ -11716,22 +11712,22 @@
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="80">
+      <c r="B4" s="73">
         <v>2026</v>
       </c>
-      <c r="C4" s="80">
+      <c r="C4" s="73">
         <f>B4+1</f>
         <v>2027</v>
       </c>
-      <c r="D4" s="80">
+      <c r="D4" s="73">
         <f t="shared" ref="D4:F4" si="0">C4+1</f>
         <v>2028</v>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="73">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="F4" s="85">
+      <c r="F4" s="78">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -11751,23 +11747,23 @@
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="47" cm="1">
+      <c r="B5" s="45" cm="1">
         <f t="array" ref="B5:B11">expenses_value</f>
         <v>725000</v>
       </c>
-      <c r="C5" s="43" cm="1">
+      <c r="C5" s="41" cm="1">
         <f t="array" ref="C5">ROUND(B5*(1+inflation_rate),0)</f>
         <v>746750</v>
       </c>
-      <c r="D5" s="43" cm="1">
+      <c r="D5" s="41" cm="1">
         <f t="array" ref="D5">ROUND(C5*(1+inflation_rate),0)</f>
         <v>769153</v>
       </c>
-      <c r="E5" s="43" cm="1">
+      <c r="E5" s="41" cm="1">
         <f t="array" ref="E5">ROUND(D5*(1+inflation_rate),0)</f>
         <v>792228</v>
       </c>
-      <c r="F5" s="43" cm="1">
+      <c r="F5" s="41" cm="1">
         <f t="array" ref="F5">ROUND(E5*(1+inflation_rate),0)</f>
         <v>815995</v>
       </c>
@@ -11787,22 +11783,22 @@
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="46">
         <v>135000</v>
       </c>
-      <c r="C6" s="43" cm="1">
+      <c r="C6" s="41" cm="1">
         <f t="array" ref="C6">ROUND(B6*(1+inflation_rate),0)</f>
         <v>139050</v>
       </c>
-      <c r="D6" s="43" cm="1">
+      <c r="D6" s="41" cm="1">
         <f t="array" ref="D6">ROUND(C6*(1+inflation_rate),0)</f>
         <v>143222</v>
       </c>
-      <c r="E6" s="43" cm="1">
+      <c r="E6" s="41" cm="1">
         <f t="array" ref="E6">ROUND(D6*(1+inflation_rate),0)</f>
         <v>147519</v>
       </c>
-      <c r="F6" s="43" cm="1">
+      <c r="F6" s="41" cm="1">
         <f t="array" ref="F6">ROUND(E6*(1+inflation_rate),0)</f>
         <v>151945</v>
       </c>
@@ -11819,25 +11815,25 @@
       <c r="Q6" s="26"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="41">
         <v>64000</v>
       </c>
-      <c r="C7" s="43" cm="1">
+      <c r="C7" s="57" cm="1">
         <f t="array" ref="C7">ROUND(B7*(1+inflation_rate),0)</f>
         <v>65920</v>
       </c>
-      <c r="D7" s="43" cm="1">
+      <c r="D7" s="41" cm="1">
         <f t="array" ref="D7">ROUND(C7*(1+inflation_rate),0)</f>
         <v>67898</v>
       </c>
-      <c r="E7" s="43" cm="1">
+      <c r="E7" s="41" cm="1">
         <f t="array" ref="E7">ROUND(D7*(1+inflation_rate),0)</f>
         <v>69935</v>
       </c>
-      <c r="F7" s="43" cm="1">
+      <c r="F7" s="41" cm="1">
         <f t="array" ref="F7">ROUND(E7*(1+inflation_rate),0)</f>
         <v>72033</v>
       </c>
@@ -11854,25 +11850,25 @@
       <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="92">
+      <c r="B8" s="41">
         <v>130500</v>
       </c>
-      <c r="C8" s="93" cm="1">
+      <c r="C8" s="72" cm="1">
         <f t="array" ref="C8">ROUND(B8*(1+inflation_rate),0)</f>
         <v>134415</v>
       </c>
-      <c r="D8" s="93" cm="1">
+      <c r="D8" s="86" cm="1">
         <f t="array" ref="D8">ROUND(C8*(1+inflation_rate),0)</f>
         <v>138447</v>
       </c>
-      <c r="E8" s="93" cm="1">
+      <c r="E8" s="86" cm="1">
         <f t="array" ref="E8">ROUND(D8*(1+inflation_rate),0)</f>
         <v>142600</v>
       </c>
-      <c r="F8" s="93" cm="1">
+      <c r="F8" s="86" cm="1">
         <f t="array" ref="F8">ROUND(E8*(1+inflation_rate),0)</f>
         <v>146878</v>
       </c>
@@ -11892,22 +11888,22 @@
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="85">
         <v>52000</v>
       </c>
-      <c r="C9" s="43" cm="1">
+      <c r="C9" s="41" cm="1">
         <f t="array" ref="C9">ROUND(B9*(1+inflation_rate),0)</f>
         <v>53560</v>
       </c>
-      <c r="D9" s="43" cm="1">
+      <c r="D9" s="41" cm="1">
         <f t="array" ref="D9">ROUND(C9*(1+inflation_rate),0)</f>
         <v>55167</v>
       </c>
-      <c r="E9" s="43" cm="1">
+      <c r="E9" s="41" cm="1">
         <f t="array" ref="E9">ROUND(D9*(1+inflation_rate),0)</f>
         <v>56822</v>
       </c>
-      <c r="F9" s="43" cm="1">
+      <c r="F9" s="41" cm="1">
         <f t="array" ref="F9">ROUND(E9*(1+inflation_rate),0)</f>
         <v>58527</v>
       </c>
@@ -11927,22 +11923,22 @@
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="45">
         <v>250000</v>
       </c>
-      <c r="C10" s="43" cm="1">
+      <c r="C10" s="41" cm="1">
         <f t="array" ref="C10">ROUND(B10*(1+inflation_rate),0)</f>
         <v>257500</v>
       </c>
-      <c r="D10" s="43" cm="1">
+      <c r="D10" s="41" cm="1">
         <f t="array" ref="D10">ROUND(C10*(1+inflation_rate),0)</f>
         <v>265225</v>
       </c>
-      <c r="E10" s="43" cm="1">
+      <c r="E10" s="41" cm="1">
         <f t="array" ref="E10">ROUND(D10*(1+inflation_rate),0)</f>
         <v>273182</v>
       </c>
-      <c r="F10" s="43" cm="1">
+      <c r="F10" s="41" cm="1">
         <f t="array" ref="F10">ROUND(E10*(1+inflation_rate),0)</f>
         <v>281377</v>
       </c>
@@ -11962,22 +11958,22 @@
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="48">
+      <c r="B11" s="46">
         <v>144000</v>
       </c>
-      <c r="C11" s="46" cm="1">
+      <c r="C11" s="44" cm="1">
         <f t="array" ref="C11">ROUND(B11*(1+inflation_rate),0)</f>
         <v>148320</v>
       </c>
-      <c r="D11" s="46" cm="1">
+      <c r="D11" s="44" cm="1">
         <f t="array" ref="D11">ROUND(C11*(1+inflation_rate),0)</f>
         <v>152770</v>
       </c>
-      <c r="E11" s="46" cm="1">
+      <c r="E11" s="44" cm="1">
         <f t="array" ref="E11">ROUND(D11*(1+inflation_rate),0)</f>
         <v>157353</v>
       </c>
-      <c r="F11" s="46" cm="1">
+      <c r="F11" s="44" cm="1">
         <f t="array" ref="F11">ROUND(E11*(1+inflation_rate),0)</f>
         <v>162074</v>
       </c>
@@ -11994,26 +11990,26 @@
       <c r="Q11" s="26"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="43">
         <f>SUM(B5:B11)</f>
         <v>1500500</v>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="43">
         <f t="shared" ref="C12:F12" si="1">SUM(C5:C11)</f>
         <v>1545515</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="43">
         <f t="shared" si="1"/>
         <v>1591882</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="43">
         <f t="shared" si="1"/>
         <v>1639639</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="43">
         <f t="shared" si="1"/>
         <v>1688829</v>
       </c>
@@ -12049,14 +12045,14 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="1:17" ht="15.75">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="148"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="141"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -12070,25 +12066,25 @@
       <c r="Q14" s="26"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="80">
+      <c r="B15" s="73">
         <v>2026</v>
       </c>
-      <c r="C15" s="80">
+      <c r="C15" s="73">
         <f>B15+1</f>
         <v>2027</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="73">
         <f>C15+1</f>
         <v>2028</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="73">
         <f>D15+1</f>
         <v>2029</v>
       </c>
-      <c r="F15" s="85">
+      <c r="F15" s="78">
         <f>E15+1</f>
         <v>2030</v>
       </c>
@@ -12105,23 +12101,23 @@
       <c r="Q15" s="26"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="96" cm="1">
+      <c r="B16" s="89" cm="1">
         <f t="array" ref="B16:F16">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C16" s="96">
+      <c r="C16" s="89">
         <v>165000</v>
       </c>
-      <c r="D16" s="96">
+      <c r="D16" s="89">
         <v>175000</v>
       </c>
-      <c r="E16" s="96">
+      <c r="E16" s="89">
         <v>175000</v>
       </c>
-      <c r="F16" s="96">
+      <c r="F16" s="89">
         <v>175000</v>
       </c>
       <c r="G16" s="26"/>
@@ -12156,26 +12152,26 @@
       <c r="Q17" s="26"/>
     </row>
     <row r="18" spans="1:17" ht="15.75">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="50">
+      <c r="B18" s="48">
         <f>SUM(B16+B12)</f>
         <v>1665500</v>
       </c>
-      <c r="C18" s="50">
+      <c r="C18" s="48">
         <f t="shared" ref="C18:F18" si="2">SUM(C16+C12)</f>
         <v>1710515</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="48">
         <f t="shared" si="2"/>
         <v>1766882</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="48">
         <f t="shared" si="2"/>
         <v>1814639</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="48">
         <f t="shared" si="2"/>
         <v>1863829</v>
       </c>
@@ -12503,16 +12499,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="18.75">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -12523,14 +12519,14 @@
       <c r="P1" s="26"/>
     </row>
     <row r="2" spans="1:42" ht="18.75">
-      <c r="A2" s="108"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
+      <c r="A2" s="101"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
@@ -12541,26 +12537,26 @@
       <c r="P2" s="26"/>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="21" cm="1">
+      <c r="B3" s="61" cm="1">
         <f t="array" ref="B3">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="61">
         <f>B3+1</f>
         <v>2027</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="61">
         <f t="shared" ref="D3:F3" si="0">C3+1</f>
         <v>2028</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="61">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="61">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
@@ -12576,23 +12572,23 @@
       <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="69" cm="1">
+      <c r="B4" s="41" cm="1">
         <f t="array" ref="B4:F4">total_operating_revenue_row</f>
         <v>1620495</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="41">
         <v>1761846</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="41">
         <v>1835517</v>
       </c>
-      <c r="E4" s="69">
+      <c r="E4" s="41">
         <v>1854114</v>
       </c>
-      <c r="F4" s="70">
+      <c r="F4" s="41">
         <v>1927887</v>
       </c>
       <c r="G4" s="26"/>
@@ -12607,23 +12603,23 @@
       <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="69" cm="1">
+      <c r="B5" s="41" cm="1">
         <f t="array" ref="B5:F5">total_cost_of_service_row</f>
         <v>1665500</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="41">
         <v>1710515</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="41">
         <v>1766882</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="41">
         <v>1814639</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="41">
         <v>1863829</v>
       </c>
       <c r="G5" s="26"/>
@@ -12636,48 +12632,48 @@
       <c r="N5" s="26"/>
       <c r="O5" s="26"/>
       <c r="P5" s="26"/>
-      <c r="AL5" s="72" cm="1">
+      <c r="AL5" s="68" cm="1">
         <f t="array" ref="AL5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AM5" s="72" cm="1">
+      <c r="AM5" s="68" cm="1">
         <f t="array" ref="AM5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AN5" s="72" cm="1">
+      <c r="AN5" s="68" cm="1">
         <f t="array" ref="AN5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AO5" s="72" cm="1">
+      <c r="AO5" s="68" cm="1">
         <f t="array" ref="AO5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AP5" s="72" cm="1">
+      <c r="AP5" s="68" cm="1">
         <f t="array" ref="AP5">target_dscr</f>
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="41">
         <f>B4-B5</f>
         <v>-45005</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="41">
         <f t="shared" ref="C6:F6" si="1">C4-C5</f>
         <v>51331</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="41">
         <f t="shared" si="1"/>
         <v>68635</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="41">
         <f t="shared" si="1"/>
         <v>39475</v>
       </c>
-      <c r="F6" s="70">
+      <c r="F6" s="41">
         <f t="shared" si="1"/>
         <v>64058</v>
       </c>
@@ -12693,26 +12689,26 @@
       <c r="P6" s="26"/>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="41">
         <f>B6</f>
         <v>-45005</v>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="41">
         <f>B7+C6</f>
         <v>6326</v>
       </c>
-      <c r="D7" s="78">
+      <c r="D7" s="41">
         <f t="shared" ref="D7:F7" si="2">C7+D6</f>
         <v>74961</v>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="41">
         <f t="shared" si="2"/>
         <v>114436</v>
       </c>
-      <c r="F7" s="79">
+      <c r="F7" s="41">
         <f t="shared" si="2"/>
         <v>178494</v>
       </c>
@@ -12746,26 +12742,26 @@
       <c r="P8" s="26"/>
     </row>
     <row r="9" spans="1:42">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="21" cm="1">
+      <c r="B9" s="61" cm="1">
         <f t="array" ref="B9">currentyear</f>
         <v>2026</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="61">
         <f>B9+1</f>
         <v>2027</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="61">
         <f t="shared" ref="D9:F9" si="3">C9+1</f>
         <v>2028</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="61">
         <f t="shared" si="3"/>
         <v>2029</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="61">
         <f t="shared" si="3"/>
         <v>2030</v>
       </c>
@@ -12784,20 +12780,20 @@
       <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="69" cm="1">
+      <c r="B10" s="41" cm="1">
         <f t="array" ref="B10:F10">total_operating_revenue_row - total_operating_expenses</f>
         <v>119995</v>
       </c>
-      <c r="C10" s="69">
+      <c r="C10" s="41">
         <v>216331</v>
       </c>
-      <c r="D10" s="69">
+      <c r="D10" s="41">
         <v>243635</v>
       </c>
-      <c r="E10" s="69">
+      <c r="E10" s="41">
         <v>214475</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="41">
         <v>239058</v>
       </c>
       <c r="G10" s="26"/>
@@ -12815,20 +12811,20 @@
       <c r="A11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="69" cm="1">
+      <c r="B11" s="41" cm="1">
         <f t="array" ref="B11:F11">debt_service_values</f>
         <v>165000</v>
       </c>
-      <c r="C11" s="69">
+      <c r="C11" s="41">
         <v>165000</v>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="41">
         <v>175000</v>
       </c>
-      <c r="E11" s="69">
+      <c r="E11" s="41">
         <v>175000</v>
       </c>
-      <c r="F11" s="70">
+      <c r="F11" s="41">
         <v>175000</v>
       </c>
       <c r="G11" s="26"/>
@@ -12842,27 +12838,27 @@
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
     </row>
-    <row r="12" spans="1:42" ht="21" customHeight="1">
-      <c r="A12" s="71" t="s">
+    <row r="12" spans="1:42" ht="15.75" customHeight="1">
+      <c r="A12" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="148">
         <f>B10/B11</f>
         <v>0.72724242424242425</v>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="148">
         <f t="shared" ref="C12:F12" si="4">C10/C11</f>
         <v>1.3110969696969696</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="148">
         <f t="shared" si="4"/>
         <v>1.3922000000000001</v>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="148">
         <f t="shared" si="4"/>
         <v>1.2255714285714285</v>
       </c>
-      <c r="F12" s="73">
+      <c r="F12" s="148">
         <f t="shared" si="4"/>
         <v>1.3660457142857143</v>
       </c>
@@ -12878,26 +12874,26 @@
       <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="75" t="str" cm="1">
+      <c r="B13" s="149" t="str" cm="1">
         <f t="array" ref="B13">IF(B12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Insufficient</v>
       </c>
-      <c r="C13" s="75" t="str" cm="1">
+      <c r="C13" s="149" t="str" cm="1">
         <f t="array" ref="C13">IF(C12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="D13" s="75" t="str" cm="1">
+      <c r="D13" s="149" t="str" cm="1">
         <f t="array" ref="D13">IF(D12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="E13" s="75" t="str" cm="1">
+      <c r="E13" s="149" t="str" cm="1">
         <f t="array" ref="E13">IF(E12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
-      <c r="F13" s="76" t="str" cm="1">
+      <c r="F13" s="149" t="str" cm="1">
         <f t="array" ref="F13">IF(F12&gt;=target_dscr, "Sufficient", "Insufficient")</f>
         <v>Sufficient</v>
       </c>
@@ -12943,7 +12939,7 @@
       <c r="D15" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="111" t="s">
+      <c r="E15" s="104" t="s">
         <v>75</v>
       </c>
       <c r="F15" s="26"/>
@@ -12963,19 +12959,19 @@
         <f t="array" ref="A16">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="B16" s="51" cm="1">
+      <c r="B16" s="49" cm="1">
         <f t="array" ref="B16">RS1_base_charge2026</f>
         <v>17</v>
       </c>
-      <c r="C16" s="51" cm="1">
+      <c r="C16" s="49" cm="1">
         <f t="array" ref="C16">ROUND(SUM(RS1_block_consumption2026 * RS1_vrates2026)/num_accountsRS1,2)</f>
         <v>15.75</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="49">
         <f>B16+C16</f>
         <v>32.75</v>
       </c>
-      <c r="E16" s="54" cm="1">
+      <c r="E16" s="52" cm="1">
         <f t="array" ref="E16">((D16*num_accountsRS1) + (D17*num_accountsRS2)) / num_accounts</f>
         <v>43.98827361563518</v>
       </c>
@@ -12996,15 +12992,15 @@
         <f t="array" ref="A17">rate_structure_2</f>
         <v>Commerical, inside</v>
       </c>
-      <c r="B17" s="51" cm="1">
+      <c r="B17" s="49" cm="1">
         <f t="array" ref="B17">RS2_base_charge2026</f>
         <v>38</v>
       </c>
-      <c r="C17" s="51" cm="1">
+      <c r="C17" s="49" cm="1">
         <f t="array" ref="C17">ROUND(SUM(RS2_block_consumption2026 * RS2_vrates2026)/num_accountsRS2,2)</f>
         <v>57.48</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="49">
         <f>B17+C17</f>
         <v>95.47999999999999</v>
       </c>
@@ -13052,7 +13048,7 @@
       <c r="D19" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="111" t="s">
+      <c r="E19" s="104" t="s">
         <v>75</v>
       </c>
       <c r="F19" s="26"/>
@@ -13072,19 +13068,19 @@
         <f t="array" ref="A20">rate_structure_1</f>
         <v>Residential water, inside</v>
       </c>
-      <c r="B20" s="51" cm="1">
+      <c r="B20" s="49" cm="1">
         <f t="array" ref="B20">base_chargeRS12027</f>
         <v>20</v>
       </c>
-      <c r="C20" s="51" cm="1">
+      <c r="C20" s="49" cm="1">
         <f t="array" ref="C20">ROUND(SUM(RS1_block_consumption2026 * RS1_vrates2027)/num_accountsRS1,2)</f>
         <v>15.75</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="49">
         <f>B20+C20</f>
         <v>35.75</v>
       </c>
-      <c r="E20" s="54" cm="1">
+      <c r="E20" s="52" cm="1">
         <f t="array" ref="E20">((D20*num_accountsRS1) + (D21*num_accountsRS2))/num_accounts</f>
         <v>47.346579804560264</v>
       </c>
@@ -13105,15 +13101,15 @@
         <f t="array" ref="A21">rate_structure_2</f>
         <v>Commerical, inside</v>
       </c>
-      <c r="B21" s="51" cm="1">
+      <c r="B21" s="49" cm="1">
         <f t="array" ref="B21">RS2_base_charge2027</f>
         <v>43</v>
       </c>
-      <c r="C21" s="51" cm="1">
+      <c r="C21" s="49" cm="1">
         <f t="array" ref="C21">ROUND(SUM(RS2_block_consumption2026 * RS2_vrates2027)/num_accountsRS2,2)</f>
         <v>57.48</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="49">
         <f>B21+C21</f>
         <v>100.47999999999999</v>
       </c>
